--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1327</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1490</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1327"/>
+  <dimension ref="A1:J1490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -52875,7 +52875,6 @@
       <c r="F1238" t="n">
         <v>4725</v>
       </c>
-      <c r="G1238" t="inlineStr"/>
       <c r="H1238" t="inlineStr">
         <is>
           <t>BTSTT CALL CRISIL खरीदें PRICE 4848.80 TARGET 4980/5000 STOP LOSS 4725</t>
@@ -52917,7 +52916,6 @@
       <c r="F1239" t="n">
         <v>4725</v>
       </c>
-      <c r="G1239" t="inlineStr"/>
       <c r="H1239" t="inlineStr">
         <is>
           <t>BTSTT CALL CRISIL खरीदें PRICE 4844.70 TARGET 4980/5000 STOP LOSS 4725</t>
@@ -52959,7 +52957,6 @@
       <c r="F1240" t="n">
         <v>4725</v>
       </c>
-      <c r="G1240" t="inlineStr"/>
       <c r="H1240" t="inlineStr">
         <is>
           <t>BTSTT CALL CRISIL खरीदें PRICE 4844.70 TARGET 4980/5000 STOP LOSS 4725</t>
@@ -53001,7 +52998,6 @@
       <c r="F1241" t="n">
         <v>790</v>
       </c>
-      <c r="G1241" t="inlineStr"/>
       <c r="H1241" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय
@@ -53048,7 +53044,6 @@
       <c r="F1242" t="n">
         <v>790</v>
       </c>
-      <c r="G1242" t="inlineStr"/>
       <c r="H1242" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय
@@ -53095,7 +53090,6 @@
       <c r="F1243" t="n">
         <v>790</v>
       </c>
-      <c r="G1243" t="inlineStr"/>
       <c r="H1243" t="inlineStr">
         <is>
           <t>10 की कमाई Amara Raja खरीदें PRICE 865.95 TARGET 1100/1200 STOP LOSS 790</t>
@@ -53134,7 +53128,6 @@
       <c r="E1244" t="n">
         <v>1400</v>
       </c>
-      <c r="G1244" t="inlineStr"/>
       <c r="H1244" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53173,7 +53166,6 @@
       <c r="E1245" t="n">
         <v>1800</v>
       </c>
-      <c r="G1245" t="inlineStr"/>
       <c r="H1245" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53212,7 +53204,6 @@
       <c r="E1246" t="n">
         <v>2500</v>
       </c>
-      <c r="G1246" t="inlineStr"/>
       <c r="H1246" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53254,7 +53245,6 @@
       <c r="F1247" t="n">
         <v>1318</v>
       </c>
-      <c r="G1247" t="inlineStr"/>
       <c r="H1247" t="inlineStr">
         <is>
           <t>Reliance Ind Fut खरीदें PRICE 1339.30 TARGET 1360/1386 STOP LOSS 1318</t>
@@ -53296,7 +53286,6 @@
       <c r="F1248" t="n">
         <v>1318</v>
       </c>
-      <c r="G1248" t="inlineStr"/>
       <c r="H1248" t="inlineStr">
         <is>
           <t>Reliance Ind Fut खरीदें PRICE 1339.30 TARGET 1360/1386 STOP LOSS 1318</t>
@@ -53338,7 +53327,6 @@
       <c r="F1249" t="n">
         <v>1318</v>
       </c>
-      <c r="G1249" t="inlineStr"/>
       <c r="H1249" t="inlineStr">
         <is>
           <t>BTSTT CALL
@@ -53382,7 +53370,6 @@
       <c r="E1250" t="n">
         <v>2500</v>
       </c>
-      <c r="G1250" t="inlineStr"/>
       <c r="H1250" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53421,7 +53408,6 @@
       <c r="E1251" t="n">
         <v>1400</v>
       </c>
-      <c r="G1251" t="inlineStr"/>
       <c r="H1251" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53460,7 +53446,6 @@
       <c r="E1252" t="n">
         <v>1800</v>
       </c>
-      <c r="G1252" t="inlineStr"/>
       <c r="H1252" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53499,7 +53484,6 @@
       <c r="E1253" t="n">
         <v>2500</v>
       </c>
-      <c r="G1253" t="inlineStr"/>
       <c r="H1253" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53538,7 +53522,6 @@
       <c r="E1254" t="n">
         <v>1400</v>
       </c>
-      <c r="G1254" t="inlineStr"/>
       <c r="H1254" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53577,7 +53560,6 @@
       <c r="E1255" t="n">
         <v>1800</v>
       </c>
-      <c r="G1255" t="inlineStr"/>
       <c r="H1255" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53616,7 +53598,6 @@
       <c r="E1256" t="n">
         <v>2500</v>
       </c>
-      <c r="G1256" t="inlineStr"/>
       <c r="H1256" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53655,7 +53636,6 @@
       <c r="E1257" t="n">
         <v>1400</v>
       </c>
-      <c r="G1257" t="inlineStr"/>
       <c r="H1257" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53694,7 +53674,6 @@
       <c r="E1258" t="n">
         <v>1800</v>
       </c>
-      <c r="G1258" t="inlineStr"/>
       <c r="H1258" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53733,7 +53712,6 @@
       <c r="E1259" t="n">
         <v>2500</v>
       </c>
-      <c r="G1259" t="inlineStr"/>
       <c r="H1259" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -53772,7 +53750,6 @@
       <c r="E1260" t="n">
         <v>1260</v>
       </c>
-      <c r="G1260" t="inlineStr"/>
       <c r="H1260" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Innova Captab खरीदें PRICE 1165.00 TARGET 1260/1270 STOP LOSS --</t>
@@ -53811,7 +53788,6 @@
       <c r="E1261" t="n">
         <v>1260</v>
       </c>
-      <c r="G1261" t="inlineStr"/>
       <c r="H1261" t="inlineStr">
         <is>
           <t>Innova Captab खरीदें PRICE 1164.60 TARGET 1260/1270 STOP LOSS --</t>
@@ -53850,7 +53826,6 @@
       <c r="E1262" t="n">
         <v>1270</v>
       </c>
-      <c r="G1262" t="inlineStr"/>
       <c r="H1262" t="inlineStr">
         <is>
           <t>Innova Captab खरीदें PRICE 1164.60 TARGET 1260/1270 STOP LOSS --</t>
@@ -53889,7 +53864,6 @@
       <c r="E1263" t="n">
         <v>1270</v>
       </c>
-      <c r="G1263" t="inlineStr"/>
       <c r="H1263" t="inlineStr">
         <is>
           <t>जैन साब के GEMS Innova Captab खरीदें PRICE 1163.70 TARGET 1260/1270 STOP LOSS --</t>
@@ -53928,7 +53902,6 @@
       <c r="E1264" t="n">
         <v>1260</v>
       </c>
-      <c r="G1264" t="inlineStr"/>
       <c r="H1264" t="inlineStr">
         <is>
           <t>Innova Captab खरीदें PRICE 1163.60 TARGET 1260/1270 STOP LOSS --</t>
@@ -53967,7 +53940,6 @@
       <c r="E1265" t="n">
         <v>1400</v>
       </c>
-      <c r="G1265" t="inlineStr"/>
       <c r="H1265" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन
@@ -54010,7 +53982,6 @@
       <c r="E1266" t="n">
         <v>1800</v>
       </c>
-      <c r="G1266" t="inlineStr"/>
       <c r="H1266" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन
@@ -54053,7 +54024,6 @@
       <c r="E1267" t="n">
         <v>2500</v>
       </c>
-      <c r="G1267" t="inlineStr"/>
       <c r="H1267" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन
@@ -54096,7 +54066,6 @@
       <c r="E1268" t="n">
         <v>1400</v>
       </c>
-      <c r="G1268" t="inlineStr"/>
       <c r="H1268" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -54135,7 +54104,6 @@
       <c r="E1269" t="n">
         <v>1800</v>
       </c>
-      <c r="G1269" t="inlineStr"/>
       <c r="H1269" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -54174,7 +54142,6 @@
       <c r="E1270" t="n">
         <v>1800</v>
       </c>
-      <c r="G1270" t="inlineStr"/>
       <c r="H1270" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -54213,7 +54180,6 @@
       <c r="E1271" t="n">
         <v>2500</v>
       </c>
-      <c r="G1271" t="inlineStr"/>
       <c r="H1271" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -54246,14 +54212,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1272" t="inlineStr"/>
       <c r="E1272" t="n">
         <v>1380</v>
       </c>
       <c r="F1272" t="n">
         <v>12500</v>
       </c>
-      <c r="G1272" t="inlineStr"/>
       <c r="H1272" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1380/12500</t>
@@ -54286,11 +54250,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1273" t="inlineStr"/>
       <c r="E1273" t="n">
         <v>18000</v>
       </c>
-      <c r="G1273" t="inlineStr"/>
       <c r="H1273" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 14000,18000</t>
@@ -54332,7 +54294,6 @@
       <c r="F1274" t="n">
         <v>1248</v>
       </c>
-      <c r="G1274" t="inlineStr"/>
       <c r="H1274" t="inlineStr">
         <is>
           <t>Bharat Dynamics Fut खरीदें PRICE 1266.00 TARGET 1284/1306 STOP LOSS 1248</t>
@@ -54374,7 +54335,6 @@
       <c r="F1275" t="n">
         <v>1248</v>
       </c>
-      <c r="G1275" t="inlineStr"/>
       <c r="H1275" t="inlineStr">
         <is>
           <t>Bharat Dynamics Fut खरीदें PRICE 1266.00 TARGET 1284/1306 STOP LOSS 1248</t>
@@ -54416,7 +54376,6 @@
       <c r="F1276" t="n">
         <v>1248</v>
       </c>
-      <c r="G1276" t="inlineStr"/>
       <c r="H1276" t="inlineStr">
         <is>
           <t>Bharat Dynamics Fut PRICE 1265.00 TARGET 1284/1305 STOP LOSS 1248</t>
@@ -54458,7 +54417,6 @@
       <c r="F1277" t="n">
         <v>1248</v>
       </c>
-      <c r="G1277" t="inlineStr"/>
       <c r="H1277" t="inlineStr">
         <is>
           <t>Bharat Dynamics Fut PRICE 1265.00 TARGET 1284/1305 STOP LOSS 1248</t>
@@ -54500,7 +54458,6 @@
       <c r="F1278" t="n">
         <v>1930</v>
       </c>
-      <c r="G1278" t="inlineStr"/>
       <c r="H1278" t="inlineStr">
         <is>
           <t>Coforge Ltd खरीदें PRICE 1975.90 TARGET 2025/2050 STOP LOSS 1930 RESULT TODAY</t>
@@ -54542,7 +54499,6 @@
       <c r="F1279" t="n">
         <v>1930</v>
       </c>
-      <c r="G1279" t="inlineStr"/>
       <c r="H1279" t="inlineStr">
         <is>
           <t>सुमित बंगडिया की राय Coforge Ltd खरीदें PRICE 1975.90 TARGET 2025/2050 STOP LOSS 1930</t>
@@ -54575,7 +54531,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1280" t="inlineStr"/>
       <c r="E1280" t="n">
         <v>1800</v>
       </c>
@@ -54625,7 +54580,6 @@
       <c r="E1281" t="n">
         <v>2500</v>
       </c>
-      <c r="G1281" t="inlineStr"/>
       <c r="H1281" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का मुनाफे का मक्खन Anthem Biosciences BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -54664,7 +54618,6 @@
       <c r="E1282" t="n">
         <v>1400</v>
       </c>
-      <c r="G1282" t="inlineStr"/>
       <c r="H1282" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -54703,7 +54656,6 @@
       <c r="E1283" t="n">
         <v>1800</v>
       </c>
-      <c r="G1283" t="inlineStr"/>
       <c r="H1283" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -54742,7 +54694,6 @@
       <c r="E1284" t="n">
         <v>2500</v>
       </c>
-      <c r="G1284" t="inlineStr"/>
       <c r="H1284" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 1400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -54781,7 +54732,6 @@
       <c r="E1285" t="n">
         <v>2500</v>
       </c>
-      <c r="G1285" t="inlineStr"/>
       <c r="H1285" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की पसंद गुरु STOCKS Jubilant Pharmova BUY लक्ष्य 400, 1800, 2500 अवधि- 1-3 साल</t>
@@ -54814,14 +54764,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1286" t="inlineStr"/>
       <c r="E1286" t="n">
         <v>5000</v>
       </c>
       <c r="F1286" t="n">
         <v>3000</v>
       </c>
-      <c r="G1286" t="inlineStr"/>
       <c r="H1286" t="inlineStr">
         <is>
           <t>Angel One Fut 304.45 17.00 5.91% Vol: 7.33 m BUY लक्ष्य 3000, 4000, 5000 अवधि- 1-3 साल</t>
@@ -54854,14 +54802,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1287" t="inlineStr"/>
       <c r="E1287" t="n">
         <v>5000</v>
       </c>
       <c r="F1287" t="n">
         <v>4000</v>
       </c>
-      <c r="G1287" t="inlineStr"/>
       <c r="H1287" t="inlineStr">
         <is>
           <t>Angel One Fut 304.45 17.00 5.91% Vol: 7.33 m BUY लक्ष्य 3000, 4000, 5000 अवधि- 1-3 साल</t>
@@ -54900,7 +54846,6 @@
       <c r="E1288" t="n">
         <v>1218</v>
       </c>
-      <c r="G1288" t="inlineStr"/>
       <c r="H1288" t="inlineStr">
         <is>
           <t>FII INVESTMENT REPORT मॉर्गन स्टैनली UNDERWEIGHT Cipla 1394.70 TARGET ₹1218</t>
@@ -54939,7 +54884,6 @@
       <c r="E1289" t="n">
         <v>14700</v>
       </c>
-      <c r="G1289" t="inlineStr"/>
       <c r="H1289" t="inlineStr">
         <is>
           <t>FII INVESTMENT REPORT मॉर्गन स्टैनली OVERWEIGHT UltraTech 11275.00 Unch TARGET ₹14700</t>
@@ -54978,7 +54922,6 @@
       <c r="E1290" t="n">
         <v>2640</v>
       </c>
-      <c r="G1290" t="inlineStr"/>
       <c r="H1290" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -55022,7 +54965,6 @@
       <c r="E1291" t="n">
         <v>2740</v>
       </c>
-      <c r="G1291" t="inlineStr"/>
       <c r="H1291" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -55066,7 +55008,6 @@
       <c r="E1292" t="n">
         <v>2840</v>
       </c>
-      <c r="G1292" t="inlineStr"/>
       <c r="H1292" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय
@@ -55113,7 +55054,6 @@
       <c r="F1293" t="n">
         <v>1220</v>
       </c>
-      <c r="G1293" t="inlineStr"/>
       <c r="H1293" t="inlineStr">
         <is>
           <t>सच्चितानंद उत्तकर की राय CDSL BUY PRICE 1394.00 TARGET 1960 STOP LOSS 1220</t>
@@ -55152,7 +55092,6 @@
       <c r="E1294" t="n">
         <v>1960</v>
       </c>
-      <c r="G1294" t="inlineStr"/>
       <c r="H1294" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर की राय CDSL BUY PRICE 1394.00 TARGET 1960 DURATION 1220</t>
@@ -55191,7 +55130,6 @@
       <c r="E1295" t="n">
         <v>1800</v>
       </c>
-      <c r="G1295" t="inlineStr"/>
       <c r="H1295" t="inlineStr">
         <is>
           <t>अंबरीश बलिगा की राय Vinati Org BUY PRICE 1313.70 TARGET 1800 STOP LOSS --</t>
@@ -55233,7 +55171,6 @@
       <c r="F1296" t="n">
         <v>188</v>
       </c>
-      <c r="G1296" t="inlineStr"/>
       <c r="H1296" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Groww BUY PRICE 190.24 TARGET 192, 194, 196 STOP LOSS 188</t>
@@ -55275,7 +55212,6 @@
       <c r="F1297" t="n">
         <v>188</v>
       </c>
-      <c r="G1297" t="inlineStr"/>
       <c r="H1297" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Groww BUY PRICE 190.24 TARGET 192, 194, 196 STOP LOSS 188</t>
@@ -55317,7 +55253,6 @@
       <c r="F1298" t="n">
         <v>201</v>
       </c>
-      <c r="G1298" t="inlineStr"/>
       <c r="H1298" t="inlineStr">
         <is>
           <t>INVESTMENT RVNL B 230 201</t>
@@ -55359,7 +55294,6 @@
       <c r="F1299" t="n">
         <v>85.5</v>
       </c>
-      <c r="G1299" t="inlineStr"/>
       <c r="H1299" t="inlineStr">
         <is>
           <t>TECHNO IDFC FIRST BANK B 91 85.5</t>
@@ -55401,7 +55335,6 @@
       <c r="F1300" t="n">
         <v>499</v>
       </c>
-      <c r="G1300" t="inlineStr"/>
       <c r="H1300" t="inlineStr">
         <is>
           <t>CASH SARDA ENERGY B 525 499</t>
@@ -55443,7 +55376,6 @@
       <c r="F1301" t="n">
         <v>262</v>
       </c>
-      <c r="G1301" t="inlineStr"/>
       <c r="H1301" t="inlineStr">
         <is>
           <t>NEWS IMPACT POWER GRID B 272 262</t>
@@ -55482,7 +55414,6 @@
       <c r="E1302" t="n">
         <v>110</v>
       </c>
-      <c r="G1302" t="inlineStr"/>
       <c r="H1302" t="inlineStr">
         <is>
           <t>INVESTMENT GMR AIRPORTS B 110 12 MONTH</t>
@@ -55524,7 +55455,6 @@
       <c r="F1303" t="n">
         <v>1001</v>
       </c>
-      <c r="G1303" t="inlineStr"/>
       <c r="H1303" t="inlineStr">
         <is>
           <t>MY CHOICE MOTILAL OSWAL B 1032 1001</t>
@@ -55566,7 +55496,6 @@
       <c r="F1304" t="n">
         <v>1120</v>
       </c>
-      <c r="G1304" t="inlineStr"/>
       <c r="H1304" t="inlineStr">
         <is>
           <t>TECHNO INFOSYS B 1154 1120</t>
@@ -55608,7 +55537,6 @@
       <c r="F1305" t="n">
         <v>33</v>
       </c>
-      <c r="G1305" t="inlineStr"/>
       <c r="H1305" t="inlineStr">
         <is>
           <t>FUNDA AU SMALL FINANCE B 11500 33</t>
@@ -55650,7 +55578,6 @@
       <c r="F1306" t="n">
         <v>1112</v>
       </c>
-      <c r="G1306" t="inlineStr"/>
       <c r="H1306" t="inlineStr">
         <is>
           <t>TECHNO INFOSYS B 11154 1112</t>
@@ -55692,7 +55619,6 @@
       <c r="F1307" t="n">
         <v>1961</v>
       </c>
-      <c r="G1307" t="inlineStr"/>
       <c r="H1307" t="inlineStr">
         <is>
           <t>FUTURE BHARAT FORGE FUT B 2020 1961</t>
@@ -55734,7 +55660,6 @@
       <c r="F1308" t="n">
         <v>1799</v>
       </c>
-      <c r="G1308" t="inlineStr"/>
       <c r="H1308" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -55781,7 +55706,6 @@
       <c r="F1309" t="n">
         <v>188</v>
       </c>
-      <c r="G1309" t="inlineStr"/>
       <c r="H1309" t="inlineStr">
         <is>
           <t>अंश के शेयर Groww खरीदें PRICE 190.24 TARGET 197 STOP LOSS 188</t>
@@ -55820,7 +55744,6 @@
       <c r="E1310" t="n">
         <v>8697</v>
       </c>
-      <c r="G1310" t="inlineStr"/>
       <c r="H1310" t="inlineStr">
         <is>
           <t>MY CHOICE Polycab India Ltd Fut PRICE 8875.50 TARGET 8697</t>
@@ -55862,7 +55785,6 @@
       <c r="F1311" t="n">
         <v>11191</v>
       </c>
-      <c r="G1311" t="inlineStr"/>
       <c r="H1311" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -55909,7 +55831,6 @@
       <c r="F1312" t="n">
         <v>262</v>
       </c>
-      <c r="G1312" t="inlineStr"/>
       <c r="H1312" t="inlineStr">
         <is>
           <t>पूजा के शेयर
@@ -55953,7 +55874,6 @@
       <c r="E1313" t="n">
         <v>110</v>
       </c>
-      <c r="G1313" t="inlineStr"/>
       <c r="H1313" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK GMR Airports खरीदें PRICE 96.87 TARGET 110 DURATION 12 महीने</t>
@@ -55995,7 +55915,6 @@
       <c r="F1314" t="n">
         <v>201</v>
       </c>
-      <c r="G1314" t="inlineStr"/>
       <c r="H1314" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK
@@ -56039,7 +55958,6 @@
       <c r="E1315" t="n">
         <v>1150</v>
       </c>
-      <c r="G1315" t="inlineStr"/>
       <c r="H1315" t="inlineStr">
         <is>
           <t>FUNDA PICK AU Small Fin खरीदें PRICE 1072.00 TARGET 1150 DURATION 3 महीने</t>
@@ -56081,7 +55999,6 @@
       <c r="F1316" t="n">
         <v>1120</v>
       </c>
-      <c r="G1316" t="inlineStr"/>
       <c r="H1316" t="inlineStr">
         <is>
           <t>TECHNO PICK Infosys खरीदें PRICE 1130.30 TARGET 1154 STOP LOSS 1120</t>
@@ -56123,7 +56040,6 @@
       <c r="F1317" t="n">
         <v>85.5</v>
       </c>
-      <c r="G1317" t="inlineStr"/>
       <c r="H1317" t="inlineStr">
         <is>
           <t>TECHNO PICK IDFC First Bank खरीदें PRICE 87.50 TARGET 91 STOP LOSS 85.5</t>
@@ -56165,7 +56081,6 @@
       <c r="F1318" t="n">
         <v>15</v>
       </c>
-      <c r="G1318" t="inlineStr"/>
       <c r="H1318" t="inlineStr">
         <is>
           <t>Axis Bank 1260 की कॉल @ 30 खरीदें STOP LOSS 15 TARGET 80 Axis Bank 1267.00</t>
@@ -56207,7 +56122,6 @@
       <c r="F1319" t="n">
         <v>1961</v>
       </c>
-      <c r="G1319" t="inlineStr"/>
       <c r="H1319" t="inlineStr">
         <is>
           <t>आज का FUTURE Bharat Forge Fut खरीदें PRICE 1997.80 TARGET 2020 STOP LOSS 1961</t>
@@ -56249,7 +56163,6 @@
       <c r="F1320" t="n">
         <v>499</v>
       </c>
-      <c r="G1320" t="inlineStr"/>
       <c r="H1320" t="inlineStr">
         <is>
           <t>CASH का शेयर Sarda Energy खरीदें PRICE 506.55 TARGET 525 STOP LOSS 499</t>
@@ -56288,7 +56201,6 @@
       <c r="E1321" t="n">
         <v>14065</v>
       </c>
-      <c r="G1321" t="inlineStr"/>
       <c r="H1321" t="inlineStr">
         <is>
           <t>UltraTech 11275.00 -118.00 BUY लक्ष्य ₹14065</t>
@@ -56327,7 +56239,6 @@
       <c r="E1322" t="n">
         <v>14065</v>
       </c>
-      <c r="G1322" t="inlineStr"/>
       <c r="H1322" t="inlineStr">
         <is>
           <t>RVNL 209.30 ▲ 1.60% ईस्ट कोस्ट रेलवे जोन से जुड़ा है रेलवे का प्रोजेक्ट BROKERAGE CALLS BUY लक्ष्य ₹14065</t>
@@ -56366,7 +56277,6 @@
       <c r="E1323" t="n">
         <v>1530</v>
       </c>
-      <c r="G1323" t="inlineStr"/>
       <c r="H1323" t="inlineStr">
         <is>
           <t>खबरों वाले शेयर GE Shipping 1353.60 ▲ 3.68% बायबैक प्राइस ₹1530/शेयर</t>
@@ -56405,7 +56315,6 @@
       <c r="E1324" t="n">
         <v>105</v>
       </c>
-      <c r="G1324" t="inlineStr"/>
       <c r="H1324" t="inlineStr">
         <is>
           <t>अभिनाश गोरेश्कर की पसंद Bank of Maha BUY TARGET 105-106 DURATION 6-12 महीने Bank of Maha 86.32 4.76%</t>
@@ -56444,7 +56353,6 @@
       <c r="E1325" t="n">
         <v>106</v>
       </c>
-      <c r="G1325" t="inlineStr"/>
       <c r="H1325" t="inlineStr">
         <is>
           <t>LONG-TERM CALL Bank of Maha BUY TARGET 105-106 DURATION 6-12 महीने Bank of Maha 86.32 4.76%</t>
@@ -56483,7 +56391,6 @@
       <c r="E1326" t="n">
         <v>1750</v>
       </c>
-      <c r="G1326" t="inlineStr"/>
       <c r="H1326" t="inlineStr">
         <is>
           <t>POSITIONAL C Adani Ports BUY TARGET 1750 Adani Ports 1706.50</t>
@@ -56525,7 +56432,6 @@
       <c r="F1327" t="n">
         <v>1690</v>
       </c>
-      <c r="G1327" t="inlineStr"/>
       <c r="H1327" t="inlineStr">
         <is>
           <t>POSITIONAL CALL Adani Ports BUY TARGET 1750 STOP LOSS 1690 Adani Ports 1706.50 2.02%</t>
@@ -56542,8 +56448,6808 @@
         </is>
       </c>
     </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:35:04</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>DIVISLAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr"/>
+      <c r="E1328" t="n">
+        <v>9235</v>
+      </c>
+      <c r="G1328" t="inlineStr"/>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>Divi's Lab Fut 9548.00 222.00 BUY TARGET HIT 9235</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1328" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:35:02</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>DIVISLAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr"/>
+      <c r="E1329" t="n">
+        <v>9480</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>9235</v>
+      </c>
+      <c r="G1329" t="inlineStr"/>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>Divi's Lab Fut 9548.00 222.00 BUY TGT 9480 SL 9235</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1329" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:35:01</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>DIVISLAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr"/>
+      <c r="E1330" t="n">
+        <v>9480</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>9235</v>
+      </c>
+      <c r="G1330" t="inlineStr"/>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>Divi's Lab Fut 9548.00 2.38% BUY TGT 9480 SL 9235</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1330" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:35:00</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>DIVISLAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr"/>
+      <c r="E1331" t="n">
+        <v>9480</v>
+      </c>
+      <c r="G1331" t="inlineStr"/>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>Divi's Lab Fut 9548.00 222.00 BUY TGT 9480</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1331" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:35:00</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1332" t="n">
+        <v>8369</v>
+      </c>
+      <c r="E1332" t="n">
+        <v>8600</v>
+      </c>
+      <c r="G1332" t="inlineStr"/>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>SUPER SID
+Polycab India
+8364.00 110.00
+BUY
+TGT 8600
+SL --</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1332" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:35:00</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1333" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="E1333" t="n">
+        <v>175</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>161</v>
+      </c>
+      <c r="G1333" t="inlineStr"/>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट Bandhan Bank 171.30 6.60 BUY TGT 175 SL 161</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1333" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:35:00</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1334" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="E1334" t="n">
+        <v>175</v>
+      </c>
+      <c r="G1334" t="inlineStr"/>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>Bandhan Bank 171.37 ▲ 6.67 BUY TGT 175</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1334" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:35:00</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1335" t="n">
+        <v>532.85</v>
+      </c>
+      <c r="E1335" t="n">
+        <v>535</v>
+      </c>
+      <c r="G1335" t="inlineStr"/>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>Hind Copper 532.45 4.63% BUY TGT 535 DUR 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1335" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:35:00</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1336" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E1336" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>999</v>
+      </c>
+      <c r="G1336" t="inlineStr"/>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट Hindalco 1018.80 12.80 BUY TGT 1040 SL 999</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1336" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:34:03</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr"/>
+      <c r="E1337" t="n">
+        <v>930</v>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला Jubilant Pharmova 1011.30 6.42% BUY TARGET HIT 930</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1337" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:34:02</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr"/>
+      <c r="E1338" t="n">
+        <v>730</v>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला Jubilant Pharmova 1011.30 61.00 BUY TARGET 730</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1338" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:33:59</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr"/>
+      <c r="E1339" t="n">
+        <v>990</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>930</v>
+      </c>
+      <c r="G1339" t="inlineStr"/>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Jubilant Pharmova 1011.20 6.41% BUY TGT 990 SL 930</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1339" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:21:00</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1340" t="n">
+        <v>1928.2</v>
+      </c>
+      <c r="E1340" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>1890</v>
+      </c>
+      <c r="G1340" t="inlineStr"/>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>11 बजे की लेडीज स्पेशल
+Laurus Labs
+खरीदें
+PRICE ▸ 1927.20
+TARGET ▸ 2000
+STOP LOSS ▸ 1890</t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1340" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:10:29</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr"/>
+      <c r="E1341" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>5675</v>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>GE Vernova T&amp;D पर नोमुरा GE Vernova T&amp;D 4738.50 ▲ 371.30 खरीदारी की राय, लक्ष्य ₹5675 से बढ़ाकर ₹6000</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1341" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:11:00</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1342" t="n">
+        <v>4730.8</v>
+      </c>
+      <c r="E1342" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>GE Vernova T&amp;D पर नोमुरा GE Vernova T&amp;D 4738.50 ▲ 371.30 खरीदारी की राय, लक्ष्य ₹5675 से बढ़ाकर ₹6000</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1342" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:11:00</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1343" t="n">
+        <v>4730.8</v>
+      </c>
+      <c r="E1343" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G1343" t="inlineStr"/>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>BUZZING STOCK GE Vernova T&amp;D 4739.00 ▲ 8.51% खरीदारी की राश, लक्ष्य ₹5675 से बढ़ाकर ₹6000</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1343" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:07:49</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>DIVISLAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr"/>
+      <c r="E1344" t="n">
+        <v>9480</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>9235</v>
+      </c>
+      <c r="G1344" t="inlineStr"/>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>जय का JACKPOT
+Divi's Lab Fut
+9515.00 189.00
+BUY
+TGT 9480
+SL 9235</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1344" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:07:48</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>DIVISLAB29SEP26</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr"/>
+      <c r="E1345" t="n">
+        <v>9480</v>
+      </c>
+      <c r="G1345" t="inlineStr"/>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>Divi's Lab Fut 9514.50 188.50 BUY TGT 9480</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1345" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:07:21</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr"/>
+      <c r="E1346" t="n">
+        <v>425</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>408</v>
+      </c>
+      <c r="G1346" t="inlineStr"/>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+LIC
+413.60 2.10
+BUY
+TGT 425
+SL 408</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1346" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:08:00</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1347" t="n">
+        <v>169.28</v>
+      </c>
+      <c r="E1347" t="n">
+        <v>175</v>
+      </c>
+      <c r="F1347" t="n">
+        <v>161</v>
+      </c>
+      <c r="G1347" t="inlineStr"/>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट
+Bandhan Bank
+169.05 4.35
+BUY
+TGT 175
+SL 161</t>
+        </is>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1347" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:07:00</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1348" t="n">
+        <v>1022</v>
+      </c>
+      <c r="E1348" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>999</v>
+      </c>
+      <c r="G1348" t="inlineStr"/>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>Hindalco 1022.00 16.00 BUY TGT 1040 SL 999</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1348" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:53:00</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1349" t="n">
+        <v>769</v>
+      </c>
+      <c r="E1349" t="n">
+        <v>830</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>728</v>
+      </c>
+      <c r="G1349" t="inlineStr"/>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>SHORT MIDCAP STOCKS TD Power खरीदें STOP LOSS 728 TARGET 810/830 DURATION -- TD Power 769.00</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1349" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:53:00</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1350" t="n">
+        <v>769</v>
+      </c>
+      <c r="E1350" t="n">
+        <v>810</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>728</v>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय TD Power खरीदें STOP LOSS 728 TARGET 810/830 DURATION -- TD Power 769.00 34.85</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1350" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:42:00</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>SOUTHWEST</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1351" t="n">
+        <v>221.17</v>
+      </c>
+      <c r="E1351" t="n">
+        <v>245</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>215</v>
+      </c>
+      <c r="G1351" t="inlineStr"/>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय South West Pinnacle खरीदें STOP LOSS 215 TARGET 240/245 DURATION -- South West Pinnacle 222.67 ▲ 0.18%</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1351" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:42:00</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>SOUTHWEST</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1352" t="n">
+        <v>221.17</v>
+      </c>
+      <c r="E1352" t="n">
+        <v>240</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>215</v>
+      </c>
+      <c r="G1352" t="inlineStr"/>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय South West Pinnacle खरीदें STOP LOSS 215 TARGET 240/245 DURATION -- South West Pinnacle 222.67 ▲ 0.18%</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1352" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:40:04</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>BHARATSE</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr"/>
+      <c r="E1353" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>218</v>
+      </c>
+      <c r="G1353" t="inlineStr"/>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>POSITIONAL MIDCAP STOCK BHARAT SEATS LIMITED खरीदें STOP LOSS 218 TARGET 250/255 DURATION</t>
+        </is>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1353" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:40:04</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>BHARATSE</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr"/>
+      <c r="E1354" t="n">
+        <v>255</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>218</v>
+      </c>
+      <c r="G1354" t="inlineStr"/>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>POSITIONAL MIDCAP STOCK BHARAT SEATS LIMITED खरीदें STOP LOSS 218 TARGET 250/255 DURATION</t>
+        </is>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1354" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:31:44</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>MYSORPETRO-BE</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr"/>
+      <c r="E1355" t="n">
+        <v>158</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>132</v>
+      </c>
+      <c r="G1355" t="inlineStr"/>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>TN Petro खरीदें PRICE 143.57 TARGET 158/170 STOP LOSS 132</t>
+        </is>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1355" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:32:00</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>BEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1356" t="n">
+        <v>417.3</v>
+      </c>
+      <c r="E1356" t="n">
+        <v>418</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>406</v>
+      </c>
+      <c r="G1356" t="inlineStr"/>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>BEL Fut 417.50 11.15 BUY TGT 418 SL 406</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1356" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:31:00</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1357" t="n">
+        <v>1745.9</v>
+      </c>
+      <c r="E1357" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1357" t="inlineStr"/>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS Astra Micro 1745.50 33.90 BUY TGT 1950 SL --</t>
+        </is>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1357" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:31:00</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1358" t="n">
+        <v>170.15</v>
+      </c>
+      <c r="E1358" t="n">
+        <v>175</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>161</v>
+      </c>
+      <c r="G1358" t="inlineStr"/>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>Bandhan Bank 170.45 5.75 BUY TGT 175 SL 161</t>
+        </is>
+      </c>
+      <c r="I1358" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1358" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:31:00</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1359" t="n">
+        <v>4802</v>
+      </c>
+      <c r="E1359" t="n">
+        <v>5150</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>4580</v>
+      </c>
+      <c r="G1359" t="inlineStr"/>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>POSITIONAL MIDCAP STOCKS
+CRISIL
+खरीदें
+STOP LOSS 4580 | TARGET 5100/5150 | DURATION --
+CRISIL 4799.90 ▲ 13.30</t>
+        </is>
+      </c>
+      <c r="I1359" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1359" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:31:00</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>CRISIL</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1360" t="n">
+        <v>4802</v>
+      </c>
+      <c r="E1360" t="n">
+        <v>5100</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>4580</v>
+      </c>
+      <c r="G1360" t="inlineStr"/>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>CRISIL खरीदें STOP LOSS 4580 TARGET 5100/5150 DURATION -- CRISIL 4799.90 13.30</t>
+        </is>
+      </c>
+      <c r="I1360" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1360" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:31:00</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1361" t="n">
+        <v>415.05</v>
+      </c>
+      <c r="E1361" t="n">
+        <v>421</v>
+      </c>
+      <c r="G1361" t="inlineStr"/>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>SUPER SID BEL 415.10 11.10 BUY TGT 421 DUR 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1361" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1361" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:30:29</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr"/>
+      <c r="E1362" t="n">
+        <v>535</v>
+      </c>
+      <c r="G1362" t="inlineStr"/>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>SUPER SID
+Hind Copper
+533.35 24.45
+BUY
+TGT 535
+DUR 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1362" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1362" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:31:00</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1363" t="n">
+        <v>1023.1</v>
+      </c>
+      <c r="E1363" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>999</v>
+      </c>
+      <c r="G1363" t="inlineStr"/>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>Hindalco 1023.40 17.40 BUY TGT 1040 SL 999</t>
+        </is>
+      </c>
+      <c r="I1363" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1363" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:31:00</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1364" t="n">
+        <v>1023.1</v>
+      </c>
+      <c r="E1364" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G1364" t="inlineStr"/>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>Hindalco 1023.00 17.00 BUY TGT 1040</t>
+        </is>
+      </c>
+      <c r="I1364" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1364" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:30:00</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>BHARATSE</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1365" t="n">
+        <v>226.8</v>
+      </c>
+      <c r="E1365" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>218</v>
+      </c>
+      <c r="G1365" t="inlineStr"/>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>POSITIONAL MIDCAP STOCKS
+BHARAT SEATS LIMITED
+खरीदें
+STOP LOSS 218
+TARGET 250/255
+DURATION --
+Bharat Seats Ltd 225.63 ▼ 0.89%</t>
+        </is>
+      </c>
+      <c r="I1365" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1365" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:30:00</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>BHARATSE</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1366" t="n">
+        <v>226.8</v>
+      </c>
+      <c r="E1366" t="n">
+        <v>255</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>218</v>
+      </c>
+      <c r="G1366" t="inlineStr"/>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>BHARAT SEATS LIMITED खरीदें STOP LOSS 218 TARGET 250/255 DURATION -- Bharat Seats Ltd 225.63</t>
+        </is>
+      </c>
+      <c r="I1366" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1366" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:28:00</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1367" t="n">
+        <v>1247.5</v>
+      </c>
+      <c r="E1367" t="n">
+        <v>1430</v>
+      </c>
+      <c r="G1367" t="inlineStr"/>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS Aegis Logistics खरीदें STOP LOSS -- TARGET 1430/1450 DURATION 6-12 महीने Aegis Logistics 1247.20 6.50</t>
+        </is>
+      </c>
+      <c r="I1367" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1367" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:28:00</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1368" t="n">
+        <v>1247.5</v>
+      </c>
+      <c r="E1368" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G1368" t="inlineStr"/>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCKS Aegis Logistics खरीदें STOP LOSS -- TARGET 1430/1450 DURATION 6-12 महीने Aegis Logistics 1247.20 6.50</t>
+        </is>
+      </c>
+      <c r="I1368" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1368" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:12:00</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1369" t="n">
+        <v>1246.8</v>
+      </c>
+      <c r="E1369" t="n">
+        <v>1430</v>
+      </c>
+      <c r="G1369" t="inlineStr"/>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>सदीप जैन का राय Aegis Logistics खरीदें STOP LOSS -- TARGET 1430/1450 DURATION 6-12 महीने Aegis Logistics 1246.90 0.54%</t>
+        </is>
+      </c>
+      <c r="I1369" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1369" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:12:00</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1370" t="n">
+        <v>1246.8</v>
+      </c>
+      <c r="E1370" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G1370" t="inlineStr"/>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Aegis Logistics खरीदें STOP LOSS -- TARGET 1430/1450 DURATION 6-12 महीने Aegis Logistics 1246.90</t>
+        </is>
+      </c>
+      <c r="I1370" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1370" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1371" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="E1371" t="n">
+        <v>195</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>159</v>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय Pine Labs खरीदें STOP LOSS 159 TARGET 185/195 DURATION -- Pine Labs 168.51 ↑ 2.44%</t>
+        </is>
+      </c>
+      <c r="I1371" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1371" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1372" t="n">
+        <v>168.5</v>
+      </c>
+      <c r="E1372" t="n">
+        <v>185</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>159</v>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय Pine Labs खरीदें STOP LOSS 159 TARGET 185/195 Pine Labs 168.51</t>
+        </is>
+      </c>
+      <c r="I1372" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1372" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:06:41</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>PFOCUS</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr"/>
+      <c r="E1373" t="n">
+        <v>420</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1373" t="inlineStr"/>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>Prime Focus खरीदें PRICE 321.10 TARGET 420/450 STOP LOSS 280</t>
+        </is>
+      </c>
+      <c r="I1373" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1373" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:07:00</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>PFOCUS</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1374" t="n">
+        <v>321.45</v>
+      </c>
+      <c r="E1374" t="n">
+        <v>420</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1374" t="inlineStr"/>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>1 की कमाई Prime Focus खरीदें PRICE 320.90 TARGET 420/450 STOP LOSS 280</t>
+        </is>
+      </c>
+      <c r="I1374" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1374" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026-09-08 10:07:00</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>PFOCUS</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1375" t="n">
+        <v>321.45</v>
+      </c>
+      <c r="E1375" t="n">
+        <v>450</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1375" t="inlineStr"/>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>Prime Focus खरीदें PRICE 321.10 TARGET 420/450 STOP LOSS 280</t>
+        </is>
+      </c>
+      <c r="I1375" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1375" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:58:00</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1376" t="n">
+        <v>8420.5</v>
+      </c>
+      <c r="E1376" t="n">
+        <v>8600</v>
+      </c>
+      <c r="G1376" t="inlineStr"/>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>SUPER SID
+Polycab India
+8403.00 1.81%
+BUY
+TGT 8600
+SL --</t>
+        </is>
+      </c>
+      <c r="I1376" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1376" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:57:00</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>BEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1377" t="n">
+        <v>416.6</v>
+      </c>
+      <c r="E1377" t="n">
+        <v>418</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>406</v>
+      </c>
+      <c r="G1377" t="inlineStr"/>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>BEL Fut 416.00 9.65 BUY TGT 418 SL 406</t>
+        </is>
+      </c>
+      <c r="I1377" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1377" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:57:00</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1378" t="n">
+        <v>1736.8</v>
+      </c>
+      <c r="E1378" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1378" t="inlineStr"/>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+Astra Micro
+1738.80 27.20
+BUY
+TGT 1950
+SL --</t>
+        </is>
+      </c>
+      <c r="I1378" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1378" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:57:00</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1379" t="n">
+        <v>414.1</v>
+      </c>
+      <c r="E1379" t="n">
+        <v>421</v>
+      </c>
+      <c r="G1379" t="inlineStr"/>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>SUPER SID
+BEL
+413.95 9.95
+BUY
+TGT 421
+DUR 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1379" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1379" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:57:00</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1380" t="n">
+        <v>414</v>
+      </c>
+      <c r="E1380" t="n">
+        <v>421</v>
+      </c>
+      <c r="G1380" t="inlineStr"/>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>SUPER SID
+BEL
+414.00 10.00
+BUY
+TGT 421
+DUR 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1380" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1380" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:57:00</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1381" t="n">
+        <v>534.15</v>
+      </c>
+      <c r="E1381" t="n">
+        <v>535</v>
+      </c>
+      <c r="G1381" t="inlineStr"/>
+      <c r="H1381" t="inlineStr">
+        <is>
+          <t>SUPER SID
+Hind Copper
+534.65 25.75
+BUY
+TGT 535
+DUR 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1381" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1381" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:57:00</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1382" t="n">
+        <v>1019.6</v>
+      </c>
+      <c r="E1382" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1382" t="n">
+        <v>999</v>
+      </c>
+      <c r="G1382" t="inlineStr"/>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>Hindalco 1020.70 14.70 BUY TGT 1040 SL 999</t>
+        </is>
+      </c>
+      <c r="I1382" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1382" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:55:00</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>EBGNG</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1383" t="n">
+        <v>626.5</v>
+      </c>
+      <c r="E1383" t="n">
+        <v>775</v>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय GNG Electronics खरीदें PRICE 623.00 TARGET 775 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1383" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1383" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:56:00</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>EBGNG</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1384" t="n">
+        <v>627.95</v>
+      </c>
+      <c r="E1384" t="n">
+        <v>775</v>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय GNG Electronics खरीदें PRICE 622.85 TARGET 775 STOP LOSS -- IT शेयर</t>
+        </is>
+      </c>
+      <c r="I1384" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1384" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:49:30</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr"/>
+      <c r="E1385" t="n">
+        <v>3880</v>
+      </c>
+      <c r="G1385" t="inlineStr"/>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>SUPER SID Sansera Engg 4034.40 BUY TGT 3880 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I1385" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1385" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:50:00</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1386" t="n">
+        <v>4031.6</v>
+      </c>
+      <c r="E1386" t="n">
+        <v>4172.5</v>
+      </c>
+      <c r="G1386" t="inlineStr"/>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>SUPER SID Sansera Engg 4034.40 138.10 BUY TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I1386" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1386" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:49:27</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr"/>
+      <c r="E1387" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G1387" t="inlineStr"/>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>SUPER SID Sansera Engg 4034.40 138.10 BUY TGT 3990 SL</t>
+        </is>
+      </c>
+      <c r="I1387" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1387" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:49:24</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr"/>
+      <c r="E1388" t="n">
+        <v>3980</v>
+      </c>
+      <c r="G1388" t="inlineStr"/>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>Sansera Engg 4031.60 135.30 BUY TGT 3980 SL --</t>
+        </is>
+      </c>
+      <c r="I1388" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1388" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:50:00</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>BEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1389" t="n">
+        <v>415.4</v>
+      </c>
+      <c r="E1389" t="n">
+        <v>418</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>408</v>
+      </c>
+      <c r="G1389" t="inlineStr"/>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>विशेष के विशेष BEL Fut 414.95 9.88 BUY TGT 418 SL 408</t>
+        </is>
+      </c>
+      <c r="I1389" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1389" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:50:00</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>BEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1390" t="n">
+        <v>414.85</v>
+      </c>
+      <c r="E1390" t="n">
+        <v>418</v>
+      </c>
+      <c r="G1390" t="inlineStr"/>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>BEL Fut 415.10 8.75 BUY TGT 418</t>
+        </is>
+      </c>
+      <c r="I1390" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1390" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:49:06</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>DIVISLAB940029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr"/>
+      <c r="E1391" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>150</v>
+      </c>
+      <c r="G1391" t="inlineStr"/>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय DIVI'S LAB 9400 की कॉल @ ₹191 खरीदें STOP LOSS 150 TARGET 250/280 Divi's Lab 9400.00 ▲ 1.02%</t>
+        </is>
+      </c>
+      <c r="I1391" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1391" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:49:06</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>DIVISLAB940029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr"/>
+      <c r="E1392" t="n">
+        <v>280</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>150</v>
+      </c>
+      <c r="G1392" t="inlineStr"/>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय DIVI'S LAB 9400 की कॉल @ ₹191 खरीदें STOP LOSS 150 TARGET 250/280 Divi's Lab 9400.00 ▲ 1.02%</t>
+        </is>
+      </c>
+      <c r="I1392" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1392" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:49:04</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr"/>
+      <c r="E1393" t="n">
+        <v>425</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>408</v>
+      </c>
+      <c r="G1393" t="inlineStr"/>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+LIC 414.25 2.75
+BUY
+TGT 425
+SL 408</t>
+        </is>
+      </c>
+      <c r="I1393" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1393" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1394" t="n">
+        <v>528.85</v>
+      </c>
+      <c r="E1394" t="n">
+        <v>535</v>
+      </c>
+      <c r="G1394" t="inlineStr"/>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>SUPER SID Hind Copper 529.30 4.01% BUY TGT 535 BUR ₹ नहीं</t>
+        </is>
+      </c>
+      <c r="I1394" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1394" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:48:44</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>DIVISLAB940029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr"/>
+      <c r="E1395" t="n">
+        <v>51.15</v>
+      </c>
+      <c r="G1395" t="inlineStr"/>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>DIVISLAB 9400 CALL ▲
+204.80 ▲ 51.15 33.29%
+EXPIRY- 29 SEP 2026
+OPEN INTEREST
+1.08 Lk ▲ 0.12 Lk
+Divi's Lab 9400.50 85.50</t>
+        </is>
+      </c>
+      <c r="I1395" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1395" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1396" t="n">
+        <v>1015.4</v>
+      </c>
+      <c r="E1396" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>999</v>
+      </c>
+      <c r="G1396" t="inlineStr"/>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट Hindalco 1015.30 9.30 BUY TGT 1040 SL 999</t>
+        </is>
+      </c>
+      <c r="I1396" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1396" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:48:34</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr"/>
+      <c r="E1397" t="n">
+        <v>4705</v>
+      </c>
+      <c r="G1397" t="inlineStr"/>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Data Patterns 4798.90 4.53% BUY TARGET HIT 4705</t>
+        </is>
+      </c>
+      <c r="I1397" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1397" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:48:33</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>DIVISLAB940029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr"/>
+      <c r="E1398" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1398" t="inlineStr"/>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>DIVISLAB 9400 CALL ▲ 203.65 ▲ 50.00 32.54% EXPIRY- 29 SEP 2026 OPEN INTEREST 1.08 Lk ▲ 0.12 Lk Divi's Lab 9402.50 87.50</t>
+        </is>
+      </c>
+      <c r="I1398" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1398" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:48:33</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr"/>
+      <c r="E1399" t="n">
+        <v>4705</v>
+      </c>
+      <c r="G1399" t="inlineStr"/>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Data Patterns 4799.80 4.55% BUY TARGET HIT 4705</t>
+        </is>
+      </c>
+      <c r="I1399" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1399" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:48:32</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr"/>
+      <c r="E1400" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F1400" t="n">
+        <v>4705</v>
+      </c>
+      <c r="G1400" t="inlineStr"/>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Data Patterns 4803.50 212.70 BUY TGT 4800 SL 4705</t>
+        </is>
+      </c>
+      <c r="I1400" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1400" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:48:30</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr"/>
+      <c r="E1401" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F1401" t="n">
+        <v>4705</v>
+      </c>
+      <c r="G1401" t="inlineStr"/>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Data Patterns 4801.10 210.30 BUY TGT 4800 SL 4705</t>
+        </is>
+      </c>
+      <c r="I1401" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1401" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1402" t="n">
+        <v>8408.5</v>
+      </c>
+      <c r="E1402" t="n">
+        <v>8600</v>
+      </c>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1402" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय Polycab India खरीदें PRICE 8410.00 TARGET 8600/10600 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1402" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1402" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1403" t="n">
+        <v>8408.5</v>
+      </c>
+      <c r="E1403" t="n">
+        <v>10600</v>
+      </c>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1403" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय Polycab India खरीदें PRICE 8410.00 TARGET 8600/10600 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1403" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1403" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:48:00</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1404" t="n">
+        <v>8408.5</v>
+      </c>
+      <c r="E1404" t="n">
+        <v>8600</v>
+      </c>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय Polycab India खरीदें PRICE 8409.50 TARGET 8600/10600 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1404" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1404" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:46:19</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr"/>
+      <c r="E1405" t="n">
+        <v>421</v>
+      </c>
+      <c r="F1405" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1405" t="inlineStr"/>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>BEL खरीदें PRICE 412.45 TARGET 421/500 DURATION 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1405" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1405" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:46:00</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1406" t="n">
+        <v>412.05</v>
+      </c>
+      <c r="E1406" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1406" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय BEL खरीदें PRICE 412.30 TARGET 421/500 DURATION 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1406" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1406" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:46:00</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1407" t="n">
+        <v>412.05</v>
+      </c>
+      <c r="E1407" t="n">
+        <v>421</v>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय BEL खरीदें PRICE 412.15 TARGET 421/500 DURATION 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1407" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1407" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:46:00</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>BEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1408" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="E1408" t="n">
+        <v>418</v>
+      </c>
+      <c r="F1408" t="n">
+        <v>406</v>
+      </c>
+      <c r="G1408" t="inlineStr"/>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>विशेष चौहान की राय BEL Fut खरीदें PRICE 413.60 TARGET 418/426 STOP LOSS 406</t>
+        </is>
+      </c>
+      <c r="I1408" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1408" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:46:00</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>BEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1409" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="E1409" t="n">
+        <v>426</v>
+      </c>
+      <c r="F1409" t="n">
+        <v>406</v>
+      </c>
+      <c r="G1409" t="inlineStr"/>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>विशेष चौहान की राय BEL Fut खरीदें PRICE 413.60 TARGET 418/426 STOP LOSS 406</t>
+        </is>
+      </c>
+      <c r="I1409" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1409" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:46:00</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>BEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1410" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="E1410" t="n">
+        <v>426</v>
+      </c>
+      <c r="G1410" t="inlineStr"/>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>BEL Fut PRICE 413.55 TARGET 418/426</t>
+        </is>
+      </c>
+      <c r="I1410" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1410" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1411" t="n">
+        <v>1741.4</v>
+      </c>
+      <c r="E1411" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G1411" t="inlineStr"/>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>Astra Micro खरीदें PRICE 1742.00 TARGET 1950/1990 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1411" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1411" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1412" t="n">
+        <v>1741.4</v>
+      </c>
+      <c r="E1412" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1412" t="inlineStr"/>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>Astra Micro खरीदें PRICE 1742.00 TARGET 1950/1990 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1412" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1412" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1413" t="n">
+        <v>1741.4</v>
+      </c>
+      <c r="E1413" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1413" t="inlineStr"/>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>जन साब के GEMS
+Astra Micro
+खरीदें
+PRICE → 1741.20
+TARGET → 1950/1990
+STOP LOSS → --</t>
+        </is>
+      </c>
+      <c r="I1413" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1413" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1414" t="n">
+        <v>1741.4</v>
+      </c>
+      <c r="E1414" t="n">
+        <v>1990</v>
+      </c>
+      <c r="G1414" t="inlineStr"/>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>जन साब के GEMS
+Astra Micro
+खरीदें
+PRICE → 1741.20
+TARGET → 1950/1990
+STOP LOSS → --</t>
+        </is>
+      </c>
+      <c r="I1414" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1414" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:41:00</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1415" t="n">
+        <v>1742.9</v>
+      </c>
+      <c r="E1415" t="n">
+        <v>4822.8</v>
+      </c>
+      <c r="F1415" t="n">
+        <v>232</v>
+      </c>
+      <c r="G1415" t="inlineStr"/>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Data Patterns 4822.80 232.00 BUY</t>
+        </is>
+      </c>
+      <c r="I1415" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1415" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:40:44</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr"/>
+      <c r="E1416" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>4705</v>
+      </c>
+      <c r="G1416" t="inlineStr"/>
+      <c r="H1416" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Data Patterns 4822.00 231.20 BUY TGT 4800 SL 4705</t>
+        </is>
+      </c>
+      <c r="I1416" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1416" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:40:42</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr"/>
+      <c r="E1417" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>4705</v>
+      </c>
+      <c r="G1417" t="inlineStr"/>
+      <c r="H1417" t="inlineStr">
+        <is>
+          <t>Astra Micro 1747.50 TODAY 1783 HIGH 1783.30 LOW 1708.30 Vol: 263.96 k शुभ 'मंगला' शेयर Data Patterns 4819.40 4.98% BUY TGT 4800 SL 4705</t>
+        </is>
+      </c>
+      <c r="I1417" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1417" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:36:12</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr"/>
+      <c r="E1418" t="n">
+        <v>425</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>408</v>
+      </c>
+      <c r="G1418" t="inlineStr"/>
+      <c r="H1418" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर LIC खरीदें PRICE 415.25 TARGET 425/435 STOP LOSS 408</t>
+        </is>
+      </c>
+      <c r="I1418" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1418" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:36:12</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr"/>
+      <c r="E1419" t="n">
+        <v>435</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>408</v>
+      </c>
+      <c r="G1419" t="inlineStr"/>
+      <c r="H1419" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर LIC खरीदें PRICE 415.25 TARGET 425/435 STOP LOSS 408</t>
+        </is>
+      </c>
+      <c r="I1419" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1419" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:35:00</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1420" t="n">
+        <v>4014.7</v>
+      </c>
+      <c r="E1420" t="n">
+        <v>4100.9</v>
+      </c>
+      <c r="G1420" t="inlineStr"/>
+      <c r="H1420" t="inlineStr">
+        <is>
+          <t>SUPER SID Sansera Engg 3997.60 101.30 BUY TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I1420" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1420" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:35:00</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1421" t="n">
+        <v>527.8</v>
+      </c>
+      <c r="E1421" t="n">
+        <v>535</v>
+      </c>
+      <c r="G1421" t="inlineStr"/>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>SUPER SID
+Hind Copper
+525.85 16.95
+BUY
+TGT 535
+DUR 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1421" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1421" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1422" t="n">
+        <v>4786.8</v>
+      </c>
+      <c r="E1422" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>4705</v>
+      </c>
+      <c r="G1422" t="inlineStr"/>
+      <c r="H1422" t="inlineStr">
+        <is>
+          <t>Data Patterns 4785.00 4.23% BUY TGT 4800 SL 4705</t>
+        </is>
+      </c>
+      <c r="I1422" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1422" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:33:46</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>INTELLECT</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr"/>
+      <c r="E1423" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>4705</v>
+      </c>
+      <c r="G1423" t="inlineStr"/>
+      <c r="H1423" t="inlineStr">
+        <is>
+          <t>Intellect Design 683.70 ▲ 0.23% HIGH 688.00 LOW 677.00 Vol: 34.54 k शुभ 'मंगला' शेयर Data Patterns 4784.00 BUY TGT 4800 SL 4705</t>
+        </is>
+      </c>
+      <c r="I1423" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1423" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:32:00</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1424" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="E1424" t="n">
+        <v>175</v>
+      </c>
+      <c r="F1424" t="n">
+        <v>161</v>
+      </c>
+      <c r="G1424" t="inlineStr"/>
+      <c r="H1424" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय Bandhan Bank खरीदें PRICE 167.80 TARGET 175/184 STOP LOSS 161</t>
+        </is>
+      </c>
+      <c r="I1424" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1424" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:32:00</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1425" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="E1425" t="n">
+        <v>184</v>
+      </c>
+      <c r="F1425" t="n">
+        <v>161</v>
+      </c>
+      <c r="G1425" t="inlineStr"/>
+      <c r="H1425" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय Bandhan Bank खरीदें PRICE 167.80 TARGET 175/184 STOP LOSS 161</t>
+        </is>
+      </c>
+      <c r="I1425" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1425" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:31:00</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1426" t="n">
+        <v>410.3</v>
+      </c>
+      <c r="E1426" t="n">
+        <v>421</v>
+      </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1426" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय BEL खरीदें PRICE 409.20 TARGET 421/500 DURATION 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1426" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1426" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:31:00</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1427" t="n">
+        <v>410.3</v>
+      </c>
+      <c r="E1427" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1427" t="inlineStr"/>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>BEL खरीदें PRICE 409.20 TARGET 421/500 DURATION 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1427" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1427" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:30:00</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1428" t="n">
+        <v>409.95</v>
+      </c>
+      <c r="E1428" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1428" t="inlineStr"/>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>SUPER SID BEL खरीदें PRICE 409.10 TARGET 421/500 DURATION 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1428" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1428" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:30:00</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1429" t="n">
+        <v>409.95</v>
+      </c>
+      <c r="E1429" t="n">
+        <v>421</v>
+      </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय BEL खरीदें PRICE 409.10 TARGET 421/500 DURATION 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1429" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1429" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:27:01</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr"/>
+      <c r="E1430" t="n">
+        <v>3998</v>
+      </c>
+      <c r="G1430" t="inlineStr"/>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>SID Sansera Engg 4641.00 BUY 3998 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I1430" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1430" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:26:40</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>PCBL</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr"/>
+      <c r="E1431" t="n">
+        <v>327.25</v>
+      </c>
+      <c r="G1431" t="inlineStr"/>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>PCBL Chemical 327.25 INVESTMENT PICK 264.00 11/07/2024 RECO PRICE RETURN TILL NOW 63.25 23.96%</t>
+        </is>
+      </c>
+      <c r="I1431" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1431" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:26:12</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr"/>
+      <c r="E1432" t="n">
+        <v>4024.3</v>
+      </c>
+      <c r="G1432" t="inlineStr"/>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>Sansera Engg 4024.30 INVESTMENT PICK 1727.00 24/12/2025 RECO PRICE RETURN TILL NOW 2297.30 133.02%</t>
+        </is>
+      </c>
+      <c r="I1432" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1432" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:26:09</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr"/>
+      <c r="E1433" t="n">
+        <v>4024.9</v>
+      </c>
+      <c r="G1433" t="inlineStr"/>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>Sansera Engg 4024.90 INVESTMENT PICK 1727.00 24/12/2025 RECO PRICE RETURN TILL NOW 2297.90 133.06%</t>
+        </is>
+      </c>
+      <c r="I1433" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1433" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1434" t="n">
+        <v>524.25</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>535</v>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय
+Hind Copper
+खरीदें
+PRICE ▶ 524.25
+TARGET ▶ 535/715
+DURATION ▶ 6-8 महीने</t>
+        </is>
+      </c>
+      <c r="I1434" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1434" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1435" t="n">
+        <v>524.25</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>715</v>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1435" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय
+Hind Copper
+खरीदें
+PRICE ▶ 524.25
+TARGET ▶ 535/715
+DURATION ▶ 6-8 महीने</t>
+        </is>
+      </c>
+      <c r="I1435" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1435" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:24:31</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr"/>
+      <c r="E1436" t="n">
+        <v>535</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>715</v>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1436" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी की राय Hind Copper खरीदें PRICE 523.65 TARGET 535/715 DURATION 6-8 महीने</t>
+        </is>
+      </c>
+      <c r="I1436" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1436" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1437" t="n">
+        <v>524.25</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>535</v>
+      </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1437" t="inlineStr">
+        <is>
+          <t>SUPER SID Hind Copper PRICE 523.60 TARGET 535/700 ANALYST DISCLOSURE Siddharth Sedani Anand Rathi Shares and Stock Brokers SEBI REG NO: INH000000834</t>
+        </is>
+      </c>
+      <c r="I1437" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1437" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1438" t="n">
+        <v>524.65</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>700</v>
+      </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1438" t="inlineStr">
+        <is>
+          <t>SUPER SID Hind Copper PRICE 523.60 TARGET 535/700 ANALYST DISCLOSURE Siddharth Sedani Anand Rathi Shares and Stock Brokers SEBI REG NO: INH000000834</t>
+        </is>
+      </c>
+      <c r="I1438" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1438" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1439" t="n">
+        <v>1018.8</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>999</v>
+      </c>
+      <c r="G1439" t="inlineStr"/>
+      <c r="H1439" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय Hindalco खरीदें PRICE 1017.40 TARGET 1040/1060 STOP LOSS 999</t>
+        </is>
+      </c>
+      <c r="I1439" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1439" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1440" t="n">
+        <v>1019.3</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>1060</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>999</v>
+      </c>
+      <c r="G1440" t="inlineStr"/>
+      <c r="H1440" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय Hindalco खरीदें PRICE 1017.40 TARGET 1040/1060 STOP LOSS 999</t>
+        </is>
+      </c>
+      <c r="I1440" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1440" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>DATAPATTNS</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1441" t="n">
+        <v>4752.4</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>4705</v>
+      </c>
+      <c r="G1441" t="inlineStr"/>
+      <c r="H1441" t="inlineStr">
+        <is>
+          <t>Data Patterns खरीदें PRICE 4745.30 TARGET 4800/4840 STOP LOSS 4705</t>
+        </is>
+      </c>
+      <c r="I1441" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1441" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1442" t="n">
+        <v>4636.1</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="H1442" t="inlineStr">
+        <is>
+          <t>नोमुरा GE Vernova T&amp;D 4635.20 +6.14% BUY लक्ष्य ₹5675 से बढ़ाकर ₹6000</t>
+        </is>
+      </c>
+      <c r="I1442" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1442" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1443" t="n">
+        <v>31315</v>
+      </c>
+      <c r="E1443" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G1443" t="inlineStr"/>
+      <c r="H1443" t="inlineStr">
+        <is>
+          <t>सिटी
+Hitachi Energy
+31500.00 -0.87%
+BUY
+लक्ष्य ₹46700 से घटाकर ₹42000</t>
+        </is>
+      </c>
+      <c r="I1443" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1443" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1444" t="n">
+        <v>4048</v>
+      </c>
+      <c r="E1444" t="n">
+        <v>4954</v>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>CLSA</t>
+        </is>
+      </c>
+      <c r="H1444" t="inlineStr">
+        <is>
+          <t>CLSA Sansera Engg 4020.00 +3.17% ACCUMULATE लक्ष्य ₹4954</t>
+        </is>
+      </c>
+      <c r="I1444" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1444" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>BDL</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1445" t="n">
+        <v>1250.1</v>
+      </c>
+      <c r="E1445" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G1445" t="inlineStr"/>
+      <c r="H1445" t="inlineStr">
+        <is>
+          <t>Bharat Dynamics 1250.00 +8.30 HOLD लक्ष्य ₹1280</t>
+        </is>
+      </c>
+      <c r="I1445" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1445" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1446" t="n">
+        <v>544.25</v>
+      </c>
+      <c r="E1446" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G1446" t="inlineStr"/>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>HDFC Life 539.00 5.80 1.09% Vol: 13.81 k PRE-OPEN BROKERAGE CALLS HOLD लक्ष्य ₹1280</t>
+        </is>
+      </c>
+      <c r="I1446" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1446" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1447" t="n">
+        <v>2469.9</v>
+      </c>
+      <c r="E1447" t="n">
+        <v>2509</v>
+      </c>
+      <c r="F1447" t="n">
+        <v>2425</v>
+      </c>
+      <c r="G1447" t="inlineStr"/>
+      <c r="H1447" t="inlineStr">
+        <is>
+          <t>MY CHOICE GLENMARK PHARMA B 2509 2425</t>
+        </is>
+      </c>
+      <c r="I1447" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1447" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1448" t="n">
+        <v>2469.9</v>
+      </c>
+      <c r="E1448" t="n">
+        <v>2509</v>
+      </c>
+      <c r="G1448" t="inlineStr"/>
+      <c r="H1448" t="inlineStr">
+        <is>
+          <t>MY CHOICE GLENMARK PHARMA B 2509</t>
+        </is>
+      </c>
+      <c r="I1448" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1448" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1449" t="n">
+        <v>3350</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>3400</v>
+      </c>
+      <c r="G1449" t="inlineStr"/>
+      <c r="H1449" t="inlineStr">
+        <is>
+          <t>MY CHOICE MCX B 3400</t>
+        </is>
+      </c>
+      <c r="I1449" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1449" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>HDFCLIFE54029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1450" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1450" t="inlineStr"/>
+      <c r="H1450" t="inlineStr">
+        <is>
+          <t>HDFC LIFE 540 CE B 16 6</t>
+        </is>
+      </c>
+      <c r="I1450" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1450" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1451" t="n">
+        <v>2469.9</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>2588</v>
+      </c>
+      <c r="G1451" t="inlineStr"/>
+      <c r="H1451" t="inlineStr">
+        <is>
+          <t>PICK THE DAY Glenmark Pharma 2451.90 BUY TGT 2588</t>
+        </is>
+      </c>
+      <c r="I1451" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1451" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1452" t="n">
+        <v>8301</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>11100</v>
+      </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1452" t="inlineStr">
+        <is>
+          <t>FII INVEST ENT F PO... जेफरीज Polycab India 8261.00 39.00 TARGET ₹11100</t>
+        </is>
+      </c>
+      <c r="I1452" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1452" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1453" t="n">
+        <v>1194</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>1220</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>1145</v>
+      </c>
+      <c r="G1453" t="inlineStr"/>
+      <c r="H1453" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय
+Nippon Life India
+UY
+PRICE ▶ 1195.00
+TARGET ▶ 1220/1250
+STOP LOSS ▶ 1145</t>
+        </is>
+      </c>
+      <c r="I1453" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1453" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1454" t="n">
+        <v>1194</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>1145</v>
+      </c>
+      <c r="G1454" t="inlineStr"/>
+      <c r="H1454" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय
+Nippon Life India
+UY
+PRICE ▶ 1195.00
+TARGET ▶ 1220/1250
+STOP LOSS ▶ 1145</t>
+        </is>
+      </c>
+      <c r="I1454" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1454" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>OFSS29SEP26</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1455" t="n">
+        <v>11740</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>11400</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>12050</v>
+      </c>
+      <c r="G1455" t="inlineStr"/>
+      <c r="H1455" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Oracle Fin Fut SELL PRICE 11782.00 TARGET 11400/11000 STOP LOSS 12050</t>
+        </is>
+      </c>
+      <c r="I1455" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1455" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>OFSS29SEP26</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1456" t="n">
+        <v>11740</v>
+      </c>
+      <c r="E1456" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>12050</v>
+      </c>
+      <c r="G1456" t="inlineStr"/>
+      <c r="H1456" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Oracle Fin Fut SELL PRICE 11782.00 TARGET 11400/11000 STOP LOSS 12050</t>
+        </is>
+      </c>
+      <c r="I1456" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1456" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1457" t="n">
+        <v>2469.9</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>2530</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G1457" t="inlineStr"/>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>Glenmark Pharma BUY PRICE 2451.90 TARGET 2500/2530 STOP LOSS 2400</t>
+        </is>
+      </c>
+      <c r="I1457" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1457" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1458" t="n">
+        <v>2457.5</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G1458" t="inlineStr"/>
+      <c r="H1458" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Glenmark Pharma BUY PRICE 2451.90 TARGET 2500/2530 STOP LOSS 2400</t>
+        </is>
+      </c>
+      <c r="I1458" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1458" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1459" t="n">
+        <v>1194</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1459" t="inlineStr"/>
+      <c r="H1459" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+Nippon Life India
+BUY
+PRICE 1195.00
+TARGET 1220/1250
+STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1459" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1459" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>NAM-INDIA</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1460" t="n">
+        <v>1194</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G1460" t="inlineStr"/>
+      <c r="H1460" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+Nippon Life India
+BUY
+PRICE 1195.00
+TARGET 1220/1250
+STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1460" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1460" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>INFY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1461" t="n">
+        <v>1098.8</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>1105</v>
+      </c>
+      <c r="G1461" t="inlineStr"/>
+      <c r="H1461" t="inlineStr">
+        <is>
+          <t>विश्वेश चौहान की राय
+Infosys Fut
+SELL
+PRICE ▸ 1093.60
+TARGET ▸ 1050
+STOP LOSS ▸ 1105</t>
+        </is>
+      </c>
+      <c r="I1461" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1461" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>CARTRADE</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1462" t="n">
+        <v>3186</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>3250</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>3140</v>
+      </c>
+      <c r="G1462" t="inlineStr"/>
+      <c r="H1462" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Cartrade Tech BUY PRICE 3179.90 TARGET 3250/3280 STOP LOSS 3140</t>
+        </is>
+      </c>
+      <c r="I1462" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1462" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>CARTRADE</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1463" t="n">
+        <v>3186</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>3280</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>3140</v>
+      </c>
+      <c r="G1463" t="inlineStr"/>
+      <c r="H1463" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Cartrade Tech BUY PRICE 3179.90 TARGET 3250/3280 STOP LOSS 3140</t>
+        </is>
+      </c>
+      <c r="I1463" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1463" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1464" t="n">
+        <v>956</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>990</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>930</v>
+      </c>
+      <c r="G1464" t="inlineStr"/>
+      <c r="H1464" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Jubilant Pharmova BUY PRICE 950.30 TARGET 990/1020 STOP LOSS 930</t>
+        </is>
+      </c>
+      <c r="I1464" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1464" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>JUBLPHARMA</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1465" t="n">
+        <v>956</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>930</v>
+      </c>
+      <c r="G1465" t="inlineStr"/>
+      <c r="H1465" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Jubilant Pharmova BUY PRICE 950.30 TARGET 990/1020 STOP LOSS 930</t>
+        </is>
+      </c>
+      <c r="I1465" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1465" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>MAXHEALTH29SEP26</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1466" t="n">
+        <v>996</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>980</v>
+      </c>
+      <c r="G1466" t="inlineStr"/>
+      <c r="H1466" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Max Healthcare Fut
+BU
+PRICE ▶ 992.90
+TARGET ▶ 1000, 1010, 1020
+STOP LOSS ▶ 980</t>
+        </is>
+      </c>
+      <c r="I1466" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1466" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>MAXHEALTH29SEP26</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1467" t="n">
+        <v>993.4</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>980</v>
+      </c>
+      <c r="G1467" t="inlineStr"/>
+      <c r="H1467" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Max Healthcare Fut
+BU
+PRICE ▶ 992.90
+TARGET ▶ 1000, 1010, 1020
+STOP LOSS ▶ 980</t>
+        </is>
+      </c>
+      <c r="I1467" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1467" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>MAXHEALTH29SEP26</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1468" t="n">
+        <v>996</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>980</v>
+      </c>
+      <c r="G1468" t="inlineStr"/>
+      <c r="H1468" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Max Healthcare Fut
+BU
+PRICE ▶ 992.90
+TARGET ▶ 1000, 1010, 1020
+STOP LOSS ▶ 980</t>
+        </is>
+      </c>
+      <c r="I1468" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1468" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1469" t="n">
+        <v>3350</v>
+      </c>
+      <c r="E1469" t="n">
+        <v>3400</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>3298</v>
+      </c>
+      <c r="G1469" t="inlineStr"/>
+      <c r="H1469" t="inlineStr">
+        <is>
+          <t>MY CHOICE MCX B 3400 3298</t>
+        </is>
+      </c>
+      <c r="I1469" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1469" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>COROMANDEL</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1470" t="n">
+        <v>1960.5</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>1951</v>
+      </c>
+      <c r="G1470" t="inlineStr"/>
+      <c r="H1470" t="inlineStr">
+        <is>
+          <t>CASH COROMANDEL INT B 2023 1951</t>
+        </is>
+      </c>
+      <c r="I1470" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1470" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1471" t="n">
+        <v>170</v>
+      </c>
+      <c r="E1471" t="n">
+        <v>1910</v>
+      </c>
+      <c r="G1471" t="inlineStr"/>
+      <c r="H1471" t="inlineStr">
+        <is>
+          <t>INVESTMENT ASHOK LEYLAND B 1910 12M</t>
+        </is>
+      </c>
+      <c r="I1471" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1471" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1472" t="n">
+        <v>4903.7</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G1472" t="inlineStr"/>
+      <c r="H1472" t="inlineStr">
+        <is>
+          <t>FUNDA HAL B 5100 6 MONTH</t>
+        </is>
+      </c>
+      <c r="I1472" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1472" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1473" t="n">
+        <v>162.94</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>166</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1473" t="inlineStr"/>
+      <c r="H1473" t="inlineStr">
+        <is>
+          <t>MY CHOICE Samvardhana Motherson खरीदें PRICE 162.00 TARGET 166 STOP LOSS 160</t>
+        </is>
+      </c>
+      <c r="I1473" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1473" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1474" t="n">
+        <v>2469.9</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>2509</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>2425</v>
+      </c>
+      <c r="G1474" t="inlineStr"/>
+      <c r="H1474" t="inlineStr">
+        <is>
+          <t>MY CHOICE Glenmark Pharma खरीदें PRICE 2451.90 TARGET 2509 STOP LOSS 2425</t>
+        </is>
+      </c>
+      <c r="I1474" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1474" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1475" t="n">
+        <v>408</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>415</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1475" t="inlineStr"/>
+      <c r="H1475" t="inlineStr">
+        <is>
+          <t>MY CHOICE BEL खरीदें PRICE 404.00 TARGET 415 STOP LOSS 400</t>
+        </is>
+      </c>
+      <c r="I1475" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1475" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1476" t="n">
+        <v>408</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>415</v>
+      </c>
+      <c r="G1476" t="inlineStr"/>
+      <c r="H1476" t="inlineStr">
+        <is>
+          <t>MY CHOICE BEL PRICE 404.00 TARGET 415</t>
+        </is>
+      </c>
+      <c r="I1476" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1476" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1477" t="n">
+        <v>170</v>
+      </c>
+      <c r="E1477" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1477" t="inlineStr"/>
+      <c r="H1477" t="inlineStr">
+        <is>
+          <t>Ashok Leyland खरीदें PRICE 170.00 TARGET 190 DURATION 12 महीने</t>
+        </is>
+      </c>
+      <c r="I1477" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1477" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1478" t="n">
+        <v>23500</v>
+      </c>
+      <c r="E1478" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>22100</v>
+      </c>
+      <c r="G1478" t="inlineStr"/>
+      <c r="H1478" t="inlineStr">
+        <is>
+          <t>Shree Cement खरीदें PRICE 23365.00 TARGET 26000 STOP LOSS 22100</t>
+        </is>
+      </c>
+      <c r="I1478" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1478" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1479" t="n">
+        <v>1060</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>1085</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>1041</v>
+      </c>
+      <c r="G1479" t="inlineStr"/>
+      <c r="H1479" t="inlineStr">
+        <is>
+          <t>TECHNO PICK
+Motilal Oswal Fin
+खरीदें
+PRICE → 1055.00
+TARGET → 1085
+STOP LOSS → 1041</t>
+        </is>
+      </c>
+      <c r="I1479" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1479" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>HDFCLIFE54029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1480" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1480" t="inlineStr"/>
+      <c r="H1480" t="inlineStr">
+        <is>
+          <t>BEST ऑप्शन HDFC Life 540 की कॉल खरीदें STOP LOSS 6 TARGET 16 HDFC Life 533.20 13.20</t>
+        </is>
+      </c>
+      <c r="I1480" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1480" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>COROMANDEL</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1481" t="n">
+        <v>1960.5</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>1951</v>
+      </c>
+      <c r="G1481" t="inlineStr"/>
+      <c r="H1481" t="inlineStr">
+        <is>
+          <t>CASH का शेयर Coromandel Intl खरीदें PRICE 1974.60 TARGET 2023 STOP LOSS 1951</t>
+        </is>
+      </c>
+      <c r="I1481" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1481" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>BLEL</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1482" t="n">
+        <v>477.75</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>478.3</v>
+      </c>
+      <c r="G1482" t="inlineStr"/>
+      <c r="H1482" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर
+कामकाजी मुनाफा 21% बढ़कर ₹27.6 रहा
+Behari Lal Engineering 478.30 ▲ 5.55%</t>
+        </is>
+      </c>
+      <c r="I1482" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1482" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1483" t="n">
+        <v>194.78</v>
+      </c>
+      <c r="E1483" t="n">
+        <v>240</v>
+      </c>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1483" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT जेफरीज BUY Groww 194.73 0.38% लक्ष्य ₹250 से घटाकर ₹240</t>
+        </is>
+      </c>
+      <c r="I1483" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1483" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>WIPRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1484" t="n">
+        <v>171.76</v>
+      </c>
+      <c r="E1484" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>181</v>
+      </c>
+      <c r="G1484" t="inlineStr"/>
+      <c r="H1484" t="inlineStr">
+        <is>
+          <t>अर्पित बेरीवाल की राय
+Wipro Fut
+बेचें
+PRICE → 172.02
+TARGET → 160
+STOP LOSS → 181</t>
+        </is>
+      </c>
+      <c r="I1484" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1484" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1485" t="n">
+        <v>9375.5</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G1485" t="inlineStr"/>
+      <c r="H1485" t="inlineStr">
+        <is>
+          <t>अर्पित बेरीवाल की राय
+Divi's Lab
+खरीदें
+PRICE ▶ 9315.00
+TARGET ▶ 10000
+STOP LOSS ▶ 9000</t>
+        </is>
+      </c>
+      <c r="I1485" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1485" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>GROWW</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1486" t="n">
+        <v>194.78</v>
+      </c>
+      <c r="E1486" t="n">
+        <v>250</v>
+      </c>
+      <c r="G1486" t="inlineStr"/>
+      <c r="H1486" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Groww
+194.73
+BUY
+लक्ष्य ₹240 से घटाकर ₹250</t>
+        </is>
+      </c>
+      <c r="I1486" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1486" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1487" t="n">
+        <v>1264.2</v>
+      </c>
+      <c r="E1487" t="n">
+        <v>4954</v>
+      </c>
+      <c r="G1487" t="inlineStr"/>
+      <c r="H1487" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+ACCUMULATE
+लक्ष्य ₹4954
+अजय बरगा
+मार्केट एक्सपर्ट</t>
+        </is>
+      </c>
+      <c r="I1487" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1487" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>BDL</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1488" t="n">
+        <v>1244</v>
+      </c>
+      <c r="E1488" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1488" t="inlineStr">
+        <is>
+          <t>जेफरीज Bharat Dynamics 1241.70 -1.06% HOLD लक्ष्य ₹1280</t>
+        </is>
+      </c>
+      <c r="I1488" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1488" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1489" t="n">
+        <v>8596</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>8850</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>8475</v>
+      </c>
+      <c r="G1489" t="inlineStr"/>
+      <c r="H1489" t="inlineStr">
+        <is>
+          <t>INTRADAY CALL Navin Fluorine BUY TARGET 8850 STOP LOSS 8475 Navin Fluorine 8603.50 0.54%</t>
+        </is>
+      </c>
+      <c r="I1489" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1489" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>M&amp;MFIN</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1490" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>396</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>360</v>
+      </c>
+      <c r="G1490" t="inlineStr"/>
+      <c r="H1490" t="inlineStr">
+        <is>
+          <t>POSITIONAL CALL M&amp;M Fin BUY TARGET 396 STOP LOSS 360 M&amp;M Fin 372.35 0.35%</t>
+        </is>
+      </c>
+      <c r="I1490" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1490" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1327"/>
+  <autoFilter ref="A1:J1490"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1562</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1490"/>
+  <dimension ref="A1:J1562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -56464,11 +56464,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1328" t="inlineStr"/>
       <c r="E1328" t="n">
         <v>9235</v>
       </c>
-      <c r="G1328" t="inlineStr"/>
       <c r="H1328" t="inlineStr">
         <is>
           <t>Divi's Lab Fut 9548.00 222.00 BUY TARGET HIT 9235</t>
@@ -56501,14 +56499,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1329" t="inlineStr"/>
       <c r="E1329" t="n">
         <v>9480</v>
       </c>
       <c r="F1329" t="n">
         <v>9235</v>
       </c>
-      <c r="G1329" t="inlineStr"/>
       <c r="H1329" t="inlineStr">
         <is>
           <t>Divi's Lab Fut 9548.00 222.00 BUY TGT 9480 SL 9235</t>
@@ -56541,14 +56537,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1330" t="inlineStr"/>
       <c r="E1330" t="n">
         <v>9480</v>
       </c>
       <c r="F1330" t="n">
         <v>9235</v>
       </c>
-      <c r="G1330" t="inlineStr"/>
       <c r="H1330" t="inlineStr">
         <is>
           <t>Divi's Lab Fut 9548.00 2.38% BUY TGT 9480 SL 9235</t>
@@ -56581,11 +56575,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1331" t="inlineStr"/>
       <c r="E1331" t="n">
         <v>9480</v>
       </c>
-      <c r="G1331" t="inlineStr"/>
       <c r="H1331" t="inlineStr">
         <is>
           <t>Divi's Lab Fut 9548.00 222.00 BUY TGT 9480</t>
@@ -56624,7 +56616,6 @@
       <c r="E1332" t="n">
         <v>8600</v>
       </c>
-      <c r="G1332" t="inlineStr"/>
       <c r="H1332" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -56671,7 +56662,6 @@
       <c r="F1333" t="n">
         <v>161</v>
       </c>
-      <c r="G1333" t="inlineStr"/>
       <c r="H1333" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट Bandhan Bank 171.30 6.60 BUY TGT 175 SL 161</t>
@@ -56710,7 +56700,6 @@
       <c r="E1334" t="n">
         <v>175</v>
       </c>
-      <c r="G1334" t="inlineStr"/>
       <c r="H1334" t="inlineStr">
         <is>
           <t>Bandhan Bank 171.37 ▲ 6.67 BUY TGT 175</t>
@@ -56749,7 +56738,6 @@
       <c r="E1335" t="n">
         <v>535</v>
       </c>
-      <c r="G1335" t="inlineStr"/>
       <c r="H1335" t="inlineStr">
         <is>
           <t>Hind Copper 532.45 4.63% BUY TGT 535 DUR 6 महीने</t>
@@ -56791,7 +56779,6 @@
       <c r="F1336" t="n">
         <v>999</v>
       </c>
-      <c r="G1336" t="inlineStr"/>
       <c r="H1336" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट Hindalco 1018.80 12.80 BUY TGT 1040 SL 999</t>
@@ -56824,7 +56811,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1337" t="inlineStr"/>
       <c r="E1337" t="n">
         <v>930</v>
       </c>
@@ -56865,7 +56851,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1338" t="inlineStr"/>
       <c r="E1338" t="n">
         <v>730</v>
       </c>
@@ -56906,14 +56891,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1339" t="inlineStr"/>
       <c r="E1339" t="n">
         <v>990</v>
       </c>
       <c r="F1339" t="n">
         <v>930</v>
       </c>
-      <c r="G1339" t="inlineStr"/>
       <c r="H1339" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Jubilant Pharmova 1011.20 6.41% BUY TGT 990 SL 930</t>
@@ -56955,7 +56938,6 @@
       <c r="F1340" t="n">
         <v>1890</v>
       </c>
-      <c r="G1340" t="inlineStr"/>
       <c r="H1340" t="inlineStr">
         <is>
           <t>11 बजे की लेडीज स्पेशल
@@ -56993,7 +56975,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1341" t="inlineStr"/>
       <c r="E1341" t="n">
         <v>6000</v>
       </c>
@@ -57086,7 +57067,6 @@
       <c r="E1343" t="n">
         <v>6000</v>
       </c>
-      <c r="G1343" t="inlineStr"/>
       <c r="H1343" t="inlineStr">
         <is>
           <t>BUZZING STOCK GE Vernova T&amp;D 4739.00 ▲ 8.51% खरीदारी की राश, लक्ष्य ₹5675 से बढ़ाकर ₹6000</t>
@@ -57119,14 +57099,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1344" t="inlineStr"/>
       <c r="E1344" t="n">
         <v>9480</v>
       </c>
       <c r="F1344" t="n">
         <v>9235</v>
       </c>
-      <c r="G1344" t="inlineStr"/>
       <c r="H1344" t="inlineStr">
         <is>
           <t>जय का JACKPOT
@@ -57164,11 +57142,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1345" t="inlineStr"/>
       <c r="E1345" t="n">
         <v>9480</v>
       </c>
-      <c r="G1345" t="inlineStr"/>
       <c r="H1345" t="inlineStr">
         <is>
           <t>Divi's Lab Fut 9514.50 188.50 BUY TGT 9480</t>
@@ -57201,14 +57177,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1346" t="inlineStr"/>
       <c r="E1346" t="n">
         <v>425</v>
       </c>
       <c r="F1346" t="n">
         <v>408</v>
       </c>
-      <c r="G1346" t="inlineStr"/>
       <c r="H1346" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -57255,7 +57229,6 @@
       <c r="F1347" t="n">
         <v>161</v>
       </c>
-      <c r="G1347" t="inlineStr"/>
       <c r="H1347" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट
@@ -57302,7 +57275,6 @@
       <c r="F1348" t="n">
         <v>999</v>
       </c>
-      <c r="G1348" t="inlineStr"/>
       <c r="H1348" t="inlineStr">
         <is>
           <t>Hindalco 1022.00 16.00 BUY TGT 1040 SL 999</t>
@@ -57344,7 +57316,6 @@
       <c r="F1349" t="n">
         <v>728</v>
       </c>
-      <c r="G1349" t="inlineStr"/>
       <c r="H1349" t="inlineStr">
         <is>
           <t>SHORT MIDCAP STOCKS TD Power खरीदें STOP LOSS 728 TARGET 810/830 DURATION -- TD Power 769.00</t>
@@ -57432,7 +57403,6 @@
       <c r="F1351" t="n">
         <v>215</v>
       </c>
-      <c r="G1351" t="inlineStr"/>
       <c r="H1351" t="inlineStr">
         <is>
           <t>संदीप जैन की राय South West Pinnacle खरीदें STOP LOSS 215 TARGET 240/245 DURATION -- South West Pinnacle 222.67 ▲ 0.18%</t>
@@ -57474,7 +57444,6 @@
       <c r="F1352" t="n">
         <v>215</v>
       </c>
-      <c r="G1352" t="inlineStr"/>
       <c r="H1352" t="inlineStr">
         <is>
           <t>संदीप जैन की राय South West Pinnacle खरीदें STOP LOSS 215 TARGET 240/245 DURATION -- South West Pinnacle 222.67 ▲ 0.18%</t>
@@ -57507,14 +57476,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1353" t="inlineStr"/>
       <c r="E1353" t="n">
         <v>250</v>
       </c>
       <c r="F1353" t="n">
         <v>218</v>
       </c>
-      <c r="G1353" t="inlineStr"/>
       <c r="H1353" t="inlineStr">
         <is>
           <t>POSITIONAL MIDCAP STOCK BHARAT SEATS LIMITED खरीदें STOP LOSS 218 TARGET 250/255 DURATION</t>
@@ -57547,14 +57514,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1354" t="inlineStr"/>
       <c r="E1354" t="n">
         <v>255</v>
       </c>
       <c r="F1354" t="n">
         <v>218</v>
       </c>
-      <c r="G1354" t="inlineStr"/>
       <c r="H1354" t="inlineStr">
         <is>
           <t>POSITIONAL MIDCAP STOCK BHARAT SEATS LIMITED खरीदें STOP LOSS 218 TARGET 250/255 DURATION</t>
@@ -57587,14 +57552,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1355" t="inlineStr"/>
       <c r="E1355" t="n">
         <v>158</v>
       </c>
       <c r="F1355" t="n">
         <v>132</v>
       </c>
-      <c r="G1355" t="inlineStr"/>
       <c r="H1355" t="inlineStr">
         <is>
           <t>TN Petro खरीदें PRICE 143.57 TARGET 158/170 STOP LOSS 132</t>
@@ -57636,7 +57599,6 @@
       <c r="F1356" t="n">
         <v>406</v>
       </c>
-      <c r="G1356" t="inlineStr"/>
       <c r="H1356" t="inlineStr">
         <is>
           <t>BEL Fut 417.50 11.15 BUY TGT 418 SL 406</t>
@@ -57675,7 +57637,6 @@
       <c r="E1357" t="n">
         <v>1950</v>
       </c>
-      <c r="G1357" t="inlineStr"/>
       <c r="H1357" t="inlineStr">
         <is>
           <t>जैन साब के GEMS Astra Micro 1745.50 33.90 BUY TGT 1950 SL --</t>
@@ -57717,7 +57678,6 @@
       <c r="F1358" t="n">
         <v>161</v>
       </c>
-      <c r="G1358" t="inlineStr"/>
       <c r="H1358" t="inlineStr">
         <is>
           <t>Bandhan Bank 170.45 5.75 BUY TGT 175 SL 161</t>
@@ -57759,7 +57719,6 @@
       <c r="F1359" t="n">
         <v>4580</v>
       </c>
-      <c r="G1359" t="inlineStr"/>
       <c r="H1359" t="inlineStr">
         <is>
           <t>POSITIONAL MIDCAP STOCKS
@@ -57805,7 +57764,6 @@
       <c r="F1360" t="n">
         <v>4580</v>
       </c>
-      <c r="G1360" t="inlineStr"/>
       <c r="H1360" t="inlineStr">
         <is>
           <t>CRISIL खरीदें STOP LOSS 4580 TARGET 5100/5150 DURATION -- CRISIL 4799.90 13.30</t>
@@ -57844,7 +57802,6 @@
       <c r="E1361" t="n">
         <v>421</v>
       </c>
-      <c r="G1361" t="inlineStr"/>
       <c r="H1361" t="inlineStr">
         <is>
           <t>SUPER SID BEL 415.10 11.10 BUY TGT 421 DUR 6 महीने</t>
@@ -57877,11 +57834,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1362" t="inlineStr"/>
       <c r="E1362" t="n">
         <v>535</v>
       </c>
-      <c r="G1362" t="inlineStr"/>
       <c r="H1362" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -57928,7 +57883,6 @@
       <c r="F1363" t="n">
         <v>999</v>
       </c>
-      <c r="G1363" t="inlineStr"/>
       <c r="H1363" t="inlineStr">
         <is>
           <t>Hindalco 1023.40 17.40 BUY TGT 1040 SL 999</t>
@@ -57967,7 +57921,6 @@
       <c r="E1364" t="n">
         <v>1040</v>
       </c>
-      <c r="G1364" t="inlineStr"/>
       <c r="H1364" t="inlineStr">
         <is>
           <t>Hindalco 1023.00 17.00 BUY TGT 1040</t>
@@ -58009,7 +57962,6 @@
       <c r="F1365" t="n">
         <v>218</v>
       </c>
-      <c r="G1365" t="inlineStr"/>
       <c r="H1365" t="inlineStr">
         <is>
           <t>POSITIONAL MIDCAP STOCKS
@@ -58057,7 +58009,6 @@
       <c r="F1366" t="n">
         <v>218</v>
       </c>
-      <c r="G1366" t="inlineStr"/>
       <c r="H1366" t="inlineStr">
         <is>
           <t>BHARAT SEATS LIMITED खरीदें STOP LOSS 218 TARGET 250/255 DURATION -- Bharat Seats Ltd 225.63</t>
@@ -58096,7 +58047,6 @@
       <c r="E1367" t="n">
         <v>1430</v>
       </c>
-      <c r="G1367" t="inlineStr"/>
       <c r="H1367" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS Aegis Logistics खरीदें STOP LOSS -- TARGET 1430/1450 DURATION 6-12 महीने Aegis Logistics 1247.20 6.50</t>
@@ -58135,7 +58085,6 @@
       <c r="E1368" t="n">
         <v>1450</v>
       </c>
-      <c r="G1368" t="inlineStr"/>
       <c r="H1368" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCKS Aegis Logistics खरीदें STOP LOSS -- TARGET 1430/1450 DURATION 6-12 महीने Aegis Logistics 1247.20 6.50</t>
@@ -58174,7 +58123,6 @@
       <c r="E1369" t="n">
         <v>1430</v>
       </c>
-      <c r="G1369" t="inlineStr"/>
       <c r="H1369" t="inlineStr">
         <is>
           <t>सदीप जैन का राय Aegis Logistics खरीदें STOP LOSS -- TARGET 1430/1450 DURATION 6-12 महीने Aegis Logistics 1246.90 0.54%</t>
@@ -58213,7 +58161,6 @@
       <c r="E1370" t="n">
         <v>1450</v>
       </c>
-      <c r="G1370" t="inlineStr"/>
       <c r="H1370" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Aegis Logistics खरीदें STOP LOSS -- TARGET 1430/1450 DURATION 6-12 महीने Aegis Logistics 1246.90</t>
@@ -58338,14 +58285,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1373" t="inlineStr"/>
       <c r="E1373" t="n">
         <v>420</v>
       </c>
       <c r="F1373" t="n">
         <v>280</v>
       </c>
-      <c r="G1373" t="inlineStr"/>
       <c r="H1373" t="inlineStr">
         <is>
           <t>Prime Focus खरीदें PRICE 321.10 TARGET 420/450 STOP LOSS 280</t>
@@ -58387,7 +58332,6 @@
       <c r="F1374" t="n">
         <v>280</v>
       </c>
-      <c r="G1374" t="inlineStr"/>
       <c r="H1374" t="inlineStr">
         <is>
           <t>1 की कमाई Prime Focus खरीदें PRICE 320.90 TARGET 420/450 STOP LOSS 280</t>
@@ -58429,7 +58373,6 @@
       <c r="F1375" t="n">
         <v>280</v>
       </c>
-      <c r="G1375" t="inlineStr"/>
       <c r="H1375" t="inlineStr">
         <is>
           <t>Prime Focus खरीदें PRICE 321.10 TARGET 420/450 STOP LOSS 280</t>
@@ -58468,7 +58411,6 @@
       <c r="E1376" t="n">
         <v>8600</v>
       </c>
-      <c r="G1376" t="inlineStr"/>
       <c r="H1376" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -58515,7 +58457,6 @@
       <c r="F1377" t="n">
         <v>406</v>
       </c>
-      <c r="G1377" t="inlineStr"/>
       <c r="H1377" t="inlineStr">
         <is>
           <t>BEL Fut 416.00 9.65 BUY TGT 418 SL 406</t>
@@ -58554,7 +58495,6 @@
       <c r="E1378" t="n">
         <v>1950</v>
       </c>
-      <c r="G1378" t="inlineStr"/>
       <c r="H1378" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -58598,7 +58538,6 @@
       <c r="E1379" t="n">
         <v>421</v>
       </c>
-      <c r="G1379" t="inlineStr"/>
       <c r="H1379" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -58642,7 +58581,6 @@
       <c r="E1380" t="n">
         <v>421</v>
       </c>
-      <c r="G1380" t="inlineStr"/>
       <c r="H1380" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -58686,7 +58624,6 @@
       <c r="E1381" t="n">
         <v>535</v>
       </c>
-      <c r="G1381" t="inlineStr"/>
       <c r="H1381" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -58733,7 +58670,6 @@
       <c r="F1382" t="n">
         <v>999</v>
       </c>
-      <c r="G1382" t="inlineStr"/>
       <c r="H1382" t="inlineStr">
         <is>
           <t>Hindalco 1020.70 14.70 BUY TGT 1040 SL 999</t>
@@ -58852,11 +58788,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1385" t="inlineStr"/>
       <c r="E1385" t="n">
         <v>3880</v>
       </c>
-      <c r="G1385" t="inlineStr"/>
       <c r="H1385" t="inlineStr">
         <is>
           <t>SUPER SID Sansera Engg 4034.40 BUY TGT 3880 TARGET HIT</t>
@@ -58895,7 +58829,6 @@
       <c r="E1386" t="n">
         <v>4172.5</v>
       </c>
-      <c r="G1386" t="inlineStr"/>
       <c r="H1386" t="inlineStr">
         <is>
           <t>SUPER SID Sansera Engg 4034.40 138.10 BUY TARGET HIT</t>
@@ -58928,11 +58861,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1387" t="inlineStr"/>
       <c r="E1387" t="n">
         <v>3990</v>
       </c>
-      <c r="G1387" t="inlineStr"/>
       <c r="H1387" t="inlineStr">
         <is>
           <t>SUPER SID Sansera Engg 4034.40 138.10 BUY TGT 3990 SL</t>
@@ -58965,11 +58896,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1388" t="inlineStr"/>
       <c r="E1388" t="n">
         <v>3980</v>
       </c>
-      <c r="G1388" t="inlineStr"/>
       <c r="H1388" t="inlineStr">
         <is>
           <t>Sansera Engg 4031.60 135.30 BUY TGT 3980 SL --</t>
@@ -59011,7 +58940,6 @@
       <c r="F1389" t="n">
         <v>408</v>
       </c>
-      <c r="G1389" t="inlineStr"/>
       <c r="H1389" t="inlineStr">
         <is>
           <t>विशेष के विशेष BEL Fut 414.95 9.88 BUY TGT 418 SL 408</t>
@@ -59050,7 +58978,6 @@
       <c r="E1390" t="n">
         <v>418</v>
       </c>
-      <c r="G1390" t="inlineStr"/>
       <c r="H1390" t="inlineStr">
         <is>
           <t>BEL Fut 415.10 8.75 BUY TGT 418</t>
@@ -59083,14 +59010,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1391" t="inlineStr"/>
       <c r="E1391" t="n">
         <v>250</v>
       </c>
       <c r="F1391" t="n">
         <v>150</v>
       </c>
-      <c r="G1391" t="inlineStr"/>
       <c r="H1391" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय DIVI'S LAB 9400 की कॉल @ ₹191 खरीदें STOP LOSS 150 TARGET 250/280 Divi's Lab 9400.00 ▲ 1.02%</t>
@@ -59123,14 +59048,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1392" t="inlineStr"/>
       <c r="E1392" t="n">
         <v>280</v>
       </c>
       <c r="F1392" t="n">
         <v>150</v>
       </c>
-      <c r="G1392" t="inlineStr"/>
       <c r="H1392" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय DIVI'S LAB 9400 की कॉल @ ₹191 खरीदें STOP LOSS 150 TARGET 250/280 Divi's Lab 9400.00 ▲ 1.02%</t>
@@ -59163,14 +59086,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1393" t="inlineStr"/>
       <c r="E1393" t="n">
         <v>425</v>
       </c>
       <c r="F1393" t="n">
         <v>408</v>
       </c>
-      <c r="G1393" t="inlineStr"/>
       <c r="H1393" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -59213,7 +59134,6 @@
       <c r="E1394" t="n">
         <v>535</v>
       </c>
-      <c r="G1394" t="inlineStr"/>
       <c r="H1394" t="inlineStr">
         <is>
           <t>SUPER SID Hind Copper 529.30 4.01% BUY TGT 535 BUR ₹ नहीं</t>
@@ -59246,11 +59166,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1395" t="inlineStr"/>
       <c r="E1395" t="n">
         <v>51.15</v>
       </c>
-      <c r="G1395" t="inlineStr"/>
       <c r="H1395" t="inlineStr">
         <is>
           <t>DIVISLAB 9400 CALL ▲
@@ -59297,7 +59215,6 @@
       <c r="F1396" t="n">
         <v>999</v>
       </c>
-      <c r="G1396" t="inlineStr"/>
       <c r="H1396" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट Hindalco 1015.30 9.30 BUY TGT 1040 SL 999</t>
@@ -59330,11 +59247,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1397" t="inlineStr"/>
       <c r="E1397" t="n">
         <v>4705</v>
       </c>
-      <c r="G1397" t="inlineStr"/>
       <c r="H1397" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Data Patterns 4798.90 4.53% BUY TARGET HIT 4705</t>
@@ -59367,11 +59282,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1398" t="inlineStr"/>
       <c r="E1398" t="n">
         <v>50</v>
       </c>
-      <c r="G1398" t="inlineStr"/>
       <c r="H1398" t="inlineStr">
         <is>
           <t>DIVISLAB 9400 CALL ▲ 203.65 ▲ 50.00 32.54% EXPIRY- 29 SEP 2026 OPEN INTEREST 1.08 Lk ▲ 0.12 Lk Divi's Lab 9402.50 87.50</t>
@@ -59404,11 +59317,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1399" t="inlineStr"/>
       <c r="E1399" t="n">
         <v>4705</v>
       </c>
-      <c r="G1399" t="inlineStr"/>
       <c r="H1399" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Data Patterns 4799.80 4.55% BUY TARGET HIT 4705</t>
@@ -59441,14 +59352,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1400" t="inlineStr"/>
       <c r="E1400" t="n">
         <v>4800</v>
       </c>
       <c r="F1400" t="n">
         <v>4705</v>
       </c>
-      <c r="G1400" t="inlineStr"/>
       <c r="H1400" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Data Patterns 4803.50 212.70 BUY TGT 4800 SL 4705</t>
@@ -59481,14 +59390,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1401" t="inlineStr"/>
       <c r="E1401" t="n">
         <v>4800</v>
       </c>
       <c r="F1401" t="n">
         <v>4705</v>
       </c>
-      <c r="G1401" t="inlineStr"/>
       <c r="H1401" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Data Patterns 4801.10 210.30 BUY TGT 4800 SL 4705</t>
@@ -59650,14 +59557,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1405" t="inlineStr"/>
       <c r="E1405" t="n">
         <v>421</v>
       </c>
       <c r="F1405" t="n">
         <v>500</v>
       </c>
-      <c r="G1405" t="inlineStr"/>
       <c r="H1405" t="inlineStr">
         <is>
           <t>BEL खरीदें PRICE 412.45 TARGET 421/500 DURATION 6 महीने</t>
@@ -59785,7 +59690,6 @@
       <c r="F1408" t="n">
         <v>406</v>
       </c>
-      <c r="G1408" t="inlineStr"/>
       <c r="H1408" t="inlineStr">
         <is>
           <t>विशेष चौहान की राय BEL Fut खरीदें PRICE 413.60 TARGET 418/426 STOP LOSS 406</t>
@@ -59827,7 +59731,6 @@
       <c r="F1409" t="n">
         <v>406</v>
       </c>
-      <c r="G1409" t="inlineStr"/>
       <c r="H1409" t="inlineStr">
         <is>
           <t>विशेष चौहान की राय BEL Fut खरीदें PRICE 413.60 TARGET 418/426 STOP LOSS 406</t>
@@ -59866,7 +59769,6 @@
       <c r="E1410" t="n">
         <v>426</v>
       </c>
-      <c r="G1410" t="inlineStr"/>
       <c r="H1410" t="inlineStr">
         <is>
           <t>BEL Fut PRICE 413.55 TARGET 418/426</t>
@@ -59905,7 +59807,6 @@
       <c r="E1411" t="n">
         <v>1990</v>
       </c>
-      <c r="G1411" t="inlineStr"/>
       <c r="H1411" t="inlineStr">
         <is>
           <t>Astra Micro खरीदें PRICE 1742.00 TARGET 1950/1990 STOP LOSS --</t>
@@ -59944,7 +59845,6 @@
       <c r="E1412" t="n">
         <v>1950</v>
       </c>
-      <c r="G1412" t="inlineStr"/>
       <c r="H1412" t="inlineStr">
         <is>
           <t>Astra Micro खरीदें PRICE 1742.00 TARGET 1950/1990 STOP LOSS --</t>
@@ -59983,7 +59883,6 @@
       <c r="E1413" t="n">
         <v>1950</v>
       </c>
-      <c r="G1413" t="inlineStr"/>
       <c r="H1413" t="inlineStr">
         <is>
           <t>जन साब के GEMS
@@ -60027,7 +59926,6 @@
       <c r="E1414" t="n">
         <v>1990</v>
       </c>
-      <c r="G1414" t="inlineStr"/>
       <c r="H1414" t="inlineStr">
         <is>
           <t>जन साब के GEMS
@@ -60074,7 +59972,6 @@
       <c r="F1415" t="n">
         <v>232</v>
       </c>
-      <c r="G1415" t="inlineStr"/>
       <c r="H1415" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Data Patterns 4822.80 232.00 BUY</t>
@@ -60107,14 +60004,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1416" t="inlineStr"/>
       <c r="E1416" t="n">
         <v>4800</v>
       </c>
       <c r="F1416" t="n">
         <v>4705</v>
       </c>
-      <c r="G1416" t="inlineStr"/>
       <c r="H1416" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Data Patterns 4822.00 231.20 BUY TGT 4800 SL 4705</t>
@@ -60147,14 +60042,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1417" t="inlineStr"/>
       <c r="E1417" t="n">
         <v>4800</v>
       </c>
       <c r="F1417" t="n">
         <v>4705</v>
       </c>
-      <c r="G1417" t="inlineStr"/>
       <c r="H1417" t="inlineStr">
         <is>
           <t>Astra Micro 1747.50 TODAY 1783 HIGH 1783.30 LOW 1708.30 Vol: 263.96 k शुभ 'मंगला' शेयर Data Patterns 4819.40 4.98% BUY TGT 4800 SL 4705</t>
@@ -60187,14 +60080,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1418" t="inlineStr"/>
       <c r="E1418" t="n">
         <v>425</v>
       </c>
       <c r="F1418" t="n">
         <v>408</v>
       </c>
-      <c r="G1418" t="inlineStr"/>
       <c r="H1418" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर LIC खरीदें PRICE 415.25 TARGET 425/435 STOP LOSS 408</t>
@@ -60227,14 +60118,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1419" t="inlineStr"/>
       <c r="E1419" t="n">
         <v>435</v>
       </c>
       <c r="F1419" t="n">
         <v>408</v>
       </c>
-      <c r="G1419" t="inlineStr"/>
       <c r="H1419" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर LIC खरीदें PRICE 415.25 TARGET 425/435 STOP LOSS 408</t>
@@ -60273,7 +60162,6 @@
       <c r="E1420" t="n">
         <v>4100.9</v>
       </c>
-      <c r="G1420" t="inlineStr"/>
       <c r="H1420" t="inlineStr">
         <is>
           <t>SUPER SID Sansera Engg 3997.60 101.30 BUY TARGET HIT</t>
@@ -60312,7 +60200,6 @@
       <c r="E1421" t="n">
         <v>535</v>
       </c>
-      <c r="G1421" t="inlineStr"/>
       <c r="H1421" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -60359,7 +60246,6 @@
       <c r="F1422" t="n">
         <v>4705</v>
       </c>
-      <c r="G1422" t="inlineStr"/>
       <c r="H1422" t="inlineStr">
         <is>
           <t>Data Patterns 4785.00 4.23% BUY TGT 4800 SL 4705</t>
@@ -60392,14 +60278,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1423" t="inlineStr"/>
       <c r="E1423" t="n">
         <v>4800</v>
       </c>
       <c r="F1423" t="n">
         <v>4705</v>
       </c>
-      <c r="G1423" t="inlineStr"/>
       <c r="H1423" t="inlineStr">
         <is>
           <t>Intellect Design 683.70 ▲ 0.23% HIGH 688.00 LOW 677.00 Vol: 34.54 k शुभ 'मंगला' शेयर Data Patterns 4784.00 BUY TGT 4800 SL 4705</t>
@@ -60441,7 +60325,6 @@
       <c r="F1424" t="n">
         <v>161</v>
       </c>
-      <c r="G1424" t="inlineStr"/>
       <c r="H1424" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय Bandhan Bank खरीदें PRICE 167.80 TARGET 175/184 STOP LOSS 161</t>
@@ -60483,7 +60366,6 @@
       <c r="F1425" t="n">
         <v>161</v>
       </c>
-      <c r="G1425" t="inlineStr"/>
       <c r="H1425" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय Bandhan Bank खरीदें PRICE 167.80 TARGET 175/184 STOP LOSS 161</t>
@@ -60565,7 +60447,6 @@
       <c r="E1427" t="n">
         <v>500</v>
       </c>
-      <c r="G1427" t="inlineStr"/>
       <c r="H1427" t="inlineStr">
         <is>
           <t>BEL खरीदें PRICE 409.20 TARGET 421/500 DURATION 6 महीने</t>
@@ -60604,7 +60485,6 @@
       <c r="E1428" t="n">
         <v>500</v>
       </c>
-      <c r="G1428" t="inlineStr"/>
       <c r="H1428" t="inlineStr">
         <is>
           <t>SUPER SID BEL खरीदें PRICE 409.10 TARGET 421/500 DURATION 6 महीने</t>
@@ -60680,11 +60560,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1430" t="inlineStr"/>
       <c r="E1430" t="n">
         <v>3998</v>
       </c>
-      <c r="G1430" t="inlineStr"/>
       <c r="H1430" t="inlineStr">
         <is>
           <t>SID Sansera Engg 4641.00 BUY 3998 TARGET HIT</t>
@@ -60717,11 +60595,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1431" t="inlineStr"/>
       <c r="E1431" t="n">
         <v>327.25</v>
       </c>
-      <c r="G1431" t="inlineStr"/>
       <c r="H1431" t="inlineStr">
         <is>
           <t>PCBL Chemical 327.25 INVESTMENT PICK 264.00 11/07/2024 RECO PRICE RETURN TILL NOW 63.25 23.96%</t>
@@ -60754,11 +60630,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1432" t="inlineStr"/>
       <c r="E1432" t="n">
         <v>4024.3</v>
       </c>
-      <c r="G1432" t="inlineStr"/>
       <c r="H1432" t="inlineStr">
         <is>
           <t>Sansera Engg 4024.30 INVESTMENT PICK 1727.00 24/12/2025 RECO PRICE RETURN TILL NOW 2297.30 133.02%</t>
@@ -60791,11 +60665,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1433" t="inlineStr"/>
       <c r="E1433" t="n">
         <v>4024.9</v>
       </c>
-      <c r="G1433" t="inlineStr"/>
       <c r="H1433" t="inlineStr">
         <is>
           <t>Sansera Engg 4024.90 INVESTMENT PICK 1727.00 24/12/2025 RECO PRICE RETURN TILL NOW 2297.90 133.06%</t>
@@ -60924,7 +60796,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1436" t="inlineStr"/>
       <c r="E1436" t="n">
         <v>535</v>
       </c>
@@ -61063,7 +60934,6 @@
       <c r="F1439" t="n">
         <v>999</v>
       </c>
-      <c r="G1439" t="inlineStr"/>
       <c r="H1439" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय Hindalco खरीदें PRICE 1017.40 TARGET 1040/1060 STOP LOSS 999</t>
@@ -61105,7 +60975,6 @@
       <c r="F1440" t="n">
         <v>999</v>
       </c>
-      <c r="G1440" t="inlineStr"/>
       <c r="H1440" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय Hindalco खरीदें PRICE 1017.40 TARGET 1040/1060 STOP LOSS 999</t>
@@ -61147,7 +61016,6 @@
       <c r="F1441" t="n">
         <v>4705</v>
       </c>
-      <c r="G1441" t="inlineStr"/>
       <c r="H1441" t="inlineStr">
         <is>
           <t>Data Patterns खरीदें PRICE 4745.30 TARGET 4800/4840 STOP LOSS 4705</t>
@@ -61229,7 +61097,6 @@
       <c r="E1443" t="n">
         <v>42000</v>
       </c>
-      <c r="G1443" t="inlineStr"/>
       <c r="H1443" t="inlineStr">
         <is>
           <t>सिटी
@@ -61315,7 +61182,6 @@
       <c r="E1445" t="n">
         <v>1280</v>
       </c>
-      <c r="G1445" t="inlineStr"/>
       <c r="H1445" t="inlineStr">
         <is>
           <t>Bharat Dynamics 1250.00 +8.30 HOLD लक्ष्य ₹1280</t>
@@ -61354,7 +61220,6 @@
       <c r="E1446" t="n">
         <v>1280</v>
       </c>
-      <c r="G1446" t="inlineStr"/>
       <c r="H1446" t="inlineStr">
         <is>
           <t>HDFC Life 539.00 5.80 1.09% Vol: 13.81 k PRE-OPEN BROKERAGE CALLS HOLD लक्ष्य ₹1280</t>
@@ -61396,7 +61261,6 @@
       <c r="F1447" t="n">
         <v>2425</v>
       </c>
-      <c r="G1447" t="inlineStr"/>
       <c r="H1447" t="inlineStr">
         <is>
           <t>MY CHOICE GLENMARK PHARMA B 2509 2425</t>
@@ -61435,7 +61299,6 @@
       <c r="E1448" t="n">
         <v>2509</v>
       </c>
-      <c r="G1448" t="inlineStr"/>
       <c r="H1448" t="inlineStr">
         <is>
           <t>MY CHOICE GLENMARK PHARMA B 2509</t>
@@ -61474,7 +61337,6 @@
       <c r="E1449" t="n">
         <v>3400</v>
       </c>
-      <c r="G1449" t="inlineStr"/>
       <c r="H1449" t="inlineStr">
         <is>
           <t>MY CHOICE MCX B 3400</t>
@@ -61513,7 +61375,6 @@
       <c r="F1450" t="n">
         <v>6</v>
       </c>
-      <c r="G1450" t="inlineStr"/>
       <c r="H1450" t="inlineStr">
         <is>
           <t>HDFC LIFE 540 CE B 16 6</t>
@@ -61552,7 +61413,6 @@
       <c r="E1451" t="n">
         <v>2588</v>
       </c>
-      <c r="G1451" t="inlineStr"/>
       <c r="H1451" t="inlineStr">
         <is>
           <t>PICK THE DAY Glenmark Pharma 2451.90 BUY TGT 2588</t>
@@ -61637,7 +61497,6 @@
       <c r="F1453" t="n">
         <v>1145</v>
       </c>
-      <c r="G1453" t="inlineStr"/>
       <c r="H1453" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय
@@ -61684,7 +61543,6 @@
       <c r="F1454" t="n">
         <v>1145</v>
       </c>
-      <c r="G1454" t="inlineStr"/>
       <c r="H1454" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय
@@ -61731,7 +61589,6 @@
       <c r="F1455" t="n">
         <v>12050</v>
       </c>
-      <c r="G1455" t="inlineStr"/>
       <c r="H1455" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Oracle Fin Fut SELL PRICE 11782.00 TARGET 11400/11000 STOP LOSS 12050</t>
@@ -61773,7 +61630,6 @@
       <c r="F1456" t="n">
         <v>12050</v>
       </c>
-      <c r="G1456" t="inlineStr"/>
       <c r="H1456" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Oracle Fin Fut SELL PRICE 11782.00 TARGET 11400/11000 STOP LOSS 12050</t>
@@ -61815,7 +61671,6 @@
       <c r="F1457" t="n">
         <v>2400</v>
       </c>
-      <c r="G1457" t="inlineStr"/>
       <c r="H1457" t="inlineStr">
         <is>
           <t>Glenmark Pharma BUY PRICE 2451.90 TARGET 2500/2530 STOP LOSS 2400</t>
@@ -61857,7 +61712,6 @@
       <c r="F1458" t="n">
         <v>2400</v>
       </c>
-      <c r="G1458" t="inlineStr"/>
       <c r="H1458" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Glenmark Pharma BUY PRICE 2451.90 TARGET 2500/2530 STOP LOSS 2400</t>
@@ -61896,7 +61750,6 @@
       <c r="E1459" t="n">
         <v>1220</v>
       </c>
-      <c r="G1459" t="inlineStr"/>
       <c r="H1459" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -61940,7 +61793,6 @@
       <c r="E1460" t="n">
         <v>1250</v>
       </c>
-      <c r="G1460" t="inlineStr"/>
       <c r="H1460" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -61987,7 +61839,6 @@
       <c r="F1461" t="n">
         <v>1105</v>
       </c>
-      <c r="G1461" t="inlineStr"/>
       <c r="H1461" t="inlineStr">
         <is>
           <t>विश्वेश चौहान की राय
@@ -62034,7 +61885,6 @@
       <c r="F1462" t="n">
         <v>3140</v>
       </c>
-      <c r="G1462" t="inlineStr"/>
       <c r="H1462" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Cartrade Tech BUY PRICE 3179.90 TARGET 3250/3280 STOP LOSS 3140</t>
@@ -62076,7 +61926,6 @@
       <c r="F1463" t="n">
         <v>3140</v>
       </c>
-      <c r="G1463" t="inlineStr"/>
       <c r="H1463" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Cartrade Tech BUY PRICE 3179.90 TARGET 3250/3280 STOP LOSS 3140</t>
@@ -62118,7 +61967,6 @@
       <c r="F1464" t="n">
         <v>930</v>
       </c>
-      <c r="G1464" t="inlineStr"/>
       <c r="H1464" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Jubilant Pharmova BUY PRICE 950.30 TARGET 990/1020 STOP LOSS 930</t>
@@ -62160,7 +62008,6 @@
       <c r="F1465" t="n">
         <v>930</v>
       </c>
-      <c r="G1465" t="inlineStr"/>
       <c r="H1465" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Jubilant Pharmova BUY PRICE 950.30 TARGET 990/1020 STOP LOSS 930</t>
@@ -62202,7 +62049,6 @@
       <c r="F1466" t="n">
         <v>980</v>
       </c>
-      <c r="G1466" t="inlineStr"/>
       <c r="H1466" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -62249,7 +62095,6 @@
       <c r="F1467" t="n">
         <v>980</v>
       </c>
-      <c r="G1467" t="inlineStr"/>
       <c r="H1467" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -62296,7 +62141,6 @@
       <c r="F1468" t="n">
         <v>980</v>
       </c>
-      <c r="G1468" t="inlineStr"/>
       <c r="H1468" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -62343,7 +62187,6 @@
       <c r="F1469" t="n">
         <v>3298</v>
       </c>
-      <c r="G1469" t="inlineStr"/>
       <c r="H1469" t="inlineStr">
         <is>
           <t>MY CHOICE MCX B 3400 3298</t>
@@ -62385,7 +62228,6 @@
       <c r="F1470" t="n">
         <v>1951</v>
       </c>
-      <c r="G1470" t="inlineStr"/>
       <c r="H1470" t="inlineStr">
         <is>
           <t>CASH COROMANDEL INT B 2023 1951</t>
@@ -62424,7 +62266,6 @@
       <c r="E1471" t="n">
         <v>1910</v>
       </c>
-      <c r="G1471" t="inlineStr"/>
       <c r="H1471" t="inlineStr">
         <is>
           <t>INVESTMENT ASHOK LEYLAND B 1910 12M</t>
@@ -62463,7 +62304,6 @@
       <c r="E1472" t="n">
         <v>5100</v>
       </c>
-      <c r="G1472" t="inlineStr"/>
       <c r="H1472" t="inlineStr">
         <is>
           <t>FUNDA HAL B 5100 6 MONTH</t>
@@ -62505,7 +62345,6 @@
       <c r="F1473" t="n">
         <v>160</v>
       </c>
-      <c r="G1473" t="inlineStr"/>
       <c r="H1473" t="inlineStr">
         <is>
           <t>MY CHOICE Samvardhana Motherson खरीदें PRICE 162.00 TARGET 166 STOP LOSS 160</t>
@@ -62547,7 +62386,6 @@
       <c r="F1474" t="n">
         <v>2425</v>
       </c>
-      <c r="G1474" t="inlineStr"/>
       <c r="H1474" t="inlineStr">
         <is>
           <t>MY CHOICE Glenmark Pharma खरीदें PRICE 2451.90 TARGET 2509 STOP LOSS 2425</t>
@@ -62589,7 +62427,6 @@
       <c r="F1475" t="n">
         <v>400</v>
       </c>
-      <c r="G1475" t="inlineStr"/>
       <c r="H1475" t="inlineStr">
         <is>
           <t>MY CHOICE BEL खरीदें PRICE 404.00 TARGET 415 STOP LOSS 400</t>
@@ -62628,7 +62465,6 @@
       <c r="E1476" t="n">
         <v>415</v>
       </c>
-      <c r="G1476" t="inlineStr"/>
       <c r="H1476" t="inlineStr">
         <is>
           <t>MY CHOICE BEL PRICE 404.00 TARGET 415</t>
@@ -62667,7 +62503,6 @@
       <c r="E1477" t="n">
         <v>190</v>
       </c>
-      <c r="G1477" t="inlineStr"/>
       <c r="H1477" t="inlineStr">
         <is>
           <t>Ashok Leyland खरीदें PRICE 170.00 TARGET 190 DURATION 12 महीने</t>
@@ -62709,7 +62544,6 @@
       <c r="F1478" t="n">
         <v>22100</v>
       </c>
-      <c r="G1478" t="inlineStr"/>
       <c r="H1478" t="inlineStr">
         <is>
           <t>Shree Cement खरीदें PRICE 23365.00 TARGET 26000 STOP LOSS 22100</t>
@@ -62751,7 +62585,6 @@
       <c r="F1479" t="n">
         <v>1041</v>
       </c>
-      <c r="G1479" t="inlineStr"/>
       <c r="H1479" t="inlineStr">
         <is>
           <t>TECHNO PICK
@@ -62798,7 +62631,6 @@
       <c r="F1480" t="n">
         <v>6</v>
       </c>
-      <c r="G1480" t="inlineStr"/>
       <c r="H1480" t="inlineStr">
         <is>
           <t>BEST ऑप्शन HDFC Life 540 की कॉल खरीदें STOP LOSS 6 TARGET 16 HDFC Life 533.20 13.20</t>
@@ -62840,7 +62672,6 @@
       <c r="F1481" t="n">
         <v>1951</v>
       </c>
-      <c r="G1481" t="inlineStr"/>
       <c r="H1481" t="inlineStr">
         <is>
           <t>CASH का शेयर Coromandel Intl खरीदें PRICE 1974.60 TARGET 2023 STOP LOSS 1951</t>
@@ -62879,7 +62710,6 @@
       <c r="E1482" t="n">
         <v>478.3</v>
       </c>
-      <c r="G1482" t="inlineStr"/>
       <c r="H1482" t="inlineStr">
         <is>
           <t>पूजा के शेयर
@@ -62966,7 +62796,6 @@
       <c r="F1484" t="n">
         <v>181</v>
       </c>
-      <c r="G1484" t="inlineStr"/>
       <c r="H1484" t="inlineStr">
         <is>
           <t>अर्पित बेरीवाल की राय
@@ -63013,7 +62842,6 @@
       <c r="F1485" t="n">
         <v>9000</v>
       </c>
-      <c r="G1485" t="inlineStr"/>
       <c r="H1485" t="inlineStr">
         <is>
           <t>अर्पित बेरीवाल की राय
@@ -63057,7 +62885,6 @@
       <c r="E1486" t="n">
         <v>250</v>
       </c>
-      <c r="G1486" t="inlineStr"/>
       <c r="H1486" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -63100,7 +62927,6 @@
       <c r="E1487" t="n">
         <v>4954</v>
       </c>
-      <c r="G1487" t="inlineStr"/>
       <c r="H1487" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -63189,7 +63015,6 @@
       <c r="F1489" t="n">
         <v>8475</v>
       </c>
-      <c r="G1489" t="inlineStr"/>
       <c r="H1489" t="inlineStr">
         <is>
           <t>INTRADAY CALL Navin Fluorine BUY TARGET 8850 STOP LOSS 8475 Navin Fluorine 8603.50 0.54%</t>
@@ -63231,7 +63056,6 @@
       <c r="F1490" t="n">
         <v>360</v>
       </c>
-      <c r="G1490" t="inlineStr"/>
       <c r="H1490" t="inlineStr">
         <is>
           <t>POSITIONAL CALL M&amp;M Fin BUY TARGET 396 STOP LOSS 360 M&amp;M Fin 372.35 0.35%</t>
@@ -63248,8 +63072,3066 @@
         </is>
       </c>
     </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:22:42</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>RPSGVENT</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr"/>
+      <c r="E1491" t="n">
+        <v>950</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>810</v>
+      </c>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H1491" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय RPSG Ventures @ 857 खरीदें STOP LOSS 810 TARGET 950 DURATION 4-8 महीने RPSG Ventures 873.45 6.64%</t>
+        </is>
+      </c>
+      <c r="I1491" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1491" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:15:00</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>ASAHIINDIA</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1492" t="n">
+        <v>953.5</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>1125</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>870</v>
+      </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H1492" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय
+Asahi India Glass @950
+खरीदें
+STOP LOSS 870 | TARGET 1125 | DURATION 9-12 महीने
+Asahi India Glass 956.85 ▲ 0.13%</t>
+        </is>
+      </c>
+      <c r="I1492" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1492" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:03:00</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>GMDCLTD</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1493" t="n">
+        <v>579</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>640</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>550</v>
+      </c>
+      <c r="G1493" t="inlineStr"/>
+      <c r="H1493" t="inlineStr">
+        <is>
+          <t>Super KOOL MEHUL GMDC 579.00 10.15 BUY TGT 640 SL 550</t>
+        </is>
+      </c>
+      <c r="I1493" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1493" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:03:00</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1494" t="n">
+        <v>433.45</v>
+      </c>
+      <c r="E1494" t="n">
+        <v>445</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>416</v>
+      </c>
+      <c r="G1494" t="inlineStr"/>
+      <c r="H1494" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट Coal India 433.30 13.05 BUY TGT 445 SL 416</t>
+        </is>
+      </c>
+      <c r="I1494" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1494" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:03:00</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1495" t="n">
+        <v>433.45</v>
+      </c>
+      <c r="E1495" t="n">
+        <v>445</v>
+      </c>
+      <c r="G1495" t="inlineStr"/>
+      <c r="H1495" t="inlineStr">
+        <is>
+          <t>Coal India 433.05 12.80 BUY TGT 445</t>
+        </is>
+      </c>
+      <c r="I1495" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1495" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:03:00</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1496" t="n">
+        <v>1034.5</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>1055</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>999</v>
+      </c>
+      <c r="G1496" t="inlineStr"/>
+      <c r="H1496" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Max Healthcare 1030.30 3.76% BUY TGT 1055 SL 999</t>
+        </is>
+      </c>
+      <c r="I1496" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1496" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:03:00</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1497" t="n">
+        <v>538.1</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>560</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>515</v>
+      </c>
+      <c r="G1497" t="inlineStr">
+        <is>
+          <t>Mehul</t>
+        </is>
+      </c>
+      <c r="H1497" t="inlineStr">
+        <is>
+          <t>Super KOOL MEHUL JSW Energy 538.20 11.80 BUY TGT 560 SL 515</t>
+        </is>
+      </c>
+      <c r="I1497" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1497" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:51:00</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1498" t="n">
+        <v>318.9</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1498" t="inlineStr"/>
+      <c r="H1498" t="inlineStr">
+        <is>
+          <t>SID Eternal (Zomato) CMP 318.90 TARGET 400 25% ALLOCATION</t>
+        </is>
+      </c>
+      <c r="I1498" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1498" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:50:00</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>MEESHO</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1499" t="n">
+        <v>213.49</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>230</v>
+      </c>
+      <c r="G1499" t="inlineStr"/>
+      <c r="H1499" t="inlineStr">
+        <is>
+          <t>'Gift Hamper' थीम Meesho CMP 213.50 TARGET 230 25% ALLOCATION</t>
+        </is>
+      </c>
+      <c r="I1499" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1499" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:37:03</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>SAMBHV</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr"/>
+      <c r="E1500" t="n">
+        <v>150</v>
+      </c>
+      <c r="G1500" t="inlineStr"/>
+      <c r="H1500" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS Sambhv Steel @ 130 खरीदें STOP LOSS -- TARGET 150 Sambhv Steel 131.55 ▲ 2.10%</t>
+        </is>
+      </c>
+      <c r="I1500" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1500" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:24:43</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>EIEL</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr"/>
+      <c r="E1501" t="n">
+        <v>192</v>
+      </c>
+      <c r="G1501" t="inlineStr"/>
+      <c r="H1501" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Enviro Infra 213.26 8.70% BUY TARGET HIT 192</t>
+        </is>
+      </c>
+      <c r="I1501" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1501" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:21:39</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr"/>
+      <c r="E1502" t="n">
+        <v>705</v>
+      </c>
+      <c r="G1502" t="inlineStr"/>
+      <c r="H1502" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Graphite India 806.90 72.65 BUY TARGET HIT 705</t>
+        </is>
+      </c>
+      <c r="I1502" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1502" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:22:00</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>BIOCON</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1503" t="n">
+        <v>402.7</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>807.05</v>
+      </c>
+      <c r="G1503" t="inlineStr"/>
+      <c r="H1503" t="inlineStr">
+        <is>
+          <t>Biocon 401.65 9.35 2.38% Vol: 2.3 m ▲ PICK OF THE DAY 807.05 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="I1503" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1503" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:21:35</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr"/>
+      <c r="E1504" t="n">
+        <v>760</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>705</v>
+      </c>
+      <c r="G1504" t="inlineStr"/>
+      <c r="H1504" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Graphite India 806.60 72.35 BUY TGT 760 SL 705</t>
+        </is>
+      </c>
+      <c r="I1504" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1504" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:21:29</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>HEG-BE</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr"/>
+      <c r="E1505" t="n">
+        <v>252</v>
+      </c>
+      <c r="G1505" t="inlineStr"/>
+      <c r="H1505" t="inlineStr">
+        <is>
+          <t>मेहुल कोटारी HEG Ltd 263.95 2.07% BUY TARGET HIT 252</t>
+        </is>
+      </c>
+      <c r="I1505" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1505" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:22:00</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>HEG-BE</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1506" t="n">
+        <v>264.95</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>265</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>252</v>
+      </c>
+      <c r="G1506" t="inlineStr"/>
+      <c r="H1506" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+HEG Ltd
+263.95 5.35
+BUY
+TGT 265
+SL 252</t>
+        </is>
+      </c>
+      <c r="I1506" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1506" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:22:00</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>JSWENERGY</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1507" t="n">
+        <v>533.6</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>560</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>515</v>
+      </c>
+      <c r="G1507" t="inlineStr"/>
+      <c r="H1507" t="inlineStr">
+        <is>
+          <t>Super Kool Menu
+JSW Energy
+खरीदें
+PRICE 532.75
+TARGET 560
+STOP LOSS 515</t>
+        </is>
+      </c>
+      <c r="I1507" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1507" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>BSE29SEP26</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1508" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E1508" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>3460</v>
+      </c>
+      <c r="G1508" t="inlineStr"/>
+      <c r="H1508" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+BSE Fut
+SELL
+PRICE ▶ 3403.20
+TARGET ▶ 3370, 3340, 3300
+STOP LOSS ▶ 3460</t>
+        </is>
+      </c>
+      <c r="I1508" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1508" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1509" t="n">
+        <v>237.8</v>
+      </c>
+      <c r="E1509" t="n">
+        <v>242</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>230</v>
+      </c>
+      <c r="G1509" t="inlineStr"/>
+      <c r="H1509" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY ONGC 236.00 2.30 BUY TGT 242 SL 230</t>
+        </is>
+      </c>
+      <c r="I1509" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1509" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>BPCL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1510" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="E1510" t="n">
+        <v>287</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>310</v>
+      </c>
+      <c r="G1510" t="inlineStr"/>
+      <c r="H1510" t="inlineStr">
+        <is>
+          <t>BPCL Fut SELL PRICE 303.60 TARGET 295/287 STOP LOSS 310</t>
+        </is>
+      </c>
+      <c r="I1510" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1510" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>BPCL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1511" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="E1511" t="n">
+        <v>295</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>310</v>
+      </c>
+      <c r="G1511" t="inlineStr"/>
+      <c r="H1511" t="inlineStr">
+        <is>
+          <t>BPCL Fut SELL PRICE 303.60 TARGET 295/287 STOP LOSS 310</t>
+        </is>
+      </c>
+      <c r="I1511" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1511" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>AXISCADES</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1512" t="n">
+        <v>1859</v>
+      </c>
+      <c r="E1512" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>1779</v>
+      </c>
+      <c r="G1512" t="inlineStr"/>
+      <c r="H1512" t="inlineStr">
+        <is>
+          <t>Axiscades BUY PRICE 1848.60 TARGET 2000 STOP LOSS 1779</t>
+        </is>
+      </c>
+      <c r="I1512" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1512" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1513" t="n">
+        <v>539.4</v>
+      </c>
+      <c r="E1513" t="n">
+        <v>585</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>510</v>
+      </c>
+      <c r="G1513" t="inlineStr"/>
+      <c r="H1513" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+Hind Copper
+BUY
+PRICE 532.85
+TARGET 570/585
+STOP LOSS 510</t>
+        </is>
+      </c>
+      <c r="I1513" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1513" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1514" t="n">
+        <v>539.35</v>
+      </c>
+      <c r="E1514" t="n">
+        <v>570</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>510</v>
+      </c>
+      <c r="G1514" t="inlineStr"/>
+      <c r="H1514" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+Hind Copper
+BUY
+PRICE 532.85
+TARGET 570/585
+STOP LOSS 510</t>
+        </is>
+      </c>
+      <c r="I1514" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1514" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>RAYMONDLSL</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1515" t="n">
+        <v>720</v>
+      </c>
+      <c r="E1515" t="n">
+        <v>725</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>690</v>
+      </c>
+      <c r="G1515" t="inlineStr"/>
+      <c r="H1515" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Raymond Lifestyle BUY PRICE 697 TARGET 705, 715, 725 STOP LOSS 690</t>
+        </is>
+      </c>
+      <c r="I1515" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1515" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1516" t="n">
+        <v>213.43</v>
+      </c>
+      <c r="E1516" t="n">
+        <v>215</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>204</v>
+      </c>
+      <c r="G1516" t="inlineStr"/>
+      <c r="H1516" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Welspun Living
+BUY
+PRICE 208
+TARGET 210, 212, 215
+STOP LOSS 204</t>
+        </is>
+      </c>
+      <c r="I1516" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1516" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>FINCABLES</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1517" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E1517" t="n">
+        <v>1418</v>
+      </c>
+      <c r="G1517" t="inlineStr"/>
+      <c r="H1517" t="inlineStr">
+        <is>
+          <t>CALLS Finolex Cables 1302 BUY लक्ष्य ₹1418</t>
+        </is>
+      </c>
+      <c r="I1517" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1517" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:08</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>JKLAKSHMI</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1518" t="n">
+        <v>499.55</v>
+      </c>
+      <c r="E1518" t="n">
+        <v>1410</v>
+      </c>
+      <c r="G1518" t="inlineStr"/>
+      <c r="H1518" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS BUY लक्ष्मी ₹1410</t>
+        </is>
+      </c>
+      <c r="I1518" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1518" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:03</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1519" t="n">
+        <v>3299.9</v>
+      </c>
+      <c r="E1519" t="n">
+        <v>2820</v>
+      </c>
+      <c r="G1519" t="inlineStr"/>
+      <c r="H1519" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+BSE Ltd.
+3394.00 -52.20
+UNDER PERFORM
+लक्ष्य ₹2820</t>
+        </is>
+      </c>
+      <c r="I1519" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1519" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1520" t="n">
+        <v>213.43</v>
+      </c>
+      <c r="E1520" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1520" t="inlineStr">
+        <is>
+          <t>जेफरीज Welspun Living 207.87 -4.08 BUY लक्ष्य ₹260</t>
+        </is>
+      </c>
+      <c r="I1520" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1520" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>RAYMONDLSL</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1521" t="n">
+        <v>720</v>
+      </c>
+      <c r="E1521" t="n">
+        <v>900</v>
+      </c>
+      <c r="G1521" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1521" t="inlineStr">
+        <is>
+          <t>जेफरीज Raymond Lifestyle 696.85 +23.95 BUY लक्ष्य ₹900</t>
+        </is>
+      </c>
+      <c r="I1521" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1521" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>BPCL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1522" t="n">
+        <v>301.95</v>
+      </c>
+      <c r="E1522" t="n">
+        <v>295</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>307</v>
+      </c>
+      <c r="G1522" t="inlineStr"/>
+      <c r="H1522" t="inlineStr">
+        <is>
+          <t>MY CHOICE BPCL FUT S 295 307</t>
+        </is>
+      </c>
+      <c r="I1522" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1522" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>ASIANPAINT29SEP26</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1523" t="n">
+        <v>2470</v>
+      </c>
+      <c r="E1523" t="n">
+        <v>2430</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>2505</v>
+      </c>
+      <c r="G1523" t="inlineStr"/>
+      <c r="H1523" t="inlineStr">
+        <is>
+          <t>MY CHOICE ASIAN PAINTS FUT S 2430 2505</t>
+        </is>
+      </c>
+      <c r="I1523" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1523" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>HINDPETRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1524" t="n">
+        <v>347</v>
+      </c>
+      <c r="E1524" t="n">
+        <v>339</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1524" t="inlineStr"/>
+      <c r="H1524" t="inlineStr">
+        <is>
+          <t>MY CHOICE HPCL FUT S 339 350</t>
+        </is>
+      </c>
+      <c r="I1524" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1524" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1525" t="n">
+        <v>213.43</v>
+      </c>
+      <c r="E1525" t="n">
+        <v>230</v>
+      </c>
+      <c r="G1525" t="inlineStr"/>
+      <c r="H1525" t="inlineStr">
+        <is>
+          <t>INVESTMENT WELSPUN LIVING B 230 12 MONTH</t>
+        </is>
+      </c>
+      <c r="I1525" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1525" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>FINCABLES</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1526" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E1526" t="n">
+        <v>1328</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>1289</v>
+      </c>
+      <c r="G1526" t="inlineStr"/>
+      <c r="H1526" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT FINOLEX CABLES B 1328 1289</t>
+        </is>
+      </c>
+      <c r="I1526" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1526" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1527" t="n">
+        <v>538</v>
+      </c>
+      <c r="E1527" t="n">
+        <v>545</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>527</v>
+      </c>
+      <c r="G1527" t="inlineStr"/>
+      <c r="H1527" t="inlineStr">
+        <is>
+          <t>CASH HINDUSTAN COPPER B 545 527</t>
+        </is>
+      </c>
+      <c r="I1527" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1527" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1528" t="n">
+        <v>2105</v>
+      </c>
+      <c r="E1528" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G1528" t="inlineStr"/>
+      <c r="H1528" t="inlineStr">
+        <is>
+          <t>FUNDA BEML B 2200 6 MONTHS</t>
+        </is>
+      </c>
+      <c r="I1528" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1528" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>NATIONALUM29SEP26</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1529" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="E1529" t="n">
+        <v>380</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>367</v>
+      </c>
+      <c r="G1529" t="inlineStr"/>
+      <c r="H1529" t="inlineStr">
+        <is>
+          <t>FUTURE NALCO FUT B 380 367</t>
+        </is>
+      </c>
+      <c r="I1529" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1529" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>HDFCBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1530" t="n">
+        <v>702.9</v>
+      </c>
+      <c r="E1530" t="n">
+        <v>694</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>715</v>
+      </c>
+      <c r="G1530" t="inlineStr"/>
+      <c r="H1530" t="inlineStr">
+        <is>
+          <t>TECHNO HDFC BANK FUT S 694 715</t>
+        </is>
+      </c>
+      <c r="I1530" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1530" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1531" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="E1531" t="n">
+        <v>282</v>
+      </c>
+      <c r="F1531" t="n">
+        <v>268</v>
+      </c>
+      <c r="G1531" t="inlineStr"/>
+      <c r="H1531" t="inlineStr">
+        <is>
+          <t>CASH NLC INDIA B 282 268</t>
+        </is>
+      </c>
+      <c r="I1531" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1531" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>HAL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1532" t="n">
+        <v>5063.8</v>
+      </c>
+      <c r="E1532" t="n">
+        <v>5180</v>
+      </c>
+      <c r="F1532" t="n">
+        <v>4981</v>
+      </c>
+      <c r="G1532" t="inlineStr"/>
+      <c r="H1532" t="inlineStr">
+        <is>
+          <t>FUTURE HAL FUT B 5180 4981</t>
+        </is>
+      </c>
+      <c r="I1532" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1532" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>BPCL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1533" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="E1533" t="n">
+        <v>295</v>
+      </c>
+      <c r="F1533" t="n">
+        <v>307</v>
+      </c>
+      <c r="G1533" t="inlineStr"/>
+      <c r="H1533" t="inlineStr">
+        <is>
+          <t>MY CHOICE BPCL Fut बेचें PRICE 303.60 TARGET 295 STOP LOSS 307</t>
+        </is>
+      </c>
+      <c r="I1533" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1533" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>ASIANPAINT29SEP26</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1534" t="n">
+        <v>2470</v>
+      </c>
+      <c r="E1534" t="n">
+        <v>2430</v>
+      </c>
+      <c r="F1534" t="n">
+        <v>2505</v>
+      </c>
+      <c r="G1534" t="inlineStr"/>
+      <c r="H1534" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर
+Asian Paints Fut
+बेचें
+PRICE 2499.50
+TARGET 2430
+STOP LOSS 2505</t>
+        </is>
+      </c>
+      <c r="I1534" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1534" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1535" t="n">
+        <v>237.8</v>
+      </c>
+      <c r="E1535" t="n">
+        <v>241</v>
+      </c>
+      <c r="F1535" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="G1535" t="inlineStr"/>
+      <c r="H1535" t="inlineStr">
+        <is>
+          <t>MY CHOICE ONGC खरीदें PRICE 236.00 TARGET 241 STOP LOSS 233.5</t>
+        </is>
+      </c>
+      <c r="I1535" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1535" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1536" t="n">
+        <v>237.8</v>
+      </c>
+      <c r="E1536" t="n">
+        <v>241</v>
+      </c>
+      <c r="G1536" t="inlineStr"/>
+      <c r="H1536" t="inlineStr">
+        <is>
+          <t>MY CHOICE ONGC PRICE 236.00 TARGET 241</t>
+        </is>
+      </c>
+      <c r="I1536" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1536" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1537" t="n">
+        <v>498</v>
+      </c>
+      <c r="E1537" t="n">
+        <v>506.5</v>
+      </c>
+      <c r="F1537" t="n">
+        <v>488</v>
+      </c>
+      <c r="G1537" t="inlineStr"/>
+      <c r="H1537" t="inlineStr">
+        <is>
+          <t>नेहा के शेयर
+Oil India
+खरीदें
+PRICE ▶ 495.40
+TARGET ▶ 506.5
+STOP LOSS ▶ 488</t>
+        </is>
+      </c>
+      <c r="I1537" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1537" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>EIEL</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1538" t="n">
+        <v>205.39</v>
+      </c>
+      <c r="E1538" t="n">
+        <v>206</v>
+      </c>
+      <c r="F1538" t="n">
+        <v>191</v>
+      </c>
+      <c r="G1538" t="inlineStr"/>
+      <c r="H1538" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+Enviro Infra
+खरीदें
+PRICE ▶ 196.20
+TARGET ▶ 206
+STOP LOSS ▶ 191</t>
+        </is>
+      </c>
+      <c r="I1538" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1538" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>FINCABLES</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1539" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E1539" t="n">
+        <v>1328</v>
+      </c>
+      <c r="F1539" t="n">
+        <v>1289</v>
+      </c>
+      <c r="G1539" t="inlineStr"/>
+      <c r="H1539" t="inlineStr">
+        <is>
+          <t>खबर के दम पर Finolex Cables खरीदें PRICE 1302.30 TARGET 1328 STOP LOSS 1289 STOCK OF THE DAY 8:25 AM 9AM</t>
+        </is>
+      </c>
+      <c r="I1539" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1539" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1540" t="n">
+        <v>213.43</v>
+      </c>
+      <c r="E1540" t="n">
+        <v>230</v>
+      </c>
+      <c r="G1540" t="inlineStr"/>
+      <c r="H1540" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर Welspun Living खरीदें PRICE 207.87 TARGET 230 DURATION 12 महीने</t>
+        </is>
+      </c>
+      <c r="I1540" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1540" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:07</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>GNA</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1541" t="n">
+        <v>556</v>
+      </c>
+      <c r="E1541" t="n">
+        <v>700</v>
+      </c>
+      <c r="F1541" t="n">
+        <v>490</v>
+      </c>
+      <c r="G1541" t="inlineStr"/>
+      <c r="H1541" t="inlineStr">
+        <is>
+          <t>नेहा के शेयर
+GNA Axles
+खरीदें
+PRICE ▶ 553.40
+TARGET ▶ 700
+STOP LOSS ▶ 490</t>
+        </is>
+      </c>
+      <c r="I1541" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1541" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1542" t="n">
+        <v>1013.9</v>
+      </c>
+      <c r="E1542" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F1542" t="n">
+        <v>990</v>
+      </c>
+      <c r="G1542" t="inlineStr"/>
+      <c r="H1542" t="inlineStr">
+        <is>
+          <t>नेहा के शेयर Hindalco खरीदें PRICE 1009.00 TARGET 1025 STOP LOSS 990</t>
+        </is>
+      </c>
+      <c r="I1542" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1542" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>BEML</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1543" t="n">
+        <v>2105.8</v>
+      </c>
+      <c r="E1543" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G1543" t="inlineStr"/>
+      <c r="H1543" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर
+BEML
+खरीदें
+PRICE ▶ 2105.60
+TARGET ▶ 2200
+DURATION ▶ 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1543" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1543" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>INDIGO500029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1544" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="E1544" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1544" t="n">
+        <v>60</v>
+      </c>
+      <c r="G1544" t="inlineStr"/>
+      <c r="H1544" t="inlineStr">
+        <is>
+          <t>BEST ऑप्शन Interglobe Aviation 5000 की पुट @119.35 खरीदें STOP LOSS 60 TARGET 250</t>
+        </is>
+      </c>
+      <c r="I1544" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1544" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>HDFCBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1545" t="n">
+        <v>702.9</v>
+      </c>
+      <c r="E1545" t="n">
+        <v>694</v>
+      </c>
+      <c r="F1545" t="n">
+        <v>715</v>
+      </c>
+      <c r="G1545" t="inlineStr"/>
+      <c r="H1545" t="inlineStr">
+        <is>
+          <t>TECHNO PICK
+HDFC Bank Fut
+बेचें
+PRICE ▶ 708.80
+TARGET ▶ 694
+STOP LOSS ▶ 715</t>
+        </is>
+      </c>
+      <c r="I1545" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1545" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1546" t="n">
+        <v>595</v>
+      </c>
+      <c r="E1546" t="n">
+        <v>621</v>
+      </c>
+      <c r="F1546" t="n">
+        <v>580</v>
+      </c>
+      <c r="G1546" t="inlineStr"/>
+      <c r="H1546" t="inlineStr">
+        <is>
+          <t>TECHNO PICK
+Hindustan Zinc
+खरीदें
+PRICE ▶ 595.50
+TARGET ▶ 621
+STOP LOSS ▶ 580</t>
+        </is>
+      </c>
+      <c r="I1546" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1546" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>AXISBANK124029SEP26PE</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1547" t="n">
+        <v>18</v>
+      </c>
+      <c r="E1547" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1547" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1547" t="inlineStr"/>
+      <c r="H1547" t="inlineStr">
+        <is>
+          <t>नेहा के शेयर Axis Bank 1240 की पुट @ 24.8 खरीदें STOP LOSS 12 TARGET 50 Axis Bank 1244.90 1.67%</t>
+        </is>
+      </c>
+      <c r="I1547" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1547" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>AXISBANK124029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1548" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E1548" t="n">
+        <v>50</v>
+      </c>
+      <c r="F1548" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1548" t="inlineStr"/>
+      <c r="H1548" t="inlineStr">
+        <is>
+          <t>Axis Bank 1240 की पुट @ 24.8 खरीदें STOP LOSS 12 TARGET 50 Axis Bank 1244.90 1.67%</t>
+        </is>
+      </c>
+      <c r="I1548" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1548" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>NATIONALUM29SEP26</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1549" t="n">
+        <v>373.05</v>
+      </c>
+      <c r="E1549" t="n">
+        <v>380</v>
+      </c>
+      <c r="F1549" t="n">
+        <v>367</v>
+      </c>
+      <c r="G1549" t="inlineStr"/>
+      <c r="H1549" t="inlineStr">
+        <is>
+          <t>आज का FUTURE
+NALCO Fut
+खरीदें
+PRICE → 370.35
+TARGET → 380
+STOP LOSS → 367</t>
+        </is>
+      </c>
+      <c r="I1549" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1549" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>HAL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1550" t="n">
+        <v>5063.8</v>
+      </c>
+      <c r="E1550" t="n">
+        <v>5180</v>
+      </c>
+      <c r="F1550" t="n">
+        <v>4981</v>
+      </c>
+      <c r="G1550" t="inlineStr"/>
+      <c r="H1550" t="inlineStr">
+        <is>
+          <t>नेहा के शेयर
+HAL Fut
+खरीदें
+PRICE ▸ 5063.80
+TARGET ▸ 5180
+STOP LOSS ▸ 4981</t>
+        </is>
+      </c>
+      <c r="I1550" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1550" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:03</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1551" t="n">
+        <v>274.7</v>
+      </c>
+      <c r="E1551" t="n">
+        <v>282</v>
+      </c>
+      <c r="F1551" t="n">
+        <v>268</v>
+      </c>
+      <c r="G1551" t="inlineStr"/>
+      <c r="H1551" t="inlineStr">
+        <is>
+          <t>CASH का शेयर
+NLC India
+खरीदें
+PRICE ▶ 272.25
+TARGET ▶ 282
+STOP LOSS ▶ 268</t>
+        </is>
+      </c>
+      <c r="I1551" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1551" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:03</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>NLCINDIA</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1552" t="n">
+        <v>274.7</v>
+      </c>
+      <c r="E1552" t="n">
+        <v>282</v>
+      </c>
+      <c r="G1552" t="inlineStr"/>
+      <c r="H1552" t="inlineStr">
+        <is>
+          <t>CASH का शेयर
+NLC India
+PRICE 272.25
+TARGET 282</t>
+        </is>
+      </c>
+      <c r="I1552" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1552" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1553" t="n">
+        <v>539.35</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>545</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>527</v>
+      </c>
+      <c r="G1553" t="inlineStr"/>
+      <c r="H1553" t="inlineStr">
+        <is>
+          <t>CASH का शेयर Hind Copper खरीदें PRICE 532.85 TARGET 545 STOP LOSS 527</t>
+        </is>
+      </c>
+      <c r="I1553" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1553" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1554" t="n">
+        <v>214.22</v>
+      </c>
+      <c r="E1554" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1554" t="inlineStr"/>
+      <c r="H1554" t="inlineStr">
+        <is>
+          <t>Welspun Living BUY 260</t>
+        </is>
+      </c>
+      <c r="I1554" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1554" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>RAYMONDLSL</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1555" t="n">
+        <v>720</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>900</v>
+      </c>
+      <c r="G1555" t="inlineStr"/>
+      <c r="H1555" t="inlineStr">
+        <is>
+          <t>Raymond Lifestyle BUY 900</t>
+        </is>
+      </c>
+      <c r="I1555" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1555" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1556" t="n">
+        <v>560</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>595</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>548</v>
+      </c>
+      <c r="G1556" t="inlineStr"/>
+      <c r="H1556" t="inlineStr">
+        <is>
+          <t>TRADING CALL LIC Hsg Fin खरीदें PRICE 563.00 TARGET 585/595 STOP LOSS 548</t>
+        </is>
+      </c>
+      <c r="I1556" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1556" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1557" t="n">
+        <v>560</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>585</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>548</v>
+      </c>
+      <c r="G1557" t="inlineStr"/>
+      <c r="H1557" t="inlineStr">
+        <is>
+          <t>TRADING CALL LIC Hsg Fin खरीदें PRICE 563.00 TARGET 585/595 STOP LOSS 548</t>
+        </is>
+      </c>
+      <c r="I1557" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1557" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1558" t="n">
+        <v>411.75</v>
+      </c>
+      <c r="E1558" t="n">
+        <v>430</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>404</v>
+      </c>
+      <c r="G1558" t="inlineStr"/>
+      <c r="H1558" t="inlineStr">
+        <is>
+          <t>TRADING CALL BEL खरीदें PRICE 410.55 TARGET 425/430 STOP LOSS 404</t>
+        </is>
+      </c>
+      <c r="I1558" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1558" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1559" t="n">
+        <v>412</v>
+      </c>
+      <c r="E1559" t="n">
+        <v>425</v>
+      </c>
+      <c r="F1559" t="n">
+        <v>404</v>
+      </c>
+      <c r="G1559" t="inlineStr"/>
+      <c r="H1559" t="inlineStr">
+        <is>
+          <t>TRADING CALL BEL खरीदें PRICE 410.55 TARGET 425/430 STOP LOSS 404</t>
+        </is>
+      </c>
+      <c r="I1559" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1559" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1560" t="n">
+        <v>5047.7</v>
+      </c>
+      <c r="E1560" t="n">
+        <v>6175</v>
+      </c>
+      <c r="G1560" t="inlineStr"/>
+      <c r="H1560" t="inlineStr">
+        <is>
+          <t>सिटी HAL 5031.10 +175.90 BUY लक्ष्य ₹6175</t>
+        </is>
+      </c>
+      <c r="I1560" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1560" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>FINCABLES</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1561" t="n">
+        <v>1319.9</v>
+      </c>
+      <c r="E1561" t="n">
+        <v>1410</v>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1561" t="inlineStr">
+        <is>
+          <t>जेफरीज Finolex Cables 1302.30 +75.30 BUY लक्ष्य ₹1410</t>
+        </is>
+      </c>
+      <c r="I1561" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1561" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>NELCO</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1562" t="n">
+        <v>976.1</v>
+      </c>
+      <c r="E1562" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F1562" t="n">
+        <v>910</v>
+      </c>
+      <c r="G1562" t="inlineStr"/>
+      <c r="H1562" t="inlineStr">
+        <is>
+          <t>POSITIONAL CALL NELCO BUY TARGET 1070 STOP LOSS 910 NELCO 973.10 ▲ 39.90</t>
+        </is>
+      </c>
+      <c r="I1562" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1562" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1490"/>
+  <autoFilter ref="A1:J1562"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -63088,7 +63088,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1491" t="inlineStr"/>
       <c r="E1491" t="n">
         <v>950</v>
       </c>
@@ -63191,7 +63190,6 @@
       <c r="F1493" t="n">
         <v>550</v>
       </c>
-      <c r="G1493" t="inlineStr"/>
       <c r="H1493" t="inlineStr">
         <is>
           <t>Super KOOL MEHUL GMDC 579.00 10.15 BUY TGT 640 SL 550</t>
@@ -63233,7 +63231,6 @@
       <c r="F1494" t="n">
         <v>416</v>
       </c>
-      <c r="G1494" t="inlineStr"/>
       <c r="H1494" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट Coal India 433.30 13.05 BUY TGT 445 SL 416</t>
@@ -63272,7 +63269,6 @@
       <c r="E1495" t="n">
         <v>445</v>
       </c>
-      <c r="G1495" t="inlineStr"/>
       <c r="H1495" t="inlineStr">
         <is>
           <t>Coal India 433.05 12.80 BUY TGT 445</t>
@@ -63314,7 +63310,6 @@
       <c r="F1496" t="n">
         <v>999</v>
       </c>
-      <c r="G1496" t="inlineStr"/>
       <c r="H1496" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Max Healthcare 1030.30 3.76% BUY TGT 1055 SL 999</t>
@@ -63399,7 +63394,6 @@
       <c r="E1498" t="n">
         <v>400</v>
       </c>
-      <c r="G1498" t="inlineStr"/>
       <c r="H1498" t="inlineStr">
         <is>
           <t>SID Eternal (Zomato) CMP 318.90 TARGET 400 25% ALLOCATION</t>
@@ -63438,7 +63432,6 @@
       <c r="E1499" t="n">
         <v>230</v>
       </c>
-      <c r="G1499" t="inlineStr"/>
       <c r="H1499" t="inlineStr">
         <is>
           <t>'Gift Hamper' थीम Meesho CMP 213.50 TARGET 230 25% ALLOCATION</t>
@@ -63471,11 +63464,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1500" t="inlineStr"/>
       <c r="E1500" t="n">
         <v>150</v>
       </c>
-      <c r="G1500" t="inlineStr"/>
       <c r="H1500" t="inlineStr">
         <is>
           <t>जैन साब के GEMS Sambhv Steel @ 130 खरीदें STOP LOSS -- TARGET 150 Sambhv Steel 131.55 ▲ 2.10%</t>
@@ -63508,11 +63499,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1501" t="inlineStr"/>
       <c r="E1501" t="n">
         <v>192</v>
       </c>
-      <c r="G1501" t="inlineStr"/>
       <c r="H1501" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Enviro Infra 213.26 8.70% BUY TARGET HIT 192</t>
@@ -63545,11 +63534,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1502" t="inlineStr"/>
       <c r="E1502" t="n">
         <v>705</v>
       </c>
-      <c r="G1502" t="inlineStr"/>
       <c r="H1502" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Graphite India 806.90 72.65 BUY TARGET HIT 705</t>
@@ -63588,7 +63575,6 @@
       <c r="E1503" t="n">
         <v>807.05</v>
       </c>
-      <c r="G1503" t="inlineStr"/>
       <c r="H1503" t="inlineStr">
         <is>
           <t>Biocon 401.65 9.35 2.38% Vol: 2.3 m ▲ PICK OF THE DAY 807.05 TARGET HIT</t>
@@ -63621,14 +63607,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1504" t="inlineStr"/>
       <c r="E1504" t="n">
         <v>760</v>
       </c>
       <c r="F1504" t="n">
         <v>705</v>
       </c>
-      <c r="G1504" t="inlineStr"/>
       <c r="H1504" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Graphite India 806.60 72.35 BUY TGT 760 SL 705</t>
@@ -63661,11 +63645,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1505" t="inlineStr"/>
       <c r="E1505" t="n">
         <v>252</v>
       </c>
-      <c r="G1505" t="inlineStr"/>
       <c r="H1505" t="inlineStr">
         <is>
           <t>मेहुल कोटारी HEG Ltd 263.95 2.07% BUY TARGET HIT 252</t>
@@ -63707,7 +63689,6 @@
       <c r="F1506" t="n">
         <v>252</v>
       </c>
-      <c r="G1506" t="inlineStr"/>
       <c r="H1506" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -63754,7 +63735,6 @@
       <c r="F1507" t="n">
         <v>515</v>
       </c>
-      <c r="G1507" t="inlineStr"/>
       <c r="H1507" t="inlineStr">
         <is>
           <t>Super Kool Menu
@@ -63801,7 +63781,6 @@
       <c r="F1508" t="n">
         <v>3460</v>
       </c>
-      <c r="G1508" t="inlineStr"/>
       <c r="H1508" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -63848,7 +63827,6 @@
       <c r="F1509" t="n">
         <v>230</v>
       </c>
-      <c r="G1509" t="inlineStr"/>
       <c r="H1509" t="inlineStr">
         <is>
           <t>PICK OF THE DAY ONGC 236.00 2.30 BUY TGT 242 SL 230</t>
@@ -63890,7 +63868,6 @@
       <c r="F1510" t="n">
         <v>310</v>
       </c>
-      <c r="G1510" t="inlineStr"/>
       <c r="H1510" t="inlineStr">
         <is>
           <t>BPCL Fut SELL PRICE 303.60 TARGET 295/287 STOP LOSS 310</t>
@@ -63932,7 +63909,6 @@
       <c r="F1511" t="n">
         <v>310</v>
       </c>
-      <c r="G1511" t="inlineStr"/>
       <c r="H1511" t="inlineStr">
         <is>
           <t>BPCL Fut SELL PRICE 303.60 TARGET 295/287 STOP LOSS 310</t>
@@ -63974,7 +63950,6 @@
       <c r="F1512" t="n">
         <v>1779</v>
       </c>
-      <c r="G1512" t="inlineStr"/>
       <c r="H1512" t="inlineStr">
         <is>
           <t>Axiscades BUY PRICE 1848.60 TARGET 2000 STOP LOSS 1779</t>
@@ -64016,7 +63991,6 @@
       <c r="F1513" t="n">
         <v>510</v>
       </c>
-      <c r="G1513" t="inlineStr"/>
       <c r="H1513" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -64063,7 +64037,6 @@
       <c r="F1514" t="n">
         <v>510</v>
       </c>
-      <c r="G1514" t="inlineStr"/>
       <c r="H1514" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -64110,7 +64083,6 @@
       <c r="F1515" t="n">
         <v>690</v>
       </c>
-      <c r="G1515" t="inlineStr"/>
       <c r="H1515" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Raymond Lifestyle BUY PRICE 697 TARGET 705, 715, 725 STOP LOSS 690</t>
@@ -64152,7 +64124,6 @@
       <c r="F1516" t="n">
         <v>204</v>
       </c>
-      <c r="G1516" t="inlineStr"/>
       <c r="H1516" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -64196,7 +64167,6 @@
       <c r="E1517" t="n">
         <v>1418</v>
       </c>
-      <c r="G1517" t="inlineStr"/>
       <c r="H1517" t="inlineStr">
         <is>
           <t>CALLS Finolex Cables 1302 BUY लक्ष्य ₹1418</t>
@@ -64235,7 +64205,6 @@
       <c r="E1518" t="n">
         <v>1410</v>
       </c>
-      <c r="G1518" t="inlineStr"/>
       <c r="H1518" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS BUY लक्ष्मी ₹1410</t>
@@ -64274,7 +64243,6 @@
       <c r="E1519" t="n">
         <v>2820</v>
       </c>
-      <c r="G1519" t="inlineStr"/>
       <c r="H1519" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -64406,7 +64374,6 @@
       <c r="F1522" t="n">
         <v>307</v>
       </c>
-      <c r="G1522" t="inlineStr"/>
       <c r="H1522" t="inlineStr">
         <is>
           <t>MY CHOICE BPCL FUT S 295 307</t>
@@ -64448,7 +64415,6 @@
       <c r="F1523" t="n">
         <v>2505</v>
       </c>
-      <c r="G1523" t="inlineStr"/>
       <c r="H1523" t="inlineStr">
         <is>
           <t>MY CHOICE ASIAN PAINTS FUT S 2430 2505</t>
@@ -64490,7 +64456,6 @@
       <c r="F1524" t="n">
         <v>350</v>
       </c>
-      <c r="G1524" t="inlineStr"/>
       <c r="H1524" t="inlineStr">
         <is>
           <t>MY CHOICE HPCL FUT S 339 350</t>
@@ -64529,7 +64494,6 @@
       <c r="E1525" t="n">
         <v>230</v>
       </c>
-      <c r="G1525" t="inlineStr"/>
       <c r="H1525" t="inlineStr">
         <is>
           <t>INVESTMENT WELSPUN LIVING B 230 12 MONTH</t>
@@ -64571,7 +64535,6 @@
       <c r="F1526" t="n">
         <v>1289</v>
       </c>
-      <c r="G1526" t="inlineStr"/>
       <c r="H1526" t="inlineStr">
         <is>
           <t>NEWS IMPACT FINOLEX CABLES B 1328 1289</t>
@@ -64613,7 +64576,6 @@
       <c r="F1527" t="n">
         <v>527</v>
       </c>
-      <c r="G1527" t="inlineStr"/>
       <c r="H1527" t="inlineStr">
         <is>
           <t>CASH HINDUSTAN COPPER B 545 527</t>
@@ -64652,7 +64614,6 @@
       <c r="E1528" t="n">
         <v>2200</v>
       </c>
-      <c r="G1528" t="inlineStr"/>
       <c r="H1528" t="inlineStr">
         <is>
           <t>FUNDA BEML B 2200 6 MONTHS</t>
@@ -64694,7 +64655,6 @@
       <c r="F1529" t="n">
         <v>367</v>
       </c>
-      <c r="G1529" t="inlineStr"/>
       <c r="H1529" t="inlineStr">
         <is>
           <t>FUTURE NALCO FUT B 380 367</t>
@@ -64736,7 +64696,6 @@
       <c r="F1530" t="n">
         <v>715</v>
       </c>
-      <c r="G1530" t="inlineStr"/>
       <c r="H1530" t="inlineStr">
         <is>
           <t>TECHNO HDFC BANK FUT S 694 715</t>
@@ -64778,7 +64737,6 @@
       <c r="F1531" t="n">
         <v>268</v>
       </c>
-      <c r="G1531" t="inlineStr"/>
       <c r="H1531" t="inlineStr">
         <is>
           <t>CASH NLC INDIA B 282 268</t>
@@ -64820,7 +64778,6 @@
       <c r="F1532" t="n">
         <v>4981</v>
       </c>
-      <c r="G1532" t="inlineStr"/>
       <c r="H1532" t="inlineStr">
         <is>
           <t>FUTURE HAL FUT B 5180 4981</t>
@@ -64862,7 +64819,6 @@
       <c r="F1533" t="n">
         <v>307</v>
       </c>
-      <c r="G1533" t="inlineStr"/>
       <c r="H1533" t="inlineStr">
         <is>
           <t>MY CHOICE BPCL Fut बेचें PRICE 303.60 TARGET 295 STOP LOSS 307</t>
@@ -64904,7 +64860,6 @@
       <c r="F1534" t="n">
         <v>2505</v>
       </c>
-      <c r="G1534" t="inlineStr"/>
       <c r="H1534" t="inlineStr">
         <is>
           <t>पूजा के शेयर
@@ -64951,7 +64906,6 @@
       <c r="F1535" t="n">
         <v>233.5</v>
       </c>
-      <c r="G1535" t="inlineStr"/>
       <c r="H1535" t="inlineStr">
         <is>
           <t>MY CHOICE ONGC खरीदें PRICE 236.00 TARGET 241 STOP LOSS 233.5</t>
@@ -64990,7 +64944,6 @@
       <c r="E1536" t="n">
         <v>241</v>
       </c>
-      <c r="G1536" t="inlineStr"/>
       <c r="H1536" t="inlineStr">
         <is>
           <t>MY CHOICE ONGC PRICE 236.00 TARGET 241</t>
@@ -65032,7 +64985,6 @@
       <c r="F1537" t="n">
         <v>488</v>
       </c>
-      <c r="G1537" t="inlineStr"/>
       <c r="H1537" t="inlineStr">
         <is>
           <t>नेहा के शेयर
@@ -65079,7 +65031,6 @@
       <c r="F1538" t="n">
         <v>191</v>
       </c>
-      <c r="G1538" t="inlineStr"/>
       <c r="H1538" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -65126,7 +65077,6 @@
       <c r="F1539" t="n">
         <v>1289</v>
       </c>
-      <c r="G1539" t="inlineStr"/>
       <c r="H1539" t="inlineStr">
         <is>
           <t>खबर के दम पर Finolex Cables खरीदें PRICE 1302.30 TARGET 1328 STOP LOSS 1289 STOCK OF THE DAY 8:25 AM 9AM</t>
@@ -65165,7 +65115,6 @@
       <c r="E1540" t="n">
         <v>230</v>
       </c>
-      <c r="G1540" t="inlineStr"/>
       <c r="H1540" t="inlineStr">
         <is>
           <t>पूजा के शेयर Welspun Living खरीदें PRICE 207.87 TARGET 230 DURATION 12 महीने</t>
@@ -65207,7 +65156,6 @@
       <c r="F1541" t="n">
         <v>490</v>
       </c>
-      <c r="G1541" t="inlineStr"/>
       <c r="H1541" t="inlineStr">
         <is>
           <t>नेहा के शेयर
@@ -65254,7 +65202,6 @@
       <c r="F1542" t="n">
         <v>990</v>
       </c>
-      <c r="G1542" t="inlineStr"/>
       <c r="H1542" t="inlineStr">
         <is>
           <t>नेहा के शेयर Hindalco खरीदें PRICE 1009.00 TARGET 1025 STOP LOSS 990</t>
@@ -65293,7 +65240,6 @@
       <c r="E1543" t="n">
         <v>2200</v>
       </c>
-      <c r="G1543" t="inlineStr"/>
       <c r="H1543" t="inlineStr">
         <is>
           <t>पूजा के शेयर
@@ -65340,7 +65286,6 @@
       <c r="F1544" t="n">
         <v>60</v>
       </c>
-      <c r="G1544" t="inlineStr"/>
       <c r="H1544" t="inlineStr">
         <is>
           <t>BEST ऑप्शन Interglobe Aviation 5000 की पुट @119.35 खरीदें STOP LOSS 60 TARGET 250</t>
@@ -65382,7 +65327,6 @@
       <c r="F1545" t="n">
         <v>715</v>
       </c>
-      <c r="G1545" t="inlineStr"/>
       <c r="H1545" t="inlineStr">
         <is>
           <t>TECHNO PICK
@@ -65429,7 +65373,6 @@
       <c r="F1546" t="n">
         <v>580</v>
       </c>
-      <c r="G1546" t="inlineStr"/>
       <c r="H1546" t="inlineStr">
         <is>
           <t>TECHNO PICK
@@ -65476,7 +65419,6 @@
       <c r="F1547" t="n">
         <v>12</v>
       </c>
-      <c r="G1547" t="inlineStr"/>
       <c r="H1547" t="inlineStr">
         <is>
           <t>नेहा के शेयर Axis Bank 1240 की पुट @ 24.8 खरीदें STOP LOSS 12 TARGET 50 Axis Bank 1244.90 1.67%</t>
@@ -65518,7 +65460,6 @@
       <c r="F1548" t="n">
         <v>12</v>
       </c>
-      <c r="G1548" t="inlineStr"/>
       <c r="H1548" t="inlineStr">
         <is>
           <t>Axis Bank 1240 की पुट @ 24.8 खरीदें STOP LOSS 12 TARGET 50 Axis Bank 1244.90 1.67%</t>
@@ -65560,7 +65501,6 @@
       <c r="F1549" t="n">
         <v>367</v>
       </c>
-      <c r="G1549" t="inlineStr"/>
       <c r="H1549" t="inlineStr">
         <is>
           <t>आज का FUTURE
@@ -65607,7 +65547,6 @@
       <c r="F1550" t="n">
         <v>4981</v>
       </c>
-      <c r="G1550" t="inlineStr"/>
       <c r="H1550" t="inlineStr">
         <is>
           <t>नेहा के शेयर
@@ -65654,7 +65593,6 @@
       <c r="F1551" t="n">
         <v>268</v>
       </c>
-      <c r="G1551" t="inlineStr"/>
       <c r="H1551" t="inlineStr">
         <is>
           <t>CASH का शेयर
@@ -65698,7 +65636,6 @@
       <c r="E1552" t="n">
         <v>282</v>
       </c>
-      <c r="G1552" t="inlineStr"/>
       <c r="H1552" t="inlineStr">
         <is>
           <t>CASH का शेयर
@@ -65743,7 +65680,6 @@
       <c r="F1553" t="n">
         <v>527</v>
       </c>
-      <c r="G1553" t="inlineStr"/>
       <c r="H1553" t="inlineStr">
         <is>
           <t>CASH का शेयर Hind Copper खरीदें PRICE 532.85 TARGET 545 STOP LOSS 527</t>
@@ -65782,7 +65718,6 @@
       <c r="E1554" t="n">
         <v>260</v>
       </c>
-      <c r="G1554" t="inlineStr"/>
       <c r="H1554" t="inlineStr">
         <is>
           <t>Welspun Living BUY 260</t>
@@ -65821,7 +65756,6 @@
       <c r="E1555" t="n">
         <v>900</v>
       </c>
-      <c r="G1555" t="inlineStr"/>
       <c r="H1555" t="inlineStr">
         <is>
           <t>Raymond Lifestyle BUY 900</t>
@@ -65863,7 +65797,6 @@
       <c r="F1556" t="n">
         <v>548</v>
       </c>
-      <c r="G1556" t="inlineStr"/>
       <c r="H1556" t="inlineStr">
         <is>
           <t>TRADING CALL LIC Hsg Fin खरीदें PRICE 563.00 TARGET 585/595 STOP LOSS 548</t>
@@ -65905,7 +65838,6 @@
       <c r="F1557" t="n">
         <v>548</v>
       </c>
-      <c r="G1557" t="inlineStr"/>
       <c r="H1557" t="inlineStr">
         <is>
           <t>TRADING CALL LIC Hsg Fin खरीदें PRICE 563.00 TARGET 585/595 STOP LOSS 548</t>
@@ -65947,7 +65879,6 @@
       <c r="F1558" t="n">
         <v>404</v>
       </c>
-      <c r="G1558" t="inlineStr"/>
       <c r="H1558" t="inlineStr">
         <is>
           <t>TRADING CALL BEL खरीदें PRICE 410.55 TARGET 425/430 STOP LOSS 404</t>
@@ -65989,7 +65920,6 @@
       <c r="F1559" t="n">
         <v>404</v>
       </c>
-      <c r="G1559" t="inlineStr"/>
       <c r="H1559" t="inlineStr">
         <is>
           <t>TRADING CALL BEL खरीदें PRICE 410.55 TARGET 425/430 STOP LOSS 404</t>
@@ -66028,7 +65958,6 @@
       <c r="E1560" t="n">
         <v>6175</v>
       </c>
-      <c r="G1560" t="inlineStr"/>
       <c r="H1560" t="inlineStr">
         <is>
           <t>सिटी HAL 5031.10 +175.90 BUY लक्ष्य ₹6175</t>
@@ -66113,7 +66042,6 @@
       <c r="F1562" t="n">
         <v>910</v>
       </c>
-      <c r="G1562" t="inlineStr"/>
       <c r="H1562" t="inlineStr">
         <is>
           <t>POSITIONAL CALL NELCO BUY TARGET 1070 STOP LOSS 910 NELCO 973.10 ▲ 39.90</t>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1562</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1664</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1562"/>
+  <dimension ref="A1:J1664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -66058,8 +66058,4274 @@
         </is>
       </c>
     </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1563" t="n">
+        <v>2739</v>
+      </c>
+      <c r="E1563" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G1563" t="inlineStr"/>
+      <c r="H1563" t="inlineStr">
+        <is>
+          <t>Caplin Point खरीदें PRICE 2733.70 TARGET 3500 DURATION 6-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1563" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1563" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1564" t="n">
+        <v>276.3</v>
+      </c>
+      <c r="E1564" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1564" t="inlineStr"/>
+      <c r="H1564" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1564" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1564" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1565" t="n">
+        <v>276.3</v>
+      </c>
+      <c r="E1565" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1565" t="inlineStr"/>
+      <c r="H1565" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1565" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1565" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1566" t="n">
+        <v>276.3</v>
+      </c>
+      <c r="E1566" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1566" t="inlineStr"/>
+      <c r="H1566" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1566" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1566" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>GENESYS</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1567" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="E1567" t="n">
+        <v>400</v>
+      </c>
+      <c r="F1567" t="n">
+        <v>270</v>
+      </c>
+      <c r="G1567" t="inlineStr"/>
+      <c r="H1567" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय Genesys Intl खरीदें STOP LOSS 270 TARGET 400 DURATION 4-8 महीने Genesys Intl 311.66</t>
+        </is>
+      </c>
+      <c r="I1567" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1567" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:22:00</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>RAMCOIND</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1568" t="n">
+        <v>316</v>
+      </c>
+      <c r="E1568" t="n">
+        <v>360</v>
+      </c>
+      <c r="F1568" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1568" t="inlineStr"/>
+      <c r="H1568" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Ramco Ind @ 314 खरीदें STOP LOSS 300 TARGET 355/360 DURATION 4-8 महीने Ramco Ind 315.90</t>
+        </is>
+      </c>
+      <c r="I1568" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1568" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:22:00</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>SIKA</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1569" t="n">
+        <v>1092</v>
+      </c>
+      <c r="E1569" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1569" t="inlineStr"/>
+      <c r="H1569" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+Sika Interplant
+1095.00 70.15
+BUY
+TGT 1220
+SL --</t>
+        </is>
+      </c>
+      <c r="I1569" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1569" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:22:00</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1570" t="n">
+        <v>1544</v>
+      </c>
+      <c r="E1570" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F1570" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G1570" t="inlineStr"/>
+      <c r="H1570" t="inlineStr">
+        <is>
+          <t>Tech Mahindra 1544.60 18.80 BUY TGT 1580 SL 1500</t>
+        </is>
+      </c>
+      <c r="I1570" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1570" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:21:00</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1571" t="n">
+        <v>1847.1</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G1571" t="inlineStr"/>
+      <c r="H1571" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel 1846.80 BUY TGT 1870</t>
+        </is>
+      </c>
+      <c r="I1571" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1571" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:20:49</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr"/>
+      <c r="E1572" t="n">
+        <v>185</v>
+      </c>
+      <c r="F1572" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1572" t="inlineStr"/>
+      <c r="H1572" t="inlineStr">
+        <is>
+          <t>Pine Labs 191.50 18.59% BUY TGT 185 SL 169</t>
+        </is>
+      </c>
+      <c r="I1572" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1572" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:21:00</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1573" t="n">
+        <v>1147</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>1156</v>
+      </c>
+      <c r="F1573" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G1573" t="inlineStr"/>
+      <c r="H1573" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर
+Dr Reddy's Fut
+1145.00 0.76%
+BUY
+TGT 1156
+SL 1133</t>
+        </is>
+      </c>
+      <c r="I1573" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1573" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:21:00</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>BHARTIARTL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1574" t="n">
+        <v>1849.3</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>1870</v>
+      </c>
+      <c r="F1574" t="n">
+        <v>1833</v>
+      </c>
+      <c r="G1574" t="inlineStr"/>
+      <c r="H1574" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर
+Bharti Airtel Fut
+1849.00 0.47%
+BUY
+TGT 1870
+SL 1833</t>
+        </is>
+      </c>
+      <c r="I1574" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1574" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:20:00</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>AJANTPHARM</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1575" t="n">
+        <v>3491</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>3950</v>
+      </c>
+      <c r="G1575" t="inlineStr"/>
+      <c r="H1575" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Ajanta Ph @ 3470 खरीदें STOP LOSS -- TARGET 3950 DURATION 9-12 महीने Ajanta Ph 3490.00 30.00</t>
+        </is>
+      </c>
+      <c r="I1575" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1575" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:13:00</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>ASAHIINDIA</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1576" t="n">
+        <v>980</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F1576" t="n">
+        <v>940</v>
+      </c>
+      <c r="G1576" t="inlineStr"/>
+      <c r="H1576" t="inlineStr">
+        <is>
+          <t>Asahi India Glass खरीदें PRICE 981.00 TARGET 1100/1150 STOP LOSS 940</t>
+        </is>
+      </c>
+      <c r="I1576" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1576" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>AJANTPHARM</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1577" t="n">
+        <v>3490.9</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>3950</v>
+      </c>
+      <c r="G1577" t="inlineStr"/>
+      <c r="H1577" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCK Ajanta Ph @ 3470 खरीदें STOP LOSS TARGET 3950 DURATION 9-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1577" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1577" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1578" t="n">
+        <v>1028.6</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G1578" t="inlineStr"/>
+      <c r="H1578" t="inlineStr">
+        <is>
+          <t>SUPER SID
+Max Healthcare
+1028.90 0.93%
+BUY
+TGT 1060
+SL --</t>
+        </is>
+      </c>
+      <c r="I1578" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1578" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>SIKA</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1579" t="n">
+        <v>1094.5</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1579" t="inlineStr"/>
+      <c r="H1579" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+Sika Interplant
+1091.50 66.65
+BUY
+TGT 1220
+SL --</t>
+        </is>
+      </c>
+      <c r="I1579" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1579" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1580" t="n">
+        <v>1543</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>1388</v>
+      </c>
+      <c r="G1580" t="inlineStr"/>
+      <c r="H1580" t="inlineStr">
+        <is>
+          <t>Tech Mahindra 1543.00 BUY TGT 1588 SL 1388</t>
+        </is>
+      </c>
+      <c r="I1580" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1580" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1581" t="n">
+        <v>1543</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G1581" t="inlineStr"/>
+      <c r="H1581" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट
+Tech Mahindra
+1543.40 1.15%
+BUY
+TGT 1580
+SL 1500</t>
+        </is>
+      </c>
+      <c r="I1581" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1581" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1582" t="n">
+        <v>1543</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>1580</v>
+      </c>
+      <c r="G1582" t="inlineStr"/>
+      <c r="H1582" t="inlineStr">
+        <is>
+          <t>Tech Mahindra 1543.40 17.60 BUY TGT 1580</t>
+        </is>
+      </c>
+      <c r="I1582" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1582" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:09:00</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1583" t="n">
+        <v>1848</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G1583" t="inlineStr"/>
+      <c r="H1583" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel 1848.20 9.20 BUY TGT 1870 SL --</t>
+        </is>
+      </c>
+      <c r="I1583" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1583" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:08:53</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr"/>
+      <c r="E1584" t="n">
+        <v>185</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1584" t="inlineStr"/>
+      <c r="H1584" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Pine Labs 185.25 12.08 BUY TGT 185 SL 169</t>
+        </is>
+      </c>
+      <c r="I1584" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1584" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:09:00</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1585" t="n">
+        <v>1143.6</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>1156</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G1585" t="inlineStr"/>
+      <c r="H1585" t="inlineStr">
+        <is>
+          <t>Dr Reddy's Fut 1142.90 BUY TGT 1156 SL 1133</t>
+        </is>
+      </c>
+      <c r="I1585" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1585" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:09:00</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>BHARTIARTL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1586" t="n">
+        <v>1851.3</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>1870</v>
+      </c>
+      <c r="F1586" t="n">
+        <v>1833</v>
+      </c>
+      <c r="G1586" t="inlineStr"/>
+      <c r="H1586" t="inlineStr">
+        <is>
+          <t>BTST BUY TODAY Bharti Airtel Fut 1851.50 11.10 BUY TGT 1870 SL 1833</t>
+        </is>
+      </c>
+      <c r="I1586" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1586" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:08:00</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1587" t="n">
+        <v>184.35</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>240</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1587" t="inlineStr"/>
+      <c r="H1587" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय Pine Labs खरीदें STOP LOSS 160 TARGET 240/250 DURATION 9-12 महीने Pine Labs 184.25</t>
+        </is>
+      </c>
+      <c r="I1587" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1587" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:08:00</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1588" t="n">
+        <v>184.35</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1588" t="inlineStr"/>
+      <c r="H1588" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय Pine Labs खरीदें STOP LOSS 160 TARGET 240/250 DURATION 9-12 महीने Pine Labs 184.25</t>
+        </is>
+      </c>
+      <c r="I1588" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1588" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:04:00</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>SSWL</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1589" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1589" t="inlineStr"/>
+      <c r="H1589" t="inlineStr">
+        <is>
+          <t>Steel Strip Wheels खरीदें PRICE 371.00 TARGET 450 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1589" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1589" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:04:00</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>SSWL</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1590" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1590" t="inlineStr"/>
+      <c r="H1590" t="inlineStr">
+        <is>
+          <t>10 की कमाई
+Steel Strip Wheels
+खरीदें
+PRICE → 370.95
+TARGET → 450
+STOP LOSS → --</t>
+        </is>
+      </c>
+      <c r="I1590" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1590" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>BANKNIFTY5650029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1591" t="n">
+        <v>505.3</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>600</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>390</v>
+      </c>
+      <c r="G1591" t="inlineStr"/>
+      <c r="H1591" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय NIFTY BANK 56500 की कॉल @ 506/470 खरीदें STOP LOSS 390 TARGET 600/650 Nifty Bank 55905.30</t>
+        </is>
+      </c>
+      <c r="I1591" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1591" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>BANKNIFTY5650029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1592" t="n">
+        <v>505.3</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>650</v>
+      </c>
+      <c r="F1592" t="n">
+        <v>390</v>
+      </c>
+      <c r="G1592" t="inlineStr"/>
+      <c r="H1592" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय NIFTY BANK 56500 की कॉल @ 506/470 खरीदें STOP LOSS 390 TARGET 600/650 Nifty Bank 55905.30</t>
+        </is>
+      </c>
+      <c r="I1592" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1592" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>BANKNIFTY5650029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1593" t="n">
+        <v>505.3</v>
+      </c>
+      <c r="E1593" t="n">
+        <v>600.65</v>
+      </c>
+      <c r="F1593" t="n">
+        <v>390</v>
+      </c>
+      <c r="G1593" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H1593" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय NIFTY BANK 56500 की कॉल @ 506/470 खरीदें STOP LOSS 390 TARGET 600/650</t>
+        </is>
+      </c>
+      <c r="I1593" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1593" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:57:00</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1594" t="n">
+        <v>274.8</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1594" t="inlineStr"/>
+      <c r="H1594" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1594" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1594" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:52:20</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr"/>
+      <c r="E1595" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="G1595" t="inlineStr"/>
+      <c r="H1595" t="inlineStr">
+        <is>
+          <t>Vodafone Idea 15.03 INVESTMENT PICK 6.55 28/08/2025 RECO PRICE RETURN TILL NOW 8.48 129.47%</t>
+        </is>
+      </c>
+      <c r="I1595" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1595" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:51:59</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr"/>
+      <c r="E1596" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="G1596" t="inlineStr"/>
+      <c r="H1596" t="inlineStr">
+        <is>
+          <t>Vodafone Idea 15.03 INVESTMENT PICK 6.55 28/08/2025 RECO PRICE RETURN TILL NOW 8.48 129.47%</t>
+        </is>
+      </c>
+      <c r="I1596" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1596" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1597" t="n">
+        <v>275.75</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1597" t="inlineStr"/>
+      <c r="H1597" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1597" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1597" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1598" t="n">
+        <v>275.75</v>
+      </c>
+      <c r="E1598" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1598" t="inlineStr"/>
+      <c r="H1598" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1598" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1598" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1599" t="n">
+        <v>275.75</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1599" t="inlineStr"/>
+      <c r="H1599" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1599" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1599" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>WABAG</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1600" t="n">
+        <v>2204.7</v>
+      </c>
+      <c r="E1600" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>2130</v>
+      </c>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>Kunal Saraogi</t>
+        </is>
+      </c>
+      <c r="H1600" t="inlineStr">
+        <is>
+          <t>कनाल सरावगी की राय Va Tech Wabag खरीदें PRICE 2195.90 TARGET 2300/2350 STOP LOSS 2130</t>
+        </is>
+      </c>
+      <c r="I1600" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1600" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>WABAG</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1601" t="n">
+        <v>2204.7</v>
+      </c>
+      <c r="E1601" t="n">
+        <v>2350</v>
+      </c>
+      <c r="F1601" t="n">
+        <v>2130</v>
+      </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>Kunal Saraogi</t>
+        </is>
+      </c>
+      <c r="H1601" t="inlineStr">
+        <is>
+          <t>कनाल सरावगी की राय Va Tech Wabag खरीदें PRICE 2195.90 TARGET 2300/2350 STOP LOSS 2130</t>
+        </is>
+      </c>
+      <c r="I1601" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1601" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>WABAG</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1602" t="n">
+        <v>2204.7</v>
+      </c>
+      <c r="E1602" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F1602" t="n">
+        <v>2130</v>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>Kunal Saraogi</t>
+        </is>
+      </c>
+      <c r="H1602" t="inlineStr">
+        <is>
+          <t>कुणाल सरावगी की राय Va Tech Wabag खरीदें PRICE 2199.90 TARGET 2300/2350 STOP LOSS 2130</t>
+        </is>
+      </c>
+      <c r="I1602" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1602" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:47:00</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>WABAG</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1603" t="n">
+        <v>2204.7</v>
+      </c>
+      <c r="E1603" t="n">
+        <v>2350</v>
+      </c>
+      <c r="F1603" t="n">
+        <v>2130</v>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>Kunal Saraogi</t>
+        </is>
+      </c>
+      <c r="H1603" t="inlineStr">
+        <is>
+          <t>कुणाल सरावगी की राय Va Tech Wabag खरीदें PRICE 2198.90 TARGET 2300/2350 STOP LOSS 2130</t>
+        </is>
+      </c>
+      <c r="I1603" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1603" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1604" t="n">
+        <v>1027.1</v>
+      </c>
+      <c r="E1604" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1604" t="inlineStr"/>
+      <c r="H1604" t="inlineStr">
+        <is>
+          <t>Max Healthcare खरीदें PRICE 1026.50 TARGET 1060/1220 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1604" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1604" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1605" t="n">
+        <v>1027.1</v>
+      </c>
+      <c r="E1605" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G1605" t="inlineStr"/>
+      <c r="H1605" t="inlineStr">
+        <is>
+          <t>Max Healthcare खरीदें PRICE 1026.00 TARGET 1060/1220 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1605" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1605" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:41:00</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1606" t="n">
+        <v>1143</v>
+      </c>
+      <c r="E1606" t="n">
+        <v>1180</v>
+      </c>
+      <c r="F1606" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G1606" t="inlineStr"/>
+      <c r="H1606" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर की राय
+Dr Reddy's Fut
+खरीदें
+PRICE ▶ 1143.50
+TARGET ▶ 1156/1180
+STOP LOSS ▶ 1133</t>
+        </is>
+      </c>
+      <c r="I1606" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1606" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:41:00</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1607" t="n">
+        <v>1143</v>
+      </c>
+      <c r="E1607" t="n">
+        <v>1156</v>
+      </c>
+      <c r="F1607" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G1607" t="inlineStr"/>
+      <c r="H1607" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर की राय
+Dr Reddy's Fut
+खरीदें
+PRICE ▶ 1143.50
+TARGET ▶ 1156/1180
+STOP LOSS ▶ 1133</t>
+        </is>
+      </c>
+      <c r="I1607" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1607" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:39:51</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr"/>
+      <c r="E1608" t="n">
+        <v>1450.6</v>
+      </c>
+      <c r="F1608" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G1608" t="inlineStr"/>
+      <c r="H1608" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 3350, 4450, 6 3महीने-1133</t>
+        </is>
+      </c>
+      <c r="I1608" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1608" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:40:00</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1609" t="n">
+        <v>276.45</v>
+      </c>
+      <c r="E1609" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1609" t="inlineStr"/>
+      <c r="H1609" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1609" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1609" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:39:04</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>SIKA</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr"/>
+      <c r="E1610" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1610" t="inlineStr"/>
+      <c r="H1610" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+SIKA INTERPLANT @ 996
+खरीदें
+STOP LOSS --
+TARGET 1220</t>
+        </is>
+      </c>
+      <c r="I1610" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1610" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:29:00</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1611" t="n">
+        <v>1537.5</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G1611" t="inlineStr"/>
+      <c r="H1611" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट Tech Mahindra खरीदें PRICE 1537.30 TARGET 1580/1600 STOP LOSS 1500</t>
+        </is>
+      </c>
+      <c r="I1611" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1611" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:29:00</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1612" t="n">
+        <v>1537.5</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G1612" t="inlineStr"/>
+      <c r="H1612" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट Tech Mahindra खरीदें PRICE 1537.30 TARGET 1580/1600 STOP LOSS 1500</t>
+        </is>
+      </c>
+      <c r="I1612" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1612" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1613" t="n">
+        <v>1844.5</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1613" t="inlineStr"/>
+      <c r="H1613" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel खरीदें PRICE 1843.70 TARGET 1870/2500 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1613" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1613" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1614" t="n">
+        <v>1844.5</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G1614" t="inlineStr"/>
+      <c r="H1614" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel खरीदें PRICE 1843.70 TARGET 1870/2500 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1614" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1614" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1615" t="n">
+        <v>1843.5</v>
+      </c>
+      <c r="E1615" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1615" t="inlineStr"/>
+      <c r="H1615" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel खरीदें PRICE 1842.90 TARGET 1870/2500 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1615" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1615" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1616" t="n">
+        <v>1844.6</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G1616" t="inlineStr"/>
+      <c r="H1616" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel खरीदें PRICE 1842.90 TARGET 1870/2500 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1616" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1616" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1617" t="n">
+        <v>175.39</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>185</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1617" t="inlineStr"/>
+      <c r="H1617" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Pine Labs खरीदें PRICE 176.92 TARGET 185/190 STOP LOSS 169</t>
+        </is>
+      </c>
+      <c r="I1617" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1617" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1618" t="n">
+        <v>175.39</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1618" t="inlineStr"/>
+      <c r="H1618" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Pine Labs खरीदें PRICE 176.92 TARGET 185/190 STOP LOSS 169</t>
+        </is>
+      </c>
+      <c r="I1618" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1618" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>BHARTIARTL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1619" t="n">
+        <v>1846.9</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>1870</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>1833</v>
+      </c>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>Sachitanand Uttekar</t>
+        </is>
+      </c>
+      <c r="H1619" t="inlineStr">
+        <is>
+          <t>Sacchitanand Uttkar Tradebulls Securities SEBI REG NO: INH000004486 Bharti Airtel Fut खरीदें PRICE 1844.80 TARGET 1870 STOP LOSS 1833</t>
+        </is>
+      </c>
+      <c r="I1619" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1619" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1620" t="n">
+        <v>1755</v>
+      </c>
+      <c r="E1620" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G1620" t="inlineStr"/>
+      <c r="H1620" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Adani Ports
+1750.00
+OUTPERFORM
+लक्ष्य ₹1860 से बढ़ाकर ₹2100</t>
+        </is>
+      </c>
+      <c r="I1620" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1620" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1621" t="n">
+        <v>281</v>
+      </c>
+      <c r="E1621" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1621" t="inlineStr"/>
+      <c r="H1621" t="inlineStr">
+        <is>
+          <t>अनिल सिंधवी की सलाह Birlasoft BUY PRICE 276 TARGET 350, 450, 600 DURATION 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1621" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1621" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1622" t="n">
+        <v>281</v>
+      </c>
+      <c r="E1622" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1622" t="inlineStr"/>
+      <c r="H1622" t="inlineStr">
+        <is>
+          <t>अनिल सिंधवी की सलाह Birlasoft BUY PRICE 276 TARGET 350, 450, 600 DURATION 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1622" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1622" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1623" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="E1623" t="n">
+        <v>430</v>
+      </c>
+      <c r="G1623" t="inlineStr"/>
+      <c r="H1623" t="inlineStr">
+        <is>
+          <t>सुमीत बगडिया की राय Kotak Bank BUY PRICE 416.55 TARGET 430/450 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1623" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1623" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1624" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="E1624" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1624" t="inlineStr"/>
+      <c r="H1624" t="inlineStr">
+        <is>
+          <t>सुमीत बगडिया की राय Kotak Bank BUY PRICE 416.55 TARGET 430/450 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1624" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1624" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1625" t="n">
+        <v>718</v>
+      </c>
+      <c r="E1625" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>645</v>
+      </c>
+      <c r="G1625" t="inlineStr"/>
+      <c r="H1625" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उतेकर की राय HBL ENGINEERING BUY PRICE 720.90 TARGET 980 STOP LOSS 645</t>
+        </is>
+      </c>
+      <c r="I1625" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1625" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1626" t="n">
+        <v>416</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>475</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>414</v>
+      </c>
+      <c r="G1626" t="inlineStr"/>
+      <c r="H1626" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर की राय Exide Ind BUY PRICE 420.85 TARGET 439/475 STOP LOSS 414</t>
+        </is>
+      </c>
+      <c r="I1626" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1626" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>TIMKEN</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1627" t="n">
+        <v>3280</v>
+      </c>
+      <c r="E1627" t="n">
+        <v>3450</v>
+      </c>
+      <c r="F1627" t="n">
+        <v>3260</v>
+      </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1627" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Timken India BUY PRICE 3297.20 TARGET 3400/3450 STOP LOSS 3260</t>
+        </is>
+      </c>
+      <c r="I1627" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1627" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>VARROC</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1628" t="n">
+        <v>877.4</v>
+      </c>
+      <c r="E1628" t="n">
+        <v>990</v>
+      </c>
+      <c r="F1628" t="n">
+        <v>845</v>
+      </c>
+      <c r="G1628" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1628" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Varroc Engg BUY PRICE 884.40 TARGET 950/990 STOP LOSS 845</t>
+        </is>
+      </c>
+      <c r="I1628" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1628" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>VARROC</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1629" t="n">
+        <v>877.4</v>
+      </c>
+      <c r="E1629" t="n">
+        <v>950</v>
+      </c>
+      <c r="F1629" t="n">
+        <v>845</v>
+      </c>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1629" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Varroc Engg BUY PRICE 884.40 TARGET 950/990 STOP LOSS 845</t>
+        </is>
+      </c>
+      <c r="I1629" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1629" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>DIXON29SEP26</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1630" t="n">
+        <v>13250</v>
+      </c>
+      <c r="E1630" t="n">
+        <v>13100</v>
+      </c>
+      <c r="F1630" t="n">
+        <v>13800</v>
+      </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>Kunal Saraogi</t>
+        </is>
+      </c>
+      <c r="H1630" t="inlineStr">
+        <is>
+          <t>कुणाल सरावगी की राय Dixon Tech Fut SELL PRICE 13302.00 TARGET 13100/12800 STOP LOSS 13800</t>
+        </is>
+      </c>
+      <c r="I1630" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1630" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>DIXON29SEP26</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1631" t="n">
+        <v>13250</v>
+      </c>
+      <c r="E1631" t="n">
+        <v>12800</v>
+      </c>
+      <c r="F1631" t="n">
+        <v>13800</v>
+      </c>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>Kunal Saraogi</t>
+        </is>
+      </c>
+      <c r="H1631" t="inlineStr">
+        <is>
+          <t>कुणाल सरावगी की राय Dixon Tech Fut SELL PRICE 13302.00 TARGET 13100/12800 STOP LOSS 13800</t>
+        </is>
+      </c>
+      <c r="I1631" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1631" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1632" t="n">
+        <v>4599</v>
+      </c>
+      <c r="E1632" t="n">
+        <v>6150</v>
+      </c>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1632" t="inlineStr">
+        <is>
+          <t>जेफरीज KEI Industries 4640.00 -0.63% BUY लक्ष्य ₹6920 से घटाकर ₹6150</t>
+        </is>
+      </c>
+      <c r="I1632" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1632" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>ABCAPITAL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1633" t="n">
+        <v>397.45</v>
+      </c>
+      <c r="E1633" t="n">
+        <v>394</v>
+      </c>
+      <c r="F1633" t="n">
+        <v>406</v>
+      </c>
+      <c r="G1633" t="inlineStr"/>
+      <c r="H1633" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह AB Capital Futures SELL PRICE 402 TARGET 398, 394, 390 STOP LOSS 406</t>
+        </is>
+      </c>
+      <c r="I1633" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1633" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>ABCAPITAL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1634" t="n">
+        <v>397.45</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>390</v>
+      </c>
+      <c r="F1634" t="n">
+        <v>406</v>
+      </c>
+      <c r="G1634" t="inlineStr"/>
+      <c r="H1634" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह AB Capital Futures SELL PRICE 402 TARGET 398, 394, 390 STOP LOSS 406</t>
+        </is>
+      </c>
+      <c r="I1634" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1634" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>LTF29SEP26</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1635" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="E1635" t="n">
+        <v>305</v>
+      </c>
+      <c r="F1635" t="n">
+        <v>314</v>
+      </c>
+      <c r="G1635" t="inlineStr"/>
+      <c r="H1635" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह L&amp;T Fin Futures SELL PRICE 312 TARGET 308, 305, 302 STOP LOSS 314</t>
+        </is>
+      </c>
+      <c r="I1635" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1635" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>LTF29SEP26</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1636" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="E1636" t="n">
+        <v>302</v>
+      </c>
+      <c r="F1636" t="n">
+        <v>314</v>
+      </c>
+      <c r="G1636" t="inlineStr"/>
+      <c r="H1636" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह L&amp;T Fin Futures SELL PRICE 312 TARGET 308, 305, 302 STOP LOSS 314</t>
+        </is>
+      </c>
+      <c r="I1636" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1636" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>ASHOKLEY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1637" t="n">
+        <v>163.97</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1637" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1637" t="inlineStr"/>
+      <c r="H1637" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Ashok Leyland Fut SELL PRICE 166 TARGET 164, 162, 160 STOP LOSS 168</t>
+        </is>
+      </c>
+      <c r="I1637" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1637" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1638" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="E1638" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1638" t="inlineStr">
+        <is>
+          <t>Voda Idea कल जेफरीज ने दिया ₹ 20 का टार्गेट</t>
+        </is>
+      </c>
+      <c r="I1638" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1638" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>REDINGTON</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1639" t="n">
+        <v>395.85</v>
+      </c>
+      <c r="E1639" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G1639" t="inlineStr"/>
+      <c r="H1639" t="inlineStr">
+        <is>
+          <t>MY CHOICE REDINGTON B 4000 3</t>
+        </is>
+      </c>
+      <c r="I1639" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1639" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN29SEP26</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1640" t="n">
+        <v>2790</v>
+      </c>
+      <c r="E1640" t="n">
+        <v>2785</v>
+      </c>
+      <c r="F1640" t="n">
+        <v>2869</v>
+      </c>
+      <c r="G1640" t="inlineStr"/>
+      <c r="H1640" t="inlineStr">
+        <is>
+          <t>FUTURE MUTHOOT FINANCE FUT S 2785 2869</t>
+        </is>
+      </c>
+      <c r="I1640" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1640" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1641" t="n">
+        <v>760</v>
+      </c>
+      <c r="E1641" t="n">
+        <v>805</v>
+      </c>
+      <c r="F1641" t="n">
+        <v>740</v>
+      </c>
+      <c r="G1641" t="inlineStr"/>
+      <c r="H1641" t="inlineStr">
+        <is>
+          <t>TECHNO TD POWER B 805 740</t>
+        </is>
+      </c>
+      <c r="I1641" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1641" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:04</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>KIMS</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1642" t="n">
+        <v>775.65</v>
+      </c>
+      <c r="E1642" t="n">
+        <v>801</v>
+      </c>
+      <c r="F1642" t="n">
+        <v>755</v>
+      </c>
+      <c r="G1642" t="inlineStr"/>
+      <c r="H1642" t="inlineStr">
+        <is>
+          <t>CASH KIMS B 801 755</t>
+        </is>
+      </c>
+      <c r="I1642" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1642" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>OIL50029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1643" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E1643" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1643" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1643" t="inlineStr"/>
+      <c r="H1643" t="inlineStr">
+        <is>
+          <t>OPTION OIL INDIA 500 CE @ 15 B 24 10</t>
+        </is>
+      </c>
+      <c r="I1643" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1643" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>REDINGTON</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1644" t="n">
+        <v>395.85</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>400</v>
+      </c>
+      <c r="F1644" t="n">
+        <v>388</v>
+      </c>
+      <c r="G1644" t="inlineStr"/>
+      <c r="H1644" t="inlineStr">
+        <is>
+          <t>MY CHOICE Redington खरीदें PRICE 392.00 TARGET 400 STOP LOSS 388</t>
+        </is>
+      </c>
+      <c r="I1644" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1644" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>TEXRAIL</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1645" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="E1645" t="n">
+        <v>122</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>112</v>
+      </c>
+      <c r="G1645" t="inlineStr"/>
+      <c r="H1645" t="inlineStr">
+        <is>
+          <t>MY CHOICE Texmaco Rail खरीदें PRICE 117.77 TARGET 122 STOP LOSS 112</t>
+        </is>
+      </c>
+      <c r="I1645" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1645" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1646" t="n">
+        <v>269.85</v>
+      </c>
+      <c r="E1646" t="n">
+        <v>280</v>
+      </c>
+      <c r="F1646" t="n">
+        <v>265</v>
+      </c>
+      <c r="G1646" t="inlineStr"/>
+      <c r="H1646" t="inlineStr">
+        <is>
+          <t>MY CHOICE Power Grid खरीदें PRICE 271.75 TARGET 280 STOP LOSS 265</t>
+        </is>
+      </c>
+      <c r="I1646" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1646" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1647" t="n">
+        <v>4885</v>
+      </c>
+      <c r="E1647" t="n">
+        <v>4840</v>
+      </c>
+      <c r="F1647" t="n">
+        <v>5001</v>
+      </c>
+      <c r="G1647" t="inlineStr"/>
+      <c r="H1647" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+Interglobe Aviation Fut
+बेचें
+PRICE → 4933.50
+TARGET → 4840
+STOP LOSS → 5001</t>
+        </is>
+      </c>
+      <c r="I1647" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1647" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>STLTECH-BE</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1648" t="n">
+        <v>860</v>
+      </c>
+      <c r="E1648" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1648" t="n">
+        <v>849</v>
+      </c>
+      <c r="G1648" t="inlineStr"/>
+      <c r="H1648" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+Sterlite Tech
+खरीदें
+PRICE → 854.75
+TARGET → 880
+STOP LOSS → 849</t>
+        </is>
+      </c>
+      <c r="I1648" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1648" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1649" t="n">
+        <v>1237.9</v>
+      </c>
+      <c r="E1649" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G1649" t="inlineStr"/>
+      <c r="H1649" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK
+Axis Bank
+खरीदें
+PRICE → 1246.00
+TARGET → 1380
+DURATION → 12 महीने</t>
+        </is>
+      </c>
+      <c r="I1649" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1649" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>TVSSCS</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1650" t="n">
+        <v>129.09</v>
+      </c>
+      <c r="E1650" t="n">
+        <v>175</v>
+      </c>
+      <c r="F1650" t="n">
+        <v>105</v>
+      </c>
+      <c r="G1650" t="inlineStr"/>
+      <c r="H1650" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK TVS Supply Chain खरीदें PRICE 128.73 TARGET 175 STOP LOSS 105</t>
+        </is>
+      </c>
+      <c r="I1650" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1650" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1651" t="n">
+        <v>427</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>440</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>421</v>
+      </c>
+      <c r="G1651" t="inlineStr"/>
+      <c r="H1651" t="inlineStr">
+        <is>
+          <t>FUNDA PICK
+BHEL
+खरीदें
+PRICE ▶ 429.50
+TARGET ▶ 440
+STOP LOSS ▶ 421</t>
+        </is>
+      </c>
+      <c r="I1651" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1651" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1652" t="n">
+        <v>333</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>360</v>
+      </c>
+      <c r="G1652" t="inlineStr"/>
+      <c r="H1652" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर NTPC खरीदें PRICE 335.00 TARGET 360 DURATION 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1652" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1652" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>HINDPETRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1653" t="n">
+        <v>346.95</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>340</v>
+      </c>
+      <c r="F1653" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1653" t="inlineStr"/>
+      <c r="H1653" t="inlineStr">
+        <is>
+          <t>TECHNO PICK HPCL Fut बेचें PRICE 350.90 TARGET 340 STOP LOSS 355</t>
+        </is>
+      </c>
+      <c r="I1653" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1653" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1654" t="n">
+        <v>760.75</v>
+      </c>
+      <c r="E1654" t="n">
+        <v>805</v>
+      </c>
+      <c r="F1654" t="n">
+        <v>740</v>
+      </c>
+      <c r="G1654" t="inlineStr"/>
+      <c r="H1654" t="inlineStr">
+        <is>
+          <t>TECHNO PICK TD Power खरीदें PRICE 762.75 TARGET 805 STOP LOSS 740</t>
+        </is>
+      </c>
+      <c r="I1654" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1654" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>KEI460029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1655" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1655" t="inlineStr"/>
+      <c r="H1655" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर KEI Industries 4600 की पुट @88.65 खरीदें STOP LOSS 40 TARGET 200 KEI Industries 4640.00 0.63%</t>
+        </is>
+      </c>
+      <c r="I1655" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1655" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1656" t="n">
+        <v>295</v>
+      </c>
+      <c r="E1656" t="n">
+        <v>360</v>
+      </c>
+      <c r="G1656" t="inlineStr"/>
+      <c r="H1656" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Angel One 297.30 -1.75 NEUTRAL लक्ष्य ₹360</t>
+        </is>
+      </c>
+      <c r="I1656" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1656" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1657" t="n">
+        <v>1373</v>
+      </c>
+      <c r="E1657" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G1657" t="inlineStr"/>
+      <c r="H1657" t="inlineStr">
+        <is>
+          <t>Cipla 1373.30 +10.20 OUTPERFORM लक्ष्य ₹1675</t>
+        </is>
+      </c>
+      <c r="I1657" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1657" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>WIPRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1658" t="n">
+        <v>164.8</v>
+      </c>
+      <c r="E1658" t="n">
+        <v>157</v>
+      </c>
+      <c r="F1658" t="n">
+        <v>171</v>
+      </c>
+      <c r="G1658" t="inlineStr"/>
+      <c r="H1658" t="inlineStr">
+        <is>
+          <t>Wipro Fut बेचें PRICE 164.77 TARGET 160/157 STOP LOSS 171 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
+        </is>
+      </c>
+      <c r="I1658" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1658" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>WIPRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1659" t="n">
+        <v>163.6</v>
+      </c>
+      <c r="E1659" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1659" t="n">
+        <v>171</v>
+      </c>
+      <c r="G1659" t="inlineStr"/>
+      <c r="H1659" t="inlineStr">
+        <is>
+          <t>Wipro Fut बेचें PRICE 164.77 TARGET 160/157 STOP LOSS 171 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
+        </is>
+      </c>
+      <c r="I1659" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1659" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1660" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E1660" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G1660" t="inlineStr"/>
+      <c r="H1660" t="inlineStr">
+        <is>
+          <t>ICICI Lombard 1465.00 -9.00 NEUTRAL लक्ष्य ₹1930 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
+        </is>
+      </c>
+      <c r="I1660" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1660" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1661" t="n">
+        <v>1230.1</v>
+      </c>
+      <c r="E1661" t="n">
+        <v>1550</v>
+      </c>
+      <c r="G1661" t="inlineStr"/>
+      <c r="H1661" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Axis Bank 1246.00 +7.50 ACCUMULATE श्रीकांत चौहान कोटक सिक्योरिटीज लक्ष्य ₹1550</t>
+        </is>
+      </c>
+      <c r="I1661" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1661" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1662" t="n">
+        <v>1749.8</v>
+      </c>
+      <c r="E1662" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G1662" t="inlineStr"/>
+      <c r="H1662" t="inlineStr">
+        <is>
+          <t>बर्नस्टीन Paytm 1739.00 -0.71% OUTPERFORM लक्ष्य ₹2200</t>
+        </is>
+      </c>
+      <c r="I1662" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1662" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1663" t="n">
+        <v>3614.5</v>
+      </c>
+      <c r="E1663" t="n">
+        <v>4100</v>
+      </c>
+      <c r="G1663" t="inlineStr"/>
+      <c r="H1663" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Thermax 3645.40 +6.80 NEUTRAL लक्ष्य ₹4100</t>
+        </is>
+      </c>
+      <c r="I1663" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1663" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1664" t="n">
+        <v>1757.6</v>
+      </c>
+      <c r="E1664" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G1664" t="inlineStr"/>
+      <c r="H1664" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Adani Ports
+1768.00
+OUTPERFORM
+लक्ष्य ₹1860 से बढ़ाकर ₹2100</t>
+        </is>
+      </c>
+      <c r="I1664" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1664" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1562"/>
+  <autoFilter ref="A1:J1664"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1664</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1756</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1664"/>
+  <dimension ref="A1:J1756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -66080,7 +66080,6 @@
       <c r="E1563" t="n">
         <v>3500</v>
       </c>
-      <c r="G1563" t="inlineStr"/>
       <c r="H1563" t="inlineStr">
         <is>
           <t>Caplin Point खरीदें PRICE 2733.70 TARGET 3500 DURATION 6-12 महीने</t>
@@ -66119,7 +66118,6 @@
       <c r="E1564" t="n">
         <v>350</v>
       </c>
-      <c r="G1564" t="inlineStr"/>
       <c r="H1564" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -66158,7 +66156,6 @@
       <c r="E1565" t="n">
         <v>450</v>
       </c>
-      <c r="G1565" t="inlineStr"/>
       <c r="H1565" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -66197,7 +66194,6 @@
       <c r="E1566" t="n">
         <v>600</v>
       </c>
-      <c r="G1566" t="inlineStr"/>
       <c r="H1566" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -66239,7 +66235,6 @@
       <c r="F1567" t="n">
         <v>270</v>
       </c>
-      <c r="G1567" t="inlineStr"/>
       <c r="H1567" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय Genesys Intl खरीदें STOP LOSS 270 TARGET 400 DURATION 4-8 महीने Genesys Intl 311.66</t>
@@ -66281,7 +66276,6 @@
       <c r="F1568" t="n">
         <v>300</v>
       </c>
-      <c r="G1568" t="inlineStr"/>
       <c r="H1568" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Ramco Ind @ 314 खरीदें STOP LOSS 300 TARGET 355/360 DURATION 4-8 महीने Ramco Ind 315.90</t>
@@ -66320,7 +66314,6 @@
       <c r="E1569" t="n">
         <v>1220</v>
       </c>
-      <c r="G1569" t="inlineStr"/>
       <c r="H1569" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -66367,7 +66360,6 @@
       <c r="F1570" t="n">
         <v>1500</v>
       </c>
-      <c r="G1570" t="inlineStr"/>
       <c r="H1570" t="inlineStr">
         <is>
           <t>Tech Mahindra 1544.60 18.80 BUY TGT 1580 SL 1500</t>
@@ -66406,7 +66398,6 @@
       <c r="E1571" t="n">
         <v>1870</v>
       </c>
-      <c r="G1571" t="inlineStr"/>
       <c r="H1571" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel 1846.80 BUY TGT 1870</t>
@@ -66439,14 +66430,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1572" t="inlineStr"/>
       <c r="E1572" t="n">
         <v>185</v>
       </c>
       <c r="F1572" t="n">
         <v>169</v>
       </c>
-      <c r="G1572" t="inlineStr"/>
       <c r="H1572" t="inlineStr">
         <is>
           <t>Pine Labs 191.50 18.59% BUY TGT 185 SL 169</t>
@@ -66488,7 +66477,6 @@
       <c r="F1573" t="n">
         <v>1133</v>
       </c>
-      <c r="G1573" t="inlineStr"/>
       <c r="H1573" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर
@@ -66535,7 +66523,6 @@
       <c r="F1574" t="n">
         <v>1833</v>
       </c>
-      <c r="G1574" t="inlineStr"/>
       <c r="H1574" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर
@@ -66579,7 +66566,6 @@
       <c r="E1575" t="n">
         <v>3950</v>
       </c>
-      <c r="G1575" t="inlineStr"/>
       <c r="H1575" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Ajanta Ph @ 3470 खरीदें STOP LOSS -- TARGET 3950 DURATION 9-12 महीने Ajanta Ph 3490.00 30.00</t>
@@ -66621,7 +66607,6 @@
       <c r="F1576" t="n">
         <v>940</v>
       </c>
-      <c r="G1576" t="inlineStr"/>
       <c r="H1576" t="inlineStr">
         <is>
           <t>Asahi India Glass खरीदें PRICE 981.00 TARGET 1100/1150 STOP LOSS 940</t>
@@ -66660,7 +66645,6 @@
       <c r="E1577" t="n">
         <v>3950</v>
       </c>
-      <c r="G1577" t="inlineStr"/>
       <c r="H1577" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCK Ajanta Ph @ 3470 खरीदें STOP LOSS TARGET 3950 DURATION 9-12 महीने</t>
@@ -66699,7 +66683,6 @@
       <c r="E1578" t="n">
         <v>1060</v>
       </c>
-      <c r="G1578" t="inlineStr"/>
       <c r="H1578" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -66743,7 +66726,6 @@
       <c r="E1579" t="n">
         <v>1220</v>
       </c>
-      <c r="G1579" t="inlineStr"/>
       <c r="H1579" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -66790,7 +66772,6 @@
       <c r="F1580" t="n">
         <v>1388</v>
       </c>
-      <c r="G1580" t="inlineStr"/>
       <c r="H1580" t="inlineStr">
         <is>
           <t>Tech Mahindra 1543.00 BUY TGT 1588 SL 1388</t>
@@ -66832,7 +66813,6 @@
       <c r="F1581" t="n">
         <v>1500</v>
       </c>
-      <c r="G1581" t="inlineStr"/>
       <c r="H1581" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट
@@ -66876,7 +66856,6 @@
       <c r="E1582" t="n">
         <v>1580</v>
       </c>
-      <c r="G1582" t="inlineStr"/>
       <c r="H1582" t="inlineStr">
         <is>
           <t>Tech Mahindra 1543.40 17.60 BUY TGT 1580</t>
@@ -66915,7 +66894,6 @@
       <c r="E1583" t="n">
         <v>1870</v>
       </c>
-      <c r="G1583" t="inlineStr"/>
       <c r="H1583" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel 1848.20 9.20 BUY TGT 1870 SL --</t>
@@ -66948,14 +66926,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1584" t="inlineStr"/>
       <c r="E1584" t="n">
         <v>185</v>
       </c>
       <c r="F1584" t="n">
         <v>169</v>
       </c>
-      <c r="G1584" t="inlineStr"/>
       <c r="H1584" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Pine Labs 185.25 12.08 BUY TGT 185 SL 169</t>
@@ -66997,7 +66973,6 @@
       <c r="F1585" t="n">
         <v>1133</v>
       </c>
-      <c r="G1585" t="inlineStr"/>
       <c r="H1585" t="inlineStr">
         <is>
           <t>Dr Reddy's Fut 1142.90 BUY TGT 1156 SL 1133</t>
@@ -67039,7 +67014,6 @@
       <c r="F1586" t="n">
         <v>1833</v>
       </c>
-      <c r="G1586" t="inlineStr"/>
       <c r="H1586" t="inlineStr">
         <is>
           <t>BTST BUY TODAY Bharti Airtel Fut 1851.50 11.10 BUY TGT 1870 SL 1833</t>
@@ -67081,7 +67055,6 @@
       <c r="F1587" t="n">
         <v>160</v>
       </c>
-      <c r="G1587" t="inlineStr"/>
       <c r="H1587" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय Pine Labs खरीदें STOP LOSS 160 TARGET 240/250 DURATION 9-12 महीने Pine Labs 184.25</t>
@@ -67123,7 +67096,6 @@
       <c r="F1588" t="n">
         <v>160</v>
       </c>
-      <c r="G1588" t="inlineStr"/>
       <c r="H1588" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय Pine Labs खरीदें STOP LOSS 160 TARGET 240/250 DURATION 9-12 महीने Pine Labs 184.25</t>
@@ -67162,7 +67134,6 @@
       <c r="E1589" t="n">
         <v>450</v>
       </c>
-      <c r="G1589" t="inlineStr"/>
       <c r="H1589" t="inlineStr">
         <is>
           <t>Steel Strip Wheels खरीदें PRICE 371.00 TARGET 450 STOP LOSS --</t>
@@ -67201,7 +67172,6 @@
       <c r="E1590" t="n">
         <v>450</v>
       </c>
-      <c r="G1590" t="inlineStr"/>
       <c r="H1590" t="inlineStr">
         <is>
           <t>10 की कमाई
@@ -67248,7 +67218,6 @@
       <c r="F1591" t="n">
         <v>390</v>
       </c>
-      <c r="G1591" t="inlineStr"/>
       <c r="H1591" t="inlineStr">
         <is>
           <t>जय ठक्कर की राय NIFTY BANK 56500 की कॉल @ 506/470 खरीदें STOP LOSS 390 TARGET 600/650 Nifty Bank 55905.30</t>
@@ -67290,7 +67259,6 @@
       <c r="F1592" t="n">
         <v>390</v>
       </c>
-      <c r="G1592" t="inlineStr"/>
       <c r="H1592" t="inlineStr">
         <is>
           <t>जय ठक्कर की राय NIFTY BANK 56500 की कॉल @ 506/470 खरीदें STOP LOSS 390 TARGET 600/650 Nifty Bank 55905.30</t>
@@ -67375,7 +67343,6 @@
       <c r="E1594" t="n">
         <v>600</v>
       </c>
-      <c r="G1594" t="inlineStr"/>
       <c r="H1594" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -67408,11 +67375,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1595" t="inlineStr"/>
       <c r="E1595" t="n">
         <v>6.55</v>
       </c>
-      <c r="G1595" t="inlineStr"/>
       <c r="H1595" t="inlineStr">
         <is>
           <t>Vodafone Idea 15.03 INVESTMENT PICK 6.55 28/08/2025 RECO PRICE RETURN TILL NOW 8.48 129.47%</t>
@@ -67445,11 +67410,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1596" t="inlineStr"/>
       <c r="E1596" t="n">
         <v>15.03</v>
       </c>
-      <c r="G1596" t="inlineStr"/>
       <c r="H1596" t="inlineStr">
         <is>
           <t>Vodafone Idea 15.03 INVESTMENT PICK 6.55 28/08/2025 RECO PRICE RETURN TILL NOW 8.48 129.47%</t>
@@ -67488,7 +67451,6 @@
       <c r="E1597" t="n">
         <v>600</v>
       </c>
-      <c r="G1597" t="inlineStr"/>
       <c r="H1597" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -67527,7 +67489,6 @@
       <c r="E1598" t="n">
         <v>350</v>
       </c>
-      <c r="G1598" t="inlineStr"/>
       <c r="H1598" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -67566,7 +67527,6 @@
       <c r="E1599" t="n">
         <v>450</v>
       </c>
-      <c r="G1599" t="inlineStr"/>
       <c r="H1599" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -67789,7 +67749,6 @@
       <c r="E1604" t="n">
         <v>1220</v>
       </c>
-      <c r="G1604" t="inlineStr"/>
       <c r="H1604" t="inlineStr">
         <is>
           <t>Max Healthcare खरीदें PRICE 1026.50 TARGET 1060/1220 STOP LOSS --</t>
@@ -67828,7 +67787,6 @@
       <c r="E1605" t="n">
         <v>1060</v>
       </c>
-      <c r="G1605" t="inlineStr"/>
       <c r="H1605" t="inlineStr">
         <is>
           <t>Max Healthcare खरीदें PRICE 1026.00 TARGET 1060/1220 STOP LOSS --</t>
@@ -67870,7 +67828,6 @@
       <c r="F1606" t="n">
         <v>1133</v>
       </c>
-      <c r="G1606" t="inlineStr"/>
       <c r="H1606" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर की राय
@@ -67917,7 +67874,6 @@
       <c r="F1607" t="n">
         <v>1133</v>
       </c>
-      <c r="G1607" t="inlineStr"/>
       <c r="H1607" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर की राय
@@ -67955,14 +67911,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1608" t="inlineStr"/>
       <c r="E1608" t="n">
         <v>1450.6</v>
       </c>
       <c r="F1608" t="n">
         <v>1133</v>
       </c>
-      <c r="G1608" t="inlineStr"/>
       <c r="H1608" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 3350, 4450, 6 3महीने-1133</t>
@@ -68001,7 +67955,6 @@
       <c r="E1609" t="n">
         <v>600</v>
       </c>
-      <c r="G1609" t="inlineStr"/>
       <c r="H1609" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -68034,11 +67987,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1610" t="inlineStr"/>
       <c r="E1610" t="n">
         <v>1220</v>
       </c>
-      <c r="G1610" t="inlineStr"/>
       <c r="H1610" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -68084,7 +68035,6 @@
       <c r="F1611" t="n">
         <v>1500</v>
       </c>
-      <c r="G1611" t="inlineStr"/>
       <c r="H1611" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट Tech Mahindra खरीदें PRICE 1537.30 TARGET 1580/1600 STOP LOSS 1500</t>
@@ -68126,7 +68076,6 @@
       <c r="F1612" t="n">
         <v>1500</v>
       </c>
-      <c r="G1612" t="inlineStr"/>
       <c r="H1612" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट Tech Mahindra खरीदें PRICE 1537.30 TARGET 1580/1600 STOP LOSS 1500</t>
@@ -68165,7 +68114,6 @@
       <c r="E1613" t="n">
         <v>2500</v>
       </c>
-      <c r="G1613" t="inlineStr"/>
       <c r="H1613" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel खरीदें PRICE 1843.70 TARGET 1870/2500 STOP LOSS --</t>
@@ -68204,7 +68152,6 @@
       <c r="E1614" t="n">
         <v>1870</v>
       </c>
-      <c r="G1614" t="inlineStr"/>
       <c r="H1614" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel खरीदें PRICE 1843.70 TARGET 1870/2500 STOP LOSS --</t>
@@ -68243,7 +68190,6 @@
       <c r="E1615" t="n">
         <v>2500</v>
       </c>
-      <c r="G1615" t="inlineStr"/>
       <c r="H1615" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel खरीदें PRICE 1842.90 TARGET 1870/2500 STOP LOSS --</t>
@@ -68282,7 +68228,6 @@
       <c r="E1616" t="n">
         <v>1870</v>
       </c>
-      <c r="G1616" t="inlineStr"/>
       <c r="H1616" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel खरीदें PRICE 1842.90 TARGET 1870/2500 STOP LOSS --</t>
@@ -68324,7 +68269,6 @@
       <c r="F1617" t="n">
         <v>169</v>
       </c>
-      <c r="G1617" t="inlineStr"/>
       <c r="H1617" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Pine Labs खरीदें PRICE 176.92 TARGET 185/190 STOP LOSS 169</t>
@@ -68366,7 +68310,6 @@
       <c r="F1618" t="n">
         <v>169</v>
       </c>
-      <c r="G1618" t="inlineStr"/>
       <c r="H1618" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Pine Labs खरीदें PRICE 176.92 TARGET 185/190 STOP LOSS 169</t>
@@ -68451,7 +68394,6 @@
       <c r="E1620" t="n">
         <v>2100</v>
       </c>
-      <c r="G1620" t="inlineStr"/>
       <c r="H1620" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -68494,7 +68436,6 @@
       <c r="E1621" t="n">
         <v>450</v>
       </c>
-      <c r="G1621" t="inlineStr"/>
       <c r="H1621" t="inlineStr">
         <is>
           <t>अनिल सिंधवी की सलाह Birlasoft BUY PRICE 276 TARGET 350, 450, 600 DURATION 1-3 साल</t>
@@ -68533,7 +68474,6 @@
       <c r="E1622" t="n">
         <v>350</v>
       </c>
-      <c r="G1622" t="inlineStr"/>
       <c r="H1622" t="inlineStr">
         <is>
           <t>अनिल सिंधवी की सलाह Birlasoft BUY PRICE 276 TARGET 350, 450, 600 DURATION 1-3 साल</t>
@@ -68572,7 +68512,6 @@
       <c r="E1623" t="n">
         <v>430</v>
       </c>
-      <c r="G1623" t="inlineStr"/>
       <c r="H1623" t="inlineStr">
         <is>
           <t>सुमीत बगडिया की राय Kotak Bank BUY PRICE 416.55 TARGET 430/450 STOP LOSS --</t>
@@ -68611,7 +68550,6 @@
       <c r="E1624" t="n">
         <v>450</v>
       </c>
-      <c r="G1624" t="inlineStr"/>
       <c r="H1624" t="inlineStr">
         <is>
           <t>सुमीत बगडिया की राय Kotak Bank BUY PRICE 416.55 TARGET 430/450 STOP LOSS --</t>
@@ -68653,7 +68591,6 @@
       <c r="F1625" t="n">
         <v>645</v>
       </c>
-      <c r="G1625" t="inlineStr"/>
       <c r="H1625" t="inlineStr">
         <is>
           <t>सच्चितानंद उतेकर की राय HBL ENGINEERING BUY PRICE 720.90 TARGET 980 STOP LOSS 645</t>
@@ -68695,7 +68632,6 @@
       <c r="F1626" t="n">
         <v>414</v>
       </c>
-      <c r="G1626" t="inlineStr"/>
       <c r="H1626" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर की राय Exide Ind BUY PRICE 420.85 TARGET 439/475 STOP LOSS 414</t>
@@ -69010,7 +68946,6 @@
       <c r="F1633" t="n">
         <v>406</v>
       </c>
-      <c r="G1633" t="inlineStr"/>
       <c r="H1633" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह AB Capital Futures SELL PRICE 402 TARGET 398, 394, 390 STOP LOSS 406</t>
@@ -69052,7 +68987,6 @@
       <c r="F1634" t="n">
         <v>406</v>
       </c>
-      <c r="G1634" t="inlineStr"/>
       <c r="H1634" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह AB Capital Futures SELL PRICE 402 TARGET 398, 394, 390 STOP LOSS 406</t>
@@ -69094,7 +69028,6 @@
       <c r="F1635" t="n">
         <v>314</v>
       </c>
-      <c r="G1635" t="inlineStr"/>
       <c r="H1635" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह L&amp;T Fin Futures SELL PRICE 312 TARGET 308, 305, 302 STOP LOSS 314</t>
@@ -69136,7 +69069,6 @@
       <c r="F1636" t="n">
         <v>314</v>
       </c>
-      <c r="G1636" t="inlineStr"/>
       <c r="H1636" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह L&amp;T Fin Futures SELL PRICE 312 TARGET 308, 305, 302 STOP LOSS 314</t>
@@ -69178,7 +69110,6 @@
       <c r="F1637" t="n">
         <v>168</v>
       </c>
-      <c r="G1637" t="inlineStr"/>
       <c r="H1637" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Ashok Leyland Fut SELL PRICE 166 TARGET 164, 162, 160 STOP LOSS 168</t>
@@ -69260,7 +69191,6 @@
       <c r="E1639" t="n">
         <v>4000</v>
       </c>
-      <c r="G1639" t="inlineStr"/>
       <c r="H1639" t="inlineStr">
         <is>
           <t>MY CHOICE REDINGTON B 4000 3</t>
@@ -69302,7 +69232,6 @@
       <c r="F1640" t="n">
         <v>2869</v>
       </c>
-      <c r="G1640" t="inlineStr"/>
       <c r="H1640" t="inlineStr">
         <is>
           <t>FUTURE MUTHOOT FINANCE FUT S 2785 2869</t>
@@ -69344,7 +69273,6 @@
       <c r="F1641" t="n">
         <v>740</v>
       </c>
-      <c r="G1641" t="inlineStr"/>
       <c r="H1641" t="inlineStr">
         <is>
           <t>TECHNO TD POWER B 805 740</t>
@@ -69386,7 +69314,6 @@
       <c r="F1642" t="n">
         <v>755</v>
       </c>
-      <c r="G1642" t="inlineStr"/>
       <c r="H1642" t="inlineStr">
         <is>
           <t>CASH KIMS B 801 755</t>
@@ -69428,7 +69355,6 @@
       <c r="F1643" t="n">
         <v>10</v>
       </c>
-      <c r="G1643" t="inlineStr"/>
       <c r="H1643" t="inlineStr">
         <is>
           <t>OPTION OIL INDIA 500 CE @ 15 B 24 10</t>
@@ -69470,7 +69396,6 @@
       <c r="F1644" t="n">
         <v>388</v>
       </c>
-      <c r="G1644" t="inlineStr"/>
       <c r="H1644" t="inlineStr">
         <is>
           <t>MY CHOICE Redington खरीदें PRICE 392.00 TARGET 400 STOP LOSS 388</t>
@@ -69512,7 +69437,6 @@
       <c r="F1645" t="n">
         <v>112</v>
       </c>
-      <c r="G1645" t="inlineStr"/>
       <c r="H1645" t="inlineStr">
         <is>
           <t>MY CHOICE Texmaco Rail खरीदें PRICE 117.77 TARGET 122 STOP LOSS 112</t>
@@ -69554,7 +69478,6 @@
       <c r="F1646" t="n">
         <v>265</v>
       </c>
-      <c r="G1646" t="inlineStr"/>
       <c r="H1646" t="inlineStr">
         <is>
           <t>MY CHOICE Power Grid खरीदें PRICE 271.75 TARGET 280 STOP LOSS 265</t>
@@ -69596,7 +69519,6 @@
       <c r="F1647" t="n">
         <v>5001</v>
       </c>
-      <c r="G1647" t="inlineStr"/>
       <c r="H1647" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -69643,7 +69565,6 @@
       <c r="F1648" t="n">
         <v>849</v>
       </c>
-      <c r="G1648" t="inlineStr"/>
       <c r="H1648" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -69687,7 +69608,6 @@
       <c r="E1649" t="n">
         <v>1380</v>
       </c>
-      <c r="G1649" t="inlineStr"/>
       <c r="H1649" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK
@@ -69734,7 +69654,6 @@
       <c r="F1650" t="n">
         <v>105</v>
       </c>
-      <c r="G1650" t="inlineStr"/>
       <c r="H1650" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK TVS Supply Chain खरीदें PRICE 128.73 TARGET 175 STOP LOSS 105</t>
@@ -69776,7 +69695,6 @@
       <c r="F1651" t="n">
         <v>421</v>
       </c>
-      <c r="G1651" t="inlineStr"/>
       <c r="H1651" t="inlineStr">
         <is>
           <t>FUNDA PICK
@@ -69820,7 +69738,6 @@
       <c r="E1652" t="n">
         <v>360</v>
       </c>
-      <c r="G1652" t="inlineStr"/>
       <c r="H1652" t="inlineStr">
         <is>
           <t>पूजा के शेयर NTPC खरीदें PRICE 335.00 TARGET 360 DURATION 6 महीने</t>
@@ -69862,7 +69779,6 @@
       <c r="F1653" t="n">
         <v>355</v>
       </c>
-      <c r="G1653" t="inlineStr"/>
       <c r="H1653" t="inlineStr">
         <is>
           <t>TECHNO PICK HPCL Fut बेचें PRICE 350.90 TARGET 340 STOP LOSS 355</t>
@@ -69904,7 +69820,6 @@
       <c r="F1654" t="n">
         <v>740</v>
       </c>
-      <c r="G1654" t="inlineStr"/>
       <c r="H1654" t="inlineStr">
         <is>
           <t>TECHNO PICK TD Power खरीदें PRICE 762.75 TARGET 805 STOP LOSS 740</t>
@@ -69946,7 +69861,6 @@
       <c r="F1655" t="n">
         <v>40</v>
       </c>
-      <c r="G1655" t="inlineStr"/>
       <c r="H1655" t="inlineStr">
         <is>
           <t>पूजा के शेयर KEI Industries 4600 की पुट @88.65 खरीदें STOP LOSS 40 TARGET 200 KEI Industries 4640.00 0.63%</t>
@@ -69985,7 +69899,6 @@
       <c r="E1656" t="n">
         <v>360</v>
       </c>
-      <c r="G1656" t="inlineStr"/>
       <c r="H1656" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Angel One 297.30 -1.75 NEUTRAL लक्ष्य ₹360</t>
@@ -70024,7 +69937,6 @@
       <c r="E1657" t="n">
         <v>1675</v>
       </c>
-      <c r="G1657" t="inlineStr"/>
       <c r="H1657" t="inlineStr">
         <is>
           <t>Cipla 1373.30 +10.20 OUTPERFORM लक्ष्य ₹1675</t>
@@ -70066,7 +69978,6 @@
       <c r="F1658" t="n">
         <v>171</v>
       </c>
-      <c r="G1658" t="inlineStr"/>
       <c r="H1658" t="inlineStr">
         <is>
           <t>Wipro Fut बेचें PRICE 164.77 TARGET 160/157 STOP LOSS 171 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
@@ -70108,7 +70019,6 @@
       <c r="F1659" t="n">
         <v>171</v>
       </c>
-      <c r="G1659" t="inlineStr"/>
       <c r="H1659" t="inlineStr">
         <is>
           <t>Wipro Fut बेचें PRICE 164.77 TARGET 160/157 STOP LOSS 171 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
@@ -70147,7 +70057,6 @@
       <c r="E1660" t="n">
         <v>1930</v>
       </c>
-      <c r="G1660" t="inlineStr"/>
       <c r="H1660" t="inlineStr">
         <is>
           <t>ICICI Lombard 1465.00 -9.00 NEUTRAL लक्ष्य ₹1930 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
@@ -70186,7 +70095,6 @@
       <c r="E1661" t="n">
         <v>1550</v>
       </c>
-      <c r="G1661" t="inlineStr"/>
       <c r="H1661" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Axis Bank 1246.00 +7.50 ACCUMULATE श्रीकांत चौहान कोटक सिक्योरिटीज लक्ष्य ₹1550</t>
@@ -70225,7 +70133,6 @@
       <c r="E1662" t="n">
         <v>2200</v>
       </c>
-      <c r="G1662" t="inlineStr"/>
       <c r="H1662" t="inlineStr">
         <is>
           <t>बर्नस्टीन Paytm 1739.00 -0.71% OUTPERFORM लक्ष्य ₹2200</t>
@@ -70264,7 +70171,6 @@
       <c r="E1663" t="n">
         <v>4100</v>
       </c>
-      <c r="G1663" t="inlineStr"/>
       <c r="H1663" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Thermax 3645.40 +6.80 NEUTRAL लक्ष्य ₹4100</t>
@@ -70303,7 +70209,6 @@
       <c r="E1664" t="n">
         <v>2100</v>
       </c>
-      <c r="G1664" t="inlineStr"/>
       <c r="H1664" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -70324,8 +70229,3793 @@
         </is>
       </c>
     </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:30:43</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr"/>
+      <c r="E1665" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1665" t="inlineStr"/>
+      <c r="H1665" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1665" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1665" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:30:43</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr"/>
+      <c r="E1666" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1666" t="inlineStr"/>
+      <c r="H1666" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1666" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1666" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:30:43</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr"/>
+      <c r="E1667" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1667" t="inlineStr"/>
+      <c r="H1667" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1667" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1667" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1668" t="n">
+        <v>2739</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G1668" t="inlineStr"/>
+      <c r="H1668" t="inlineStr">
+        <is>
+          <t>Caplin Point खरीदें PRICE 2733.70 TARGET 3500 DURATION 6-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1668" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1668" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1669" t="n">
+        <v>276.3</v>
+      </c>
+      <c r="E1669" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1669" t="inlineStr"/>
+      <c r="H1669" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1669" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1669" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1670" t="n">
+        <v>276.3</v>
+      </c>
+      <c r="E1670" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1670" t="inlineStr"/>
+      <c r="H1670" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1670" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1670" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1671" t="n">
+        <v>276.3</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1671" t="inlineStr"/>
+      <c r="H1671" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1671" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1671" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>GENESYS</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1672" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>400</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>270</v>
+      </c>
+      <c r="G1672" t="inlineStr"/>
+      <c r="H1672" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय Genesys Intl खरीदें STOP LOSS 270 TARGET 400 DURATION 4-8 महीने Genesys Intl 311.66</t>
+        </is>
+      </c>
+      <c r="I1672" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1672" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:22:00</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>RAMCOIND</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1673" t="n">
+        <v>316</v>
+      </c>
+      <c r="E1673" t="n">
+        <v>360</v>
+      </c>
+      <c r="F1673" t="n">
+        <v>300</v>
+      </c>
+      <c r="G1673" t="inlineStr"/>
+      <c r="H1673" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Ramco Ind @ 314 खरीदें STOP LOSS 300 TARGET 355/360 DURATION 4-8 महीने Ramco Ind 315.90</t>
+        </is>
+      </c>
+      <c r="I1673" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1673" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:22:00</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>SIKA</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1674" t="n">
+        <v>1092</v>
+      </c>
+      <c r="E1674" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1674" t="inlineStr"/>
+      <c r="H1674" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+Sika Interplant
+1095.00 70.15
+BUY
+TGT 1220
+SL --</t>
+        </is>
+      </c>
+      <c r="I1674" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1674" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:22:00</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1675" t="n">
+        <v>1544</v>
+      </c>
+      <c r="E1675" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G1675" t="inlineStr"/>
+      <c r="H1675" t="inlineStr">
+        <is>
+          <t>Tech Mahindra 1544.60 18.80 BUY TGT 1580 SL 1500</t>
+        </is>
+      </c>
+      <c r="I1675" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1675" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:21:00</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1676" t="n">
+        <v>1847.1</v>
+      </c>
+      <c r="E1676" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G1676" t="inlineStr"/>
+      <c r="H1676" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel 1846.80 BUY TGT 1870</t>
+        </is>
+      </c>
+      <c r="I1676" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1676" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:20:49</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr"/>
+      <c r="E1677" t="n">
+        <v>185</v>
+      </c>
+      <c r="F1677" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1677" t="inlineStr"/>
+      <c r="H1677" t="inlineStr">
+        <is>
+          <t>Pine Labs 191.50 18.59% BUY TGT 185 SL 169</t>
+        </is>
+      </c>
+      <c r="I1677" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1677" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:21:00</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1678" t="n">
+        <v>1147</v>
+      </c>
+      <c r="E1678" t="n">
+        <v>1156</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G1678" t="inlineStr"/>
+      <c r="H1678" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर
+Dr Reddy's Fut
+1145.00 0.76%
+BUY
+TGT 1156
+SL 1133</t>
+        </is>
+      </c>
+      <c r="I1678" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1678" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:21:00</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>BHARTIARTL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1679" t="n">
+        <v>1849.3</v>
+      </c>
+      <c r="E1679" t="n">
+        <v>1870</v>
+      </c>
+      <c r="F1679" t="n">
+        <v>1833</v>
+      </c>
+      <c r="G1679" t="inlineStr"/>
+      <c r="H1679" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर
+Bharti Airtel Fut
+1849.00 0.47%
+BUY
+TGT 1870
+SL 1833</t>
+        </is>
+      </c>
+      <c r="I1679" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1679" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:20:00</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>AJANTPHARM</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1680" t="n">
+        <v>3491</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>3950</v>
+      </c>
+      <c r="G1680" t="inlineStr"/>
+      <c r="H1680" t="inlineStr">
+        <is>
+          <t>संदीप जैन की राय Ajanta Ph @ 3470 खरीदें STOP LOSS -- TARGET 3950 DURATION 9-12 महीने Ajanta Ph 3490.00 30.00</t>
+        </is>
+      </c>
+      <c r="I1680" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1680" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:13:00</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>ASAHIINDIA</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1681" t="n">
+        <v>980</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>940</v>
+      </c>
+      <c r="G1681" t="inlineStr"/>
+      <c r="H1681" t="inlineStr">
+        <is>
+          <t>Asahi India Glass खरीदें PRICE 981.00 TARGET 1100/1150 STOP LOSS 940</t>
+        </is>
+      </c>
+      <c r="I1681" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1681" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>AJANTPHARM</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1682" t="n">
+        <v>3490.9</v>
+      </c>
+      <c r="E1682" t="n">
+        <v>3950</v>
+      </c>
+      <c r="G1682" t="inlineStr"/>
+      <c r="H1682" t="inlineStr">
+        <is>
+          <t>LONG MIDCAP STOCK Ajanta Ph @ 3470 खरीदें STOP LOSS TARGET 3950 DURATION 9-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1682" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1682" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1683" t="n">
+        <v>1028.6</v>
+      </c>
+      <c r="E1683" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G1683" t="inlineStr"/>
+      <c r="H1683" t="inlineStr">
+        <is>
+          <t>SUPER SID
+Max Healthcare
+1028.90 0.93%
+BUY
+TGT 1060
+SL --</t>
+        </is>
+      </c>
+      <c r="I1683" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1683" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>SIKA</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1684" t="n">
+        <v>1094.5</v>
+      </c>
+      <c r="E1684" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1684" t="inlineStr"/>
+      <c r="H1684" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+Sika Interplant
+1091.50 66.65
+BUY
+TGT 1220
+SL --</t>
+        </is>
+      </c>
+      <c r="I1684" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1684" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1685" t="n">
+        <v>1543</v>
+      </c>
+      <c r="E1685" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F1685" t="n">
+        <v>1388</v>
+      </c>
+      <c r="G1685" t="inlineStr"/>
+      <c r="H1685" t="inlineStr">
+        <is>
+          <t>Tech Mahindra 1543.00 BUY TGT 1588 SL 1388</t>
+        </is>
+      </c>
+      <c r="I1685" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1685" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1686" t="n">
+        <v>1543</v>
+      </c>
+      <c r="E1686" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G1686" t="inlineStr"/>
+      <c r="H1686" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट
+Tech Mahindra
+1543.40 1.15%
+BUY
+TGT 1580
+SL 1500</t>
+        </is>
+      </c>
+      <c r="I1686" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1686" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1687" t="n">
+        <v>1543</v>
+      </c>
+      <c r="E1687" t="n">
+        <v>1580</v>
+      </c>
+      <c r="G1687" t="inlineStr"/>
+      <c r="H1687" t="inlineStr">
+        <is>
+          <t>Tech Mahindra 1543.40 17.60 BUY TGT 1580</t>
+        </is>
+      </c>
+      <c r="I1687" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1687" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:09:00</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1688" t="n">
+        <v>1848</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G1688" t="inlineStr"/>
+      <c r="H1688" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel 1848.20 9.20 BUY TGT 1870 SL --</t>
+        </is>
+      </c>
+      <c r="I1688" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1688" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:08:53</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr"/>
+      <c r="E1689" t="n">
+        <v>185</v>
+      </c>
+      <c r="F1689" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1689" t="inlineStr"/>
+      <c r="H1689" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Pine Labs 185.25 12.08 BUY TGT 185 SL 169</t>
+        </is>
+      </c>
+      <c r="I1689" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1689" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:09:00</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1690" t="n">
+        <v>1143.6</v>
+      </c>
+      <c r="E1690" t="n">
+        <v>1156</v>
+      </c>
+      <c r="F1690" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G1690" t="inlineStr"/>
+      <c r="H1690" t="inlineStr">
+        <is>
+          <t>Dr Reddy's Fut 1142.90 BUY TGT 1156 SL 1133</t>
+        </is>
+      </c>
+      <c r="I1690" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1690" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:09:00</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>BHARTIARTL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1691" t="n">
+        <v>1851.3</v>
+      </c>
+      <c r="E1691" t="n">
+        <v>1870</v>
+      </c>
+      <c r="F1691" t="n">
+        <v>1833</v>
+      </c>
+      <c r="G1691" t="inlineStr"/>
+      <c r="H1691" t="inlineStr">
+        <is>
+          <t>BTST BUY TODAY Bharti Airtel Fut 1851.50 11.10 BUY TGT 1870 SL 1833</t>
+        </is>
+      </c>
+      <c r="I1691" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1691" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:08:00</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1692" t="n">
+        <v>184.35</v>
+      </c>
+      <c r="E1692" t="n">
+        <v>240</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1692" t="inlineStr"/>
+      <c r="H1692" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय Pine Labs खरीदें STOP LOSS 160 TARGET 240/250 DURATION 9-12 महीने Pine Labs 184.25</t>
+        </is>
+      </c>
+      <c r="I1692" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1692" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:08:00</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1693" t="n">
+        <v>184.35</v>
+      </c>
+      <c r="E1693" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1693" t="n">
+        <v>160</v>
+      </c>
+      <c r="G1693" t="inlineStr"/>
+      <c r="H1693" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय Pine Labs खरीदें STOP LOSS 160 TARGET 240/250 DURATION 9-12 महीने Pine Labs 184.25</t>
+        </is>
+      </c>
+      <c r="I1693" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1693" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:04:00</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>SSWL</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1694" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="E1694" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1694" t="inlineStr"/>
+      <c r="H1694" t="inlineStr">
+        <is>
+          <t>Steel Strip Wheels खरीदें PRICE 371.00 TARGET 450 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1694" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1694" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:04:00</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>SSWL</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1695" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="E1695" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1695" t="inlineStr"/>
+      <c r="H1695" t="inlineStr">
+        <is>
+          <t>10 की कमाई
+Steel Strip Wheels
+खरीदें
+PRICE → 370.95
+TARGET → 450
+STOP LOSS → --</t>
+        </is>
+      </c>
+      <c r="I1695" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1695" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>BANKNIFTY5650029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1696" t="n">
+        <v>505.3</v>
+      </c>
+      <c r="E1696" t="n">
+        <v>600</v>
+      </c>
+      <c r="F1696" t="n">
+        <v>390</v>
+      </c>
+      <c r="G1696" t="inlineStr"/>
+      <c r="H1696" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय NIFTY BANK 56500 की कॉल @ 506/470 खरीदें STOP LOSS 390 TARGET 600/650 Nifty Bank 55905.30</t>
+        </is>
+      </c>
+      <c r="I1696" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1696" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>2026-09-11 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>BANKNIFTY5650029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1697" t="n">
+        <v>505.3</v>
+      </c>
+      <c r="E1697" t="n">
+        <v>650</v>
+      </c>
+      <c r="F1697" t="n">
+        <v>390</v>
+      </c>
+      <c r="G1697" t="inlineStr"/>
+      <c r="H1697" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय NIFTY BANK 56500 की कॉल @ 506/470 खरीदें STOP LOSS 390 TARGET 600/650 Nifty Bank 55905.30</t>
+        </is>
+      </c>
+      <c r="I1697" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1697" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:57:00</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1698" t="n">
+        <v>274.8</v>
+      </c>
+      <c r="E1698" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1698" t="inlineStr"/>
+      <c r="H1698" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1698" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1698" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:52:20</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr"/>
+      <c r="E1699" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="G1699" t="inlineStr"/>
+      <c r="H1699" t="inlineStr">
+        <is>
+          <t>Vodafone Idea 15.03 INVESTMENT PICK 6.55 28/08/2025 RECO PRICE RETURN TILL NOW 8.48 129.47%</t>
+        </is>
+      </c>
+      <c r="I1699" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1699" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:51:59</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr"/>
+      <c r="E1700" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="G1700" t="inlineStr"/>
+      <c r="H1700" t="inlineStr">
+        <is>
+          <t>Vodafone Idea 15.03 INVESTMENT PICK 6.55 28/08/2025 RECO PRICE RETURN TILL NOW 8.48 129.47%</t>
+        </is>
+      </c>
+      <c r="I1700" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1700" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1701" t="n">
+        <v>275.75</v>
+      </c>
+      <c r="E1701" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1701" t="inlineStr"/>
+      <c r="H1701" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1701" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1701" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1702" t="n">
+        <v>275.75</v>
+      </c>
+      <c r="E1702" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1702" t="inlineStr"/>
+      <c r="H1702" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1702" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1702" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1703" t="n">
+        <v>275.75</v>
+      </c>
+      <c r="E1703" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1703" t="inlineStr"/>
+      <c r="H1703" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1703" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1703" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1704" t="n">
+        <v>1027.1</v>
+      </c>
+      <c r="E1704" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1704" t="inlineStr"/>
+      <c r="H1704" t="inlineStr">
+        <is>
+          <t>Max Healthcare खरीदें PRICE 1026.50 TARGET 1060/1220 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1704" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1704" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1705" t="n">
+        <v>1027.1</v>
+      </c>
+      <c r="E1705" t="n">
+        <v>1060</v>
+      </c>
+      <c r="G1705" t="inlineStr"/>
+      <c r="H1705" t="inlineStr">
+        <is>
+          <t>Max Healthcare खरीदें PRICE 1026.00 TARGET 1060/1220 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1705" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1705" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:41:00</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1706" t="n">
+        <v>1143</v>
+      </c>
+      <c r="E1706" t="n">
+        <v>1180</v>
+      </c>
+      <c r="F1706" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G1706" t="inlineStr"/>
+      <c r="H1706" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर की राय
+Dr Reddy's Fut
+खरीदें
+PRICE ▶ 1143.50
+TARGET ▶ 1156/1180
+STOP LOSS ▶ 1133</t>
+        </is>
+      </c>
+      <c r="I1706" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1706" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:41:00</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1707" t="n">
+        <v>1143</v>
+      </c>
+      <c r="E1707" t="n">
+        <v>1156</v>
+      </c>
+      <c r="F1707" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G1707" t="inlineStr"/>
+      <c r="H1707" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर की राय
+Dr Reddy's Fut
+खरीदें
+PRICE ▶ 1143.50
+TARGET ▶ 1156/1180
+STOP LOSS ▶ 1133</t>
+        </is>
+      </c>
+      <c r="I1707" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1707" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:39:51</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr"/>
+      <c r="E1708" t="n">
+        <v>1450.6</v>
+      </c>
+      <c r="F1708" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G1708" t="inlineStr"/>
+      <c r="H1708" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 3350, 4450, 6 3महीने-1133</t>
+        </is>
+      </c>
+      <c r="I1708" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1708" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:40:00</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1709" t="n">
+        <v>276.45</v>
+      </c>
+      <c r="E1709" t="n">
+        <v>600</v>
+      </c>
+      <c r="G1709" t="inlineStr"/>
+      <c r="H1709" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1709" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1709" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:39:04</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>SIKA</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr"/>
+      <c r="E1710" t="n">
+        <v>1220</v>
+      </c>
+      <c r="G1710" t="inlineStr"/>
+      <c r="H1710" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+SIKA INTERPLANT @ 996
+खरीदें
+STOP LOSS --
+TARGET 1220</t>
+        </is>
+      </c>
+      <c r="I1710" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1710" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:29:00</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1711" t="n">
+        <v>1537.5</v>
+      </c>
+      <c r="E1711" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F1711" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G1711" t="inlineStr"/>
+      <c r="H1711" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट Tech Mahindra खरीदें PRICE 1537.30 TARGET 1580/1600 STOP LOSS 1500</t>
+        </is>
+      </c>
+      <c r="I1711" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1711" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:29:00</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1712" t="n">
+        <v>1537.5</v>
+      </c>
+      <c r="E1712" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F1712" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G1712" t="inlineStr"/>
+      <c r="H1712" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट Tech Mahindra खरीदें PRICE 1537.30 TARGET 1580/1600 STOP LOSS 1500</t>
+        </is>
+      </c>
+      <c r="I1712" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1712" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1713" t="n">
+        <v>1844.5</v>
+      </c>
+      <c r="E1713" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1713" t="inlineStr"/>
+      <c r="H1713" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel खरीदें PRICE 1843.70 TARGET 1870/2500 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1713" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1713" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1714" t="n">
+        <v>1844.5</v>
+      </c>
+      <c r="E1714" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G1714" t="inlineStr"/>
+      <c r="H1714" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel खरीदें PRICE 1843.70 TARGET 1870/2500 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1714" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1714" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1715" t="n">
+        <v>1843.5</v>
+      </c>
+      <c r="E1715" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G1715" t="inlineStr"/>
+      <c r="H1715" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel खरीदें PRICE 1842.90 TARGET 1870/2500 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1715" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1715" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>BHARTIARTL</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1716" t="n">
+        <v>1844.6</v>
+      </c>
+      <c r="E1716" t="n">
+        <v>1870</v>
+      </c>
+      <c r="G1716" t="inlineStr"/>
+      <c r="H1716" t="inlineStr">
+        <is>
+          <t>SUPER SID Bharti Airtel खरीदें PRICE 1842.90 TARGET 1870/2500 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1716" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1716" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1717" t="n">
+        <v>175.39</v>
+      </c>
+      <c r="E1717" t="n">
+        <v>185</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1717" t="inlineStr"/>
+      <c r="H1717" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Pine Labs खरीदें PRICE 176.92 TARGET 185/190 STOP LOSS 169</t>
+        </is>
+      </c>
+      <c r="I1717" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1717" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:24:00</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1718" t="n">
+        <v>175.39</v>
+      </c>
+      <c r="E1718" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1718" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1718" t="inlineStr"/>
+      <c r="H1718" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Pine Labs खरीदें PRICE 176.92 TARGET 185/190 STOP LOSS 169</t>
+        </is>
+      </c>
+      <c r="I1718" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1718" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1719" t="n">
+        <v>1755</v>
+      </c>
+      <c r="E1719" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G1719" t="inlineStr"/>
+      <c r="H1719" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Adani Ports
+1750.00
+OUTPERFORM
+लक्ष्य ₹1860 से बढ़ाकर ₹2100</t>
+        </is>
+      </c>
+      <c r="I1719" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1719" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1720" t="n">
+        <v>281</v>
+      </c>
+      <c r="E1720" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1720" t="inlineStr"/>
+      <c r="H1720" t="inlineStr">
+        <is>
+          <t>अनिल सिंधवी की सलाह Birlasoft BUY PRICE 276 TARGET 350, 450, 600 DURATION 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1720" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1720" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1721" t="n">
+        <v>281</v>
+      </c>
+      <c r="E1721" t="n">
+        <v>350</v>
+      </c>
+      <c r="G1721" t="inlineStr"/>
+      <c r="H1721" t="inlineStr">
+        <is>
+          <t>अनिल सिंधवी की सलाह Birlasoft BUY PRICE 276 TARGET 350, 450, 600 DURATION 1-3 साल</t>
+        </is>
+      </c>
+      <c r="I1721" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1721" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1722" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="E1722" t="n">
+        <v>430</v>
+      </c>
+      <c r="G1722" t="inlineStr"/>
+      <c r="H1722" t="inlineStr">
+        <is>
+          <t>सुमीत बगडिया की राय Kotak Bank BUY PRICE 416.55 TARGET 430/450 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1722" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1722" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1723" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="E1723" t="n">
+        <v>450</v>
+      </c>
+      <c r="G1723" t="inlineStr"/>
+      <c r="H1723" t="inlineStr">
+        <is>
+          <t>सुमीत बगडिया की राय Kotak Bank BUY PRICE 416.55 TARGET 430/450 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1723" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1723" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1724" t="n">
+        <v>718</v>
+      </c>
+      <c r="E1724" t="n">
+        <v>980</v>
+      </c>
+      <c r="F1724" t="n">
+        <v>645</v>
+      </c>
+      <c r="G1724" t="inlineStr"/>
+      <c r="H1724" t="inlineStr">
+        <is>
+          <t>सच्चितानंद उतेकर की राय HBL ENGINEERING BUY PRICE 720.90 TARGET 980 STOP LOSS 645</t>
+        </is>
+      </c>
+      <c r="I1724" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1724" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1725" t="n">
+        <v>416</v>
+      </c>
+      <c r="E1725" t="n">
+        <v>475</v>
+      </c>
+      <c r="F1725" t="n">
+        <v>414</v>
+      </c>
+      <c r="G1725" t="inlineStr"/>
+      <c r="H1725" t="inlineStr">
+        <is>
+          <t>सच्चिदानंद उतेकर की राय Exide Ind BUY PRICE 420.85 TARGET 439/475 STOP LOSS 414</t>
+        </is>
+      </c>
+      <c r="I1725" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1725" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>ABCAPITAL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1726" t="n">
+        <v>397.45</v>
+      </c>
+      <c r="E1726" t="n">
+        <v>394</v>
+      </c>
+      <c r="F1726" t="n">
+        <v>406</v>
+      </c>
+      <c r="G1726" t="inlineStr"/>
+      <c r="H1726" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह AB Capital Futures SELL PRICE 402 TARGET 398, 394, 390 STOP LOSS 406</t>
+        </is>
+      </c>
+      <c r="I1726" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1726" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>ABCAPITAL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1727" t="n">
+        <v>397.45</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>390</v>
+      </c>
+      <c r="F1727" t="n">
+        <v>406</v>
+      </c>
+      <c r="G1727" t="inlineStr"/>
+      <c r="H1727" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह AB Capital Futures SELL PRICE 402 TARGET 398, 394, 390 STOP LOSS 406</t>
+        </is>
+      </c>
+      <c r="I1727" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1727" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>LTF29SEP26</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1728" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="E1728" t="n">
+        <v>305</v>
+      </c>
+      <c r="F1728" t="n">
+        <v>314</v>
+      </c>
+      <c r="G1728" t="inlineStr"/>
+      <c r="H1728" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह L&amp;T Fin Futures SELL PRICE 312 TARGET 308, 305, 302 STOP LOSS 314</t>
+        </is>
+      </c>
+      <c r="I1728" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1728" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>LTF29SEP26</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1729" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>302</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>314</v>
+      </c>
+      <c r="G1729" t="inlineStr"/>
+      <c r="H1729" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह L&amp;T Fin Futures SELL PRICE 312 TARGET 308, 305, 302 STOP LOSS 314</t>
+        </is>
+      </c>
+      <c r="I1729" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1729" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>ASHOKLEY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1730" t="n">
+        <v>163.97</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1730" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1730" t="inlineStr"/>
+      <c r="H1730" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Ashok Leyland Fut SELL PRICE 166 TARGET 164, 162, 160 STOP LOSS 168</t>
+        </is>
+      </c>
+      <c r="I1730" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1730" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>REDINGTON</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1731" t="n">
+        <v>395.85</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G1731" t="inlineStr"/>
+      <c r="H1731" t="inlineStr">
+        <is>
+          <t>MY CHOICE REDINGTON B 4000 3</t>
+        </is>
+      </c>
+      <c r="I1731" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1731" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN29SEP26</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1732" t="n">
+        <v>2790</v>
+      </c>
+      <c r="E1732" t="n">
+        <v>2785</v>
+      </c>
+      <c r="F1732" t="n">
+        <v>2869</v>
+      </c>
+      <c r="G1732" t="inlineStr"/>
+      <c r="H1732" t="inlineStr">
+        <is>
+          <t>FUTURE MUTHOOT FINANCE FUT S 2785 2869</t>
+        </is>
+      </c>
+      <c r="I1732" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1732" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1733" t="n">
+        <v>760</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>805</v>
+      </c>
+      <c r="F1733" t="n">
+        <v>740</v>
+      </c>
+      <c r="G1733" t="inlineStr"/>
+      <c r="H1733" t="inlineStr">
+        <is>
+          <t>TECHNO TD POWER B 805 740</t>
+        </is>
+      </c>
+      <c r="I1733" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1733" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:04</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>KIMS</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1734" t="n">
+        <v>775.65</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>801</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>755</v>
+      </c>
+      <c r="G1734" t="inlineStr"/>
+      <c r="H1734" t="inlineStr">
+        <is>
+          <t>CASH KIMS B 801 755</t>
+        </is>
+      </c>
+      <c r="I1734" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1734" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>OIL50029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1735" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E1735" t="n">
+        <v>24</v>
+      </c>
+      <c r="F1735" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1735" t="inlineStr"/>
+      <c r="H1735" t="inlineStr">
+        <is>
+          <t>OPTION OIL INDIA 500 CE @ 15 B 24 10</t>
+        </is>
+      </c>
+      <c r="I1735" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1735" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>REDINGTON</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1736" t="n">
+        <v>395.85</v>
+      </c>
+      <c r="E1736" t="n">
+        <v>400</v>
+      </c>
+      <c r="F1736" t="n">
+        <v>388</v>
+      </c>
+      <c r="G1736" t="inlineStr"/>
+      <c r="H1736" t="inlineStr">
+        <is>
+          <t>MY CHOICE Redington खरीदें PRICE 392.00 TARGET 400 STOP LOSS 388</t>
+        </is>
+      </c>
+      <c r="I1736" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1736" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>TEXRAIL</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1737" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>122</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>112</v>
+      </c>
+      <c r="G1737" t="inlineStr"/>
+      <c r="H1737" t="inlineStr">
+        <is>
+          <t>MY CHOICE Texmaco Rail खरीदें PRICE 117.77 TARGET 122 STOP LOSS 112</t>
+        </is>
+      </c>
+      <c r="I1737" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1737" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1738" t="n">
+        <v>269.85</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>280</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>265</v>
+      </c>
+      <c r="G1738" t="inlineStr"/>
+      <c r="H1738" t="inlineStr">
+        <is>
+          <t>MY CHOICE Power Grid खरीदें PRICE 271.75 TARGET 280 STOP LOSS 265</t>
+        </is>
+      </c>
+      <c r="I1738" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1738" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1739" t="n">
+        <v>4885</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>4840</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>5001</v>
+      </c>
+      <c r="G1739" t="inlineStr"/>
+      <c r="H1739" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+Interglobe Aviation Fut
+बेचें
+PRICE → 4933.50
+TARGET → 4840
+STOP LOSS → 5001</t>
+        </is>
+      </c>
+      <c r="I1739" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1739" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>STLTECH-BE</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1740" t="n">
+        <v>860</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>880</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>849</v>
+      </c>
+      <c r="G1740" t="inlineStr"/>
+      <c r="H1740" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+Sterlite Tech
+खरीदें
+PRICE → 854.75
+TARGET → 880
+STOP LOSS → 849</t>
+        </is>
+      </c>
+      <c r="I1740" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1740" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1741" t="n">
+        <v>1237.9</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G1741" t="inlineStr"/>
+      <c r="H1741" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK
+Axis Bank
+खरीदें
+PRICE → 1246.00
+TARGET → 1380
+DURATION → 12 महीने</t>
+        </is>
+      </c>
+      <c r="I1741" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1741" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>TVSSCS</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1742" t="n">
+        <v>129.09</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>175</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>105</v>
+      </c>
+      <c r="G1742" t="inlineStr"/>
+      <c r="H1742" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK TVS Supply Chain खरीदें PRICE 128.73 TARGET 175 STOP LOSS 105</t>
+        </is>
+      </c>
+      <c r="I1742" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1742" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1743" t="n">
+        <v>427</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>440</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>421</v>
+      </c>
+      <c r="G1743" t="inlineStr"/>
+      <c r="H1743" t="inlineStr">
+        <is>
+          <t>FUNDA PICK
+BHEL
+खरीदें
+PRICE ▶ 429.50
+TARGET ▶ 440
+STOP LOSS ▶ 421</t>
+        </is>
+      </c>
+      <c r="I1743" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1743" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1744" t="n">
+        <v>333</v>
+      </c>
+      <c r="E1744" t="n">
+        <v>360</v>
+      </c>
+      <c r="G1744" t="inlineStr"/>
+      <c r="H1744" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर NTPC खरीदें PRICE 335.00 TARGET 360 DURATION 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1744" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1744" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>HINDPETRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1745" t="n">
+        <v>346.95</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>340</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1745" t="inlineStr"/>
+      <c r="H1745" t="inlineStr">
+        <is>
+          <t>TECHNO PICK HPCL Fut बेचें PRICE 350.90 TARGET 340 STOP LOSS 355</t>
+        </is>
+      </c>
+      <c r="I1745" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1745" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1746" t="n">
+        <v>760.75</v>
+      </c>
+      <c r="E1746" t="n">
+        <v>805</v>
+      </c>
+      <c r="F1746" t="n">
+        <v>740</v>
+      </c>
+      <c r="G1746" t="inlineStr"/>
+      <c r="H1746" t="inlineStr">
+        <is>
+          <t>TECHNO PICK TD Power खरीदें PRICE 762.75 TARGET 805 STOP LOSS 740</t>
+        </is>
+      </c>
+      <c r="I1746" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1746" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:01</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>KEI460029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1747" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>200</v>
+      </c>
+      <c r="F1747" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1747" t="inlineStr"/>
+      <c r="H1747" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर KEI Industries 4600 की पुट @88.65 खरीदें STOP LOSS 40 TARGET 200 KEI Industries 4640.00 0.63%</t>
+        </is>
+      </c>
+      <c r="I1747" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J1747" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1748" t="n">
+        <v>295</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>360</v>
+      </c>
+      <c r="G1748" t="inlineStr"/>
+      <c r="H1748" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Angel One 297.30 -1.75 NEUTRAL लक्ष्य ₹360</t>
+        </is>
+      </c>
+      <c r="I1748" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1748" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>CIPLA</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1749" t="n">
+        <v>1373</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G1749" t="inlineStr"/>
+      <c r="H1749" t="inlineStr">
+        <is>
+          <t>Cipla 1373.30 +10.20 OUTPERFORM लक्ष्य ₹1675</t>
+        </is>
+      </c>
+      <c r="I1749" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1749" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>WIPRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1750" t="n">
+        <v>164.8</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>157</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>171</v>
+      </c>
+      <c r="G1750" t="inlineStr"/>
+      <c r="H1750" t="inlineStr">
+        <is>
+          <t>Wipro Fut बेचें PRICE 164.77 TARGET 160/157 STOP LOSS 171 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
+        </is>
+      </c>
+      <c r="I1750" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1750" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>WIPRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1751" t="n">
+        <v>163.6</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>171</v>
+      </c>
+      <c r="G1751" t="inlineStr"/>
+      <c r="H1751" t="inlineStr">
+        <is>
+          <t>Wipro Fut बेचें PRICE 164.77 TARGET 160/157 STOP LOSS 171 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
+        </is>
+      </c>
+      <c r="I1751" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1751" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1752" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G1752" t="inlineStr"/>
+      <c r="H1752" t="inlineStr">
+        <is>
+          <t>ICICI Lombard 1465.00 -9.00 NEUTRAL लक्ष्य ₹1930 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
+        </is>
+      </c>
+      <c r="I1752" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1752" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1753" t="n">
+        <v>1230.1</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>1550</v>
+      </c>
+      <c r="G1753" t="inlineStr"/>
+      <c r="H1753" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Axis Bank 1246.00 +7.50 ACCUMULATE श्रीकांत चौहान कोटक सिक्योरिटीज लक्ष्य ₹1550</t>
+        </is>
+      </c>
+      <c r="I1753" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1753" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:02</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1754" t="n">
+        <v>1749.8</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G1754" t="inlineStr"/>
+      <c r="H1754" t="inlineStr">
+        <is>
+          <t>बर्नस्टीन Paytm 1739.00 -0.71% OUTPERFORM लक्ष्य ₹2200</t>
+        </is>
+      </c>
+      <c r="I1754" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1754" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>THERMAX</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1755" t="n">
+        <v>3614.5</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>4100</v>
+      </c>
+      <c r="G1755" t="inlineStr"/>
+      <c r="H1755" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Thermax 3645.40 +6.80 NEUTRAL लक्ष्य ₹4100</t>
+        </is>
+      </c>
+      <c r="I1755" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1755" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1756" t="n">
+        <v>1757.6</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G1756" t="inlineStr"/>
+      <c r="H1756" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Adani Ports
+1768.00
+OUTPERFORM
+लक्ष्य ₹1860 से बढ़ाकर ₹2100</t>
+        </is>
+      </c>
+      <c r="I1756" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1756" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1664"/>
+  <autoFilter ref="A1:J1756"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -70245,11 +70245,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1665" t="inlineStr"/>
       <c r="E1665" t="n">
         <v>450</v>
       </c>
-      <c r="G1665" t="inlineStr"/>
       <c r="H1665" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -70282,11 +70280,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1666" t="inlineStr"/>
       <c r="E1666" t="n">
         <v>350</v>
       </c>
-      <c r="G1666" t="inlineStr"/>
       <c r="H1666" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -70319,11 +70315,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1667" t="inlineStr"/>
       <c r="E1667" t="n">
         <v>600</v>
       </c>
-      <c r="G1667" t="inlineStr"/>
       <c r="H1667" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -70362,7 +70356,6 @@
       <c r="E1668" t="n">
         <v>3500</v>
       </c>
-      <c r="G1668" t="inlineStr"/>
       <c r="H1668" t="inlineStr">
         <is>
           <t>Caplin Point खरीदें PRICE 2733.70 TARGET 3500 DURATION 6-12 महीने</t>
@@ -70401,7 +70394,6 @@
       <c r="E1669" t="n">
         <v>350</v>
       </c>
-      <c r="G1669" t="inlineStr"/>
       <c r="H1669" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -70440,7 +70432,6 @@
       <c r="E1670" t="n">
         <v>450</v>
       </c>
-      <c r="G1670" t="inlineStr"/>
       <c r="H1670" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -70479,7 +70470,6 @@
       <c r="E1671" t="n">
         <v>600</v>
       </c>
-      <c r="G1671" t="inlineStr"/>
       <c r="H1671" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -70521,7 +70511,6 @@
       <c r="F1672" t="n">
         <v>270</v>
       </c>
-      <c r="G1672" t="inlineStr"/>
       <c r="H1672" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय Genesys Intl खरीदें STOP LOSS 270 TARGET 400 DURATION 4-8 महीने Genesys Intl 311.66</t>
@@ -70563,7 +70552,6 @@
       <c r="F1673" t="n">
         <v>300</v>
       </c>
-      <c r="G1673" t="inlineStr"/>
       <c r="H1673" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Ramco Ind @ 314 खरीदें STOP LOSS 300 TARGET 355/360 DURATION 4-8 महीने Ramco Ind 315.90</t>
@@ -70602,7 +70590,6 @@
       <c r="E1674" t="n">
         <v>1220</v>
       </c>
-      <c r="G1674" t="inlineStr"/>
       <c r="H1674" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -70649,7 +70636,6 @@
       <c r="F1675" t="n">
         <v>1500</v>
       </c>
-      <c r="G1675" t="inlineStr"/>
       <c r="H1675" t="inlineStr">
         <is>
           <t>Tech Mahindra 1544.60 18.80 BUY TGT 1580 SL 1500</t>
@@ -70688,7 +70674,6 @@
       <c r="E1676" t="n">
         <v>1870</v>
       </c>
-      <c r="G1676" t="inlineStr"/>
       <c r="H1676" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel 1846.80 BUY TGT 1870</t>
@@ -70721,14 +70706,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1677" t="inlineStr"/>
       <c r="E1677" t="n">
         <v>185</v>
       </c>
       <c r="F1677" t="n">
         <v>169</v>
       </c>
-      <c r="G1677" t="inlineStr"/>
       <c r="H1677" t="inlineStr">
         <is>
           <t>Pine Labs 191.50 18.59% BUY TGT 185 SL 169</t>
@@ -70770,7 +70753,6 @@
       <c r="F1678" t="n">
         <v>1133</v>
       </c>
-      <c r="G1678" t="inlineStr"/>
       <c r="H1678" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर
@@ -70817,7 +70799,6 @@
       <c r="F1679" t="n">
         <v>1833</v>
       </c>
-      <c r="G1679" t="inlineStr"/>
       <c r="H1679" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर
@@ -70861,7 +70842,6 @@
       <c r="E1680" t="n">
         <v>3950</v>
       </c>
-      <c r="G1680" t="inlineStr"/>
       <c r="H1680" t="inlineStr">
         <is>
           <t>संदीप जैन की राय Ajanta Ph @ 3470 खरीदें STOP LOSS -- TARGET 3950 DURATION 9-12 महीने Ajanta Ph 3490.00 30.00</t>
@@ -70903,7 +70883,6 @@
       <c r="F1681" t="n">
         <v>940</v>
       </c>
-      <c r="G1681" t="inlineStr"/>
       <c r="H1681" t="inlineStr">
         <is>
           <t>Asahi India Glass खरीदें PRICE 981.00 TARGET 1100/1150 STOP LOSS 940</t>
@@ -70942,7 +70921,6 @@
       <c r="E1682" t="n">
         <v>3950</v>
       </c>
-      <c r="G1682" t="inlineStr"/>
       <c r="H1682" t="inlineStr">
         <is>
           <t>LONG MIDCAP STOCK Ajanta Ph @ 3470 खरीदें STOP LOSS TARGET 3950 DURATION 9-12 महीने</t>
@@ -70981,7 +70959,6 @@
       <c r="E1683" t="n">
         <v>1060</v>
       </c>
-      <c r="G1683" t="inlineStr"/>
       <c r="H1683" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -71025,7 +71002,6 @@
       <c r="E1684" t="n">
         <v>1220</v>
       </c>
-      <c r="G1684" t="inlineStr"/>
       <c r="H1684" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -71072,7 +71048,6 @@
       <c r="F1685" t="n">
         <v>1388</v>
       </c>
-      <c r="G1685" t="inlineStr"/>
       <c r="H1685" t="inlineStr">
         <is>
           <t>Tech Mahindra 1543.00 BUY TGT 1588 SL 1388</t>
@@ -71114,7 +71089,6 @@
       <c r="F1686" t="n">
         <v>1500</v>
       </c>
-      <c r="G1686" t="inlineStr"/>
       <c r="H1686" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट
@@ -71158,7 +71132,6 @@
       <c r="E1687" t="n">
         <v>1580</v>
       </c>
-      <c r="G1687" t="inlineStr"/>
       <c r="H1687" t="inlineStr">
         <is>
           <t>Tech Mahindra 1543.40 17.60 BUY TGT 1580</t>
@@ -71197,7 +71170,6 @@
       <c r="E1688" t="n">
         <v>1870</v>
       </c>
-      <c r="G1688" t="inlineStr"/>
       <c r="H1688" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel 1848.20 9.20 BUY TGT 1870 SL --</t>
@@ -71230,14 +71202,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1689" t="inlineStr"/>
       <c r="E1689" t="n">
         <v>185</v>
       </c>
       <c r="F1689" t="n">
         <v>169</v>
       </c>
-      <c r="G1689" t="inlineStr"/>
       <c r="H1689" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Pine Labs 185.25 12.08 BUY TGT 185 SL 169</t>
@@ -71279,7 +71249,6 @@
       <c r="F1690" t="n">
         <v>1133</v>
       </c>
-      <c r="G1690" t="inlineStr"/>
       <c r="H1690" t="inlineStr">
         <is>
           <t>Dr Reddy's Fut 1142.90 BUY TGT 1156 SL 1133</t>
@@ -71321,7 +71290,6 @@
       <c r="F1691" t="n">
         <v>1833</v>
       </c>
-      <c r="G1691" t="inlineStr"/>
       <c r="H1691" t="inlineStr">
         <is>
           <t>BTST BUY TODAY Bharti Airtel Fut 1851.50 11.10 BUY TGT 1870 SL 1833</t>
@@ -71363,7 +71331,6 @@
       <c r="F1692" t="n">
         <v>160</v>
       </c>
-      <c r="G1692" t="inlineStr"/>
       <c r="H1692" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय Pine Labs खरीदें STOP LOSS 160 TARGET 240/250 DURATION 9-12 महीने Pine Labs 184.25</t>
@@ -71405,7 +71372,6 @@
       <c r="F1693" t="n">
         <v>160</v>
       </c>
-      <c r="G1693" t="inlineStr"/>
       <c r="H1693" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय Pine Labs खरीदें STOP LOSS 160 TARGET 240/250 DURATION 9-12 महीने Pine Labs 184.25</t>
@@ -71444,7 +71410,6 @@
       <c r="E1694" t="n">
         <v>450</v>
       </c>
-      <c r="G1694" t="inlineStr"/>
       <c r="H1694" t="inlineStr">
         <is>
           <t>Steel Strip Wheels खरीदें PRICE 371.00 TARGET 450 STOP LOSS --</t>
@@ -71483,7 +71448,6 @@
       <c r="E1695" t="n">
         <v>450</v>
       </c>
-      <c r="G1695" t="inlineStr"/>
       <c r="H1695" t="inlineStr">
         <is>
           <t>10 की कमाई
@@ -71530,7 +71494,6 @@
       <c r="F1696" t="n">
         <v>390</v>
       </c>
-      <c r="G1696" t="inlineStr"/>
       <c r="H1696" t="inlineStr">
         <is>
           <t>जय ठक्कर की राय NIFTY BANK 56500 की कॉल @ 506/470 खरीदें STOP LOSS 390 TARGET 600/650 Nifty Bank 55905.30</t>
@@ -71572,7 +71535,6 @@
       <c r="F1697" t="n">
         <v>390</v>
       </c>
-      <c r="G1697" t="inlineStr"/>
       <c r="H1697" t="inlineStr">
         <is>
           <t>जय ठक्कर की राय NIFTY BANK 56500 की कॉल @ 506/470 खरीदें STOP LOSS 390 TARGET 600/650 Nifty Bank 55905.30</t>
@@ -71611,7 +71573,6 @@
       <c r="E1698" t="n">
         <v>600</v>
       </c>
-      <c r="G1698" t="inlineStr"/>
       <c r="H1698" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -71644,11 +71605,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1699" t="inlineStr"/>
       <c r="E1699" t="n">
         <v>6.55</v>
       </c>
-      <c r="G1699" t="inlineStr"/>
       <c r="H1699" t="inlineStr">
         <is>
           <t>Vodafone Idea 15.03 INVESTMENT PICK 6.55 28/08/2025 RECO PRICE RETURN TILL NOW 8.48 129.47%</t>
@@ -71681,11 +71640,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1700" t="inlineStr"/>
       <c r="E1700" t="n">
         <v>15.03</v>
       </c>
-      <c r="G1700" t="inlineStr"/>
       <c r="H1700" t="inlineStr">
         <is>
           <t>Vodafone Idea 15.03 INVESTMENT PICK 6.55 28/08/2025 RECO PRICE RETURN TILL NOW 8.48 129.47%</t>
@@ -71724,7 +71681,6 @@
       <c r="E1701" t="n">
         <v>600</v>
       </c>
-      <c r="G1701" t="inlineStr"/>
       <c r="H1701" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -71763,7 +71719,6 @@
       <c r="E1702" t="n">
         <v>350</v>
       </c>
-      <c r="G1702" t="inlineStr"/>
       <c r="H1702" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -71802,7 +71757,6 @@
       <c r="E1703" t="n">
         <v>450</v>
       </c>
-      <c r="G1703" t="inlineStr"/>
       <c r="H1703" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -71841,7 +71795,6 @@
       <c r="E1704" t="n">
         <v>1220</v>
       </c>
-      <c r="G1704" t="inlineStr"/>
       <c r="H1704" t="inlineStr">
         <is>
           <t>Max Healthcare खरीदें PRICE 1026.50 TARGET 1060/1220 STOP LOSS --</t>
@@ -71880,7 +71833,6 @@
       <c r="E1705" t="n">
         <v>1060</v>
       </c>
-      <c r="G1705" t="inlineStr"/>
       <c r="H1705" t="inlineStr">
         <is>
           <t>Max Healthcare खरीदें PRICE 1026.00 TARGET 1060/1220 STOP LOSS --</t>
@@ -71922,7 +71874,6 @@
       <c r="F1706" t="n">
         <v>1133</v>
       </c>
-      <c r="G1706" t="inlineStr"/>
       <c r="H1706" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर की राय
@@ -71969,7 +71920,6 @@
       <c r="F1707" t="n">
         <v>1133</v>
       </c>
-      <c r="G1707" t="inlineStr"/>
       <c r="H1707" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर की राय
@@ -72007,14 +71957,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1708" t="inlineStr"/>
       <c r="E1708" t="n">
         <v>1450.6</v>
       </c>
       <c r="F1708" t="n">
         <v>1133</v>
       </c>
-      <c r="G1708" t="inlineStr"/>
       <c r="H1708" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विश्लेषणात्मक शेयर Birlasoft BUY लक्ष्य 3350, 4450, 6 3महीने-1133</t>
@@ -72053,7 +72001,6 @@
       <c r="E1709" t="n">
         <v>600</v>
       </c>
-      <c r="G1709" t="inlineStr"/>
       <c r="H1709" t="inlineStr">
         <is>
           <t>अनिल सिंघवी का विज्ञहर्ता शेयर Birlasoft BUY लक्ष्य 350, 450, 600 अवधि- 1-3 साल</t>
@@ -72086,11 +72033,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1710" t="inlineStr"/>
       <c r="E1710" t="n">
         <v>1220</v>
       </c>
-      <c r="G1710" t="inlineStr"/>
       <c r="H1710" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -72136,7 +72081,6 @@
       <c r="F1711" t="n">
         <v>1500</v>
       </c>
-      <c r="G1711" t="inlineStr"/>
       <c r="H1711" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट Tech Mahindra खरीदें PRICE 1537.30 TARGET 1580/1600 STOP LOSS 1500</t>
@@ -72178,7 +72122,6 @@
       <c r="F1712" t="n">
         <v>1500</v>
       </c>
-      <c r="G1712" t="inlineStr"/>
       <c r="H1712" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट Tech Mahindra खरीदें PRICE 1537.30 TARGET 1580/1600 STOP LOSS 1500</t>
@@ -72217,7 +72160,6 @@
       <c r="E1713" t="n">
         <v>2500</v>
       </c>
-      <c r="G1713" t="inlineStr"/>
       <c r="H1713" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel खरीदें PRICE 1843.70 TARGET 1870/2500 STOP LOSS --</t>
@@ -72256,7 +72198,6 @@
       <c r="E1714" t="n">
         <v>1870</v>
       </c>
-      <c r="G1714" t="inlineStr"/>
       <c r="H1714" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel खरीदें PRICE 1843.70 TARGET 1870/2500 STOP LOSS --</t>
@@ -72295,7 +72236,6 @@
       <c r="E1715" t="n">
         <v>2500</v>
       </c>
-      <c r="G1715" t="inlineStr"/>
       <c r="H1715" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel खरीदें PRICE 1842.90 TARGET 1870/2500 STOP LOSS --</t>
@@ -72334,7 +72274,6 @@
       <c r="E1716" t="n">
         <v>1870</v>
       </c>
-      <c r="G1716" t="inlineStr"/>
       <c r="H1716" t="inlineStr">
         <is>
           <t>SUPER SID Bharti Airtel खरीदें PRICE 1842.90 TARGET 1870/2500 STOP LOSS --</t>
@@ -72376,7 +72315,6 @@
       <c r="F1717" t="n">
         <v>169</v>
       </c>
-      <c r="G1717" t="inlineStr"/>
       <c r="H1717" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Pine Labs खरीदें PRICE 176.92 TARGET 185/190 STOP LOSS 169</t>
@@ -72418,7 +72356,6 @@
       <c r="F1718" t="n">
         <v>169</v>
       </c>
-      <c r="G1718" t="inlineStr"/>
       <c r="H1718" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Pine Labs खरीदें PRICE 176.92 TARGET 185/190 STOP LOSS 169</t>
@@ -72457,7 +72394,6 @@
       <c r="E1719" t="n">
         <v>2100</v>
       </c>
-      <c r="G1719" t="inlineStr"/>
       <c r="H1719" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -72500,7 +72436,6 @@
       <c r="E1720" t="n">
         <v>450</v>
       </c>
-      <c r="G1720" t="inlineStr"/>
       <c r="H1720" t="inlineStr">
         <is>
           <t>अनिल सिंधवी की सलाह Birlasoft BUY PRICE 276 TARGET 350, 450, 600 DURATION 1-3 साल</t>
@@ -72539,7 +72474,6 @@
       <c r="E1721" t="n">
         <v>350</v>
       </c>
-      <c r="G1721" t="inlineStr"/>
       <c r="H1721" t="inlineStr">
         <is>
           <t>अनिल सिंधवी की सलाह Birlasoft BUY PRICE 276 TARGET 350, 450, 600 DURATION 1-3 साल</t>
@@ -72578,7 +72512,6 @@
       <c r="E1722" t="n">
         <v>430</v>
       </c>
-      <c r="G1722" t="inlineStr"/>
       <c r="H1722" t="inlineStr">
         <is>
           <t>सुमीत बगडिया की राय Kotak Bank BUY PRICE 416.55 TARGET 430/450 STOP LOSS --</t>
@@ -72617,7 +72550,6 @@
       <c r="E1723" t="n">
         <v>450</v>
       </c>
-      <c r="G1723" t="inlineStr"/>
       <c r="H1723" t="inlineStr">
         <is>
           <t>सुमीत बगडिया की राय Kotak Bank BUY PRICE 416.55 TARGET 430/450 STOP LOSS --</t>
@@ -72659,7 +72591,6 @@
       <c r="F1724" t="n">
         <v>645</v>
       </c>
-      <c r="G1724" t="inlineStr"/>
       <c r="H1724" t="inlineStr">
         <is>
           <t>सच्चितानंद उतेकर की राय HBL ENGINEERING BUY PRICE 720.90 TARGET 980 STOP LOSS 645</t>
@@ -72701,7 +72632,6 @@
       <c r="F1725" t="n">
         <v>414</v>
       </c>
-      <c r="G1725" t="inlineStr"/>
       <c r="H1725" t="inlineStr">
         <is>
           <t>सच्चिदानंद उतेकर की राय Exide Ind BUY PRICE 420.85 TARGET 439/475 STOP LOSS 414</t>
@@ -72743,7 +72673,6 @@
       <c r="F1726" t="n">
         <v>406</v>
       </c>
-      <c r="G1726" t="inlineStr"/>
       <c r="H1726" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह AB Capital Futures SELL PRICE 402 TARGET 398, 394, 390 STOP LOSS 406</t>
@@ -72785,7 +72714,6 @@
       <c r="F1727" t="n">
         <v>406</v>
       </c>
-      <c r="G1727" t="inlineStr"/>
       <c r="H1727" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह AB Capital Futures SELL PRICE 402 TARGET 398, 394, 390 STOP LOSS 406</t>
@@ -72827,7 +72755,6 @@
       <c r="F1728" t="n">
         <v>314</v>
       </c>
-      <c r="G1728" t="inlineStr"/>
       <c r="H1728" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह L&amp;T Fin Futures SELL PRICE 312 TARGET 308, 305, 302 STOP LOSS 314</t>
@@ -72869,7 +72796,6 @@
       <c r="F1729" t="n">
         <v>314</v>
       </c>
-      <c r="G1729" t="inlineStr"/>
       <c r="H1729" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह L&amp;T Fin Futures SELL PRICE 312 TARGET 308, 305, 302 STOP LOSS 314</t>
@@ -72911,7 +72837,6 @@
       <c r="F1730" t="n">
         <v>168</v>
       </c>
-      <c r="G1730" t="inlineStr"/>
       <c r="H1730" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Ashok Leyland Fut SELL PRICE 166 TARGET 164, 162, 160 STOP LOSS 168</t>
@@ -72950,7 +72875,6 @@
       <c r="E1731" t="n">
         <v>4000</v>
       </c>
-      <c r="G1731" t="inlineStr"/>
       <c r="H1731" t="inlineStr">
         <is>
           <t>MY CHOICE REDINGTON B 4000 3</t>
@@ -72992,7 +72916,6 @@
       <c r="F1732" t="n">
         <v>2869</v>
       </c>
-      <c r="G1732" t="inlineStr"/>
       <c r="H1732" t="inlineStr">
         <is>
           <t>FUTURE MUTHOOT FINANCE FUT S 2785 2869</t>
@@ -73034,7 +72957,6 @@
       <c r="F1733" t="n">
         <v>740</v>
       </c>
-      <c r="G1733" t="inlineStr"/>
       <c r="H1733" t="inlineStr">
         <is>
           <t>TECHNO TD POWER B 805 740</t>
@@ -73076,7 +72998,6 @@
       <c r="F1734" t="n">
         <v>755</v>
       </c>
-      <c r="G1734" t="inlineStr"/>
       <c r="H1734" t="inlineStr">
         <is>
           <t>CASH KIMS B 801 755</t>
@@ -73118,7 +73039,6 @@
       <c r="F1735" t="n">
         <v>10</v>
       </c>
-      <c r="G1735" t="inlineStr"/>
       <c r="H1735" t="inlineStr">
         <is>
           <t>OPTION OIL INDIA 500 CE @ 15 B 24 10</t>
@@ -73160,7 +73080,6 @@
       <c r="F1736" t="n">
         <v>388</v>
       </c>
-      <c r="G1736" t="inlineStr"/>
       <c r="H1736" t="inlineStr">
         <is>
           <t>MY CHOICE Redington खरीदें PRICE 392.00 TARGET 400 STOP LOSS 388</t>
@@ -73202,7 +73121,6 @@
       <c r="F1737" t="n">
         <v>112</v>
       </c>
-      <c r="G1737" t="inlineStr"/>
       <c r="H1737" t="inlineStr">
         <is>
           <t>MY CHOICE Texmaco Rail खरीदें PRICE 117.77 TARGET 122 STOP LOSS 112</t>
@@ -73244,7 +73162,6 @@
       <c r="F1738" t="n">
         <v>265</v>
       </c>
-      <c r="G1738" t="inlineStr"/>
       <c r="H1738" t="inlineStr">
         <is>
           <t>MY CHOICE Power Grid खरीदें PRICE 271.75 TARGET 280 STOP LOSS 265</t>
@@ -73286,7 +73203,6 @@
       <c r="F1739" t="n">
         <v>5001</v>
       </c>
-      <c r="G1739" t="inlineStr"/>
       <c r="H1739" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -73333,7 +73249,6 @@
       <c r="F1740" t="n">
         <v>849</v>
       </c>
-      <c r="G1740" t="inlineStr"/>
       <c r="H1740" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -73377,7 +73292,6 @@
       <c r="E1741" t="n">
         <v>1380</v>
       </c>
-      <c r="G1741" t="inlineStr"/>
       <c r="H1741" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK
@@ -73424,7 +73338,6 @@
       <c r="F1742" t="n">
         <v>105</v>
       </c>
-      <c r="G1742" t="inlineStr"/>
       <c r="H1742" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK TVS Supply Chain खरीदें PRICE 128.73 TARGET 175 STOP LOSS 105</t>
@@ -73466,7 +73379,6 @@
       <c r="F1743" t="n">
         <v>421</v>
       </c>
-      <c r="G1743" t="inlineStr"/>
       <c r="H1743" t="inlineStr">
         <is>
           <t>FUNDA PICK
@@ -73510,7 +73422,6 @@
       <c r="E1744" t="n">
         <v>360</v>
       </c>
-      <c r="G1744" t="inlineStr"/>
       <c r="H1744" t="inlineStr">
         <is>
           <t>पूजा के शेयर NTPC खरीदें PRICE 335.00 TARGET 360 DURATION 6 महीने</t>
@@ -73552,7 +73463,6 @@
       <c r="F1745" t="n">
         <v>355</v>
       </c>
-      <c r="G1745" t="inlineStr"/>
       <c r="H1745" t="inlineStr">
         <is>
           <t>TECHNO PICK HPCL Fut बेचें PRICE 350.90 TARGET 340 STOP LOSS 355</t>
@@ -73594,7 +73504,6 @@
       <c r="F1746" t="n">
         <v>740</v>
       </c>
-      <c r="G1746" t="inlineStr"/>
       <c r="H1746" t="inlineStr">
         <is>
           <t>TECHNO PICK TD Power खरीदें PRICE 762.75 TARGET 805 STOP LOSS 740</t>
@@ -73636,7 +73545,6 @@
       <c r="F1747" t="n">
         <v>40</v>
       </c>
-      <c r="G1747" t="inlineStr"/>
       <c r="H1747" t="inlineStr">
         <is>
           <t>पूजा के शेयर KEI Industries 4600 की पुट @88.65 खरीदें STOP LOSS 40 TARGET 200 KEI Industries 4640.00 0.63%</t>
@@ -73675,7 +73583,6 @@
       <c r="E1748" t="n">
         <v>360</v>
       </c>
-      <c r="G1748" t="inlineStr"/>
       <c r="H1748" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Angel One 297.30 -1.75 NEUTRAL लक्ष्य ₹360</t>
@@ -73714,7 +73621,6 @@
       <c r="E1749" t="n">
         <v>1675</v>
       </c>
-      <c r="G1749" t="inlineStr"/>
       <c r="H1749" t="inlineStr">
         <is>
           <t>Cipla 1373.30 +10.20 OUTPERFORM लक्ष्य ₹1675</t>
@@ -73756,7 +73662,6 @@
       <c r="F1750" t="n">
         <v>171</v>
       </c>
-      <c r="G1750" t="inlineStr"/>
       <c r="H1750" t="inlineStr">
         <is>
           <t>Wipro Fut बेचें PRICE 164.77 TARGET 160/157 STOP LOSS 171 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
@@ -73798,7 +73703,6 @@
       <c r="F1751" t="n">
         <v>171</v>
       </c>
-      <c r="G1751" t="inlineStr"/>
       <c r="H1751" t="inlineStr">
         <is>
           <t>Wipro Fut बेचें PRICE 164.77 TARGET 160/157 STOP LOSS 171 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
@@ -73837,7 +73741,6 @@
       <c r="E1752" t="n">
         <v>1930</v>
       </c>
-      <c r="G1752" t="inlineStr"/>
       <c r="H1752" t="inlineStr">
         <is>
           <t>ICICI Lombard 1465.00 -9.00 NEUTRAL लक्ष्य ₹1930 श्रीकांत चौहान कोटक सिक्योरिटीज</t>
@@ -73876,7 +73779,6 @@
       <c r="E1753" t="n">
         <v>1550</v>
       </c>
-      <c r="G1753" t="inlineStr"/>
       <c r="H1753" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Axis Bank 1246.00 +7.50 ACCUMULATE श्रीकांत चौहान कोटक सिक्योरिटीज लक्ष्य ₹1550</t>
@@ -73915,7 +73817,6 @@
       <c r="E1754" t="n">
         <v>2200</v>
       </c>
-      <c r="G1754" t="inlineStr"/>
       <c r="H1754" t="inlineStr">
         <is>
           <t>बर्नस्टीन Paytm 1739.00 -0.71% OUTPERFORM लक्ष्य ₹2200</t>
@@ -73954,7 +73855,6 @@
       <c r="E1755" t="n">
         <v>4100</v>
       </c>
-      <c r="G1755" t="inlineStr"/>
       <c r="H1755" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Thermax 3645.40 +6.80 NEUTRAL लक्ष्य ₹4100</t>
@@ -73993,7 +73893,6 @@
       <c r="E1756" t="n">
         <v>2100</v>
       </c>
-      <c r="G1756" t="inlineStr"/>
       <c r="H1756" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1897</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1756"/>
+  <dimension ref="A1:J1897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -73913,8 +73913,6000 @@
         </is>
       </c>
     </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:38:43</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr"/>
+      <c r="E1757" t="n">
+        <v>70</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>331</v>
+      </c>
+      <c r="G1757" t="inlineStr"/>
+      <c r="H1757" t="inlineStr">
+        <is>
+          <t>Sunflag Iron @ 346 खरीदें STOP LOSS 331 TARGET 70 DURATION 1-3 महीने</t>
+        </is>
+      </c>
+      <c r="I1757" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1757" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:38:30</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr"/>
+      <c r="E1758" t="n">
+        <v>370</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>335</v>
+      </c>
+      <c r="G1758" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H1758" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय Sunflag Iron @ 346 खरीदें STOP LOSS 335 TARGET 370 DURATION 1-3 महीने Sunflag Iron 352.60 2.59%</t>
+        </is>
+      </c>
+      <c r="I1758" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1758" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:19:31</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr"/>
+      <c r="E1759" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>1180</v>
+      </c>
+      <c r="G1759" t="inlineStr"/>
+      <c r="H1759" t="inlineStr">
+        <is>
+          <t>POSITIONAL MIDCAP STOCK Action Cons खरीदें STOP LOSS 1180 TARGET 1350/1370 DURAT 4-5 दिन Action Cons 1289.79</t>
+        </is>
+      </c>
+      <c r="I1759" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1759" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:19:31</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr"/>
+      <c r="E1760" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>1180</v>
+      </c>
+      <c r="G1760" t="inlineStr"/>
+      <c r="H1760" t="inlineStr">
+        <is>
+          <t>POSITIONAL MIDCAP STOCK Action Cons खरीदें STOP LOSS 1180 TARGET 1350/1370 DURAT 4-5 दिन Action Cons 1289.79</t>
+        </is>
+      </c>
+      <c r="I1760" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1760" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:19:29</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>VEEGALAND-BE</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr"/>
+      <c r="E1761" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>1180</v>
+      </c>
+      <c r="G1761" t="inlineStr"/>
+      <c r="H1761" t="inlineStr">
+        <is>
+          <t>Action Cons खरीदें STOP LOSS 1180 TARGET 1350/1370 DURATION 4-8 महीने Action Cons 1230.70</t>
+        </is>
+      </c>
+      <c r="I1761" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1761" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:20:00</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1762" t="n">
+        <v>1232.7</v>
+      </c>
+      <c r="E1762" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F1762" t="n">
+        <v>1180</v>
+      </c>
+      <c r="G1762" t="inlineStr"/>
+      <c r="H1762" t="inlineStr">
+        <is>
+          <t>POSITIONAL MIDCAP STOCKS
+Action Cons
+खरीदें
+STOP LOSS 1180 | TARGET 1350/1370 | DURATION 4-8 महीने
+Action Cons 1230.70 ▲ 2.08%</t>
+        </is>
+      </c>
+      <c r="I1762" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1762" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:20:00</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>ACE</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1763" t="n">
+        <v>1232.7</v>
+      </c>
+      <c r="E1763" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F1763" t="n">
+        <v>1180</v>
+      </c>
+      <c r="G1763" t="inlineStr"/>
+      <c r="H1763" t="inlineStr">
+        <is>
+          <t>POSITIONAL MIDCAP STOCKS
+Action Cons
+खरीदें
+STOP LOSS 1180 | TARGET 1350/1370 | DURATION 4-8 महीने
+Action Cons 1230.70 ▲ 2.08%</t>
+        </is>
+      </c>
+      <c r="I1763" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1763" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:19:00</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1764" t="n">
+        <v>189.23</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>240</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1764" t="inlineStr"/>
+      <c r="H1764" t="inlineStr">
+        <is>
+          <t>Pine Labs खरीदें STOP LOSS 168 TARGET 240/250 DURATION 9-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1764" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1764" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:19:00</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1765" t="n">
+        <v>189.23</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1765" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1765" t="inlineStr"/>
+      <c r="H1765" t="inlineStr">
+        <is>
+          <t>Pine Labs खरीदें STOP LOSS 168 TARGET 240/250 DURATION 9-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1765" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1765" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:18:00</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>ASAHIINDIA</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1766" t="n">
+        <v>962.7</v>
+      </c>
+      <c r="E1766" t="n">
+        <v>1030</v>
+      </c>
+      <c r="F1766" t="n">
+        <v>920</v>
+      </c>
+      <c r="G1766" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H1766" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय
+Asahi India Glass @ 960
+खरीदें
+STOP LOSS 920 | TARGET 1030 | DURATION 4-8 महीने
+Asahi India Glass 965.10 ▲ 14.40</t>
+        </is>
+      </c>
+      <c r="I1766" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1766" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:17:00</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>AJANTPHARM</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1767" t="n">
+        <v>3595.9</v>
+      </c>
+      <c r="E1767" t="n">
+        <v>3770</v>
+      </c>
+      <c r="F1767" t="n">
+        <v>3540</v>
+      </c>
+      <c r="G1767" t="inlineStr"/>
+      <c r="H1767" t="inlineStr">
+        <is>
+          <t>Ajanta Ph खरीदें PRICE 3591.90 TARGET 3770/3850 STOP LOSS 3540</t>
+        </is>
+      </c>
+      <c r="I1767" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1767" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:17:00</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>AJANTPHARM</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1768" t="n">
+        <v>3595.9</v>
+      </c>
+      <c r="E1768" t="n">
+        <v>3850</v>
+      </c>
+      <c r="F1768" t="n">
+        <v>3540</v>
+      </c>
+      <c r="G1768" t="inlineStr"/>
+      <c r="H1768" t="inlineStr">
+        <is>
+          <t>Ajanta Ph खरीदें PRICE 3591.90 TARGET 3770/3850 STOP LOSS 3540</t>
+        </is>
+      </c>
+      <c r="I1768" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1768" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:15:00</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>THYROCARE</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1769" t="n">
+        <v>562.85</v>
+      </c>
+      <c r="E1769" t="n">
+        <v>800</v>
+      </c>
+      <c r="G1769" t="inlineStr"/>
+      <c r="H1769" t="inlineStr">
+        <is>
+          <t>Thyrocare PRICE 562.35 TARGET 800 DURATION 6-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1769" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1769" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:13:06</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>GRAUWEIL</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr"/>
+      <c r="E1770" t="n">
+        <v>325</v>
+      </c>
+      <c r="F1770" t="n">
+        <v>220</v>
+      </c>
+      <c r="G1770" t="inlineStr">
+        <is>
+          <t>Vikas Sethi</t>
+        </is>
+      </c>
+      <c r="H1770" t="inlineStr">
+        <is>
+          <t>विकास सेठी की राय EIL @ 264 खरीदें STOP LOSS 220 TARGET 325 DURATION 9-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1770" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1770" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:12:00</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1771" t="n">
+        <v>189.38</v>
+      </c>
+      <c r="E1771" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1771" t="inlineStr"/>
+      <c r="H1771" t="inlineStr">
+        <is>
+          <t>राजेश पालविया की राय Pine Labs खरीदें STOP LOSS 168 TARGET 240/250 DURATION 9-12 महीने Pine Labs 189.05 2.48%</t>
+        </is>
+      </c>
+      <c r="I1771" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1771" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:12:00</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1772" t="n">
+        <v>189.38</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>240</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>168</v>
+      </c>
+      <c r="G1772" t="inlineStr"/>
+      <c r="H1772" t="inlineStr">
+        <is>
+          <t>Pine Labs खरीदें STOP LOSS 168 TARGET 240/250 DURATION 9-12 महीने Pine Labs 189.05</t>
+        </is>
+      </c>
+      <c r="I1772" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1772" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:08:00</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1773" t="n">
+        <v>549.5</v>
+      </c>
+      <c r="E1773" t="n">
+        <v>720</v>
+      </c>
+      <c r="G1773" t="inlineStr"/>
+      <c r="H1773" t="inlineStr">
+        <is>
+          <t>1 की कमाई
+Arvind
+खरीदें
+PRICE ▶ 551.00
+TARGET ▶ 720
+DURATION ▶ 6-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1773" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1773" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:08:00</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>ARVIND</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1774" t="n">
+        <v>549.8</v>
+      </c>
+      <c r="E1774" t="n">
+        <v>720</v>
+      </c>
+      <c r="G1774" t="inlineStr"/>
+      <c r="H1774" t="inlineStr">
+        <is>
+          <t>Arvind
+PRICE 550 95
+TARGET 720
+DURATION 6-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1774" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1774" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:05:00</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1775" t="n">
+        <v>2736.6</v>
+      </c>
+      <c r="E1775" t="n">
+        <v>2770</v>
+      </c>
+      <c r="F1775" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G1775" t="inlineStr"/>
+      <c r="H1775" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Caplin Point
+2736.00
+BUY
+TGT 2770
+SL 2650</t>
+        </is>
+      </c>
+      <c r="I1775" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1775" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:05:00</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1776" t="n">
+        <v>2736.6</v>
+      </c>
+      <c r="E1776" t="n">
+        <v>2770</v>
+      </c>
+      <c r="F1776" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G1776" t="inlineStr"/>
+      <c r="H1776" t="inlineStr">
+        <is>
+          <t>Caplin Point 2733.50 136.90 BUY TGT 2770 SL 2650</t>
+        </is>
+      </c>
+      <c r="I1776" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1776" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:05:00</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>CARRARO</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1777" t="n">
+        <v>525</v>
+      </c>
+      <c r="E1777" t="n">
+        <v>690</v>
+      </c>
+      <c r="G1777" t="inlineStr"/>
+      <c r="H1777" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS
+Carraro India
+524.95 9.90
+BUY
+TGT 690
+SL --</t>
+        </is>
+      </c>
+      <c r="I1777" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1777" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:05:00</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1778" t="n">
+        <v>1043.4</v>
+      </c>
+      <c r="E1778" t="n">
+        <v>1078</v>
+      </c>
+      <c r="F1778" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G1778" t="inlineStr"/>
+      <c r="H1778" t="inlineStr">
+        <is>
+          <t>Max Healthcare 1044.80 BUY TGT 1078 SL 1025</t>
+        </is>
+      </c>
+      <c r="I1778" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1778" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>2026-09-18 10:05:00</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1779" t="n">
+        <v>1044.4</v>
+      </c>
+      <c r="E1779" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F1779" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G1779" t="inlineStr"/>
+      <c r="H1779" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट
+Max Healthcare
+1044.40 0.71%
+BUY
+TGT 1070
+SL 1025</t>
+        </is>
+      </c>
+      <c r="I1779" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1779" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:55:00</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1780" t="n">
+        <v>2717.8</v>
+      </c>
+      <c r="E1780" t="n">
+        <v>2770</v>
+      </c>
+      <c r="F1780" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G1780" t="inlineStr"/>
+      <c r="H1780" t="inlineStr">
+        <is>
+          <t>Caplin Point 2719.00 122.40 BUY TGT 2770 SL 2650</t>
+        </is>
+      </c>
+      <c r="I1780" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1780" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:55:00</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1781" t="n">
+        <v>802.3</v>
+      </c>
+      <c r="E1781" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1781" t="n">
+        <v>785</v>
+      </c>
+      <c r="G1781" t="inlineStr"/>
+      <c r="H1781" t="inlineStr">
+        <is>
+          <t>फुल्ला के कोटिपूर
+Sona BLW Precision
+801.50 23.60
+BUY
+TGT 820
+SL 785</t>
+        </is>
+      </c>
+      <c r="I1781" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1781" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:55:00</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>CARRARO</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1782" t="n">
+        <v>525.25</v>
+      </c>
+      <c r="E1782" t="n">
+        <v>690</v>
+      </c>
+      <c r="G1782" t="inlineStr"/>
+      <c r="H1782" t="inlineStr">
+        <is>
+          <t>Carraro India 526.25 11.20 BUY TGT 690 SL --</t>
+        </is>
+      </c>
+      <c r="I1782" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1782" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:55:00</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1783" t="n">
+        <v>1045.4</v>
+      </c>
+      <c r="E1783" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F1783" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G1783" t="inlineStr"/>
+      <c r="H1783" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट
+Max Healthcare
+1045.50 0.82%
+BUY
+TGT 1070
+SL 1025</t>
+        </is>
+      </c>
+      <c r="I1783" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1783" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:54:00</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1784" t="n">
+        <v>8335</v>
+      </c>
+      <c r="E1784" t="n">
+        <v>8550</v>
+      </c>
+      <c r="F1784" t="n">
+        <v>8200</v>
+      </c>
+      <c r="G1784" t="inlineStr"/>
+      <c r="H1784" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट Polycab India खरीदें PRICE 8328.00 TARGET 8450/8550 STOP LOSS 8200</t>
+        </is>
+      </c>
+      <c r="I1784" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1784" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:53:00</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1785" t="n">
+        <v>8336</v>
+      </c>
+      <c r="E1785" t="n">
+        <v>8450</v>
+      </c>
+      <c r="F1785" t="n">
+        <v>8200</v>
+      </c>
+      <c r="G1785" t="inlineStr"/>
+      <c r="H1785" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट Polycab India खरीदें PRICE 8325.00 TARGET 8450/8550 STOP LOSS 8200</t>
+        </is>
+      </c>
+      <c r="I1785" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1785" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:53:00</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1786" t="n">
+        <v>8326</v>
+      </c>
+      <c r="E1786" t="n">
+        <v>8550</v>
+      </c>
+      <c r="F1786" t="n">
+        <v>8200</v>
+      </c>
+      <c r="G1786" t="inlineStr"/>
+      <c r="H1786" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट Polycab India खरीदें PRICE 8325.00 TARGET 8450/8550 STOP LOSS 8200</t>
+        </is>
+      </c>
+      <c r="I1786" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1786" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:46:00</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1787" t="n">
+        <v>2707.3</v>
+      </c>
+      <c r="E1787" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F1787" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G1787" t="inlineStr"/>
+      <c r="H1787" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Caplin Point
+खरीदें
+PRICE → 2702.50
+TARGET → 2770/2800
+STOP LOSS → 2650</t>
+        </is>
+      </c>
+      <c r="I1787" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1787" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:46:00</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>CAPLIPOINT</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1788" t="n">
+        <v>2707.3</v>
+      </c>
+      <c r="E1788" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F1788" t="n">
+        <v>2650</v>
+      </c>
+      <c r="G1788" t="inlineStr"/>
+      <c r="H1788" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Caplin Point
+खरीदें
+PRICE → 2704.00
+TARGET → 2770/2800
+STOP LOSS → 2650</t>
+        </is>
+      </c>
+      <c r="I1788" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1788" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:44:38</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr"/>
+      <c r="E1789" t="n">
+        <v>1878</v>
+      </c>
+      <c r="F1789" t="n">
+        <v>1825</v>
+      </c>
+      <c r="G1789" t="inlineStr"/>
+      <c r="H1789" t="inlineStr">
+        <is>
+          <t>Max Healthcare 1043.00 BUY TGT 1878 SL 1825</t>
+        </is>
+      </c>
+      <c r="I1789" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1789" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:45:00</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1790" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E1790" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F1790" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G1790" t="inlineStr"/>
+      <c r="H1790" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट
+Max Healthcare
+1043.30 6.30
+BUY
+TGT 1070
+SL 1025</t>
+        </is>
+      </c>
+      <c r="I1790" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1790" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:45:00</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1791" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E1791" t="n">
+        <v>1070</v>
+      </c>
+      <c r="G1791" t="inlineStr"/>
+      <c r="H1791" t="inlineStr">
+        <is>
+          <t>Max Healthcare 1043.30 6.30 BUY TGT 1070</t>
+        </is>
+      </c>
+      <c r="I1791" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1791" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:44:27</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr"/>
+      <c r="E1792" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F1792" t="n">
+        <v>1405</v>
+      </c>
+      <c r="G1792" t="inlineStr"/>
+      <c r="H1792" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर
+Astral Ltd
+1401.20 2.30
+BUY
+TGT 1445
+SL 1405</t>
+        </is>
+      </c>
+      <c r="I1792" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1792" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:45:00</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>EMMVEE</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1793" t="n">
+        <v>328.8</v>
+      </c>
+      <c r="E1793" t="n">
+        <v>340</v>
+      </c>
+      <c r="G1793" t="inlineStr"/>
+      <c r="H1793" t="inlineStr">
+        <is>
+          <t>SUPER SID Emmvee Photovoltaic 328.90 3.40 BUY TGT 340 SL --</t>
+        </is>
+      </c>
+      <c r="I1793" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1793" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:42:00</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1794" t="n">
+        <v>796.35</v>
+      </c>
+      <c r="E1794" t="n">
+        <v>820</v>
+      </c>
+      <c r="F1794" t="n">
+        <v>785</v>
+      </c>
+      <c r="G1794" t="inlineStr"/>
+      <c r="H1794" t="inlineStr">
+        <is>
+          <t>कुणाल के कोहिनूर Sona BLW Precision खरीदें PRICE 795.35 TARGET 820/840 STOP LOSS 785</t>
+        </is>
+      </c>
+      <c r="I1794" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1794" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:42:00</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1795" t="n">
+        <v>796.35</v>
+      </c>
+      <c r="E1795" t="n">
+        <v>840</v>
+      </c>
+      <c r="F1795" t="n">
+        <v>785</v>
+      </c>
+      <c r="G1795" t="inlineStr"/>
+      <c r="H1795" t="inlineStr">
+        <is>
+          <t>कुणाल के कोहिनूर Sona BLW Precision खरीदें PRICE 795.35 TARGET 820/840 STOP LOSS 785</t>
+        </is>
+      </c>
+      <c r="I1795" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1795" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:41:00</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>INDHOTEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1796" t="n">
+        <v>737.9</v>
+      </c>
+      <c r="E1796" t="n">
+        <v>762</v>
+      </c>
+      <c r="F1796" t="n">
+        <v>715</v>
+      </c>
+      <c r="G1796" t="inlineStr">
+        <is>
+          <t>Kunal Shah</t>
+        </is>
+      </c>
+      <c r="H1796" t="inlineStr">
+        <is>
+          <t>BTST CALL Indian Hotels Fut खरीदें PRICE 736.50 TARGET 755/762 STOP LOSS 715 ANALYST DISCLOSURE KUNAL SHAH Mirae Asset Sharekhan SEBI REG NO: INH000001758</t>
+        </is>
+      </c>
+      <c r="I1796" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1796" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:41:00</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>INDHOTEL29SEP26</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1797" t="n">
+        <v>736.55</v>
+      </c>
+      <c r="E1797" t="n">
+        <v>755</v>
+      </c>
+      <c r="F1797" t="n">
+        <v>715</v>
+      </c>
+      <c r="G1797" t="inlineStr">
+        <is>
+          <t>Kunal Shah</t>
+        </is>
+      </c>
+      <c r="H1797" t="inlineStr">
+        <is>
+          <t>BTST CALL Indian Hotels Fut खरीदें PRICE 736.50 TARGET 755/762 STOP LOSS 715 ANALYST DISCLOSURE KUNAL SHAH Mirae Asset Sharekhan SEBI REG NO: INH000001758</t>
+        </is>
+      </c>
+      <c r="I1797" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1797" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:39:20</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>SEL1440030SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr"/>
+      <c r="E1798" t="n">
+        <v>155</v>
+      </c>
+      <c r="F1798" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1798" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H1798" t="inlineStr">
+        <is>
+          <t>जय ठाकर की राय MIDCAP SEL 14400 की पुट @ 100/80 खरीदें STOP LOSS 57 TARGET 133/155 Nifty MidCap Sel 14492.20 70.35 STOCK OF THE DAY (BUY CALL)</t>
+        </is>
+      </c>
+      <c r="I1798" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1798" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:39:09</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>NIFTY1440029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr"/>
+      <c r="E1799" t="n">
+        <v>133</v>
+      </c>
+      <c r="F1799" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1799" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H1799" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय MIDCAP SEL 14400 की पुट @ 100/80 खरीदें STOP LOSS 57 TARGET 133/155 Nifty MidCap Sel 14492.85 ▲ 71.00</t>
+        </is>
+      </c>
+      <c r="I1799" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1799" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:39:09</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>NIFTY1440029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr"/>
+      <c r="E1800" t="n">
+        <v>155</v>
+      </c>
+      <c r="F1800" t="n">
+        <v>57</v>
+      </c>
+      <c r="G1800" t="inlineStr">
+        <is>
+          <t>Jay Thakkar</t>
+        </is>
+      </c>
+      <c r="H1800" t="inlineStr">
+        <is>
+          <t>जय ठक्कर की राय MIDCAP SEL 14400 की पुट @ 100/80 खरीदें STOP LOSS 57 TARGET 133/155 Nifty MidCap Sel 14492.85 ▲ 71.00</t>
+        </is>
+      </c>
+      <c r="I1800" t="inlineStr">
+        <is>
+          <t>660334d85662a7f64ae8911f</t>
+        </is>
+      </c>
+      <c r="J1800" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:38:00</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>CARRARO</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1801" t="n">
+        <v>527.75</v>
+      </c>
+      <c r="G1801" t="inlineStr"/>
+      <c r="H1801" t="inlineStr">
+        <is>
+          <t>CARRARO INDIA @ 520 खरीदें STOP LOSS -- TARGET 590/630</t>
+        </is>
+      </c>
+      <c r="I1801" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1801" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:37:07</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>CARRARO</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr"/>
+      <c r="E1802" t="n">
+        <v>630</v>
+      </c>
+      <c r="G1802" t="inlineStr"/>
+      <c r="H1802" t="inlineStr">
+        <is>
+          <t>जैन साब के GEMS CARRARO INDIA @ 520 खरीदें STOP LOSS -- TARGET 590/630</t>
+        </is>
+      </c>
+      <c r="I1802" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1802" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1803" t="n">
+        <v>3423</v>
+      </c>
+      <c r="E1803" t="n">
+        <v>4100</v>
+      </c>
+      <c r="G1803" t="inlineStr"/>
+      <c r="H1803" t="inlineStr">
+        <is>
+          <t>Supreme Ind खरीदें PRICE 3428.60 TARGET 3530/4100 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1803" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1803" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:34:00</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1804" t="n">
+        <v>3422.8</v>
+      </c>
+      <c r="E1804" t="n">
+        <v>3530</v>
+      </c>
+      <c r="G1804" t="inlineStr"/>
+      <c r="H1804" t="inlineStr">
+        <is>
+          <t>Supreme Ind खरीदें PRICE 3428.60 TARGET 3530/4100 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1804" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1804" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:29:56</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr"/>
+      <c r="E1805" t="n">
+        <v>4132.7</v>
+      </c>
+      <c r="G1805" t="inlineStr"/>
+      <c r="H1805" t="inlineStr">
+        <is>
+          <t>Sansera Engg 4132.70 INVESTMENT PICK 1727.00 24/12/2025 RECO PRICE RETURN TILL NOW 2405.70 139.30%</t>
+        </is>
+      </c>
+      <c r="I1805" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1805" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:29:51</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr"/>
+      <c r="E1806" t="n">
+        <v>4132.8</v>
+      </c>
+      <c r="G1806" t="inlineStr"/>
+      <c r="H1806" t="inlineStr">
+        <is>
+          <t>Sansera Engg 4132.80 INVESTMENT PICK 1727.00 24/12/2025 RECO PRICE RETURN TILL NOW 2405.80 139.31%</t>
+        </is>
+      </c>
+      <c r="I1806" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1806" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:29:47</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1807" t="inlineStr"/>
+      <c r="E1807" t="n">
+        <v>4131.4</v>
+      </c>
+      <c r="G1807" t="inlineStr"/>
+      <c r="H1807" t="inlineStr">
+        <is>
+          <t>Sansera Engg 4131.40 INVESTMENT PICK 1727.00 24/12/2025 RECO PRICE RETURN TILL NOW 2404.40 139.22%</t>
+        </is>
+      </c>
+      <c r="I1807" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1807" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:30:00</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1808" t="n">
+        <v>1192.5</v>
+      </c>
+      <c r="F1808" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1808" t="inlineStr"/>
+      <c r="H1808" t="inlineStr">
+        <is>
+          <t>OPENING का HERO Dr Reddy's Fut 1191.60 ▲ 19.20 TODAY 1192 HIGH 1192.40 LOW 1180.00 Vol: 358.13 k प्राइस ₹84 के नीचे का SL लगाएं</t>
+        </is>
+      </c>
+      <c r="I1808" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1808" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>EMMVEE</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1809" t="n">
+        <v>331.3</v>
+      </c>
+      <c r="E1809" t="n">
+        <v>348</v>
+      </c>
+      <c r="G1809" t="inlineStr"/>
+      <c r="H1809" t="inlineStr">
+        <is>
+          <t>SID Emmvee Photovoltaic 331.0 BUY TGT 348</t>
+        </is>
+      </c>
+      <c r="I1809" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1809" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1810" t="n">
+        <v>1046.8</v>
+      </c>
+      <c r="E1810" t="n">
+        <v>1070</v>
+      </c>
+      <c r="F1810" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G1810" t="inlineStr"/>
+      <c r="H1810" t="inlineStr">
+        <is>
+          <t>Max Healthcare खरीदें PRICE 1047.40 TARGET 1070/1090 STOP LOSS 1025</t>
+        </is>
+      </c>
+      <c r="I1810" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1810" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>MAXHEALTH</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1811" t="n">
+        <v>1046.8</v>
+      </c>
+      <c r="E1811" t="n">
+        <v>1090</v>
+      </c>
+      <c r="F1811" t="n">
+        <v>1025</v>
+      </c>
+      <c r="G1811" t="inlineStr"/>
+      <c r="H1811" t="inlineStr">
+        <is>
+          <t>Max Healthcare खरीदें PRICE 1047.90 TARGET 1070/1090 STOP LOSS 1025</t>
+        </is>
+      </c>
+      <c r="I1811" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1811" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1812" t="n">
+        <v>1421.2</v>
+      </c>
+      <c r="E1812" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F1812" t="n">
+        <v>1405</v>
+      </c>
+      <c r="G1812" t="inlineStr"/>
+      <c r="H1812" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Astral Ltd खरीदें PRICE 1422.00 TARGET 1445/1460 STOP LOSS 1405</t>
+        </is>
+      </c>
+      <c r="I1812" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1812" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1813" t="n">
+        <v>1421.5</v>
+      </c>
+      <c r="E1813" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F1813" t="n">
+        <v>1405</v>
+      </c>
+      <c r="G1813" t="inlineStr"/>
+      <c r="H1813" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Astral Ltd खरीदें PRICE 1420.50 TARGET 1445/1460 STOP LOSS 1405</t>
+        </is>
+      </c>
+      <c r="I1813" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1813" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1814" t="n">
+        <v>1421.5</v>
+      </c>
+      <c r="E1814" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F1814" t="n">
+        <v>1405</v>
+      </c>
+      <c r="G1814" t="inlineStr"/>
+      <c r="H1814" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Astral Ltd खरीदें PRICE 1421.60 TARGET 1445/1460 STOP LOSS 1405</t>
+        </is>
+      </c>
+      <c r="I1814" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1814" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:25:00</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1815" t="n">
+        <v>1421.5</v>
+      </c>
+      <c r="E1815" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F1815" t="n">
+        <v>1405</v>
+      </c>
+      <c r="G1815" t="inlineStr"/>
+      <c r="H1815" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Astral Ltd खरीदें PRICE 1421.60 TARGET 1445/1460 STOP LOSS 1405</t>
+        </is>
+      </c>
+      <c r="I1815" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1815" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>EMMVEE</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1816" t="n">
+        <v>331.85</v>
+      </c>
+      <c r="E1816" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1816" t="inlineStr"/>
+      <c r="H1816" t="inlineStr">
+        <is>
+          <t>Emmvee Photovoltaic खरीदें PRICE 333.00 TARGET 340/410 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1816" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1816" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>EMMVEE</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1817" t="n">
+        <v>331.85</v>
+      </c>
+      <c r="E1817" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1817" t="inlineStr"/>
+      <c r="H1817" t="inlineStr">
+        <is>
+          <t>SUPER SID Emmvee Photovoltaic खरीदें PRICE 332.40 TARGET 340/410 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1817" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1817" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>EMMVEE</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1818" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="E1818" t="n">
+        <v>340</v>
+      </c>
+      <c r="G1818" t="inlineStr"/>
+      <c r="H1818" t="inlineStr">
+        <is>
+          <t>SUPER SID Emmvee Photovoltaic खरीदें PRICE 331.85 TARGET 340/410 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1818" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1818" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:23:00</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>EMMVEE</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1819" t="n">
+        <v>332.6</v>
+      </c>
+      <c r="E1819" t="n">
+        <v>410</v>
+      </c>
+      <c r="G1819" t="inlineStr"/>
+      <c r="H1819" t="inlineStr">
+        <is>
+          <t>SUPER SID Emmvee Photovoltaic खरीदें PRICE 331.85 TARGET 340/410 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1819" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1819" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>M&amp;MFIN</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1820" t="n">
+        <v>349.85</v>
+      </c>
+      <c r="E1820" t="n">
+        <v>425</v>
+      </c>
+      <c r="G1820" t="inlineStr"/>
+      <c r="H1820" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+M&amp;M Fin
+349.85 +4.15
+ACCUMULATE
+लक्ष्य ₹425</t>
+        </is>
+      </c>
+      <c r="I1820" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1820" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1821" t="n">
+        <v>725.85</v>
+      </c>
+      <c r="E1821" t="n">
+        <v>875</v>
+      </c>
+      <c r="G1821" t="inlineStr"/>
+      <c r="H1821" t="inlineStr">
+        <is>
+          <t>Indian Hotels 725.85 -0.80 BUY लक्ष्य ₹875</t>
+        </is>
+      </c>
+      <c r="I1821" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1821" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1822" t="n">
+        <v>3868.1</v>
+      </c>
+      <c r="E1822" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G1822" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1822" t="inlineStr">
+        <is>
+          <t>जेफरीज L&amp;T 3845.00 +8.80 BUY लक्ष्य ₹5000</t>
+        </is>
+      </c>
+      <c r="I1822" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1822" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1823" t="n">
+        <v>2405.6</v>
+      </c>
+      <c r="E1823" t="n">
+        <v>3130</v>
+      </c>
+      <c r="G1823" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1823" t="inlineStr">
+        <is>
+          <t>जेफरीज HDFC AMC 2424.70 +1.55% BUY लक्ष्य ₹3130</t>
+        </is>
+      </c>
+      <c r="I1823" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1823" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1824" t="n">
+        <v>2411.9</v>
+      </c>
+      <c r="E1824" t="n">
+        <v>3130</v>
+      </c>
+      <c r="G1824" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1824" t="inlineStr">
+        <is>
+          <t>जेफरीज HDFC AMC 2430.00 +42.30 BUY लक्ष्य ₹3130</t>
+        </is>
+      </c>
+      <c r="I1824" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1824" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1825" t="n">
+        <v>5335.5</v>
+      </c>
+      <c r="F1825" t="n">
+        <v>84</v>
+      </c>
+      <c r="G1825" t="inlineStr"/>
+      <c r="H1825" t="inlineStr">
+        <is>
+          <t>HERO MOTORS IPO पर सलाह लिस्टिंग के बाद IPO प्राइस ₹84 के नीचे का SL लगाएं</t>
+        </is>
+      </c>
+      <c r="I1825" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1825" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1826" t="n">
+        <v>1274.2</v>
+      </c>
+      <c r="E1826" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G1826" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1826" t="inlineStr">
+        <is>
+          <t>जेफरीज Adani Green Energy 1275.00 +0.80 BUY लक्ष्य ₹1300</t>
+        </is>
+      </c>
+      <c r="I1826" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1826" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1827" t="n">
+        <v>1380.9</v>
+      </c>
+      <c r="E1827" t="n">
+        <v>2060</v>
+      </c>
+      <c r="G1827" t="inlineStr"/>
+      <c r="H1827" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Adani Energy
+1371.00 -15.80
+BUY
+लक्ष्य ₹2060</t>
+        </is>
+      </c>
+      <c r="I1827" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1827" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1828" t="n">
+        <v>1180</v>
+      </c>
+      <c r="E1828" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G1828" t="inlineStr"/>
+      <c r="H1828" t="inlineStr">
+        <is>
+          <t>STOCK FTH D Dr Reddys Futures PRICE 1172.50 TARGET 1132, 1195, 1200</t>
+        </is>
+      </c>
+      <c r="I1828" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1828" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1829" t="n">
+        <v>1180</v>
+      </c>
+      <c r="E1829" t="n">
+        <v>1195</v>
+      </c>
+      <c r="G1829" t="inlineStr"/>
+      <c r="H1829" t="inlineStr">
+        <is>
+          <t>STOCK FTH D Dr Reddys Futures PRICE 1172.50 TARGET 1132, 1195, 1200</t>
+        </is>
+      </c>
+      <c r="I1829" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1829" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>HDFCBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1830" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="E1830" t="n">
+        <v>722</v>
+      </c>
+      <c r="F1830" t="n">
+        <v>700</v>
+      </c>
+      <c r="G1830" t="inlineStr"/>
+      <c r="H1830" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह HDFC Bank Futures PRICE 715.50 TARGET 722, 730, 738 STOP LOSS 700</t>
+        </is>
+      </c>
+      <c r="I1830" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1830" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>HDFCBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1831" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="E1831" t="n">
+        <v>730</v>
+      </c>
+      <c r="F1831" t="n">
+        <v>700</v>
+      </c>
+      <c r="G1831" t="inlineStr"/>
+      <c r="H1831" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह HDFC Bank Futures PRICE 715.50 TARGET 722, 730, 738 STOP LOSS 700</t>
+        </is>
+      </c>
+      <c r="I1831" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1831" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>HDFCBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1832" t="n">
+        <v>717.5</v>
+      </c>
+      <c r="E1832" t="n">
+        <v>738</v>
+      </c>
+      <c r="F1832" t="n">
+        <v>700</v>
+      </c>
+      <c r="G1832" t="inlineStr"/>
+      <c r="H1832" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह HDFC Bank Futures PRICE 715.50 TARGET 722, 730, 738 STOP LOSS 700</t>
+        </is>
+      </c>
+      <c r="I1832" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1832" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1833" t="n">
+        <v>1748</v>
+      </c>
+      <c r="E1833" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G1833" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1833" t="inlineStr">
+        <is>
+          <t>जेफरीज Adani Ports 1765.00 +26.70 BUY लक्ष्य ₹2160</t>
+        </is>
+      </c>
+      <c r="I1833" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1833" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1834" t="n">
+        <v>597</v>
+      </c>
+      <c r="E1834" t="n">
+        <v>725</v>
+      </c>
+      <c r="G1834" t="inlineStr"/>
+      <c r="H1834" t="inlineStr">
+        <is>
+          <t>INVESTMENT INDEGENE B 725 12 MONTH</t>
+        </is>
+      </c>
+      <c r="I1834" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1834" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1835" t="n">
+        <v>2461.3</v>
+      </c>
+      <c r="E1835" t="n">
+        <v>2503</v>
+      </c>
+      <c r="F1835" t="n">
+        <v>2429</v>
+      </c>
+      <c r="G1835" t="inlineStr"/>
+      <c r="H1835" t="inlineStr">
+        <is>
+          <t>MY CHOICE ASIAN PAINTS B 2503 2429</t>
+        </is>
+      </c>
+      <c r="I1835" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1835" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1836" t="n">
+        <v>284.85</v>
+      </c>
+      <c r="E1836" t="n">
+        <v>290</v>
+      </c>
+      <c r="F1836" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1836" t="inlineStr"/>
+      <c r="H1836" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT PETRONET LNG B 290 280</t>
+        </is>
+      </c>
+      <c r="I1836" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1836" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1837" t="n">
+        <v>557.1</v>
+      </c>
+      <c r="E1837" t="n">
+        <v>570</v>
+      </c>
+      <c r="F1837" t="n">
+        <v>550</v>
+      </c>
+      <c r="G1837" t="inlineStr"/>
+      <c r="H1837" t="inlineStr">
+        <is>
+          <t>TECHNO HDFC LIFE B 570 550</t>
+        </is>
+      </c>
+      <c r="I1837" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1837" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1838" t="n">
+        <v>419.35</v>
+      </c>
+      <c r="E1838" t="n">
+        <v>428</v>
+      </c>
+      <c r="F1838" t="n">
+        <v>408</v>
+      </c>
+      <c r="G1838" t="inlineStr"/>
+      <c r="H1838" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Exide Ind BUY PRICE 418.60 TARGET 428/438 STOP LOSS 408</t>
+        </is>
+      </c>
+      <c r="I1838" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1838" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1839" t="n">
+        <v>419.35</v>
+      </c>
+      <c r="E1839" t="n">
+        <v>438</v>
+      </c>
+      <c r="F1839" t="n">
+        <v>408</v>
+      </c>
+      <c r="G1839" t="inlineStr"/>
+      <c r="H1839" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Exide Ind BUY PRICE 418.60 TARGET 428/438 STOP LOSS 408</t>
+        </is>
+      </c>
+      <c r="I1839" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1839" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1840" t="n">
+        <v>185</v>
+      </c>
+      <c r="E1840" t="n">
+        <v>190</v>
+      </c>
+      <c r="F1840" t="n">
+        <v>145</v>
+      </c>
+      <c r="G1840" t="inlineStr"/>
+      <c r="H1840" t="inlineStr">
+        <is>
+          <t>JP मॉर्गन
+Pine Labs
+184.48 -0.66%
+NEUTRAL
+लक्ष्य ₹145 से बढ़ाकर ₹190</t>
+        </is>
+      </c>
+      <c r="I1840" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1840" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1841" t="n">
+        <v>397.4</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>405</v>
+      </c>
+      <c r="G1841" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1841" t="inlineStr">
+        <is>
+          <t>ANALYST DISCLOSURE Siddharth Sedani Anand Rathi Shares and Stock Brokers SEBI REG NO: INH000000834 ALL STOCKS DISCUSSED Financial Interest Analyst NO Analyst's Relative NO Analyst's Associate / Firm MAY BE BEL BUY PRICE 395.45 TARGET 405/500 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1841" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1841" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1842" t="n">
+        <v>397.4</v>
+      </c>
+      <c r="E1842" t="n">
+        <v>500</v>
+      </c>
+      <c r="G1842" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1842" t="inlineStr">
+        <is>
+          <t>ANALYST DISCLOSURE Siddharth Sedani Anand Rathi Shares and Stock Brokers SEBI REG NO: INH000000834 ALL STOCKS DISCUSSED Financial Interest Analyst NO Analyst's Relative NO Analyst's Associate / Firm MAY BE BEL BUY PRICE 395.45 TARGET 405/500 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1842" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1842" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>SAPPHIRE</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1843" t="n">
+        <v>235</v>
+      </c>
+      <c r="E1843" t="n">
+        <v>242</v>
+      </c>
+      <c r="F1843" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1843" t="inlineStr">
+        <is>
+          <t>Kunal Shah</t>
+        </is>
+      </c>
+      <c r="H1843" t="inlineStr">
+        <is>
+          <t>कुणाल शाह की राय Sapphire Foods BUY PRICE 233.24 TARGET 242/246 STOP LOSS 224</t>
+        </is>
+      </c>
+      <c r="I1843" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1843" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>SAPPHIRE</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1844" t="n">
+        <v>233.29</v>
+      </c>
+      <c r="E1844" t="n">
+        <v>246</v>
+      </c>
+      <c r="F1844" t="n">
+        <v>224</v>
+      </c>
+      <c r="G1844" t="inlineStr">
+        <is>
+          <t>Kunal Shah</t>
+        </is>
+      </c>
+      <c r="H1844" t="inlineStr">
+        <is>
+          <t>कुणाल शाह की राय Sapphire Foods BUY PRICE 233.24 TARGET 242/246 STOP LOSS 224</t>
+        </is>
+      </c>
+      <c r="I1844" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1844" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1845" t="n">
+        <v>86</v>
+      </c>
+      <c r="E1845" t="n">
+        <v>90</v>
+      </c>
+      <c r="F1845" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G1845" t="inlineStr"/>
+      <c r="H1845" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY IDFC First Bank BUY PRICE 86.33 TARGET 88.5/90 STOP LOSS 84.5</t>
+        </is>
+      </c>
+      <c r="I1845" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1845" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1846" t="n">
+        <v>86</v>
+      </c>
+      <c r="E1846" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="F1846" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="G1846" t="inlineStr">
+        <is>
+          <t>Kunal Shah</t>
+        </is>
+      </c>
+      <c r="H1846" t="inlineStr">
+        <is>
+          <t>कुणाल शाह की राय IDFC First Bank BUY PRICE 86.33 TARGET 88.5/90 STOP LOSS 84.5</t>
+        </is>
+      </c>
+      <c r="I1846" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1846" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1847" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="E1847" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F1847" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G1847" t="inlineStr"/>
+      <c r="H1847" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+PVR INOX
+BUY
+PRICE ▶ 1272.70
+TARGET ▶ 1310/1330
+STOP LOSS ▶ 1250</t>
+        </is>
+      </c>
+      <c r="I1847" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1847" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1848" t="n">
+        <v>1277.5</v>
+      </c>
+      <c r="E1848" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F1848" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G1848" t="inlineStr"/>
+      <c r="H1848" t="inlineStr">
+        <is>
+          <t>PICK F TH DAY PVR INOX BUY PRICE 1272.70 TARGET 1310/1330 STOP LOSS 1250</t>
+        </is>
+      </c>
+      <c r="I1848" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1848" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>VIJAYA</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1849" t="n">
+        <v>1510</v>
+      </c>
+      <c r="E1849" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F1849" t="n">
+        <v>1465</v>
+      </c>
+      <c r="G1849" t="inlineStr"/>
+      <c r="H1849" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Vijaya Diagnostic BUY PRICE 1506.10 TARGET 1580/1620 STOP LOSS 1465</t>
+        </is>
+      </c>
+      <c r="I1849" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1849" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>VIJAYA</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1850" t="n">
+        <v>1510</v>
+      </c>
+      <c r="E1850" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1850" t="n">
+        <v>1465</v>
+      </c>
+      <c r="G1850" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1850" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Vijaya Diagnostic BUY PRICE 1506.10 TARGET 1580/1620 STOP LOSS 1465</t>
+        </is>
+      </c>
+      <c r="I1850" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1850" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>VIJAYA</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1851" t="n">
+        <v>1510</v>
+      </c>
+      <c r="E1851" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F1851" t="n">
+        <v>1465</v>
+      </c>
+      <c r="G1851" t="inlineStr"/>
+      <c r="H1851" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Vijaya Diagnostic BUY PRICE 1505.10 TARGET 1580/1620 STOP LOSS 1465</t>
+        </is>
+      </c>
+      <c r="I1851" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1851" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>VIJAYA</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1852" t="n">
+        <v>1510</v>
+      </c>
+      <c r="E1852" t="n">
+        <v>1620</v>
+      </c>
+      <c r="F1852" t="n">
+        <v>1465</v>
+      </c>
+      <c r="G1852" t="inlineStr"/>
+      <c r="H1852" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Vijaya Diagnostic BUY PRICE 1505.10 TARGET 1580/1620 STOP LOSS 1465</t>
+        </is>
+      </c>
+      <c r="I1852" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1852" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1853" t="n">
+        <v>874</v>
+      </c>
+      <c r="E1853" t="n">
+        <v>910</v>
+      </c>
+      <c r="F1853" t="n">
+        <v>850</v>
+      </c>
+      <c r="G1853" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1853" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय
+Granules India
+BUY
+PRICE ▶ 870.40
+TARGET ▶ 910/930
+STOP LOSS ▶ 850</t>
+        </is>
+      </c>
+      <c r="I1853" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1853" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1854" t="n">
+        <v>874</v>
+      </c>
+      <c r="E1854" t="n">
+        <v>930</v>
+      </c>
+      <c r="F1854" t="n">
+        <v>850</v>
+      </c>
+      <c r="G1854" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H1854" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Granules India UY PRICE 870.40 TARGET 910/930 STOP LOSS 850</t>
+        </is>
+      </c>
+      <c r="I1854" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1854" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1855" t="n">
+        <v>1274.2</v>
+      </c>
+      <c r="E1855" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G1855" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1855" t="inlineStr">
+        <is>
+          <t>Adani Green Energy BUY 1300</t>
+        </is>
+      </c>
+      <c r="I1855" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1855" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>BEL</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1856" t="n">
+        <v>397.4</v>
+      </c>
+      <c r="E1856" t="n">
+        <v>550</v>
+      </c>
+      <c r="G1856" t="inlineStr"/>
+      <c r="H1856" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT मैक्वायरी OUTPERFORM BEL 395.45 2.51% TARGET ₹550</t>
+        </is>
+      </c>
+      <c r="I1856" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1856" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>PINELABS</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1857" t="n">
+        <v>185</v>
+      </c>
+      <c r="E1857" t="n">
+        <v>190</v>
+      </c>
+      <c r="G1857" t="inlineStr">
+        <is>
+          <t>JP Morgan</t>
+        </is>
+      </c>
+      <c r="H1857" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT JP मॉर्गन NEUTRAL Pine Labs 184.48 0.66% लक्ष्य ₹145 से बढ़ाकर ₹190</t>
+        </is>
+      </c>
+      <c r="I1857" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1857" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1858" t="n">
+        <v>1766</v>
+      </c>
+      <c r="E1858" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G1858" t="inlineStr">
+        <is>
+          <t>JP Morgan</t>
+        </is>
+      </c>
+      <c r="H1858" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT JP मॉर्गन OVERWEIGHT Paytm 1763.00 लक्ष्य ₹1300 से बढ़ाकर ₹2100</t>
+        </is>
+      </c>
+      <c r="I1858" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1858" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1859" t="n">
+        <v>5325</v>
+      </c>
+      <c r="E1859" t="n">
+        <v>6845</v>
+      </c>
+      <c r="G1859" t="inlineStr"/>
+      <c r="H1859" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Hero Motocorp 5325.00 +1.72% OVERWEIGHT लक्ष्य ₹6845</t>
+        </is>
+      </c>
+      <c r="I1859" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1859" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1860" t="n">
+        <v>3711.1</v>
+      </c>
+      <c r="E1860" t="n">
+        <v>3520</v>
+      </c>
+      <c r="G1860" t="inlineStr"/>
+      <c r="H1860" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Avenue Supermarts
+3711.20 -8.80
+REDUCE
+लक्ष्य ₹3530 से घटाकर ₹3520</t>
+        </is>
+      </c>
+      <c r="I1860" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1860" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1861" t="n">
+        <v>334.25</v>
+      </c>
+      <c r="E1861" t="n">
+        <v>331</v>
+      </c>
+      <c r="F1861" t="n">
+        <v>345</v>
+      </c>
+      <c r="G1861" t="inlineStr"/>
+      <c r="H1861" t="inlineStr">
+        <is>
+          <t>Federal Bank Futures SELL PRICE 334.75 TARGET 331, 328, 325 STOP LOSS 345</t>
+        </is>
+      </c>
+      <c r="I1861" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1861" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1862" t="n">
+        <v>334.25</v>
+      </c>
+      <c r="E1862" t="n">
+        <v>328</v>
+      </c>
+      <c r="F1862" t="n">
+        <v>345</v>
+      </c>
+      <c r="G1862" t="inlineStr"/>
+      <c r="H1862" t="inlineStr">
+        <is>
+          <t>Federal Bank Futures SELL PRICE 334.75 TARGET 331, 328, 325 STOP LOSS 345</t>
+        </is>
+      </c>
+      <c r="I1862" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1862" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>FEDERALBNK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1863" t="n">
+        <v>333.75</v>
+      </c>
+      <c r="E1863" t="n">
+        <v>325</v>
+      </c>
+      <c r="F1863" t="n">
+        <v>345</v>
+      </c>
+      <c r="G1863" t="inlineStr"/>
+      <c r="H1863" t="inlineStr">
+        <is>
+          <t>Federal Bank Futures SELL PRICE 334.75 TARGET 331, 328, 325 STOP LOSS 345</t>
+        </is>
+      </c>
+      <c r="I1863" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1863" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>POLICYBZR29SEP26</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1864" t="n">
+        <v>1768</v>
+      </c>
+      <c r="E1864" t="n">
+        <v>1810</v>
+      </c>
+      <c r="F1864" t="n">
+        <v>1715</v>
+      </c>
+      <c r="G1864" t="inlineStr"/>
+      <c r="H1864" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY PB Fintech Futures BUY PRICE 1761 TARGET 1775, 1790, 1810 STOP LOSS 1715</t>
+        </is>
+      </c>
+      <c r="I1864" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1864" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>INDIGO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1865" t="n">
+        <v>4922.5</v>
+      </c>
+      <c r="E1865" t="n">
+        <v>4990</v>
+      </c>
+      <c r="F1865" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G1865" t="inlineStr"/>
+      <c r="H1865" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह Indigo Futures BUY PRICE 4879 TARGET 4910, 4950, 4990 STOP LOSS 4800</t>
+        </is>
+      </c>
+      <c r="I1865" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1865" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>NATIONALUM29SEP26</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1866" t="n">
+        <v>359</v>
+      </c>
+      <c r="E1866" t="n">
+        <v>365</v>
+      </c>
+      <c r="F1866" t="n">
+        <v>354</v>
+      </c>
+      <c r="G1866" t="inlineStr"/>
+      <c r="H1866" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Nalco Futures
+PRICE ▶ 357.50
+TARGET ▶ 361, 365, 370
+STOP LOSS ▶ 354</t>
+        </is>
+      </c>
+      <c r="I1866" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1866" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>NATIONALUM29SEP26</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1867" t="n">
+        <v>359</v>
+      </c>
+      <c r="E1867" t="n">
+        <v>370</v>
+      </c>
+      <c r="F1867" t="n">
+        <v>354</v>
+      </c>
+      <c r="G1867" t="inlineStr"/>
+      <c r="H1867" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह
+Nalco Futures
+PRICE ▶ 357.50
+TARGET ▶ 361, 365, 370
+STOP LOSS ▶ 354</t>
+        </is>
+      </c>
+      <c r="I1867" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1867" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1868" t="n">
+        <v>206.05</v>
+      </c>
+      <c r="E1868" t="n">
+        <v>270</v>
+      </c>
+      <c r="G1868" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1868" t="inlineStr">
+        <is>
+          <t>जेफरीज
+Adani Power
+205.92 +1.77%
+BUY
+लक्ष्य ₹270</t>
+        </is>
+      </c>
+      <c r="I1868" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1868" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1869" t="n">
+        <v>1180</v>
+      </c>
+      <c r="E1869" t="n">
+        <v>1195</v>
+      </c>
+      <c r="F1869" t="n">
+        <v>1155</v>
+      </c>
+      <c r="G1869" t="inlineStr"/>
+      <c r="H1869" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Dr Reddys Futures
+BUY
+PRICE ▶ 1172.50
+TARGET ▶ 1182, 1195, 1205
+STOP LOSS ▶ 1155</t>
+        </is>
+      </c>
+      <c r="I1869" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1869" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>DRREDDY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1870" t="n">
+        <v>1180</v>
+      </c>
+      <c r="E1870" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F1870" t="n">
+        <v>1155</v>
+      </c>
+      <c r="G1870" t="inlineStr"/>
+      <c r="H1870" t="inlineStr">
+        <is>
+          <t>STOCK OF THE DAY
+Dr Reddys Futures
+BUY
+PRICE ▶ 1172.50
+TARGET ▶ 1182, 1195, 1205
+STOP LOSS ▶ 1155</t>
+        </is>
+      </c>
+      <c r="I1870" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1870" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1871" t="n">
+        <v>1380.9</v>
+      </c>
+      <c r="E1871" t="n">
+        <v>2060</v>
+      </c>
+      <c r="G1871" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1871" t="inlineStr">
+        <is>
+          <t>जेफरीज
+Adani Energy
+1386.80 +2.79%
+BUY
+लक्ष्य ₹2060</t>
+        </is>
+      </c>
+      <c r="I1871" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1871" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1872" t="n">
+        <v>1748</v>
+      </c>
+      <c r="E1872" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G1872" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1872" t="inlineStr">
+        <is>
+          <t>जेफरीज Adani Ports 1738.30 +0.84% BUY लक्ष्य ₹2160</t>
+        </is>
+      </c>
+      <c r="I1872" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1872" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1873" t="n">
+        <v>595.55</v>
+      </c>
+      <c r="E1873" t="n">
+        <v>725</v>
+      </c>
+      <c r="F1873" t="n">
+        <v>520</v>
+      </c>
+      <c r="G1873" t="inlineStr"/>
+      <c r="H1873" t="inlineStr">
+        <is>
+          <t>नेहा के शेयर
+Indegene
+खरीदें
+PRICE 591.75
+TARGET 725
+STOP LOSS 520</t>
+        </is>
+      </c>
+      <c r="I1873" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1873" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1874" t="n">
+        <v>135.02</v>
+      </c>
+      <c r="E1874" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="F1874" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="G1874" t="inlineStr"/>
+      <c r="H1874" t="inlineStr">
+        <is>
+          <t>MY CHOICE IOC B 137.50 132.50</t>
+        </is>
+      </c>
+      <c r="I1874" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1874" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1875" t="n">
+        <v>308.55</v>
+      </c>
+      <c r="E1875" t="n">
+        <v>312</v>
+      </c>
+      <c r="F1875" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="G1875" t="inlineStr"/>
+      <c r="H1875" t="inlineStr">
+        <is>
+          <t>MY CHOICE BPCL B 312 304.50</t>
+        </is>
+      </c>
+      <c r="I1875" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1875" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1876" t="n">
+        <v>595.55</v>
+      </c>
+      <c r="E1876" t="n">
+        <v>7725</v>
+      </c>
+      <c r="G1876" t="inlineStr"/>
+      <c r="H1876" t="inlineStr">
+        <is>
+          <t>INVESTMENT INDIGENE B 7725 12M</t>
+        </is>
+      </c>
+      <c r="I1876" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1876" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1877" t="n">
+        <v>1206.6</v>
+      </c>
+      <c r="E1877" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F1877" t="n">
+        <v>1185</v>
+      </c>
+      <c r="G1877" t="inlineStr"/>
+      <c r="H1877" t="inlineStr">
+        <is>
+          <t>CASH SCHNEIDER INFRA B 1230 1185</t>
+        </is>
+      </c>
+      <c r="I1877" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1877" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1878" t="n">
+        <v>2405.6</v>
+      </c>
+      <c r="E1878" t="n">
+        <v>2440</v>
+      </c>
+      <c r="F1878" t="n">
+        <v>2363</v>
+      </c>
+      <c r="G1878" t="inlineStr"/>
+      <c r="H1878" t="inlineStr">
+        <is>
+          <t>TECHNO HDFC AMC B 2440 2363</t>
+        </is>
+      </c>
+      <c r="I1878" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1878" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1879" t="n">
+        <v>1274.2</v>
+      </c>
+      <c r="E1879" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1879" t="n">
+        <v>1261</v>
+      </c>
+      <c r="G1879" t="inlineStr"/>
+      <c r="H1879" t="inlineStr">
+        <is>
+          <t>FUNDA ADANI GREEN B 1300 1261</t>
+        </is>
+      </c>
+      <c r="I1879" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1879" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>RBLBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1880" t="n">
+        <v>407.3</v>
+      </c>
+      <c r="E1880" t="n">
+        <v>411</v>
+      </c>
+      <c r="F1880" t="n">
+        <v>405</v>
+      </c>
+      <c r="G1880" t="inlineStr"/>
+      <c r="H1880" t="inlineStr">
+        <is>
+          <t>FUTURE RBL BANK FUT B 411 405</t>
+        </is>
+      </c>
+      <c r="I1880" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1880" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1881" t="n">
+        <v>820.05</v>
+      </c>
+      <c r="E1881" t="n">
+        <v>840</v>
+      </c>
+      <c r="F1881" t="n">
+        <v>808</v>
+      </c>
+      <c r="G1881" t="inlineStr"/>
+      <c r="H1881" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+Marico
+खरीदें
+PRICE 817.00
+TARGET 840
+STOP LOSS 808</t>
+        </is>
+      </c>
+      <c r="I1881" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1881" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>PURVA</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1882" t="n">
+        <v>218.85</v>
+      </c>
+      <c r="E1882" t="n">
+        <v>222</v>
+      </c>
+      <c r="F1882" t="n">
+        <v>215</v>
+      </c>
+      <c r="G1882" t="inlineStr"/>
+      <c r="H1882" t="inlineStr">
+        <is>
+          <t>Puravankara खरीदें PRICE 218.40 TARGET 222 STOP LOSS 215</t>
+        </is>
+      </c>
+      <c r="I1882" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1882" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1883" t="n">
+        <v>284.85</v>
+      </c>
+      <c r="E1883" t="n">
+        <v>290</v>
+      </c>
+      <c r="F1883" t="n">
+        <v>280</v>
+      </c>
+      <c r="G1883" t="inlineStr"/>
+      <c r="H1883" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+Petronet LNG
+खरीदें
+PRICE → 283.45
+TARGET → 290
+STOP LOSS → 280</t>
+        </is>
+      </c>
+      <c r="I1883" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1883" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1884" t="n">
+        <v>4125</v>
+      </c>
+      <c r="E1884" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G1884" t="inlineStr"/>
+      <c r="H1884" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK TVS Motor PRICE 4101.70 TARGET 4500</t>
+        </is>
+      </c>
+      <c r="I1884" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1884" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>INDGN</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1885" t="n">
+        <v>595.55</v>
+      </c>
+      <c r="E1885" t="n">
+        <v>725</v>
+      </c>
+      <c r="G1885" t="inlineStr"/>
+      <c r="H1885" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK
+Indegene
+खरीदें
+PRICE ▶ 591.75
+TARGET ▶ 725
+DURATION ▶ 12 महीने</t>
+        </is>
+      </c>
+      <c r="I1885" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1885" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1886" t="n">
+        <v>1274.2</v>
+      </c>
+      <c r="E1886" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1886" t="n">
+        <v>1261</v>
+      </c>
+      <c r="G1886" t="inlineStr"/>
+      <c r="H1886" t="inlineStr">
+        <is>
+          <t>FUNDA PICK
+Adani Green Energy
+खरीदें
+PRICE ▶ 1274.20
+TARGET ▶ 1300
+STOP LOSS ▶ 1261</t>
+        </is>
+      </c>
+      <c r="I1886" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1886" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1887" t="n">
+        <v>4804.9</v>
+      </c>
+      <c r="E1887" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G1887" t="inlineStr"/>
+      <c r="H1887" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर HAL खरीदें PRICE 4788.00 TARGET 5000 DURATION 6 महीने</t>
+        </is>
+      </c>
+      <c r="I1887" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1887" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1888" t="n">
+        <v>1206.6</v>
+      </c>
+      <c r="E1888" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F1888" t="n">
+        <v>1185</v>
+      </c>
+      <c r="G1888" t="inlineStr"/>
+      <c r="H1888" t="inlineStr">
+        <is>
+          <t>Schneider Electric खरीदें PRICE 1201.90 TARGET 1230 STOP LOSS 1185</t>
+        </is>
+      </c>
+      <c r="I1888" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1888" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1889" t="n">
+        <v>1274.2</v>
+      </c>
+      <c r="E1889" t="n">
+        <v>3130</v>
+      </c>
+      <c r="G1889" t="inlineStr"/>
+      <c r="H1889" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS BUY लक्ष्य ₹3130</t>
+        </is>
+      </c>
+      <c r="I1889" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1889" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1890" t="n">
+        <v>1274.2</v>
+      </c>
+      <c r="E1890" t="n">
+        <v>1380</v>
+      </c>
+      <c r="G1890" t="inlineStr"/>
+      <c r="H1890" t="inlineStr">
+        <is>
+          <t>CALLS
+Adani Green Energy
+1274 BUY
+लक्ष्य ₹1380</t>
+        </is>
+      </c>
+      <c r="I1890" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1890" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1891" t="n">
+        <v>1351.9</v>
+      </c>
+      <c r="E1891" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F1891" t="n">
+        <v>1320</v>
+      </c>
+      <c r="G1891" t="inlineStr"/>
+      <c r="H1891" t="inlineStr">
+        <is>
+          <t>श्रीकांत चौहान की राय ICICI Bank खरीदें PRICE 1347.60 TARGET 1390 STOP LOSS 1320</t>
+        </is>
+      </c>
+      <c r="I1891" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1891" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>HDFCLIFE</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1892" t="n">
+        <v>557.1</v>
+      </c>
+      <c r="E1892" t="n">
+        <v>590</v>
+      </c>
+      <c r="F1892" t="n">
+        <v>545</v>
+      </c>
+      <c r="G1892" t="inlineStr"/>
+      <c r="H1892" t="inlineStr">
+        <is>
+          <t>TRADING CALL HDFC Life खरीदें PRICE 556.75 TARGET 590 STOP LOSS 545</t>
+        </is>
+      </c>
+      <c r="I1892" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1892" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>M&amp;MFIN</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1893" t="n">
+        <v>348.15</v>
+      </c>
+      <c r="E1893" t="n">
+        <v>425</v>
+      </c>
+      <c r="G1893" t="inlineStr"/>
+      <c r="H1893" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+M&amp;M Fin
+345.70
+ACCUMULATE
+लक्ष्य ₹425</t>
+        </is>
+      </c>
+      <c r="I1893" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1893" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1894" t="n">
+        <v>725.85</v>
+      </c>
+      <c r="E1894" t="n">
+        <v>875</v>
+      </c>
+      <c r="G1894" t="inlineStr"/>
+      <c r="H1894" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Indian Hotels 726.65 +13.25 BUY लक्ष्य ₹875</t>
+        </is>
+      </c>
+      <c r="I1894" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1894" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1895" t="n">
+        <v>3866.9</v>
+      </c>
+      <c r="E1895" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G1895" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1895" t="inlineStr">
+        <is>
+          <t>जेफरीज L&amp;T 3836.20 +28.50 BUY लक्ष्य ₹5000</t>
+        </is>
+      </c>
+      <c r="I1895" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1895" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1896" t="n">
+        <v>2405.6</v>
+      </c>
+      <c r="E1896" t="n">
+        <v>3130</v>
+      </c>
+      <c r="G1896" t="inlineStr"/>
+      <c r="H1896" t="inlineStr">
+        <is>
+          <t>HDFC AMC 2387.70 +14.60 BUY लक्ष्य ₹3130</t>
+        </is>
+      </c>
+      <c r="I1896" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1896" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>2026-09-18 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1897" t="n">
+        <v>1274.2</v>
+      </c>
+      <c r="E1897" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G1897" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H1897" t="inlineStr">
+        <is>
+          <t>जेफरीज Adani Green Energy 1274.20 +4.00 BUY लक्ष्य ₹1300</t>
+        </is>
+      </c>
+      <c r="I1897" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1897" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1756"/>
+  <autoFilter ref="A1:J1897"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -73929,14 +73929,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1757" t="inlineStr"/>
       <c r="E1757" t="n">
         <v>70</v>
       </c>
       <c r="F1757" t="n">
         <v>331</v>
       </c>
-      <c r="G1757" t="inlineStr"/>
       <c r="H1757" t="inlineStr">
         <is>
           <t>Sunflag Iron @ 346 खरीदें STOP LOSS 331 TARGET 70 DURATION 1-3 महीने</t>
@@ -73969,7 +73967,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1758" t="inlineStr"/>
       <c r="E1758" t="n">
         <v>370</v>
       </c>
@@ -74013,14 +74010,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1759" t="inlineStr"/>
       <c r="E1759" t="n">
         <v>1350</v>
       </c>
       <c r="F1759" t="n">
         <v>1180</v>
       </c>
-      <c r="G1759" t="inlineStr"/>
       <c r="H1759" t="inlineStr">
         <is>
           <t>POSITIONAL MIDCAP STOCK Action Cons खरीदें STOP LOSS 1180 TARGET 1350/1370 DURAT 4-5 दिन Action Cons 1289.79</t>
@@ -74053,14 +74048,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1760" t="inlineStr"/>
       <c r="E1760" t="n">
         <v>1370</v>
       </c>
       <c r="F1760" t="n">
         <v>1180</v>
       </c>
-      <c r="G1760" t="inlineStr"/>
       <c r="H1760" t="inlineStr">
         <is>
           <t>POSITIONAL MIDCAP STOCK Action Cons खरीदें STOP LOSS 1180 TARGET 1350/1370 DURAT 4-5 दिन Action Cons 1289.79</t>
@@ -74093,14 +74086,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1761" t="inlineStr"/>
       <c r="E1761" t="n">
         <v>1370</v>
       </c>
       <c r="F1761" t="n">
         <v>1180</v>
       </c>
-      <c r="G1761" t="inlineStr"/>
       <c r="H1761" t="inlineStr">
         <is>
           <t>Action Cons खरीदें STOP LOSS 1180 TARGET 1350/1370 DURATION 4-8 महीने Action Cons 1230.70</t>
@@ -74142,7 +74133,6 @@
       <c r="F1762" t="n">
         <v>1180</v>
       </c>
-      <c r="G1762" t="inlineStr"/>
       <c r="H1762" t="inlineStr">
         <is>
           <t>POSITIONAL MIDCAP STOCKS
@@ -74188,7 +74178,6 @@
       <c r="F1763" t="n">
         <v>1180</v>
       </c>
-      <c r="G1763" t="inlineStr"/>
       <c r="H1763" t="inlineStr">
         <is>
           <t>POSITIONAL MIDCAP STOCKS
@@ -74234,7 +74223,6 @@
       <c r="F1764" t="n">
         <v>168</v>
       </c>
-      <c r="G1764" t="inlineStr"/>
       <c r="H1764" t="inlineStr">
         <is>
           <t>Pine Labs खरीदें STOP LOSS 168 TARGET 240/250 DURATION 9-12 महीने</t>
@@ -74276,7 +74264,6 @@
       <c r="F1765" t="n">
         <v>168</v>
       </c>
-      <c r="G1765" t="inlineStr"/>
       <c r="H1765" t="inlineStr">
         <is>
           <t>Pine Labs खरीदें STOP LOSS 168 TARGET 240/250 DURATION 9-12 महीने</t>
@@ -74368,7 +74355,6 @@
       <c r="F1767" t="n">
         <v>3540</v>
       </c>
-      <c r="G1767" t="inlineStr"/>
       <c r="H1767" t="inlineStr">
         <is>
           <t>Ajanta Ph खरीदें PRICE 3591.90 TARGET 3770/3850 STOP LOSS 3540</t>
@@ -74410,7 +74396,6 @@
       <c r="F1768" t="n">
         <v>3540</v>
       </c>
-      <c r="G1768" t="inlineStr"/>
       <c r="H1768" t="inlineStr">
         <is>
           <t>Ajanta Ph खरीदें PRICE 3591.90 TARGET 3770/3850 STOP LOSS 3540</t>
@@ -74449,7 +74434,6 @@
       <c r="E1769" t="n">
         <v>800</v>
       </c>
-      <c r="G1769" t="inlineStr"/>
       <c r="H1769" t="inlineStr">
         <is>
           <t>Thyrocare PRICE 562.35 TARGET 800 DURATION 6-12 महीने</t>
@@ -74482,7 +74466,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1770" t="inlineStr"/>
       <c r="E1770" t="n">
         <v>325</v>
       </c>
@@ -74535,7 +74518,6 @@
       <c r="F1771" t="n">
         <v>168</v>
       </c>
-      <c r="G1771" t="inlineStr"/>
       <c r="H1771" t="inlineStr">
         <is>
           <t>राजेश पालविया की राय Pine Labs खरीदें STOP LOSS 168 TARGET 240/250 DURATION 9-12 महीने Pine Labs 189.05 2.48%</t>
@@ -74577,7 +74559,6 @@
       <c r="F1772" t="n">
         <v>168</v>
       </c>
-      <c r="G1772" t="inlineStr"/>
       <c r="H1772" t="inlineStr">
         <is>
           <t>Pine Labs खरीदें STOP LOSS 168 TARGET 240/250 DURATION 9-12 महीने Pine Labs 189.05</t>
@@ -74616,7 +74597,6 @@
       <c r="E1773" t="n">
         <v>720</v>
       </c>
-      <c r="G1773" t="inlineStr"/>
       <c r="H1773" t="inlineStr">
         <is>
           <t>1 की कमाई
@@ -74660,7 +74640,6 @@
       <c r="E1774" t="n">
         <v>720</v>
       </c>
-      <c r="G1774" t="inlineStr"/>
       <c r="H1774" t="inlineStr">
         <is>
           <t>Arvind
@@ -74705,7 +74684,6 @@
       <c r="F1775" t="n">
         <v>2650</v>
       </c>
-      <c r="G1775" t="inlineStr"/>
       <c r="H1775" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -74752,7 +74730,6 @@
       <c r="F1776" t="n">
         <v>2650</v>
       </c>
-      <c r="G1776" t="inlineStr"/>
       <c r="H1776" t="inlineStr">
         <is>
           <t>Caplin Point 2733.50 136.90 BUY TGT 2770 SL 2650</t>
@@ -74791,7 +74768,6 @@
       <c r="E1777" t="n">
         <v>690</v>
       </c>
-      <c r="G1777" t="inlineStr"/>
       <c r="H1777" t="inlineStr">
         <is>
           <t>जैन साब के GEMS
@@ -74838,7 +74814,6 @@
       <c r="F1778" t="n">
         <v>1025</v>
       </c>
-      <c r="G1778" t="inlineStr"/>
       <c r="H1778" t="inlineStr">
         <is>
           <t>Max Healthcare 1044.80 BUY TGT 1078 SL 1025</t>
@@ -74880,7 +74855,6 @@
       <c r="F1779" t="n">
         <v>1025</v>
       </c>
-      <c r="G1779" t="inlineStr"/>
       <c r="H1779" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट
@@ -74927,7 +74901,6 @@
       <c r="F1780" t="n">
         <v>2650</v>
       </c>
-      <c r="G1780" t="inlineStr"/>
       <c r="H1780" t="inlineStr">
         <is>
           <t>Caplin Point 2719.00 122.40 BUY TGT 2770 SL 2650</t>
@@ -74969,7 +74942,6 @@
       <c r="F1781" t="n">
         <v>785</v>
       </c>
-      <c r="G1781" t="inlineStr"/>
       <c r="H1781" t="inlineStr">
         <is>
           <t>फुल्ला के कोटिपूर
@@ -75013,7 +74985,6 @@
       <c r="E1782" t="n">
         <v>690</v>
       </c>
-      <c r="G1782" t="inlineStr"/>
       <c r="H1782" t="inlineStr">
         <is>
           <t>Carraro India 526.25 11.20 BUY TGT 690 SL --</t>
@@ -75055,7 +75026,6 @@
       <c r="F1783" t="n">
         <v>1025</v>
       </c>
-      <c r="G1783" t="inlineStr"/>
       <c r="H1783" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट
@@ -75102,7 +75072,6 @@
       <c r="F1784" t="n">
         <v>8200</v>
       </c>
-      <c r="G1784" t="inlineStr"/>
       <c r="H1784" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट Polycab India खरीदें PRICE 8328.00 TARGET 8450/8550 STOP LOSS 8200</t>
@@ -75144,7 +75113,6 @@
       <c r="F1785" t="n">
         <v>8200</v>
       </c>
-      <c r="G1785" t="inlineStr"/>
       <c r="H1785" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट Polycab India खरीदें PRICE 8325.00 TARGET 8450/8550 STOP LOSS 8200</t>
@@ -75186,7 +75154,6 @@
       <c r="F1786" t="n">
         <v>8200</v>
       </c>
-      <c r="G1786" t="inlineStr"/>
       <c r="H1786" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट Polycab India खरीदें PRICE 8325.00 TARGET 8450/8550 STOP LOSS 8200</t>
@@ -75228,7 +75195,6 @@
       <c r="F1787" t="n">
         <v>2650</v>
       </c>
-      <c r="G1787" t="inlineStr"/>
       <c r="H1787" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -75275,7 +75241,6 @@
       <c r="F1788" t="n">
         <v>2650</v>
       </c>
-      <c r="G1788" t="inlineStr"/>
       <c r="H1788" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -75313,14 +75278,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1789" t="inlineStr"/>
       <c r="E1789" t="n">
         <v>1878</v>
       </c>
       <c r="F1789" t="n">
         <v>1825</v>
       </c>
-      <c r="G1789" t="inlineStr"/>
       <c r="H1789" t="inlineStr">
         <is>
           <t>Max Healthcare 1043.00 BUY TGT 1878 SL 1825</t>
@@ -75362,7 +75325,6 @@
       <c r="F1790" t="n">
         <v>1025</v>
       </c>
-      <c r="G1790" t="inlineStr"/>
       <c r="H1790" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट
@@ -75406,7 +75368,6 @@
       <c r="E1791" t="n">
         <v>1070</v>
       </c>
-      <c r="G1791" t="inlineStr"/>
       <c r="H1791" t="inlineStr">
         <is>
           <t>Max Healthcare 1043.30 6.30 BUY TGT 1070</t>
@@ -75439,14 +75400,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1792" t="inlineStr"/>
       <c r="E1792" t="n">
         <v>1445</v>
       </c>
       <c r="F1792" t="n">
         <v>1405</v>
       </c>
-      <c r="G1792" t="inlineStr"/>
       <c r="H1792" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर
@@ -75490,7 +75449,6 @@
       <c r="E1793" t="n">
         <v>340</v>
       </c>
-      <c r="G1793" t="inlineStr"/>
       <c r="H1793" t="inlineStr">
         <is>
           <t>SUPER SID Emmvee Photovoltaic 328.90 3.40 BUY TGT 340 SL --</t>
@@ -75532,7 +75490,6 @@
       <c r="F1794" t="n">
         <v>785</v>
       </c>
-      <c r="G1794" t="inlineStr"/>
       <c r="H1794" t="inlineStr">
         <is>
           <t>कुणाल के कोहिनूर Sona BLW Precision खरीदें PRICE 795.35 TARGET 820/840 STOP LOSS 785</t>
@@ -75574,7 +75531,6 @@
       <c r="F1795" t="n">
         <v>785</v>
       </c>
-      <c r="G1795" t="inlineStr"/>
       <c r="H1795" t="inlineStr">
         <is>
           <t>कुणाल के कोहिनूर Sona BLW Precision खरीदें PRICE 795.35 TARGET 820/840 STOP LOSS 785</t>
@@ -75699,7 +75655,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1798" t="inlineStr"/>
       <c r="E1798" t="n">
         <v>155</v>
       </c>
@@ -75743,7 +75698,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1799" t="inlineStr"/>
       <c r="E1799" t="n">
         <v>133</v>
       </c>
@@ -75787,7 +75741,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1800" t="inlineStr"/>
       <c r="E1800" t="n">
         <v>155</v>
       </c>
@@ -75834,7 +75787,6 @@
       <c r="D1801" t="n">
         <v>527.75</v>
       </c>
-      <c r="G1801" t="inlineStr"/>
       <c r="H1801" t="inlineStr">
         <is>
           <t>CARRARO INDIA @ 520 खरीदें STOP LOSS -- TARGET 590/630</t>
@@ -75867,11 +75819,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1802" t="inlineStr"/>
       <c r="E1802" t="n">
         <v>630</v>
       </c>
-      <c r="G1802" t="inlineStr"/>
       <c r="H1802" t="inlineStr">
         <is>
           <t>जैन साब के GEMS CARRARO INDIA @ 520 खरीदें STOP LOSS -- TARGET 590/630</t>
@@ -75910,7 +75860,6 @@
       <c r="E1803" t="n">
         <v>4100</v>
       </c>
-      <c r="G1803" t="inlineStr"/>
       <c r="H1803" t="inlineStr">
         <is>
           <t>Supreme Ind खरीदें PRICE 3428.60 TARGET 3530/4100 STOP LOSS --</t>
@@ -75949,7 +75898,6 @@
       <c r="E1804" t="n">
         <v>3530</v>
       </c>
-      <c r="G1804" t="inlineStr"/>
       <c r="H1804" t="inlineStr">
         <is>
           <t>Supreme Ind खरीदें PRICE 3428.60 TARGET 3530/4100 STOP LOSS --</t>
@@ -75982,11 +75930,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1805" t="inlineStr"/>
       <c r="E1805" t="n">
         <v>4132.7</v>
       </c>
-      <c r="G1805" t="inlineStr"/>
       <c r="H1805" t="inlineStr">
         <is>
           <t>Sansera Engg 4132.70 INVESTMENT PICK 1727.00 24/12/2025 RECO PRICE RETURN TILL NOW 2405.70 139.30%</t>
@@ -76019,11 +75965,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1806" t="inlineStr"/>
       <c r="E1806" t="n">
         <v>4132.8</v>
       </c>
-      <c r="G1806" t="inlineStr"/>
       <c r="H1806" t="inlineStr">
         <is>
           <t>Sansera Engg 4132.80 INVESTMENT PICK 1727.00 24/12/2025 RECO PRICE RETURN TILL NOW 2405.80 139.31%</t>
@@ -76056,11 +76000,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1807" t="inlineStr"/>
       <c r="E1807" t="n">
         <v>4131.4</v>
       </c>
-      <c r="G1807" t="inlineStr"/>
       <c r="H1807" t="inlineStr">
         <is>
           <t>Sansera Engg 4131.40 INVESTMENT PICK 1727.00 24/12/2025 RECO PRICE RETURN TILL NOW 2404.40 139.22%</t>
@@ -76099,7 +76041,6 @@
       <c r="F1808" t="n">
         <v>84</v>
       </c>
-      <c r="G1808" t="inlineStr"/>
       <c r="H1808" t="inlineStr">
         <is>
           <t>OPENING का HERO Dr Reddy's Fut 1191.60 ▲ 19.20 TODAY 1192 HIGH 1192.40 LOW 1180.00 Vol: 358.13 k प्राइस ₹84 के नीचे का SL लगाएं</t>
@@ -76138,7 +76079,6 @@
       <c r="E1809" t="n">
         <v>348</v>
       </c>
-      <c r="G1809" t="inlineStr"/>
       <c r="H1809" t="inlineStr">
         <is>
           <t>SID Emmvee Photovoltaic 331.0 BUY TGT 348</t>
@@ -76180,7 +76120,6 @@
       <c r="F1810" t="n">
         <v>1025</v>
       </c>
-      <c r="G1810" t="inlineStr"/>
       <c r="H1810" t="inlineStr">
         <is>
           <t>Max Healthcare खरीदें PRICE 1047.40 TARGET 1070/1090 STOP LOSS 1025</t>
@@ -76222,7 +76161,6 @@
       <c r="F1811" t="n">
         <v>1025</v>
       </c>
-      <c r="G1811" t="inlineStr"/>
       <c r="H1811" t="inlineStr">
         <is>
           <t>Max Healthcare खरीदें PRICE 1047.90 TARGET 1070/1090 STOP LOSS 1025</t>
@@ -76264,7 +76202,6 @@
       <c r="F1812" t="n">
         <v>1405</v>
       </c>
-      <c r="G1812" t="inlineStr"/>
       <c r="H1812" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Astral Ltd खरीदें PRICE 1422.00 TARGET 1445/1460 STOP LOSS 1405</t>
@@ -76306,7 +76243,6 @@
       <c r="F1813" t="n">
         <v>1405</v>
       </c>
-      <c r="G1813" t="inlineStr"/>
       <c r="H1813" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Astral Ltd खरीदें PRICE 1420.50 TARGET 1445/1460 STOP LOSS 1405</t>
@@ -76348,7 +76284,6 @@
       <c r="F1814" t="n">
         <v>1405</v>
       </c>
-      <c r="G1814" t="inlineStr"/>
       <c r="H1814" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Astral Ltd खरीदें PRICE 1421.60 TARGET 1445/1460 STOP LOSS 1405</t>
@@ -76390,7 +76325,6 @@
       <c r="F1815" t="n">
         <v>1405</v>
       </c>
-      <c r="G1815" t="inlineStr"/>
       <c r="H1815" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Astral Ltd खरीदें PRICE 1421.60 TARGET 1445/1460 STOP LOSS 1405</t>
@@ -76429,7 +76363,6 @@
       <c r="E1816" t="n">
         <v>410</v>
       </c>
-      <c r="G1816" t="inlineStr"/>
       <c r="H1816" t="inlineStr">
         <is>
           <t>Emmvee Photovoltaic खरीदें PRICE 333.00 TARGET 340/410 STOP LOSS --</t>
@@ -76468,7 +76401,6 @@
       <c r="E1817" t="n">
         <v>410</v>
       </c>
-      <c r="G1817" t="inlineStr"/>
       <c r="H1817" t="inlineStr">
         <is>
           <t>SUPER SID Emmvee Photovoltaic खरीदें PRICE 332.40 TARGET 340/410 STOP LOSS --</t>
@@ -76507,7 +76439,6 @@
       <c r="E1818" t="n">
         <v>340</v>
       </c>
-      <c r="G1818" t="inlineStr"/>
       <c r="H1818" t="inlineStr">
         <is>
           <t>SUPER SID Emmvee Photovoltaic खरीदें PRICE 331.85 TARGET 340/410 STOP LOSS --</t>
@@ -76546,7 +76477,6 @@
       <c r="E1819" t="n">
         <v>410</v>
       </c>
-      <c r="G1819" t="inlineStr"/>
       <c r="H1819" t="inlineStr">
         <is>
           <t>SUPER SID Emmvee Photovoltaic खरीदें PRICE 331.85 TARGET 340/410 STOP LOSS --</t>
@@ -76585,7 +76515,6 @@
       <c r="E1820" t="n">
         <v>425</v>
       </c>
-      <c r="G1820" t="inlineStr"/>
       <c r="H1820" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -76628,7 +76557,6 @@
       <c r="E1821" t="n">
         <v>875</v>
       </c>
-      <c r="G1821" t="inlineStr"/>
       <c r="H1821" t="inlineStr">
         <is>
           <t>Indian Hotels 725.85 -0.80 BUY लक्ष्य ₹875</t>
@@ -76796,7 +76724,6 @@
       <c r="F1825" t="n">
         <v>84</v>
       </c>
-      <c r="G1825" t="inlineStr"/>
       <c r="H1825" t="inlineStr">
         <is>
           <t>HERO MOTORS IPO पर सलाह लिस्टिंग के बाद IPO प्राइस ₹84 के नीचे का SL लगाएं</t>
@@ -76878,7 +76805,6 @@
       <c r="E1827" t="n">
         <v>2060</v>
       </c>
-      <c r="G1827" t="inlineStr"/>
       <c r="H1827" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -76921,7 +76847,6 @@
       <c r="E1828" t="n">
         <v>1200</v>
       </c>
-      <c r="G1828" t="inlineStr"/>
       <c r="H1828" t="inlineStr">
         <is>
           <t>STOCK FTH D Dr Reddys Futures PRICE 1172.50 TARGET 1132, 1195, 1200</t>
@@ -76960,7 +76885,6 @@
       <c r="E1829" t="n">
         <v>1195</v>
       </c>
-      <c r="G1829" t="inlineStr"/>
       <c r="H1829" t="inlineStr">
         <is>
           <t>STOCK FTH D Dr Reddys Futures PRICE 1172.50 TARGET 1132, 1195, 1200</t>
@@ -77002,7 +76926,6 @@
       <c r="F1830" t="n">
         <v>700</v>
       </c>
-      <c r="G1830" t="inlineStr"/>
       <c r="H1830" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह HDFC Bank Futures PRICE 715.50 TARGET 722, 730, 738 STOP LOSS 700</t>
@@ -77044,7 +76967,6 @@
       <c r="F1831" t="n">
         <v>700</v>
       </c>
-      <c r="G1831" t="inlineStr"/>
       <c r="H1831" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह HDFC Bank Futures PRICE 715.50 TARGET 722, 730, 738 STOP LOSS 700</t>
@@ -77086,7 +77008,6 @@
       <c r="F1832" t="n">
         <v>700</v>
       </c>
-      <c r="G1832" t="inlineStr"/>
       <c r="H1832" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह HDFC Bank Futures PRICE 715.50 TARGET 722, 730, 738 STOP LOSS 700</t>
@@ -77168,7 +77089,6 @@
       <c r="E1834" t="n">
         <v>725</v>
       </c>
-      <c r="G1834" t="inlineStr"/>
       <c r="H1834" t="inlineStr">
         <is>
           <t>INVESTMENT INDEGENE B 725 12 MONTH</t>
@@ -77210,7 +77130,6 @@
       <c r="F1835" t="n">
         <v>2429</v>
       </c>
-      <c r="G1835" t="inlineStr"/>
       <c r="H1835" t="inlineStr">
         <is>
           <t>MY CHOICE ASIAN PAINTS B 2503 2429</t>
@@ -77252,7 +77171,6 @@
       <c r="F1836" t="n">
         <v>280</v>
       </c>
-      <c r="G1836" t="inlineStr"/>
       <c r="H1836" t="inlineStr">
         <is>
           <t>NEWS IMPACT PETRONET LNG B 290 280</t>
@@ -77294,7 +77212,6 @@
       <c r="F1837" t="n">
         <v>550</v>
       </c>
-      <c r="G1837" t="inlineStr"/>
       <c r="H1837" t="inlineStr">
         <is>
           <t>TECHNO HDFC LIFE B 570 550</t>
@@ -77336,7 +77253,6 @@
       <c r="F1838" t="n">
         <v>408</v>
       </c>
-      <c r="G1838" t="inlineStr"/>
       <c r="H1838" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Exide Ind BUY PRICE 418.60 TARGET 428/438 STOP LOSS 408</t>
@@ -77378,7 +77294,6 @@
       <c r="F1839" t="n">
         <v>408</v>
       </c>
-      <c r="G1839" t="inlineStr"/>
       <c r="H1839" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Exide Ind BUY PRICE 418.60 TARGET 428/438 STOP LOSS 408</t>
@@ -77420,7 +77335,6 @@
       <c r="F1840" t="n">
         <v>145</v>
       </c>
-      <c r="G1840" t="inlineStr"/>
       <c r="H1840" t="inlineStr">
         <is>
           <t>JP मॉर्गन
@@ -77644,7 +77558,6 @@
       <c r="F1845" t="n">
         <v>84.5</v>
       </c>
-      <c r="G1845" t="inlineStr"/>
       <c r="H1845" t="inlineStr">
         <is>
           <t>PICK OF THE DAY IDFC First Bank BUY PRICE 86.33 TARGET 88.5/90 STOP LOSS 84.5</t>
@@ -77732,7 +77645,6 @@
       <c r="F1847" t="n">
         <v>1250</v>
       </c>
-      <c r="G1847" t="inlineStr"/>
       <c r="H1847" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -77779,7 +77691,6 @@
       <c r="F1848" t="n">
         <v>1250</v>
       </c>
-      <c r="G1848" t="inlineStr"/>
       <c r="H1848" t="inlineStr">
         <is>
           <t>PICK F TH DAY PVR INOX BUY PRICE 1272.70 TARGET 1310/1330 STOP LOSS 1250</t>
@@ -77821,7 +77732,6 @@
       <c r="F1849" t="n">
         <v>1465</v>
       </c>
-      <c r="G1849" t="inlineStr"/>
       <c r="H1849" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Vijaya Diagnostic BUY PRICE 1506.10 TARGET 1580/1620 STOP LOSS 1465</t>
@@ -77909,7 +77819,6 @@
       <c r="F1851" t="n">
         <v>1465</v>
       </c>
-      <c r="G1851" t="inlineStr"/>
       <c r="H1851" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Vijaya Diagnostic BUY PRICE 1505.10 TARGET 1580/1620 STOP LOSS 1465</t>
@@ -77951,7 +77860,6 @@
       <c r="F1852" t="n">
         <v>1465</v>
       </c>
-      <c r="G1852" t="inlineStr"/>
       <c r="H1852" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Vijaya Diagnostic BUY PRICE 1505.10 TARGET 1580/1620 STOP LOSS 1465</t>
@@ -78130,7 +78038,6 @@
       <c r="E1856" t="n">
         <v>550</v>
       </c>
-      <c r="G1856" t="inlineStr"/>
       <c r="H1856" t="inlineStr">
         <is>
           <t>FII INVESTMENT REPORT मैक्वायरी OUTPERFORM BEL 395.45 2.51% TARGET ₹550</t>
@@ -78255,7 +78162,6 @@
       <c r="E1859" t="n">
         <v>6845</v>
       </c>
-      <c r="G1859" t="inlineStr"/>
       <c r="H1859" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Hero Motocorp 5325.00 +1.72% OVERWEIGHT लक्ष्य ₹6845</t>
@@ -78294,7 +78200,6 @@
       <c r="E1860" t="n">
         <v>3520</v>
       </c>
-      <c r="G1860" t="inlineStr"/>
       <c r="H1860" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -78340,7 +78245,6 @@
       <c r="F1861" t="n">
         <v>345</v>
       </c>
-      <c r="G1861" t="inlineStr"/>
       <c r="H1861" t="inlineStr">
         <is>
           <t>Federal Bank Futures SELL PRICE 334.75 TARGET 331, 328, 325 STOP LOSS 345</t>
@@ -78382,7 +78286,6 @@
       <c r="F1862" t="n">
         <v>345</v>
       </c>
-      <c r="G1862" t="inlineStr"/>
       <c r="H1862" t="inlineStr">
         <is>
           <t>Federal Bank Futures SELL PRICE 334.75 TARGET 331, 328, 325 STOP LOSS 345</t>
@@ -78424,7 +78327,6 @@
       <c r="F1863" t="n">
         <v>345</v>
       </c>
-      <c r="G1863" t="inlineStr"/>
       <c r="H1863" t="inlineStr">
         <is>
           <t>Federal Bank Futures SELL PRICE 334.75 TARGET 331, 328, 325 STOP LOSS 345</t>
@@ -78466,7 +78368,6 @@
       <c r="F1864" t="n">
         <v>1715</v>
       </c>
-      <c r="G1864" t="inlineStr"/>
       <c r="H1864" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY PB Fintech Futures BUY PRICE 1761 TARGET 1775, 1790, 1810 STOP LOSS 1715</t>
@@ -78508,7 +78409,6 @@
       <c r="F1865" t="n">
         <v>4800</v>
       </c>
-      <c r="G1865" t="inlineStr"/>
       <c r="H1865" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह Indigo Futures BUY PRICE 4879 TARGET 4910, 4950, 4990 STOP LOSS 4800</t>
@@ -78550,7 +78450,6 @@
       <c r="F1866" t="n">
         <v>354</v>
       </c>
-      <c r="G1866" t="inlineStr"/>
       <c r="H1866" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -78596,7 +78495,6 @@
       <c r="F1867" t="n">
         <v>354</v>
       </c>
-      <c r="G1867" t="inlineStr"/>
       <c r="H1867" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह
@@ -78689,7 +78587,6 @@
       <c r="F1869" t="n">
         <v>1155</v>
       </c>
-      <c r="G1869" t="inlineStr"/>
       <c r="H1869" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -78736,7 +78633,6 @@
       <c r="F1870" t="n">
         <v>1155</v>
       </c>
-      <c r="G1870" t="inlineStr"/>
       <c r="H1870" t="inlineStr">
         <is>
           <t>STOCK OF THE DAY
@@ -78873,7 +78769,6 @@
       <c r="F1873" t="n">
         <v>520</v>
       </c>
-      <c r="G1873" t="inlineStr"/>
       <c r="H1873" t="inlineStr">
         <is>
           <t>नेहा के शेयर
@@ -78920,7 +78815,6 @@
       <c r="F1874" t="n">
         <v>132.5</v>
       </c>
-      <c r="G1874" t="inlineStr"/>
       <c r="H1874" t="inlineStr">
         <is>
           <t>MY CHOICE IOC B 137.50 132.50</t>
@@ -78962,7 +78856,6 @@
       <c r="F1875" t="n">
         <v>304.5</v>
       </c>
-      <c r="G1875" t="inlineStr"/>
       <c r="H1875" t="inlineStr">
         <is>
           <t>MY CHOICE BPCL B 312 304.50</t>
@@ -79001,7 +78894,6 @@
       <c r="E1876" t="n">
         <v>7725</v>
       </c>
-      <c r="G1876" t="inlineStr"/>
       <c r="H1876" t="inlineStr">
         <is>
           <t>INVESTMENT INDIGENE B 7725 12M</t>
@@ -79043,7 +78935,6 @@
       <c r="F1877" t="n">
         <v>1185</v>
       </c>
-      <c r="G1877" t="inlineStr"/>
       <c r="H1877" t="inlineStr">
         <is>
           <t>CASH SCHNEIDER INFRA B 1230 1185</t>
@@ -79085,7 +78976,6 @@
       <c r="F1878" t="n">
         <v>2363</v>
       </c>
-      <c r="G1878" t="inlineStr"/>
       <c r="H1878" t="inlineStr">
         <is>
           <t>TECHNO HDFC AMC B 2440 2363</t>
@@ -79127,7 +79017,6 @@
       <c r="F1879" t="n">
         <v>1261</v>
       </c>
-      <c r="G1879" t="inlineStr"/>
       <c r="H1879" t="inlineStr">
         <is>
           <t>FUNDA ADANI GREEN B 1300 1261</t>
@@ -79169,7 +79058,6 @@
       <c r="F1880" t="n">
         <v>405</v>
       </c>
-      <c r="G1880" t="inlineStr"/>
       <c r="H1880" t="inlineStr">
         <is>
           <t>FUTURE RBL BANK FUT B 411 405</t>
@@ -79211,7 +79099,6 @@
       <c r="F1881" t="n">
         <v>808</v>
       </c>
-      <c r="G1881" t="inlineStr"/>
       <c r="H1881" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -79258,7 +79145,6 @@
       <c r="F1882" t="n">
         <v>215</v>
       </c>
-      <c r="G1882" t="inlineStr"/>
       <c r="H1882" t="inlineStr">
         <is>
           <t>Puravankara खरीदें PRICE 218.40 TARGET 222 STOP LOSS 215</t>
@@ -79300,7 +79186,6 @@
       <c r="F1883" t="n">
         <v>280</v>
       </c>
-      <c r="G1883" t="inlineStr"/>
       <c r="H1883" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -79344,7 +79229,6 @@
       <c r="E1884" t="n">
         <v>4500</v>
       </c>
-      <c r="G1884" t="inlineStr"/>
       <c r="H1884" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK TVS Motor PRICE 4101.70 TARGET 4500</t>
@@ -79383,7 +79267,6 @@
       <c r="E1885" t="n">
         <v>725</v>
       </c>
-      <c r="G1885" t="inlineStr"/>
       <c r="H1885" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK
@@ -79430,7 +79313,6 @@
       <c r="F1886" t="n">
         <v>1261</v>
       </c>
-      <c r="G1886" t="inlineStr"/>
       <c r="H1886" t="inlineStr">
         <is>
           <t>FUNDA PICK
@@ -79474,7 +79356,6 @@
       <c r="E1887" t="n">
         <v>5000</v>
       </c>
-      <c r="G1887" t="inlineStr"/>
       <c r="H1887" t="inlineStr">
         <is>
           <t>पूजा के शेयर HAL खरीदें PRICE 4788.00 TARGET 5000 DURATION 6 महीने</t>
@@ -79516,7 +79397,6 @@
       <c r="F1888" t="n">
         <v>1185</v>
       </c>
-      <c r="G1888" t="inlineStr"/>
       <c r="H1888" t="inlineStr">
         <is>
           <t>Schneider Electric खरीदें PRICE 1201.90 TARGET 1230 STOP LOSS 1185</t>
@@ -79555,7 +79435,6 @@
       <c r="E1889" t="n">
         <v>3130</v>
       </c>
-      <c r="G1889" t="inlineStr"/>
       <c r="H1889" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS BUY लक्ष्य ₹3130</t>
@@ -79594,7 +79473,6 @@
       <c r="E1890" t="n">
         <v>1380</v>
       </c>
-      <c r="G1890" t="inlineStr"/>
       <c r="H1890" t="inlineStr">
         <is>
           <t>CALLS
@@ -79639,7 +79517,6 @@
       <c r="F1891" t="n">
         <v>1320</v>
       </c>
-      <c r="G1891" t="inlineStr"/>
       <c r="H1891" t="inlineStr">
         <is>
           <t>श्रीकांत चौहान की राय ICICI Bank खरीदें PRICE 1347.60 TARGET 1390 STOP LOSS 1320</t>
@@ -79681,7 +79558,6 @@
       <c r="F1892" t="n">
         <v>545</v>
       </c>
-      <c r="G1892" t="inlineStr"/>
       <c r="H1892" t="inlineStr">
         <is>
           <t>TRADING CALL HDFC Life खरीदें PRICE 556.75 TARGET 590 STOP LOSS 545</t>
@@ -79720,7 +79596,6 @@
       <c r="E1893" t="n">
         <v>425</v>
       </c>
-      <c r="G1893" t="inlineStr"/>
       <c r="H1893" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -79763,7 +79638,6 @@
       <c r="E1894" t="n">
         <v>875</v>
       </c>
-      <c r="G1894" t="inlineStr"/>
       <c r="H1894" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Indian Hotels 726.65 +13.25 BUY लक्ष्य ₹875</t>
@@ -79845,7 +79719,6 @@
       <c r="E1896" t="n">
         <v>3130</v>
       </c>
-      <c r="G1896" t="inlineStr"/>
       <c r="H1896" t="inlineStr">
         <is>
           <t>HDFC AMC 2387.70 +14.60 BUY लक्ष्य ₹3130</t>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$1897</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$2052</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1897"/>
+  <dimension ref="A1:J2052"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -79778,8 +79778,6497 @@
         </is>
       </c>
     </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:22:00</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1898" t="n">
+        <v>235.95</v>
+      </c>
+      <c r="E1898" t="n">
+        <v>247</v>
+      </c>
+      <c r="F1898" t="n">
+        <v>225</v>
+      </c>
+      <c r="G1898" t="inlineStr"/>
+      <c r="H1898" t="inlineStr">
+        <is>
+          <t>11 बजे की लेडीज स्पेशल ONGC खरीदें PRICE 236.00 TARGET 247/250 STOP LOSS 225</t>
+        </is>
+      </c>
+      <c r="I1898" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1898" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:22:00</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1899" t="n">
+        <v>235.95</v>
+      </c>
+      <c r="E1899" t="n">
+        <v>250</v>
+      </c>
+      <c r="F1899" t="n">
+        <v>225</v>
+      </c>
+      <c r="G1899" t="inlineStr"/>
+      <c r="H1899" t="inlineStr">
+        <is>
+          <t>11 बजे की लेडीज स्पेशल ONGC खरीदें PRICE 236.00 TARGET 247/250 STOP LOSS 225</t>
+        </is>
+      </c>
+      <c r="I1899" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1899" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:10:00</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>VOLTAS29SEP26</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1900" t="n">
+        <v>1121</v>
+      </c>
+      <c r="E1900" t="n">
+        <v>1165</v>
+      </c>
+      <c r="F1900" t="n">
+        <v>1098</v>
+      </c>
+      <c r="G1900" t="inlineStr"/>
+      <c r="H1900" t="inlineStr">
+        <is>
+          <t>Voltas Fut 1120.20 0.79% BUY TGT 1165 SL 1098</t>
+        </is>
+      </c>
+      <c r="I1900" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1900" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>2026-09-25 11:10:00</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1901" t="n">
+        <v>804.55</v>
+      </c>
+      <c r="E1901" t="n">
+        <v>825</v>
+      </c>
+      <c r="F1901" t="n">
+        <v>780</v>
+      </c>
+      <c r="G1901" t="inlineStr"/>
+      <c r="H1901" t="inlineStr">
+        <is>
+          <t>HBL ENGINEERING 803.50 28.20 BUY TGT 825 SL 780 Fri 25 Sep'26</t>
+        </is>
+      </c>
+      <c r="I1901" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1901" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:56:00</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1902" t="n">
+        <v>4958</v>
+      </c>
+      <c r="E1902" t="n">
+        <v>5050</v>
+      </c>
+      <c r="F1902" t="n">
+        <v>4900</v>
+      </c>
+      <c r="G1902" t="inlineStr"/>
+      <c r="H1902" t="inlineStr">
+        <is>
+          <t>श्रीकांत चौहान की राय Torrent Pharma खरीदें STOP LOSS 4900 TARGET 5050/5075 DURATION 1-3 महीने Torrent Pharma 4952.00</t>
+        </is>
+      </c>
+      <c r="I1902" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1902" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:56:00</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>JUBLINGREA</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1903" t="n">
+        <v>646.2</v>
+      </c>
+      <c r="E1903" t="n">
+        <v>800</v>
+      </c>
+      <c r="F1903" t="n">
+        <v>620</v>
+      </c>
+      <c r="G1903" t="inlineStr"/>
+      <c r="H1903" t="inlineStr">
+        <is>
+          <t>Jubilant Ingrevia खरीदें STOP LOSS 620 TARGET 775/800 DURATION 4-8 महीने Jubilant Ingrevia 646.05 10.70</t>
+        </is>
+      </c>
+      <c r="I1903" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1903" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:56:00</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>JUBLINGREA</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1904" t="n">
+        <v>646.2</v>
+      </c>
+      <c r="E1904" t="n">
+        <v>775</v>
+      </c>
+      <c r="F1904" t="n">
+        <v>620</v>
+      </c>
+      <c r="G1904" t="inlineStr"/>
+      <c r="H1904" t="inlineStr">
+        <is>
+          <t>भाग्यवान चौहान की राय Jubilant Ingrevia खरीदें STOP LOSS 620 TARGET 775/800 DURATION 4-8 महीने Jubilant Ingrevia 646.05 1.68%</t>
+        </is>
+      </c>
+      <c r="I1904" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1904" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:26:39</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>AJAXENGG</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1905" t="inlineStr"/>
+      <c r="E1905" t="n">
+        <v>555</v>
+      </c>
+      <c r="G1905" t="inlineStr"/>
+      <c r="H1905" t="inlineStr">
+        <is>
+          <t>Ajax Engineering 613.65 6.68% BUY TARGET HIT 555</t>
+        </is>
+      </c>
+      <c r="I1905" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1905" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:27:00</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1906" t="n">
+        <v>796.4</v>
+      </c>
+      <c r="E1906" t="n">
+        <v>835</v>
+      </c>
+      <c r="G1906" t="inlineStr"/>
+      <c r="H1906" t="inlineStr">
+        <is>
+          <t>HBL ENGINEERING 796.90 21.60 BUY TGT 835</t>
+        </is>
+      </c>
+      <c r="I1906" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1906" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:27:00</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1907" t="n">
+        <v>1496.9</v>
+      </c>
+      <c r="E1907" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G1907" t="inlineStr"/>
+      <c r="H1907" t="inlineStr">
+        <is>
+          <t>SUPER SID
+Ather Energy
+1498.00 1.00
+BUY
+TGT 1530
+SL --</t>
+        </is>
+      </c>
+      <c r="I1907" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1907" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:25:00</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>VOLTAS29SEP26</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1908" t="n">
+        <v>1120.9</v>
+      </c>
+      <c r="E1908" t="n">
+        <v>1165</v>
+      </c>
+      <c r="F1908" t="n">
+        <v>1098</v>
+      </c>
+      <c r="G1908" t="inlineStr"/>
+      <c r="H1908" t="inlineStr">
+        <is>
+          <t>Voltas Fut खरीदें PRICE 1118.60 TARGET 1165/1185 STOP LOSS 1098</t>
+        </is>
+      </c>
+      <c r="I1908" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1908" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:25:00</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>VOLTAS29SEP26</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1909" t="n">
+        <v>1120.9</v>
+      </c>
+      <c r="E1909" t="n">
+        <v>1185</v>
+      </c>
+      <c r="F1909" t="n">
+        <v>1098</v>
+      </c>
+      <c r="G1909" t="inlineStr"/>
+      <c r="H1909" t="inlineStr">
+        <is>
+          <t>Voltas Fut खरीदें PRICE 1118.60 TARGET 1165/1185 STOP LOSS 1098</t>
+        </is>
+      </c>
+      <c r="I1909" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1909" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:23:00</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>TARSONS</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1910" t="n">
+        <v>334</v>
+      </c>
+      <c r="E1910" t="n">
+        <v>400</v>
+      </c>
+      <c r="G1910" t="inlineStr"/>
+      <c r="H1910" t="inlineStr">
+        <is>
+          <t>अंबरीश बलिगा की राय
+Tarsons Product
+खरीदें
+STOP LOSS --
+TARGET 400
+DURATION 1-3 महीने
+Tarsons Product 334.00</t>
+        </is>
+      </c>
+      <c r="I1910" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1910" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:18:05</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>AJAXENGG</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1911" t="inlineStr"/>
+      <c r="E1911" t="n">
+        <v>355</v>
+      </c>
+      <c r="G1911" t="inlineStr"/>
+      <c r="H1911" t="inlineStr">
+        <is>
+          <t>Ajax Engineering 605.90 5.34% BUY TARGET HIT 355</t>
+        </is>
+      </c>
+      <c r="I1911" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1911" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:18:01</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>AJAXENGG</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1912" t="inlineStr"/>
+      <c r="E1912" t="n">
+        <v>610</v>
+      </c>
+      <c r="G1912" t="inlineStr"/>
+      <c r="H1912" t="inlineStr">
+        <is>
+          <t>Ajax Engineering 605.00 5.18% BUY TGT 610</t>
+        </is>
+      </c>
+      <c r="I1912" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1912" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:18:00</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1913" t="n">
+        <v>795.55</v>
+      </c>
+      <c r="E1913" t="n">
+        <v>825</v>
+      </c>
+      <c r="F1913" t="n">
+        <v>780</v>
+      </c>
+      <c r="G1913" t="inlineStr"/>
+      <c r="H1913" t="inlineStr">
+        <is>
+          <t>फुल्ल के कोहिनूर
+HBL ENGINEERING ▲
+795.35 20.05
+BUY
+TGT 825
+SL 780</t>
+        </is>
+      </c>
+      <c r="I1913" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1913" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:18:00</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1914" t="n">
+        <v>753</v>
+      </c>
+      <c r="E1914" t="n">
+        <v>775</v>
+      </c>
+      <c r="G1914" t="inlineStr"/>
+      <c r="H1914" t="inlineStr">
+        <is>
+          <t>SUPER SID
+TD Power
+752.95 10.95
+BUY
+TGT 775
+SL --
+10:17 AM</t>
+        </is>
+      </c>
+      <c r="I1914" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1914" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:18:00</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1915" t="n">
+        <v>826.7</v>
+      </c>
+      <c r="E1915" t="n">
+        <v>875</v>
+      </c>
+      <c r="F1915" t="n">
+        <v>810</v>
+      </c>
+      <c r="G1915" t="inlineStr"/>
+      <c r="H1915" t="inlineStr">
+        <is>
+          <t>Graphite India 826.65 11.95 BUY TGT 875 SL 810</t>
+        </is>
+      </c>
+      <c r="I1915" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1915" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:18:00</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1916" t="n">
+        <v>1397</v>
+      </c>
+      <c r="E1916" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F1916" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G1916" t="inlineStr"/>
+      <c r="H1916" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट Chennai Petro 1398.50 1.88% BUY TGT 1450 SL 1360</t>
+        </is>
+      </c>
+      <c r="I1916" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1916" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:18:00</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1917" t="n">
+        <v>2788.1</v>
+      </c>
+      <c r="E1917" t="n">
+        <v>49000</v>
+      </c>
+      <c r="G1917" t="inlineStr"/>
+      <c r="H1917" t="inlineStr">
+        <is>
+          <t>Welspun Corp को एक और ऑर्डर
+Welspun Corp
+2789.00 ▲ 3.60%
+ग्लोबल ऑर्डर बुक ₹49000 टीएफ पर पहुंची</t>
+        </is>
+      </c>
+      <c r="I1917" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1917" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:16:00</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>JUBLINGREA</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1918" t="n">
+        <v>651</v>
+      </c>
+      <c r="E1918" t="n">
+        <v>800</v>
+      </c>
+      <c r="F1918" t="n">
+        <v>620</v>
+      </c>
+      <c r="G1918" t="inlineStr"/>
+      <c r="H1918" t="inlineStr">
+        <is>
+          <t>खरीदें STOP LOSS 620 TARGET 775/800 DURATION 4-8 महीने Jubilant Ingrevia 650.70 2.42%</t>
+        </is>
+      </c>
+      <c r="I1918" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1918" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:16:00</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>JUBLINGREA</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1919" t="n">
+        <v>651</v>
+      </c>
+      <c r="E1919" t="n">
+        <v>775</v>
+      </c>
+      <c r="F1919" t="n">
+        <v>620</v>
+      </c>
+      <c r="G1919" t="inlineStr">
+        <is>
+          <t>Prakash Gaba</t>
+        </is>
+      </c>
+      <c r="H1919" t="inlineStr">
+        <is>
+          <t>प्रकाश गबा की राय Jubilant Ingrevia खरीदें STOP LOSS 620 TARGET 775/800 DURATION 4-8 महीने Jubilant Ingrevia 650.70 15.35</t>
+        </is>
+      </c>
+      <c r="I1919" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1919" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:14:00</t>
+        </is>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1920" t="n">
+        <v>4789.7</v>
+      </c>
+      <c r="E1920" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G1920" t="inlineStr"/>
+      <c r="H1920" t="inlineStr">
+        <is>
+          <t>श्रीकांत चौहान की राय HAL खरीदें STOP LOSS -- TARGET 5300/5800 DURATION 9-12 महीने HAL 4791.00 ▲ 0.35%</t>
+        </is>
+      </c>
+      <c r="I1920" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1920" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:14:00</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>ORKLAINDIA</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1921" t="n">
+        <v>544.9</v>
+      </c>
+      <c r="E1921" t="n">
+        <v>700</v>
+      </c>
+      <c r="G1921" t="inlineStr"/>
+      <c r="H1921" t="inlineStr">
+        <is>
+          <t>अंबरीश बलिगा की राय
+Orkla India
+खरीदें
+STOP LOSS --
+TARGET 700
+DURATION 4-8 महीने
+Orkla India 544.80 ▼ 0.21%</t>
+        </is>
+      </c>
+      <c r="I1921" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1921" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>AJAXENGG</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1922" t="n">
+        <v>603.4</v>
+      </c>
+      <c r="E1922" t="n">
+        <v>610</v>
+      </c>
+      <c r="G1922" t="inlineStr"/>
+      <c r="H1922" t="inlineStr">
+        <is>
+          <t>Ajax Engineering 602.80 4.80% BUY TGT 610</t>
+        </is>
+      </c>
+      <c r="I1922" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1922" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1923" t="n">
+        <v>796.3</v>
+      </c>
+      <c r="E1923" t="n">
+        <v>825</v>
+      </c>
+      <c r="F1923" t="n">
+        <v>780</v>
+      </c>
+      <c r="G1923" t="inlineStr"/>
+      <c r="H1923" t="inlineStr">
+        <is>
+          <t>कुल्लू के कोहिनूर
+HBL ENGINEERING ▲
+797.00 21.70
+BUY
+TGT 825
+SL 780</t>
+        </is>
+      </c>
+      <c r="I1923" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1923" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:10:00</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1924" t="n">
+        <v>754.25</v>
+      </c>
+      <c r="E1924" t="n">
+        <v>775</v>
+      </c>
+      <c r="G1924" t="inlineStr"/>
+      <c r="H1924" t="inlineStr">
+        <is>
+          <t>SUPER SID
+TD Power
+754.00 12.00
+BUY
+TGT 775
+SL --</t>
+        </is>
+      </c>
+      <c r="I1924" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1924" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:09:00</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1925" t="n">
+        <v>1495.9</v>
+      </c>
+      <c r="E1925" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G1925" t="inlineStr"/>
+      <c r="H1925" t="inlineStr">
+        <is>
+          <t>SUPER SID Ather Energy 1495.40 3.60 BUY TGT 1530 SL --</t>
+        </is>
+      </c>
+      <c r="I1925" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1925" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:08:00</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>USHAMART</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1926" t="n">
+        <v>520.55</v>
+      </c>
+      <c r="E1926" t="n">
+        <v>620</v>
+      </c>
+      <c r="G1926" t="inlineStr"/>
+      <c r="H1926" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेढानी की राय Usha Martin खरीदें PRICE 521.15 TARGET 620 DURATION 6-12 महीने</t>
+        </is>
+      </c>
+      <c r="I1926" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1926" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:05:30</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1927" t="inlineStr"/>
+      <c r="E1927" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F1927" t="n">
+        <v>5300</v>
+      </c>
+      <c r="G1927" t="inlineStr"/>
+      <c r="H1927" t="inlineStr">
+        <is>
+          <t>श्रीकांत चौहान की राय HAL खरीदें STOP LOSS 5300/TARGET 5800 DURAT 9-12 HAL 4785.60</t>
+        </is>
+      </c>
+      <c r="I1927" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1927" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:06:00</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1928" t="n">
+        <v>4785.4</v>
+      </c>
+      <c r="E1928" t="n">
+        <v>5300</v>
+      </c>
+      <c r="G1928" t="inlineStr"/>
+      <c r="H1928" t="inlineStr">
+        <is>
+          <t>श्रीकांत चौहान की राय HAL खरीदें STOP LOSS -- TARGET 5300/5800 DURATION 9-12 महीने HAL 4785.60 ▲ 0.24%</t>
+        </is>
+      </c>
+      <c r="I1928" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1928" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:06:00</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1929" t="n">
+        <v>4785.4</v>
+      </c>
+      <c r="E1929" t="n">
+        <v>5800</v>
+      </c>
+      <c r="G1929" t="inlineStr"/>
+      <c r="H1929" t="inlineStr">
+        <is>
+          <t>HAL खरीदें STOP LOSS -- TARGET 5300/5800 DURATION 9-12 महीने HAL 4785.60</t>
+        </is>
+      </c>
+      <c r="I1929" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1929" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:05:00</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1930" t="n">
+        <v>488.8</v>
+      </c>
+      <c r="E1930" t="n">
+        <v>650</v>
+      </c>
+      <c r="G1930" t="inlineStr"/>
+      <c r="H1930" t="inlineStr">
+        <is>
+          <t>Aarti Ind खरीदें STOP LOSS -- TARGET 650 DURATION 9-12 महीने Aarti Ind 488.00 0.30%</t>
+        </is>
+      </c>
+      <c r="I1930" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1930" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:02:00</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>LLOYDSENGG</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1931" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="E1931" t="n">
+        <v>120</v>
+      </c>
+      <c r="F1931" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1931" t="inlineStr"/>
+      <c r="H1931" t="inlineStr">
+        <is>
+          <t>Lloyds Engineering Works Ltd खरीदें PRICE 92.37 TARGET 120/135 STOP LOSS 75</t>
+        </is>
+      </c>
+      <c r="I1931" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1931" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:02:00</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>LLOYDSENGG</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1932" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="E1932" t="n">
+        <v>135</v>
+      </c>
+      <c r="F1932" t="n">
+        <v>75</v>
+      </c>
+      <c r="G1932" t="inlineStr"/>
+      <c r="H1932" t="inlineStr">
+        <is>
+          <t>Lloyds Engineering Works Ltd खरीदें PRICE 92.37 TARGET 120/135 STOP LOSS 75</t>
+        </is>
+      </c>
+      <c r="I1932" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1932" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:00:57</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>AJAXENGG</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1933" t="inlineStr"/>
+      <c r="E1933" t="n">
+        <v>555</v>
+      </c>
+      <c r="G1933" t="inlineStr"/>
+      <c r="H1933" t="inlineStr">
+        <is>
+          <t>Ajax Engineering 605.20 5.22% BUY TARGET HIT 555</t>
+        </is>
+      </c>
+      <c r="I1933" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1933" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>AJAXENGG</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1934" t="n">
+        <v>605.25</v>
+      </c>
+      <c r="E1934" t="n">
+        <v>610</v>
+      </c>
+      <c r="F1934" t="n">
+        <v>555</v>
+      </c>
+      <c r="G1934" t="inlineStr"/>
+      <c r="H1934" t="inlineStr">
+        <is>
+          <t>सदाबहार सेबी साब Ajax Engineering 605.20 5.22% BUY TGT 610 SL 555</t>
+        </is>
+      </c>
+      <c r="I1934" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1934" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1935" t="n">
+        <v>794</v>
+      </c>
+      <c r="E1935" t="n">
+        <v>825</v>
+      </c>
+      <c r="F1935" t="n">
+        <v>780</v>
+      </c>
+      <c r="G1935" t="inlineStr"/>
+      <c r="H1935" t="inlineStr">
+        <is>
+          <t>HBL ENGINEERING 794.50 19.20 BUY TGT 825 SL 780</t>
+        </is>
+      </c>
+      <c r="I1935" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1935" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1936" t="n">
+        <v>751.35</v>
+      </c>
+      <c r="E1936" t="n">
+        <v>775</v>
+      </c>
+      <c r="G1936" t="inlineStr"/>
+      <c r="H1936" t="inlineStr">
+        <is>
+          <t>SUPER SID TD Power 751.70 9.70 BUY TGT 775 SL --</t>
+        </is>
+      </c>
+      <c r="I1936" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1936" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1937" t="n">
+        <v>908.6</v>
+      </c>
+      <c r="E1937" t="n">
+        <v>970</v>
+      </c>
+      <c r="F1937" t="n">
+        <v>850</v>
+      </c>
+      <c r="G1937" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H1937" t="inlineStr">
+        <is>
+          <t>आरथा जैन की राय Whirlpool खरीदें PRICE 904.75 TARGET 960/970 STOP LOSS 850</t>
+        </is>
+      </c>
+      <c r="I1937" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1937" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1938" t="n">
+        <v>913.15</v>
+      </c>
+      <c r="E1938" t="n">
+        <v>960</v>
+      </c>
+      <c r="F1938" t="n">
+        <v>850</v>
+      </c>
+      <c r="G1938" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H1938" t="inlineStr">
+        <is>
+          <t>आस्था जैन की राय Whirlpool खरीदें PRICE 905.00 TARGET 960/970 STOP LOSS 850</t>
+        </is>
+      </c>
+      <c r="I1938" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1938" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1939" t="n">
+        <v>913.15</v>
+      </c>
+      <c r="E1939" t="n">
+        <v>970</v>
+      </c>
+      <c r="F1939" t="n">
+        <v>850</v>
+      </c>
+      <c r="G1939" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H1939" t="inlineStr">
+        <is>
+          <t>आस्था जैन की राय Whirlpool खरीदें PRICE 905.00 TARGET 960/970 STOP LOSS 850</t>
+        </is>
+      </c>
+      <c r="I1939" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1939" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1940" t="n">
+        <v>908.6</v>
+      </c>
+      <c r="E1940" t="n">
+        <v>960</v>
+      </c>
+      <c r="F1940" t="n">
+        <v>850</v>
+      </c>
+      <c r="G1940" t="inlineStr"/>
+      <c r="H1940" t="inlineStr">
+        <is>
+          <t>Whirlpool खरीदें PRICE 903.80 TARGET 960/970 STOP LOSS 850</t>
+        </is>
+      </c>
+      <c r="I1940" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1940" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1941" t="n">
+        <v>822</v>
+      </c>
+      <c r="E1941" t="n">
+        <v>875</v>
+      </c>
+      <c r="F1941" t="n">
+        <v>810</v>
+      </c>
+      <c r="G1941" t="inlineStr"/>
+      <c r="H1941" t="inlineStr">
+        <is>
+          <t>Graphite India 823.65 8.95 BUY TGT 875 SL 810</t>
+        </is>
+      </c>
+      <c r="I1941" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1941" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1942" t="n">
+        <v>908.6</v>
+      </c>
+      <c r="E1942" t="n">
+        <v>970</v>
+      </c>
+      <c r="F1942" t="n">
+        <v>850</v>
+      </c>
+      <c r="G1942" t="inlineStr"/>
+      <c r="H1942" t="inlineStr">
+        <is>
+          <t>Whirlpool खरीदें PRICE 902.00 TARGET 960/970 STOP LOSS 850</t>
+        </is>
+      </c>
+      <c r="I1942" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1942" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1943" t="n">
+        <v>822</v>
+      </c>
+      <c r="E1943" t="n">
+        <v>875</v>
+      </c>
+      <c r="F1943" t="n">
+        <v>810</v>
+      </c>
+      <c r="G1943" t="inlineStr"/>
+      <c r="H1943" t="inlineStr">
+        <is>
+          <t>Graphite India 824.00 9.30 BUY TGT 875 SL 810</t>
+        </is>
+      </c>
+      <c r="I1943" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1943" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1944" t="n">
+        <v>1379.8</v>
+      </c>
+      <c r="E1944" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F1944" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G1944" t="inlineStr"/>
+      <c r="H1944" t="inlineStr">
+        <is>
+          <t>Chennai Petro 1381.30 8.60 BUY TGT 1450 SL 1360</t>
+        </is>
+      </c>
+      <c r="I1944" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1944" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:01:00</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1945" t="n">
+        <v>1490</v>
+      </c>
+      <c r="E1945" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G1945" t="inlineStr"/>
+      <c r="H1945" t="inlineStr">
+        <is>
+          <t>SUPER SID Ather Energy 1491.00 BUY TGT 1530 SL -- Fri 25 Sep'26</t>
+        </is>
+      </c>
+      <c r="I1945" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1945" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>2026-09-25 10:00:07</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>VASCONEQ</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1946" t="inlineStr"/>
+      <c r="E1946" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="F1946" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G1946" t="inlineStr"/>
+      <c r="H1946" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Vascon Eng 35.25 1.96 BUY TGT 34.2 SL 31.5</t>
+        </is>
+      </c>
+      <c r="I1946" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1946" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:58:00</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1947" t="n">
+        <v>196.79</v>
+      </c>
+      <c r="E1947" t="n">
+        <v>270</v>
+      </c>
+      <c r="G1947" t="inlineStr"/>
+      <c r="H1947" t="inlineStr">
+        <is>
+          <t>Castrol India खरीदें PRICE 196.79 TARGET 270 DURATION 4-6 महीने</t>
+        </is>
+      </c>
+      <c r="I1947" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1947" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:57:00</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>PARADEEP</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1948" t="n">
+        <v>155.75</v>
+      </c>
+      <c r="E1948" t="n">
+        <v>162</v>
+      </c>
+      <c r="F1948" t="n">
+        <v>152</v>
+      </c>
+      <c r="G1948" t="inlineStr"/>
+      <c r="H1948" t="inlineStr">
+        <is>
+          <t>10 की कमाई
+Paradeep Phosphates
+खरीदें
+PRICE ▶ 155.81
+TARGET ▶ 160/162
+STOP LOSS ▶ 152</t>
+        </is>
+      </c>
+      <c r="I1948" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1948" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:57:00</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>PARADEEP</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1949" t="n">
+        <v>155.75</v>
+      </c>
+      <c r="E1949" t="n">
+        <v>160</v>
+      </c>
+      <c r="F1949" t="n">
+        <v>152</v>
+      </c>
+      <c r="G1949" t="inlineStr"/>
+      <c r="H1949" t="inlineStr">
+        <is>
+          <t>10 की कमाई Paradeep Phosphates खरीदें PRICE 155.81 TARGET 160/162 STOP LOSS 152</t>
+        </is>
+      </c>
+      <c r="I1949" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1949" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:49:01</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>AJAXENGG</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr"/>
+      <c r="E1950" t="n">
+        <v>555</v>
+      </c>
+      <c r="G1950" t="inlineStr"/>
+      <c r="H1950" t="inlineStr">
+        <is>
+          <t>Ajax Engineering 608.00 5.70% BUY TARGET HIT 555</t>
+        </is>
+      </c>
+      <c r="I1950" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1950" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>AJAXENGG</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1951" t="n">
+        <v>607.25</v>
+      </c>
+      <c r="E1951" t="n">
+        <v>610</v>
+      </c>
+      <c r="F1951" t="n">
+        <v>555</v>
+      </c>
+      <c r="G1951" t="inlineStr"/>
+      <c r="H1951" t="inlineStr">
+        <is>
+          <t>सदाबहार सेठी साब
+Ajax Engineering
+610.45 35.25
+BUY
+TGT 610
+SL 555</t>
+        </is>
+      </c>
+      <c r="I1951" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1951" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1952" t="n">
+        <v>793.55</v>
+      </c>
+      <c r="E1952" t="n">
+        <v>825</v>
+      </c>
+      <c r="F1952" t="n">
+        <v>780</v>
+      </c>
+      <c r="G1952" t="inlineStr"/>
+      <c r="H1952" t="inlineStr">
+        <is>
+          <t>HBL ENGINEERING 793.50 18.20 BUY TGT 825 SL 780</t>
+        </is>
+      </c>
+      <c r="I1952" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1952" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:49:00</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1953" t="n">
+        <v>754.55</v>
+      </c>
+      <c r="E1953" t="n">
+        <v>775</v>
+      </c>
+      <c r="G1953" t="inlineStr"/>
+      <c r="H1953" t="inlineStr">
+        <is>
+          <t>SUPER SID TD Power 753.50 11.50 BUY TGT 775 SL --</t>
+        </is>
+      </c>
+      <c r="I1953" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1953" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:46:58</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr"/>
+      <c r="E1954" t="n">
+        <v>585.35</v>
+      </c>
+      <c r="G1954" t="inlineStr"/>
+      <c r="H1954" t="inlineStr">
+        <is>
+          <t>Tilaknagar Ind 585.35 DIWALI PICK 222.50 03/11/2023 RECO PRICE RETURN TILL NOW 362.85 163.08%</t>
+        </is>
+      </c>
+      <c r="I1954" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1954" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:46:51</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr"/>
+      <c r="E1955" t="n">
+        <v>585.3</v>
+      </c>
+      <c r="G1955" t="inlineStr"/>
+      <c r="H1955" t="inlineStr">
+        <is>
+          <t>Tilaknagar Ind 585.30 DIWALI PICK 222.50 03/11/2023 RECO PRICE RETURN TILL NOW 362.80 163.06%</t>
+        </is>
+      </c>
+      <c r="I1955" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1955" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:46:45</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1956" t="inlineStr"/>
+      <c r="E1956" t="n">
+        <v>585.5</v>
+      </c>
+      <c r="G1956" t="inlineStr"/>
+      <c r="H1956" t="inlineStr">
+        <is>
+          <t>Tilaknagar Ind 585.50 DIWALI PICK 222.50 03/11/2023 RECO PRICE RETURN TILL NOW 363.00 163.15%</t>
+        </is>
+      </c>
+      <c r="I1956" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1956" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:46:34</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1957" t="inlineStr"/>
+      <c r="E1957" t="n">
+        <v>584.85</v>
+      </c>
+      <c r="G1957" t="inlineStr"/>
+      <c r="H1957" t="inlineStr">
+        <is>
+          <t>Tilaknagar Ind 584.85 PICK OF THE YEAR 292.00 05/11/2024 RECO PRICE RETURN TILL NOW 292.85 100.29%</t>
+        </is>
+      </c>
+      <c r="I1957" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1957" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:46:32</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1958" t="inlineStr"/>
+      <c r="E1958" t="n">
+        <v>584.95</v>
+      </c>
+      <c r="G1958" t="inlineStr"/>
+      <c r="H1958" t="inlineStr">
+        <is>
+          <t>Tilaknagar Ind 584.95 PICK OF THE YEAR 292.00 05/11/2024 RECO PRICE RETURN TILL NOW 292.95 100.33%</t>
+        </is>
+      </c>
+      <c r="I1958" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1958" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1959" t="n">
+        <v>789.85</v>
+      </c>
+      <c r="E1959" t="n">
+        <v>825</v>
+      </c>
+      <c r="F1959" t="n">
+        <v>780</v>
+      </c>
+      <c r="G1959" t="inlineStr"/>
+      <c r="H1959" t="inlineStr">
+        <is>
+          <t>फुल्ल के कोहिनूर
+HBL ENGINEERING
+790.00 14.70
+BUY
+TGT 825
+SL 780</t>
+        </is>
+      </c>
+      <c r="I1959" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1959" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1960" t="n">
+        <v>789.85</v>
+      </c>
+      <c r="E1960" t="n">
+        <v>825</v>
+      </c>
+      <c r="G1960" t="inlineStr"/>
+      <c r="H1960" t="inlineStr">
+        <is>
+          <t>HBL ENGINEERING 790.10 1.91% BUY TGT 825</t>
+        </is>
+      </c>
+      <c r="I1960" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1960" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1961" t="n">
+        <v>834</v>
+      </c>
+      <c r="E1961" t="n">
+        <v>875</v>
+      </c>
+      <c r="F1961" t="n">
+        <v>810</v>
+      </c>
+      <c r="G1961" t="inlineStr"/>
+      <c r="H1961" t="inlineStr">
+        <is>
+          <t>Graphite India 835.00 20.30 BUY TGT 875 SL 810</t>
+        </is>
+      </c>
+      <c r="I1961" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1961" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1962" t="n">
+        <v>1387.6</v>
+      </c>
+      <c r="E1962" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F1962" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G1962" t="inlineStr"/>
+      <c r="H1962" t="inlineStr">
+        <is>
+          <t>Chennai Petro 1387.70 1.09% BUY TGT 1450 SL 1360</t>
+        </is>
+      </c>
+      <c r="I1962" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1962" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:43:00</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1963" t="n">
+        <v>1489.8</v>
+      </c>
+      <c r="E1963" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G1963" t="inlineStr"/>
+      <c r="H1963" t="inlineStr">
+        <is>
+          <t>Ather Energy 1490.50 8.50 BUY TGT 1530 09:41 AM</t>
+        </is>
+      </c>
+      <c r="I1963" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1963" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:42:10</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>VASCONEQ</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr"/>
+      <c r="E1964" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G1964" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H1964" t="inlineStr">
+        <is>
+          <t>आरशा जैन Vascon Eng 35.67 2.38 BUY TARGET HIT 31.5</t>
+        </is>
+      </c>
+      <c r="I1964" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1964" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:42:07</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>VASCONEQ</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr"/>
+      <c r="E1965" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="F1965" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G1965" t="inlineStr"/>
+      <c r="H1965" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Vascon Eng 35.67 2.38 BUY TGT 34.2 SL 31.5</t>
+        </is>
+      </c>
+      <c r="I1965" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1965" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:42:06</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>VASCONEQ</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1966" t="inlineStr"/>
+      <c r="E1966" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="G1966" t="inlineStr"/>
+      <c r="H1966" t="inlineStr">
+        <is>
+          <t>Vascon Eng 35.67 2.38 BUY TGT 34.2</t>
+        </is>
+      </c>
+      <c r="I1966" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1966" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:42:02</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1967" t="inlineStr"/>
+      <c r="E1967" t="n">
+        <v>8550</v>
+      </c>
+      <c r="G1967" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1967" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेडानी
+Polycab India
+8425.00 0.70%
+SELL
+TGT 8550
+SL ---</t>
+        </is>
+      </c>
+      <c r="I1967" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1967" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:42:00</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1968" t="inlineStr"/>
+      <c r="E1968" t="n">
+        <v>8550</v>
+      </c>
+      <c r="G1968" t="inlineStr"/>
+      <c r="H1968" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Polycab India 8425.00 58.50 SELL TGT 8550 SL --</t>
+        </is>
+      </c>
+      <c r="I1968" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1968" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:40:00</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>SPARC</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1969" t="n">
+        <v>211.9</v>
+      </c>
+      <c r="E1969" t="n">
+        <v>220</v>
+      </c>
+      <c r="F1969" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1969" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H1969" t="inlineStr">
+        <is>
+          <t>ASTHA JAIN HEM SECURITIES SEBI REG NO: INH100002250 ALL STOCKS DISCUSSED PRICE 211.15 TARGET 218/220 STOP LOSS 200 खरीदें</t>
+        </is>
+      </c>
+      <c r="I1969" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1969" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:40:00</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>SPARC</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1970" t="n">
+        <v>209.72</v>
+      </c>
+      <c r="E1970" t="n">
+        <v>218</v>
+      </c>
+      <c r="F1970" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1970" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H1970" t="inlineStr">
+        <is>
+          <t>ASTHA JAIN HEM SECURITIES SEBI REG NO: INH100002250 ALL STOCKS DISCUSSED PRICE 211.15 TARGET 218/220 STOP LOSS 200 खरीदें</t>
+        </is>
+      </c>
+      <c r="I1970" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1970" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:38:00</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1971" t="n">
+        <v>796.95</v>
+      </c>
+      <c r="E1971" t="n">
+        <v>825</v>
+      </c>
+      <c r="F1971" t="n">
+        <v>780</v>
+      </c>
+      <c r="G1971" t="inlineStr">
+        <is>
+          <t>Kunal Saraogi</t>
+        </is>
+      </c>
+      <c r="H1971" t="inlineStr">
+        <is>
+          <t>कुणाल के कोडिंगर HBL ENGINEERING खरीदें PRICE 799.70 TARGET 825/850 STOP LOSS 780 ANALYST DISCLOSURE KUNAL SARAOGI Research Analyst SEBI REG NO: INH100001609</t>
+        </is>
+      </c>
+      <c r="I1971" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1971" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:38:00</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1972" t="n">
+        <v>796.95</v>
+      </c>
+      <c r="E1972" t="n">
+        <v>850</v>
+      </c>
+      <c r="F1972" t="n">
+        <v>780</v>
+      </c>
+      <c r="G1972" t="inlineStr"/>
+      <c r="H1972" t="inlineStr">
+        <is>
+          <t>कुणाल के कोहिनूर HBL ENGINEERING खरीदें PRICE 798.70 TARGET 825/850 STOP LOSS 780</t>
+        </is>
+      </c>
+      <c r="I1972" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1972" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:36:00</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1973" t="n">
+        <v>762</v>
+      </c>
+      <c r="E1973" t="n">
+        <v>875</v>
+      </c>
+      <c r="G1973" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1973" t="inlineStr">
+        <is>
+          <t>ANALYST DISCLOSURE Siddharth Sedani Anand Rathi Shares and Stock Brokers SEBI REG NO: INH000000834 ALL STOCKS DISCUSSED Analyst NO Analyst's Relative NO Analyst's Associate / Firm MAY BE SUPER SID TD Power खरीदें PRICE 761.65 TARGET 775/875 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1973" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1973" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:36:00</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1974" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1974" t="n">
+        <v>761.35</v>
+      </c>
+      <c r="E1974" t="n">
+        <v>875</v>
+      </c>
+      <c r="G1974" t="inlineStr"/>
+      <c r="H1974" t="inlineStr">
+        <is>
+          <t>TD Power खरीदें PRICE 760.45 TARGET 775/875 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1974" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1974" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:36:00</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="C1975" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1975" t="n">
+        <v>761.35</v>
+      </c>
+      <c r="E1975" t="n">
+        <v>775</v>
+      </c>
+      <c r="G1975" t="inlineStr"/>
+      <c r="H1975" t="inlineStr">
+        <is>
+          <t>TD Power खरीदें PRICE 760.45 TARGET 775/875 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1975" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1975" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:30:00</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C1976" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1976" t="n">
+        <v>832</v>
+      </c>
+      <c r="E1976" t="n">
+        <v>890</v>
+      </c>
+      <c r="F1976" t="n">
+        <v>810</v>
+      </c>
+      <c r="G1976" t="inlineStr"/>
+      <c r="H1976" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Graphite India खरीदें PRICE 834.45 TARGET 875/890 STOP LOSS 810</t>
+        </is>
+      </c>
+      <c r="I1976" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1976" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:30:00</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1977" t="n">
+        <v>832</v>
+      </c>
+      <c r="E1977" t="n">
+        <v>875</v>
+      </c>
+      <c r="F1977" t="n">
+        <v>810</v>
+      </c>
+      <c r="G1977" t="inlineStr"/>
+      <c r="H1977" t="inlineStr">
+        <is>
+          <t>शुभ 'मंगला' शेयर Graphite India खरीदें PRICE 834.45 TARGET 875/890 STOP LOSS 810</t>
+        </is>
+      </c>
+      <c r="I1977" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1977" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:27:00</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1978" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E1978" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F1978" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G1978" t="inlineStr"/>
+      <c r="H1978" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट Chennai Petro खरीदें PRICE 1407.00 TARGET 1450/1480 STOP LOSS 1360</t>
+        </is>
+      </c>
+      <c r="I1978" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1978" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:27:00</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>CHENNPETRO</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1979" t="n">
+        <v>1400</v>
+      </c>
+      <c r="E1979" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F1979" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G1979" t="inlineStr"/>
+      <c r="H1979" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट Chennai Petro खरीदें PRICE 1407.00 TARGET 1450/1480 STOP LOSS 1360</t>
+        </is>
+      </c>
+      <c r="I1979" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1979" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C1980" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1980" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E1980" t="n">
+        <v>1530</v>
+      </c>
+      <c r="F1980" t="n">
+        <v>555</v>
+      </c>
+      <c r="G1980" t="inlineStr"/>
+      <c r="H1980" t="inlineStr">
+        <is>
+          <t>SUPER SID Ather Energy खरीदें PRICE 1495.00 TARGET 1530/2200 STOP LOSS 555</t>
+        </is>
+      </c>
+      <c r="I1980" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1980" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C1981" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1981" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E1981" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F1981" t="n">
+        <v>555</v>
+      </c>
+      <c r="G1981" t="inlineStr"/>
+      <c r="H1981" t="inlineStr">
+        <is>
+          <t>SUPER SID Ather Energy खरीदें PRICE 1495.00 TARGET 1530/2200 STOP LOSS 555</t>
+        </is>
+      </c>
+      <c r="I1981" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1981" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C1982" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1982" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E1982" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G1982" t="inlineStr"/>
+      <c r="H1982" t="inlineStr">
+        <is>
+          <t>Ather Energy खरीदें PRICE 1493.30 TARGET 1530/2200 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1982" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1982" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C1983" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1983" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E1983" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G1983" t="inlineStr"/>
+      <c r="H1983" t="inlineStr">
+        <is>
+          <t>Ather Energy खरीदें PRICE 1493.30 TARGET 1530/2200 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1983" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1983" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1984" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E1984" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G1984" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1984" t="inlineStr">
+        <is>
+          <t>SUPER SID Ather Energy खरीदें PRICE 1489.60 TARGET 1530/2200 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1984" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1984" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:26:00</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1985" t="n">
+        <v>1495</v>
+      </c>
+      <c r="E1985" t="n">
+        <v>1530</v>
+      </c>
+      <c r="G1985" t="inlineStr">
+        <is>
+          <t>Siddharth Sedani</t>
+        </is>
+      </c>
+      <c r="H1985" t="inlineStr">
+        <is>
+          <t>SUPER SID Ather Energy खरीदें PRICE 1489.60 TARGET 1530/2200 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I1985" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1985" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1986" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E1986" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F1986" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1986" t="inlineStr"/>
+      <c r="H1986" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह IPCA Labs (Cash) BUY PRICE 1997 TARGET 2020, 2035, 2050 STOP LOSS 1950</t>
+        </is>
+      </c>
+      <c r="I1986" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1986" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1987" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E1987" t="n">
+        <v>2035</v>
+      </c>
+      <c r="F1987" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1987" t="inlineStr"/>
+      <c r="H1987" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह IPCA Labs (Cash) BUY PRICE 1997 TARGET 2020, 2035, 2050 STOP LOSS 1950</t>
+        </is>
+      </c>
+      <c r="I1987" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1987" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:16:00</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1988" t="n">
+        <v>2000.3</v>
+      </c>
+      <c r="E1988" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F1988" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1988" t="inlineStr"/>
+      <c r="H1988" t="inlineStr">
+        <is>
+          <t>अनिल सिंघवी की सलाह IPCA Labs (Cash) BUY PRICE 1997 TARGET 2020, 2035, 2050 STOP LOSS 1950</t>
+        </is>
+      </c>
+      <c r="I1988" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1988" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>SBICARD29SEP26</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1989" t="n">
+        <v>618.65</v>
+      </c>
+      <c r="E1989" t="n">
+        <v>603</v>
+      </c>
+      <c r="F1989" t="n">
+        <v>624</v>
+      </c>
+      <c r="G1989" t="inlineStr"/>
+      <c r="H1989" t="inlineStr">
+        <is>
+          <t>MY CHOICE SBI CARD FUT S 603 624</t>
+        </is>
+      </c>
+      <c r="I1989" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1989" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1990" t="n">
+        <v>1791.8</v>
+      </c>
+      <c r="E1990" t="n">
+        <v>1820</v>
+      </c>
+      <c r="F1990" t="n">
+        <v>1767</v>
+      </c>
+      <c r="G1990" t="inlineStr"/>
+      <c r="H1990" t="inlineStr">
+        <is>
+          <t>MY CHOICE ADANI PORTS B 1820 1767</t>
+        </is>
+      </c>
+      <c r="I1990" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1990" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>SBICARD29SEP26</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1991" t="n">
+        <v>615</v>
+      </c>
+      <c r="E1991" t="n">
+        <v>603</v>
+      </c>
+      <c r="G1991" t="inlineStr"/>
+      <c r="H1991" t="inlineStr">
+        <is>
+          <t>MY CHOICE SBI CARD FUT S 603</t>
+        </is>
+      </c>
+      <c r="I1991" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1991" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1992" t="n">
+        <v>1791.8</v>
+      </c>
+      <c r="E1992" t="n">
+        <v>1820</v>
+      </c>
+      <c r="F1992" t="n">
+        <v>176</v>
+      </c>
+      <c r="G1992" t="inlineStr"/>
+      <c r="H1992" t="inlineStr">
+        <is>
+          <t>MY CHOICE ADANI PORTS B 1820 176</t>
+        </is>
+      </c>
+      <c r="I1992" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1992" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1993" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E1993" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F1993" t="n">
+        <v>1941</v>
+      </c>
+      <c r="G1993" t="inlineStr"/>
+      <c r="H1993" t="inlineStr">
+        <is>
+          <t>CASH DR LAL PATHLABS B 2000 1941</t>
+        </is>
+      </c>
+      <c r="I1993" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1993" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>WIPRO29SEP26</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D1994" t="n">
+        <v>163.88</v>
+      </c>
+      <c r="E1994" t="n">
+        <v>157</v>
+      </c>
+      <c r="F1994" t="n">
+        <v>169</v>
+      </c>
+      <c r="G1994" t="inlineStr"/>
+      <c r="H1994" t="inlineStr">
+        <is>
+          <t>TECHNO WIPRO FUT S 157 169</t>
+        </is>
+      </c>
+      <c r="I1994" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1994" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1995" t="n">
+        <v>1844</v>
+      </c>
+      <c r="E1995" t="n">
+        <v>1895</v>
+      </c>
+      <c r="F1995" t="n">
+        <v>1818</v>
+      </c>
+      <c r="G1995" t="inlineStr"/>
+      <c r="H1995" t="inlineStr">
+        <is>
+          <t>FUTURE OBEROI REALTY FUT B 1895 1818</t>
+        </is>
+      </c>
+      <c r="I1995" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J1995" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1996" t="n">
+        <v>1071.6</v>
+      </c>
+      <c r="E1996" t="n">
+        <v>1110</v>
+      </c>
+      <c r="F1996" t="n">
+        <v>1065</v>
+      </c>
+      <c r="G1996" t="inlineStr"/>
+      <c r="H1996" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT 360 ONE WAM B 1110 1065</t>
+        </is>
+      </c>
+      <c r="I1996" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1996" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1997" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="E1997" t="n">
+        <v>343</v>
+      </c>
+      <c r="F1997" t="n">
+        <v>330</v>
+      </c>
+      <c r="G1997" t="inlineStr"/>
+      <c r="H1997" t="inlineStr">
+        <is>
+          <t>MY CHOICE NYKAA B 343 330</t>
+        </is>
+      </c>
+      <c r="I1997" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1997" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1998" t="n">
+        <v>1696.7</v>
+      </c>
+      <c r="E1998" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F1998" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G1998" t="inlineStr"/>
+      <c r="H1998" t="inlineStr">
+        <is>
+          <t>MY CHOICE NUVAMA WEALTH B 1730 1675</t>
+        </is>
+      </c>
+      <c r="I1998" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1998" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D1999" t="n">
+        <v>1071.6</v>
+      </c>
+      <c r="E1999" t="n">
+        <v>1110</v>
+      </c>
+      <c r="G1999" t="inlineStr"/>
+      <c r="H1999" t="inlineStr">
+        <is>
+          <t>NEWS IMPACT 360 ONE WAM B 1110 10</t>
+        </is>
+      </c>
+      <c r="I1999" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J1999" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2000" t="n">
+        <v>496</v>
+      </c>
+      <c r="E2000" t="n">
+        <v>505</v>
+      </c>
+      <c r="F2000" t="n">
+        <v>490</v>
+      </c>
+      <c r="G2000" t="inlineStr"/>
+      <c r="H2000" t="inlineStr">
+        <is>
+          <t>FUNDA HIND COPPER B 505 490</t>
+        </is>
+      </c>
+      <c r="I2000" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2000" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:16:00</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2001" t="n">
+        <v>1203.9</v>
+      </c>
+      <c r="E2001" t="n">
+        <v>1410</v>
+      </c>
+      <c r="G2001" t="inlineStr">
+        <is>
+          <t>BofA</t>
+        </is>
+      </c>
+      <c r="H2001" t="inlineStr">
+        <is>
+          <t>BofA NEUTRAL 1410 --</t>
+        </is>
+      </c>
+      <c r="I2001" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2001" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2002" t="n">
+        <v>238</v>
+      </c>
+      <c r="E2002" t="n">
+        <v>245</v>
+      </c>
+      <c r="G2002" t="inlineStr"/>
+      <c r="H2002" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY ONGC 239.00 2.10 BUY TGT 245</t>
+        </is>
+      </c>
+      <c r="I2002" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2002" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2003" t="n">
+        <v>990</v>
+      </c>
+      <c r="E2003" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G2003" t="inlineStr"/>
+      <c r="H2003" t="inlineStr">
+        <is>
+          <t>Shriram Finance 990.00 TARGET ₹1200</t>
+        </is>
+      </c>
+      <c r="I2003" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2003" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>GALAXYSURF</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2004" t="n">
+        <v>2262</v>
+      </c>
+      <c r="E2004" t="n">
+        <v>2328</v>
+      </c>
+      <c r="F2004" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G2004" t="inlineStr"/>
+      <c r="H2004" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+Galaxy Surfactants
+2246.60
+BUY
+TGT 2328
+SL 2200</t>
+        </is>
+      </c>
+      <c r="I2004" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2004" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C2005" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2005" t="n">
+        <v>238</v>
+      </c>
+      <c r="E2005" t="n">
+        <v>245.2</v>
+      </c>
+      <c r="F2005" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2005" t="inlineStr"/>
+      <c r="H2005" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY ONGC BUY PRICE 239.0 TARGET 245/2 STOP LOSS 234</t>
+        </is>
+      </c>
+      <c r="I2005" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2005" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2006" t="n">
+        <v>238</v>
+      </c>
+      <c r="E2006" t="n">
+        <v>245</v>
+      </c>
+      <c r="F2006" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2006" t="inlineStr"/>
+      <c r="H2006" t="inlineStr">
+        <is>
+          <t>सुमित बगडिया की राय ONGC BUY PRICE 239.00 TARGET 245/250 STOP LOSS 234</t>
+        </is>
+      </c>
+      <c r="I2006" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2006" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2007" t="n">
+        <v>238</v>
+      </c>
+      <c r="E2007" t="n">
+        <v>250</v>
+      </c>
+      <c r="F2007" t="n">
+        <v>234</v>
+      </c>
+      <c r="G2007" t="inlineStr"/>
+      <c r="H2007" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY ONGC BU PRICE 239.00 TARGET 245/250 STOP LOSS 234</t>
+        </is>
+      </c>
+      <c r="I2007" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2007" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C2008" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2008" t="n">
+        <v>3456</v>
+      </c>
+      <c r="E2008" t="n">
+        <v>3570</v>
+      </c>
+      <c r="F2008" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G2008" t="inlineStr"/>
+      <c r="H2008" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY MCX 3427.70 53.70 BUY TGT 3570 SL 3300</t>
+        </is>
+      </c>
+      <c r="I2008" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2008" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2009" t="n">
+        <v>2547</v>
+      </c>
+      <c r="E2009" t="n">
+        <v>2590</v>
+      </c>
+      <c r="G2009" t="inlineStr"/>
+      <c r="H2009" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+R R Kabel
+2529.80 53.10
+BUY
+TGT 2590</t>
+        </is>
+      </c>
+      <c r="I2009" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2009" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C2010" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2010" t="n">
+        <v>8394</v>
+      </c>
+      <c r="E2010" t="n">
+        <v>8550</v>
+      </c>
+      <c r="G2010" t="inlineStr"/>
+      <c r="H2010" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेहगल की राय
+Polycab India
+LL
+PRICE ▶ 8366.50
+TARGET ▶ 8550/10600
+STOP LOSS ▶ --</t>
+        </is>
+      </c>
+      <c r="I2010" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2010" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="C2011" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2011" t="n">
+        <v>8394</v>
+      </c>
+      <c r="E2011" t="n">
+        <v>10600</v>
+      </c>
+      <c r="G2011" t="inlineStr"/>
+      <c r="H2011" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेहगल की राय
+Polycab India
+LL
+PRICE ▶ 8366.50
+TARGET ▶ 8550/10600
+STOP LOSS ▶ --</t>
+        </is>
+      </c>
+      <c r="I2011" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2011" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>ADANIENT27OCT26</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2012" t="n">
+        <v>2930.1</v>
+      </c>
+      <c r="E2012" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F2012" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G2012" t="inlineStr"/>
+      <c r="H2012" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Adani Ent Oct Fut SELL PRICE 2920.20 TARGET 2850/2800 STOP LOSS 3000</t>
+        </is>
+      </c>
+      <c r="I2012" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2012" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>ADANIENT27OCT26</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2013" t="n">
+        <v>2930.1</v>
+      </c>
+      <c r="E2013" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F2013" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G2013" t="inlineStr"/>
+      <c r="H2013" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Adani Ent Oct Fut SELL PRICE 2920.20 TARGET 2850/2800 STOP LOSS 3000</t>
+        </is>
+      </c>
+      <c r="I2013" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2013" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>LGEINDIA</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2014" t="n">
+        <v>1711</v>
+      </c>
+      <c r="E2014" t="n">
+        <v>1760</v>
+      </c>
+      <c r="F2014" t="n">
+        <v>1660</v>
+      </c>
+      <c r="G2014" t="inlineStr">
+        <is>
+          <t>Kunal Shah</t>
+        </is>
+      </c>
+      <c r="H2014" t="inlineStr">
+        <is>
+          <t>कुणाल शाह की राय LG Electronics BUY PRICE 1697.70 TARGET 1740/1760 STOP LOSS 1660</t>
+        </is>
+      </c>
+      <c r="I2014" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2014" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>LGEINDIA</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2015" t="n">
+        <v>1711</v>
+      </c>
+      <c r="E2015" t="n">
+        <v>1740</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>1660</v>
+      </c>
+      <c r="G2015" t="inlineStr"/>
+      <c r="H2015" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY LG Electronics BUY PRICE 1697.70 TARGET 1740/1760 STOP LOSS 1660</t>
+        </is>
+      </c>
+      <c r="I2015" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2015" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>GALAXYSURF</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2016" t="n">
+        <v>2262</v>
+      </c>
+      <c r="E2016" t="n">
+        <v>2320</v>
+      </c>
+      <c r="F2016" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G2016" t="inlineStr"/>
+      <c r="H2016" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Galaxy Surfactants BUY PRICE 2246.60 TARGET 2320/2375 STOP LOSS 2200</t>
+        </is>
+      </c>
+      <c r="I2016" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2016" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>GALAXYSURF</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2017" t="n">
+        <v>2262</v>
+      </c>
+      <c r="E2017" t="n">
+        <v>2375</v>
+      </c>
+      <c r="F2017" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G2017" t="inlineStr"/>
+      <c r="H2017" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY Galaxy Surfactants BUY PRICE 2246.60 TARGET 2320/2375 STOP LOSS 2200</t>
+        </is>
+      </c>
+      <c r="I2017" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2017" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2018" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E2018" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F2018" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G2018" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H2018" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय IPCA Labs BUY PRICE 1997.10 TARGET 2060/2090 STOP LOSS 1970</t>
+        </is>
+      </c>
+      <c r="I2018" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2018" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C2019" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2019" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E2019" t="n">
+        <v>2090</v>
+      </c>
+      <c r="F2019" t="n">
+        <v>1970</v>
+      </c>
+      <c r="G2019" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H2019" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय IPCA Labs BUY PRICE 1997.10 TARGET 2060/2090 STOP LOSS 1970</t>
+        </is>
+      </c>
+      <c r="I2019" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2019" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="C2020" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2020" t="n">
+        <v>2550</v>
+      </c>
+      <c r="E2020" t="n">
+        <v>2620</v>
+      </c>
+      <c r="F2020" t="n">
+        <v>2495</v>
+      </c>
+      <c r="G2020" t="inlineStr"/>
+      <c r="H2020" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY
+R R Kabel
+BUY
+PRICE ▶ 2529.80
+TARGET ▶ 2590/2620
+STOP LOSS ▶ 2495</t>
+        </is>
+      </c>
+      <c r="I2020" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2020" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>RRKABEL</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2021" t="n">
+        <v>2550</v>
+      </c>
+      <c r="E2021" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F2021" t="n">
+        <v>2495</v>
+      </c>
+      <c r="G2021" t="inlineStr"/>
+      <c r="H2021" t="inlineStr">
+        <is>
+          <t>PICK OF THE DAY R R Kabel BUY PRICE 2529.80 TARGET 2590/2620 STOP LOSS 2495</t>
+        </is>
+      </c>
+      <c r="I2021" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2021" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="C2022" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2022" t="n">
+        <v>1774</v>
+      </c>
+      <c r="E2022" t="n">
+        <v>85</v>
+      </c>
+      <c r="G2022" t="inlineStr"/>
+      <c r="H2022" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Bajaj Hsg Fin
+82.96 -0.56
+SELL
+लक्ष्य ₹85</t>
+        </is>
+      </c>
+      <c r="I2022" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2022" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>GODREJIND</t>
+        </is>
+      </c>
+      <c r="C2023" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2023" t="n">
+        <v>1093</v>
+      </c>
+      <c r="E2023" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F2023" t="n">
+        <v>990</v>
+      </c>
+      <c r="G2023" t="inlineStr"/>
+      <c r="H2023" t="inlineStr">
+        <is>
+          <t>Godrej Ind खरीदें PRICE 1099.00 TARGET 1400 STOP LOSS 990</t>
+        </is>
+      </c>
+      <c r="I2023" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2023" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>GODREJIND</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2024" t="n">
+        <v>1093</v>
+      </c>
+      <c r="E2024" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G2024" t="inlineStr"/>
+      <c r="H2024" t="inlineStr">
+        <is>
+          <t>INVESTMENT GODREJ INDUSTRIES B 1400 12 MONTH</t>
+        </is>
+      </c>
+      <c r="I2024" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2024" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2025" t="n">
+        <v>2493.5</v>
+      </c>
+      <c r="E2025" t="n">
+        <v>2530</v>
+      </c>
+      <c r="F2025" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G2025" t="inlineStr"/>
+      <c r="H2025" t="inlineStr">
+        <is>
+          <t>MY CHOICE WAAREE ENERGIES B 2530 2450</t>
+        </is>
+      </c>
+      <c r="I2025" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2025" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>BAJFINANCE98029SEP26CE</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2026" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="E2026" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2026" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2026" t="inlineStr"/>
+      <c r="H2026" t="inlineStr">
+        <is>
+          <t>OPTION BAJAJ FINANCE 980 CE@14 CALL B TGT 30 SL/DUR 7</t>
+        </is>
+      </c>
+      <c r="I2026" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J2026" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>NAVA</t>
+        </is>
+      </c>
+      <c r="C2027" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2027" t="n">
+        <v>552.25</v>
+      </c>
+      <c r="E2027" t="n">
+        <v>575</v>
+      </c>
+      <c r="F2027" t="n">
+        <v>550</v>
+      </c>
+      <c r="G2027" t="inlineStr"/>
+      <c r="H2027" t="inlineStr">
+        <is>
+          <t>CASH NAVA CALL B TGT 575 SL/DUR 550</t>
+        </is>
+      </c>
+      <c r="I2027" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2027" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>SBICARD29SEP26</t>
+        </is>
+      </c>
+      <c r="C2028" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2028" t="n">
+        <v>615</v>
+      </c>
+      <c r="E2028" t="n">
+        <v>603</v>
+      </c>
+      <c r="F2028" t="n">
+        <v>624</v>
+      </c>
+      <c r="G2028" t="inlineStr"/>
+      <c r="H2028" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+SBI Card Fut
+बेचें
+PRICE ▶ 617.70
+TARGET ▶ 603
+STOP LOSS ▶ 624</t>
+        </is>
+      </c>
+      <c r="I2028" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2028" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C2029" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2029" t="n">
+        <v>1791.8</v>
+      </c>
+      <c r="E2029" t="n">
+        <v>1820</v>
+      </c>
+      <c r="F2029" t="n">
+        <v>1767</v>
+      </c>
+      <c r="G2029" t="inlineStr"/>
+      <c r="H2029" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर Adani Ports खरीदें PRICE 1785.30 TARGET 1820 STOP LOSS 1767</t>
+        </is>
+      </c>
+      <c r="I2029" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2029" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>COCHINSHIP</t>
+        </is>
+      </c>
+      <c r="C2030" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2030" t="n">
+        <v>1370</v>
+      </c>
+      <c r="E2030" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F2030" t="n">
+        <v>1356</v>
+      </c>
+      <c r="G2030" t="inlineStr"/>
+      <c r="H2030" t="inlineStr">
+        <is>
+          <t>MY CHOICE Cochin Shipyard खरीदें PRICE 1370.00 TARGET 1400 STOP LOSS 1356</t>
+        </is>
+      </c>
+      <c r="I2030" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2030" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>COCHINSHIP</t>
+        </is>
+      </c>
+      <c r="C2031" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2031" t="n">
+        <v>1370</v>
+      </c>
+      <c r="E2031" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G2031" t="inlineStr"/>
+      <c r="H2031" t="inlineStr">
+        <is>
+          <t>MY CHOICE Cochin Shipyard PRICE 1370.00 TARGET 1400</t>
+        </is>
+      </c>
+      <c r="I2031" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2031" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C2032" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2032" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E2032" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F2032" t="n">
+        <v>1675</v>
+      </c>
+      <c r="G2032" t="inlineStr"/>
+      <c r="H2032" t="inlineStr">
+        <is>
+          <t>MY CHOICE Nuvama Wealth खरीदें PRICE 1695.40 TARGET 1730 STOP LOSS 1675</t>
+        </is>
+      </c>
+      <c r="I2032" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2032" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C2033" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2033" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E2033" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G2033" t="inlineStr"/>
+      <c r="H2033" t="inlineStr">
+        <is>
+          <t>MY CHOICE
+Nuvama Wealth
+PRICE → 1695.40
+TARGET → 1730</t>
+        </is>
+      </c>
+      <c r="I2033" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2033" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="C2034" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2034" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="E2034" t="n">
+        <v>343</v>
+      </c>
+      <c r="F2034" t="n">
+        <v>330</v>
+      </c>
+      <c r="G2034" t="inlineStr"/>
+      <c r="H2034" t="inlineStr">
+        <is>
+          <t>MY CHOICE Nykaa खरीदें PRICE 335.30 TARGET 343 STOP LOSS 330</t>
+        </is>
+      </c>
+      <c r="I2034" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2034" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2035" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="C2035" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2035" t="n">
+        <v>2494.4</v>
+      </c>
+      <c r="E2035" t="n">
+        <v>2530</v>
+      </c>
+      <c r="F2035" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G2035" t="inlineStr"/>
+      <c r="H2035" t="inlineStr">
+        <is>
+          <t>MY CHOICE Waaree Energies खरीदें PRICE 2482.00 TARGET 2530 STOP LOSS 2450</t>
+        </is>
+      </c>
+      <c r="I2035" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2035" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2036" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="C2036" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2036" t="n">
+        <v>2494.4</v>
+      </c>
+      <c r="E2036" t="n">
+        <v>2530</v>
+      </c>
+      <c r="G2036" t="inlineStr"/>
+      <c r="H2036" t="inlineStr">
+        <is>
+          <t>MY CHOICE Waaree Energies PRICE 2482.00 TARGET 2530</t>
+        </is>
+      </c>
+      <c r="I2036" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2036" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2037" t="inlineStr">
+        <is>
+          <t>STLTECH-BE</t>
+        </is>
+      </c>
+      <c r="C2037" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2037" t="n">
+        <v>830</v>
+      </c>
+      <c r="E2037" t="n">
+        <v>870</v>
+      </c>
+      <c r="F2037" t="n">
+        <v>814</v>
+      </c>
+      <c r="G2037" t="inlineStr"/>
+      <c r="H2037" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर Sterlite Tech खरीदें PRICE 823.75 TARGET 870 STOP LOSS 814</t>
+        </is>
+      </c>
+      <c r="I2037" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2037" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>STLTECH-BE</t>
+        </is>
+      </c>
+      <c r="C2038" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2038" t="n">
+        <v>830</v>
+      </c>
+      <c r="E2038" t="n">
+        <v>870</v>
+      </c>
+      <c r="G2038" t="inlineStr"/>
+      <c r="H2038" t="inlineStr">
+        <is>
+          <t>खबर के दम पर Sterlite Tech PRICE 823.75 TARGET 870</t>
+        </is>
+      </c>
+      <c r="I2038" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2038" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2039" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C2039" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2039" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E2039" t="n">
+        <v>1110</v>
+      </c>
+      <c r="F2039" t="n">
+        <v>1065</v>
+      </c>
+      <c r="G2039" t="inlineStr"/>
+      <c r="H2039" t="inlineStr">
+        <is>
+          <t>खबर के दम पर
+360 One Wam
+खरीदें
+PRICE → 1080.80
+TARGET → 1110
+STOP LOSS → 1065</t>
+        </is>
+      </c>
+      <c r="I2039" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2039" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2040" t="inlineStr">
+        <is>
+          <t>GODREJIND</t>
+        </is>
+      </c>
+      <c r="C2040" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2040" t="n">
+        <v>1093</v>
+      </c>
+      <c r="E2040" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G2040" t="inlineStr"/>
+      <c r="H2040" t="inlineStr">
+        <is>
+          <t>इन्वेस्टमेंट PICK Godrej Ind खरीदें PRICE 1099.00 TARGET 1400 DURATION 990</t>
+        </is>
+      </c>
+      <c r="I2040" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2040" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="C2041" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2041" t="n">
+        <v>496</v>
+      </c>
+      <c r="E2041" t="n">
+        <v>505</v>
+      </c>
+      <c r="F2041" t="n">
+        <v>490</v>
+      </c>
+      <c r="G2041" t="inlineStr"/>
+      <c r="H2041" t="inlineStr">
+        <is>
+          <t>Funda Pick Hind Copper खरीदें PRICE 495.70 TARGET 505 STOP LOSS 490</t>
+        </is>
+      </c>
+      <c r="I2041" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2041" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2042" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C2042" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2042" t="n">
+        <v>982</v>
+      </c>
+      <c r="E2042" t="n">
+        <v>85</v>
+      </c>
+      <c r="G2042" t="inlineStr"/>
+      <c r="H2042" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS SELL लक्ष्य ₹85</t>
+        </is>
+      </c>
+      <c r="I2042" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2042" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2043" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="C2043" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2043" t="n">
+        <v>1791.8</v>
+      </c>
+      <c r="E2043" t="n">
+        <v>2160</v>
+      </c>
+      <c r="G2043" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H2043" t="inlineStr">
+        <is>
+          <t>जेफरीज
+Adani Ports
+1785.30 -22.00
+BUY
+लक्ष्य ₹2160</t>
+        </is>
+      </c>
+      <c r="I2043" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2043" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2044" t="inlineStr">
+        <is>
+          <t>MCX27OCT26</t>
+        </is>
+      </c>
+      <c r="C2044" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2044" t="n">
+        <v>3480.3</v>
+      </c>
+      <c r="E2044" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F2044" t="n">
+        <v>3401</v>
+      </c>
+      <c r="G2044" t="inlineStr"/>
+      <c r="H2044" t="inlineStr">
+        <is>
+          <t>आज का FUTURE
+MCX Oct Fut
+खरीदें
+PRICE → 3457.30
+TARGET → 3600
+STOP LOSS → 3401</t>
+        </is>
+      </c>
+      <c r="I2044" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2044" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2045" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY29SEP26</t>
+        </is>
+      </c>
+      <c r="C2045" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2045" t="n">
+        <v>1844</v>
+      </c>
+      <c r="E2045" t="n">
+        <v>1895</v>
+      </c>
+      <c r="F2045" t="n">
+        <v>1818</v>
+      </c>
+      <c r="G2045" t="inlineStr"/>
+      <c r="H2045" t="inlineStr">
+        <is>
+          <t>आज का FUTURE
+Oberoi Realty Fut
+खरीदें
+PRICE → 1847.40
+TARGET → 1895
+STOP LOSS → 1818</t>
+        </is>
+      </c>
+      <c r="I2045" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2045" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>LALPATHLAB</t>
+        </is>
+      </c>
+      <c r="C2046" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2046" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E2046" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F2046" t="n">
+        <v>1941</v>
+      </c>
+      <c r="G2046" t="inlineStr"/>
+      <c r="H2046" t="inlineStr">
+        <is>
+          <t>CASH का शेयर Dr Lal Path खरीदें PRICE 1961.30 TARGET 2000 STOP LOSS 1941</t>
+        </is>
+      </c>
+      <c r="I2046" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2046" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2047" t="inlineStr">
+        <is>
+          <t>NAVA</t>
+        </is>
+      </c>
+      <c r="C2047" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2047" t="n">
+        <v>552.25</v>
+      </c>
+      <c r="E2047" t="n">
+        <v>575</v>
+      </c>
+      <c r="F2047" t="n">
+        <v>550</v>
+      </c>
+      <c r="G2047" t="inlineStr"/>
+      <c r="H2047" t="inlineStr">
+        <is>
+          <t>नेहा के शेयर
+Nava Ltd
+खरीदें
+PRICE ▶ 557.00
+TARGET ▶ 575
+STOP LOSS ▶ 550</t>
+        </is>
+      </c>
+      <c r="I2047" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2047" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2048" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C2048" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2048" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E2048" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G2048" t="inlineStr"/>
+      <c r="H2048" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Laurus Labs
+2026.20 -7.80
+SELL
+लक्ष्य ₹1250</t>
+        </is>
+      </c>
+      <c r="I2048" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2048" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr">
+        <is>
+          <t>AUBANK29SEP26</t>
+        </is>
+      </c>
+      <c r="C2049" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2049" t="n">
+        <v>997.4</v>
+      </c>
+      <c r="E2049" t="n">
+        <v>925</v>
+      </c>
+      <c r="F2049" t="n">
+        <v>1035</v>
+      </c>
+      <c r="G2049" t="inlineStr"/>
+      <c r="H2049" t="inlineStr">
+        <is>
+          <t>श्रीकांत चौहान की राय AU Small Fin Fut बेचें PRICE 1002.60 TARGET 925 STOP LOSS 1035</t>
+        </is>
+      </c>
+      <c r="I2049" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2049" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2050" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="C2050" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2050" t="n">
+        <v>4774.2</v>
+      </c>
+      <c r="E2050" t="n">
+        <v>4900</v>
+      </c>
+      <c r="F2050" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G2050" t="inlineStr"/>
+      <c r="H2050" t="inlineStr">
+        <is>
+          <t>TRADING CALL HAL खरीदें PRICE 4774.20 TARGET 4900 STOP LOSS 4700</t>
+        </is>
+      </c>
+      <c r="I2050" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2050" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2051" t="inlineStr">
+        <is>
+          <t>KARURVYSYA</t>
+        </is>
+      </c>
+      <c r="C2051" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2051" t="n">
+        <v>325</v>
+      </c>
+      <c r="E2051" t="n">
+        <v>379</v>
+      </c>
+      <c r="G2051" t="inlineStr"/>
+      <c r="H2051" t="inlineStr">
+        <is>
+          <t>LONG-TERM CALL Karur V BUY TARGET 379 DURATION 6-12 महीने 325.00</t>
+        </is>
+      </c>
+      <c r="I2051" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2051" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" t="inlineStr">
+        <is>
+          <t>2026-09-25 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2052" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C2052" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2052" t="n">
+        <v>4075</v>
+      </c>
+      <c r="E2052" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F2052" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G2052" t="inlineStr"/>
+      <c r="H2052" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ सेदानी की पसंद TVS Motor BUY TARGET 4500 STOP LOSS 3900 TVS Motor 4091.00 1.06%</t>
+        </is>
+      </c>
+      <c r="I2052" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2052" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J1897"/>
+  <autoFilter ref="A1:J2052"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -79803,7 +79803,6 @@
       <c r="F1898" t="n">
         <v>225</v>
       </c>
-      <c r="G1898" t="inlineStr"/>
       <c r="H1898" t="inlineStr">
         <is>
           <t>11 बजे की लेडीज स्पेशल ONGC खरीदें PRICE 236.00 TARGET 247/250 STOP LOSS 225</t>
@@ -79845,7 +79844,6 @@
       <c r="F1899" t="n">
         <v>225</v>
       </c>
-      <c r="G1899" t="inlineStr"/>
       <c r="H1899" t="inlineStr">
         <is>
           <t>11 बजे की लेडीज स्पेशल ONGC खरीदें PRICE 236.00 TARGET 247/250 STOP LOSS 225</t>
@@ -79887,7 +79885,6 @@
       <c r="F1900" t="n">
         <v>1098</v>
       </c>
-      <c r="G1900" t="inlineStr"/>
       <c r="H1900" t="inlineStr">
         <is>
           <t>Voltas Fut 1120.20 0.79% BUY TGT 1165 SL 1098</t>
@@ -79929,7 +79926,6 @@
       <c r="F1901" t="n">
         <v>780</v>
       </c>
-      <c r="G1901" t="inlineStr"/>
       <c r="H1901" t="inlineStr">
         <is>
           <t>HBL ENGINEERING 803.50 28.20 BUY TGT 825 SL 780 Fri 25 Sep'26</t>
@@ -79971,7 +79967,6 @@
       <c r="F1902" t="n">
         <v>4900</v>
       </c>
-      <c r="G1902" t="inlineStr"/>
       <c r="H1902" t="inlineStr">
         <is>
           <t>श्रीकांत चौहान की राय Torrent Pharma खरीदें STOP LOSS 4900 TARGET 5050/5075 DURATION 1-3 महीने Torrent Pharma 4952.00</t>
@@ -80013,7 +80008,6 @@
       <c r="F1903" t="n">
         <v>620</v>
       </c>
-      <c r="G1903" t="inlineStr"/>
       <c r="H1903" t="inlineStr">
         <is>
           <t>Jubilant Ingrevia खरीदें STOP LOSS 620 TARGET 775/800 DURATION 4-8 महीने Jubilant Ingrevia 646.05 10.70</t>
@@ -80055,7 +80049,6 @@
       <c r="F1904" t="n">
         <v>620</v>
       </c>
-      <c r="G1904" t="inlineStr"/>
       <c r="H1904" t="inlineStr">
         <is>
           <t>भाग्यवान चौहान की राय Jubilant Ingrevia खरीदें STOP LOSS 620 TARGET 775/800 DURATION 4-8 महीने Jubilant Ingrevia 646.05 1.68%</t>
@@ -80088,11 +80081,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1905" t="inlineStr"/>
       <c r="E1905" t="n">
         <v>555</v>
       </c>
-      <c r="G1905" t="inlineStr"/>
       <c r="H1905" t="inlineStr">
         <is>
           <t>Ajax Engineering 613.65 6.68% BUY TARGET HIT 555</t>
@@ -80131,7 +80122,6 @@
       <c r="E1906" t="n">
         <v>835</v>
       </c>
-      <c r="G1906" t="inlineStr"/>
       <c r="H1906" t="inlineStr">
         <is>
           <t>HBL ENGINEERING 796.90 21.60 BUY TGT 835</t>
@@ -80170,7 +80160,6 @@
       <c r="E1907" t="n">
         <v>1530</v>
       </c>
-      <c r="G1907" t="inlineStr"/>
       <c r="H1907" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -80217,7 +80206,6 @@
       <c r="F1908" t="n">
         <v>1098</v>
       </c>
-      <c r="G1908" t="inlineStr"/>
       <c r="H1908" t="inlineStr">
         <is>
           <t>Voltas Fut खरीदें PRICE 1118.60 TARGET 1165/1185 STOP LOSS 1098</t>
@@ -80259,7 +80247,6 @@
       <c r="F1909" t="n">
         <v>1098</v>
       </c>
-      <c r="G1909" t="inlineStr"/>
       <c r="H1909" t="inlineStr">
         <is>
           <t>Voltas Fut खरीदें PRICE 1118.60 TARGET 1165/1185 STOP LOSS 1098</t>
@@ -80298,7 +80285,6 @@
       <c r="E1910" t="n">
         <v>400</v>
       </c>
-      <c r="G1910" t="inlineStr"/>
       <c r="H1910" t="inlineStr">
         <is>
           <t>अंबरीश बलिगा की राय
@@ -80337,11 +80323,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1911" t="inlineStr"/>
       <c r="E1911" t="n">
         <v>355</v>
       </c>
-      <c r="G1911" t="inlineStr"/>
       <c r="H1911" t="inlineStr">
         <is>
           <t>Ajax Engineering 605.90 5.34% BUY TARGET HIT 355</t>
@@ -80374,11 +80358,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1912" t="inlineStr"/>
       <c r="E1912" t="n">
         <v>610</v>
       </c>
-      <c r="G1912" t="inlineStr"/>
       <c r="H1912" t="inlineStr">
         <is>
           <t>Ajax Engineering 605.00 5.18% BUY TGT 610</t>
@@ -80420,7 +80402,6 @@
       <c r="F1913" t="n">
         <v>780</v>
       </c>
-      <c r="G1913" t="inlineStr"/>
       <c r="H1913" t="inlineStr">
         <is>
           <t>फुल्ल के कोहिनूर
@@ -80464,7 +80445,6 @@
       <c r="E1914" t="n">
         <v>775</v>
       </c>
-      <c r="G1914" t="inlineStr"/>
       <c r="H1914" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -80512,7 +80492,6 @@
       <c r="F1915" t="n">
         <v>810</v>
       </c>
-      <c r="G1915" t="inlineStr"/>
       <c r="H1915" t="inlineStr">
         <is>
           <t>Graphite India 826.65 11.95 BUY TGT 875 SL 810</t>
@@ -80554,7 +80533,6 @@
       <c r="F1916" t="n">
         <v>1360</v>
       </c>
-      <c r="G1916" t="inlineStr"/>
       <c r="H1916" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट Chennai Petro 1398.50 1.88% BUY TGT 1450 SL 1360</t>
@@ -80593,7 +80571,6 @@
       <c r="E1917" t="n">
         <v>49000</v>
       </c>
-      <c r="G1917" t="inlineStr"/>
       <c r="H1917" t="inlineStr">
         <is>
           <t>Welspun Corp को एक और ऑर्डर
@@ -80638,7 +80615,6 @@
       <c r="F1918" t="n">
         <v>620</v>
       </c>
-      <c r="G1918" t="inlineStr"/>
       <c r="H1918" t="inlineStr">
         <is>
           <t>खरीदें STOP LOSS 620 TARGET 775/800 DURATION 4-8 महीने Jubilant Ingrevia 650.70 2.42%</t>
@@ -80723,7 +80699,6 @@
       <c r="E1920" t="n">
         <v>5800</v>
       </c>
-      <c r="G1920" t="inlineStr"/>
       <c r="H1920" t="inlineStr">
         <is>
           <t>श्रीकांत चौहान की राय HAL खरीदें STOP LOSS -- TARGET 5300/5800 DURATION 9-12 महीने HAL 4791.00 ▲ 0.35%</t>
@@ -80762,7 +80737,6 @@
       <c r="E1921" t="n">
         <v>700</v>
       </c>
-      <c r="G1921" t="inlineStr"/>
       <c r="H1921" t="inlineStr">
         <is>
           <t>अंबरीश बलिगा की राय
@@ -80807,7 +80781,6 @@
       <c r="E1922" t="n">
         <v>610</v>
       </c>
-      <c r="G1922" t="inlineStr"/>
       <c r="H1922" t="inlineStr">
         <is>
           <t>Ajax Engineering 602.80 4.80% BUY TGT 610</t>
@@ -80849,7 +80822,6 @@
       <c r="F1923" t="n">
         <v>780</v>
       </c>
-      <c r="G1923" t="inlineStr"/>
       <c r="H1923" t="inlineStr">
         <is>
           <t>कुल्लू के कोहिनूर
@@ -80893,7 +80865,6 @@
       <c r="E1924" t="n">
         <v>775</v>
       </c>
-      <c r="G1924" t="inlineStr"/>
       <c r="H1924" t="inlineStr">
         <is>
           <t>SUPER SID
@@ -80937,7 +80908,6 @@
       <c r="E1925" t="n">
         <v>1530</v>
       </c>
-      <c r="G1925" t="inlineStr"/>
       <c r="H1925" t="inlineStr">
         <is>
           <t>SUPER SID Ather Energy 1495.40 3.60 BUY TGT 1530 SL --</t>
@@ -80976,7 +80946,6 @@
       <c r="E1926" t="n">
         <v>620</v>
       </c>
-      <c r="G1926" t="inlineStr"/>
       <c r="H1926" t="inlineStr">
         <is>
           <t>सिद्धार्थ सेढानी की राय Usha Martin खरीदें PRICE 521.15 TARGET 620 DURATION 6-12 महीने</t>
@@ -81009,14 +80978,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1927" t="inlineStr"/>
       <c r="E1927" t="n">
         <v>5800</v>
       </c>
       <c r="F1927" t="n">
         <v>5300</v>
       </c>
-      <c r="G1927" t="inlineStr"/>
       <c r="H1927" t="inlineStr">
         <is>
           <t>श्रीकांत चौहान की राय HAL खरीदें STOP LOSS 5300/TARGET 5800 DURAT 9-12 HAL 4785.60</t>
@@ -81055,7 +81022,6 @@
       <c r="E1928" t="n">
         <v>5300</v>
       </c>
-      <c r="G1928" t="inlineStr"/>
       <c r="H1928" t="inlineStr">
         <is>
           <t>श्रीकांत चौहान की राय HAL खरीदें STOP LOSS -- TARGET 5300/5800 DURATION 9-12 महीने HAL 4785.60 ▲ 0.24%</t>
@@ -81094,7 +81060,6 @@
       <c r="E1929" t="n">
         <v>5800</v>
       </c>
-      <c r="G1929" t="inlineStr"/>
       <c r="H1929" t="inlineStr">
         <is>
           <t>HAL खरीदें STOP LOSS -- TARGET 5300/5800 DURATION 9-12 महीने HAL 4785.60</t>
@@ -81133,7 +81098,6 @@
       <c r="E1930" t="n">
         <v>650</v>
       </c>
-      <c r="G1930" t="inlineStr"/>
       <c r="H1930" t="inlineStr">
         <is>
           <t>Aarti Ind खरीदें STOP LOSS -- TARGET 650 DURATION 9-12 महीने Aarti Ind 488.00 0.30%</t>
@@ -81175,7 +81139,6 @@
       <c r="F1931" t="n">
         <v>75</v>
       </c>
-      <c r="G1931" t="inlineStr"/>
       <c r="H1931" t="inlineStr">
         <is>
           <t>Lloyds Engineering Works Ltd खरीदें PRICE 92.37 TARGET 120/135 STOP LOSS 75</t>
@@ -81217,7 +81180,6 @@
       <c r="F1932" t="n">
         <v>75</v>
       </c>
-      <c r="G1932" t="inlineStr"/>
       <c r="H1932" t="inlineStr">
         <is>
           <t>Lloyds Engineering Works Ltd खरीदें PRICE 92.37 TARGET 120/135 STOP LOSS 75</t>
@@ -81250,11 +81212,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1933" t="inlineStr"/>
       <c r="E1933" t="n">
         <v>555</v>
       </c>
-      <c r="G1933" t="inlineStr"/>
       <c r="H1933" t="inlineStr">
         <is>
           <t>Ajax Engineering 605.20 5.22% BUY TARGET HIT 555</t>
@@ -81296,7 +81256,6 @@
       <c r="F1934" t="n">
         <v>555</v>
       </c>
-      <c r="G1934" t="inlineStr"/>
       <c r="H1934" t="inlineStr">
         <is>
           <t>सदाबहार सेबी साब Ajax Engineering 605.20 5.22% BUY TGT 610 SL 555</t>
@@ -81338,7 +81297,6 @@
       <c r="F1935" t="n">
         <v>780</v>
       </c>
-      <c r="G1935" t="inlineStr"/>
       <c r="H1935" t="inlineStr">
         <is>
           <t>HBL ENGINEERING 794.50 19.20 BUY TGT 825 SL 780</t>
@@ -81377,7 +81335,6 @@
       <c r="E1936" t="n">
         <v>775</v>
       </c>
-      <c r="G1936" t="inlineStr"/>
       <c r="H1936" t="inlineStr">
         <is>
           <t>SUPER SID TD Power 751.70 9.70 BUY TGT 775 SL --</t>
@@ -81557,7 +81514,6 @@
       <c r="F1940" t="n">
         <v>850</v>
       </c>
-      <c r="G1940" t="inlineStr"/>
       <c r="H1940" t="inlineStr">
         <is>
           <t>Whirlpool खरीदें PRICE 903.80 TARGET 960/970 STOP LOSS 850</t>
@@ -81599,7 +81555,6 @@
       <c r="F1941" t="n">
         <v>810</v>
       </c>
-      <c r="G1941" t="inlineStr"/>
       <c r="H1941" t="inlineStr">
         <is>
           <t>Graphite India 823.65 8.95 BUY TGT 875 SL 810</t>
@@ -81641,7 +81596,6 @@
       <c r="F1942" t="n">
         <v>850</v>
       </c>
-      <c r="G1942" t="inlineStr"/>
       <c r="H1942" t="inlineStr">
         <is>
           <t>Whirlpool खरीदें PRICE 902.00 TARGET 960/970 STOP LOSS 850</t>
@@ -81683,7 +81637,6 @@
       <c r="F1943" t="n">
         <v>810</v>
       </c>
-      <c r="G1943" t="inlineStr"/>
       <c r="H1943" t="inlineStr">
         <is>
           <t>Graphite India 824.00 9.30 BUY TGT 875 SL 810</t>
@@ -81725,7 +81678,6 @@
       <c r="F1944" t="n">
         <v>1360</v>
       </c>
-      <c r="G1944" t="inlineStr"/>
       <c r="H1944" t="inlineStr">
         <is>
           <t>Chennai Petro 1381.30 8.60 BUY TGT 1450 SL 1360</t>
@@ -81764,7 +81716,6 @@
       <c r="E1945" t="n">
         <v>1530</v>
       </c>
-      <c r="G1945" t="inlineStr"/>
       <c r="H1945" t="inlineStr">
         <is>
           <t>SUPER SID Ather Energy 1491.00 BUY TGT 1530 SL -- Fri 25 Sep'26</t>
@@ -81797,14 +81748,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1946" t="inlineStr"/>
       <c r="E1946" t="n">
         <v>34.2</v>
       </c>
       <c r="F1946" t="n">
         <v>31.5</v>
       </c>
-      <c r="G1946" t="inlineStr"/>
       <c r="H1946" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Vascon Eng 35.25 1.96 BUY TGT 34.2 SL 31.5</t>
@@ -81843,7 +81792,6 @@
       <c r="E1947" t="n">
         <v>270</v>
       </c>
-      <c r="G1947" t="inlineStr"/>
       <c r="H1947" t="inlineStr">
         <is>
           <t>Castrol India खरीदें PRICE 196.79 TARGET 270 DURATION 4-6 महीने</t>
@@ -81885,7 +81833,6 @@
       <c r="F1948" t="n">
         <v>152</v>
       </c>
-      <c r="G1948" t="inlineStr"/>
       <c r="H1948" t="inlineStr">
         <is>
           <t>10 की कमाई
@@ -81932,7 +81879,6 @@
       <c r="F1949" t="n">
         <v>152</v>
       </c>
-      <c r="G1949" t="inlineStr"/>
       <c r="H1949" t="inlineStr">
         <is>
           <t>10 की कमाई Paradeep Phosphates खरीदें PRICE 155.81 TARGET 160/162 STOP LOSS 152</t>
@@ -81965,11 +81911,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1950" t="inlineStr"/>
       <c r="E1950" t="n">
         <v>555</v>
       </c>
-      <c r="G1950" t="inlineStr"/>
       <c r="H1950" t="inlineStr">
         <is>
           <t>Ajax Engineering 608.00 5.70% BUY TARGET HIT 555</t>
@@ -82011,7 +81955,6 @@
       <c r="F1951" t="n">
         <v>555</v>
       </c>
-      <c r="G1951" t="inlineStr"/>
       <c r="H1951" t="inlineStr">
         <is>
           <t>सदाबहार सेठी साब
@@ -82058,7 +82001,6 @@
       <c r="F1952" t="n">
         <v>780</v>
       </c>
-      <c r="G1952" t="inlineStr"/>
       <c r="H1952" t="inlineStr">
         <is>
           <t>HBL ENGINEERING 793.50 18.20 BUY TGT 825 SL 780</t>
@@ -82097,7 +82039,6 @@
       <c r="E1953" t="n">
         <v>775</v>
       </c>
-      <c r="G1953" t="inlineStr"/>
       <c r="H1953" t="inlineStr">
         <is>
           <t>SUPER SID TD Power 753.50 11.50 BUY TGT 775 SL --</t>
@@ -82130,11 +82071,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1954" t="inlineStr"/>
       <c r="E1954" t="n">
         <v>585.35</v>
       </c>
-      <c r="G1954" t="inlineStr"/>
       <c r="H1954" t="inlineStr">
         <is>
           <t>Tilaknagar Ind 585.35 DIWALI PICK 222.50 03/11/2023 RECO PRICE RETURN TILL NOW 362.85 163.08%</t>
@@ -82167,11 +82106,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1955" t="inlineStr"/>
       <c r="E1955" t="n">
         <v>585.3</v>
       </c>
-      <c r="G1955" t="inlineStr"/>
       <c r="H1955" t="inlineStr">
         <is>
           <t>Tilaknagar Ind 585.30 DIWALI PICK 222.50 03/11/2023 RECO PRICE RETURN TILL NOW 362.80 163.06%</t>
@@ -82204,11 +82141,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1956" t="inlineStr"/>
       <c r="E1956" t="n">
         <v>585.5</v>
       </c>
-      <c r="G1956" t="inlineStr"/>
       <c r="H1956" t="inlineStr">
         <is>
           <t>Tilaknagar Ind 585.50 DIWALI PICK 222.50 03/11/2023 RECO PRICE RETURN TILL NOW 363.00 163.15%</t>
@@ -82241,11 +82176,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1957" t="inlineStr"/>
       <c r="E1957" t="n">
         <v>584.85</v>
       </c>
-      <c r="G1957" t="inlineStr"/>
       <c r="H1957" t="inlineStr">
         <is>
           <t>Tilaknagar Ind 584.85 PICK OF THE YEAR 292.00 05/11/2024 RECO PRICE RETURN TILL NOW 292.85 100.29%</t>
@@ -82278,11 +82211,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1958" t="inlineStr"/>
       <c r="E1958" t="n">
         <v>584.95</v>
       </c>
-      <c r="G1958" t="inlineStr"/>
       <c r="H1958" t="inlineStr">
         <is>
           <t>Tilaknagar Ind 584.95 PICK OF THE YEAR 292.00 05/11/2024 RECO PRICE RETURN TILL NOW 292.95 100.33%</t>
@@ -82324,7 +82255,6 @@
       <c r="F1959" t="n">
         <v>780</v>
       </c>
-      <c r="G1959" t="inlineStr"/>
       <c r="H1959" t="inlineStr">
         <is>
           <t>फुल्ल के कोहिनूर
@@ -82368,7 +82298,6 @@
       <c r="E1960" t="n">
         <v>825</v>
       </c>
-      <c r="G1960" t="inlineStr"/>
       <c r="H1960" t="inlineStr">
         <is>
           <t>HBL ENGINEERING 790.10 1.91% BUY TGT 825</t>
@@ -82410,7 +82339,6 @@
       <c r="F1961" t="n">
         <v>810</v>
       </c>
-      <c r="G1961" t="inlineStr"/>
       <c r="H1961" t="inlineStr">
         <is>
           <t>Graphite India 835.00 20.30 BUY TGT 875 SL 810</t>
@@ -82452,7 +82380,6 @@
       <c r="F1962" t="n">
         <v>1360</v>
       </c>
-      <c r="G1962" t="inlineStr"/>
       <c r="H1962" t="inlineStr">
         <is>
           <t>Chennai Petro 1387.70 1.09% BUY TGT 1450 SL 1360</t>
@@ -82491,7 +82418,6 @@
       <c r="E1963" t="n">
         <v>1530</v>
       </c>
-      <c r="G1963" t="inlineStr"/>
       <c r="H1963" t="inlineStr">
         <is>
           <t>Ather Energy 1490.50 8.50 BUY TGT 1530 09:41 AM</t>
@@ -82524,7 +82450,6 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1964" t="inlineStr"/>
       <c r="E1964" t="n">
         <v>31.5</v>
       </c>
@@ -82565,14 +82490,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1965" t="inlineStr"/>
       <c r="E1965" t="n">
         <v>34.2</v>
       </c>
       <c r="F1965" t="n">
         <v>31.5</v>
       </c>
-      <c r="G1965" t="inlineStr"/>
       <c r="H1965" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Vascon Eng 35.67 2.38 BUY TGT 34.2 SL 31.5</t>
@@ -82605,11 +82528,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D1966" t="inlineStr"/>
       <c r="E1966" t="n">
         <v>34.2</v>
       </c>
-      <c r="G1966" t="inlineStr"/>
       <c r="H1966" t="inlineStr">
         <is>
           <t>Vascon Eng 35.67 2.38 BUY TGT 34.2</t>
@@ -82642,7 +82563,6 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D1967" t="inlineStr"/>
       <c r="E1967" t="n">
         <v>8550</v>
       </c>
@@ -82688,11 +82608,9 @@
           <t>SELL</t>
         </is>
       </c>
-      <c r="D1968" t="inlineStr"/>
       <c r="E1968" t="n">
         <v>8550</v>
       </c>
-      <c r="G1968" t="inlineStr"/>
       <c r="H1968" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Polycab India 8425.00 58.50 SELL TGT 8550 SL --</t>
@@ -82872,7 +82790,6 @@
       <c r="F1972" t="n">
         <v>780</v>
       </c>
-      <c r="G1972" t="inlineStr"/>
       <c r="H1972" t="inlineStr">
         <is>
           <t>कुणाल के कोहिनूर HBL ENGINEERING खरीदें PRICE 798.70 TARGET 825/850 STOP LOSS 780</t>
@@ -82954,7 +82871,6 @@
       <c r="E1974" t="n">
         <v>875</v>
       </c>
-      <c r="G1974" t="inlineStr"/>
       <c r="H1974" t="inlineStr">
         <is>
           <t>TD Power खरीदें PRICE 760.45 TARGET 775/875 STOP LOSS --</t>
@@ -82993,7 +82909,6 @@
       <c r="E1975" t="n">
         <v>775</v>
       </c>
-      <c r="G1975" t="inlineStr"/>
       <c r="H1975" t="inlineStr">
         <is>
           <t>TD Power खरीदें PRICE 760.45 TARGET 775/875 STOP LOSS --</t>
@@ -83035,7 +82950,6 @@
       <c r="F1976" t="n">
         <v>810</v>
       </c>
-      <c r="G1976" t="inlineStr"/>
       <c r="H1976" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Graphite India खरीदें PRICE 834.45 TARGET 875/890 STOP LOSS 810</t>
@@ -83077,7 +82991,6 @@
       <c r="F1977" t="n">
         <v>810</v>
       </c>
-      <c r="G1977" t="inlineStr"/>
       <c r="H1977" t="inlineStr">
         <is>
           <t>शुभ 'मंगला' शेयर Graphite India खरीदें PRICE 834.45 TARGET 875/890 STOP LOSS 810</t>
@@ -83119,7 +83032,6 @@
       <c r="F1978" t="n">
         <v>1360</v>
       </c>
-      <c r="G1978" t="inlineStr"/>
       <c r="H1978" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट Chennai Petro खरीदें PRICE 1407.00 TARGET 1450/1480 STOP LOSS 1360</t>
@@ -83161,7 +83073,6 @@
       <c r="F1979" t="n">
         <v>1360</v>
       </c>
-      <c r="G1979" t="inlineStr"/>
       <c r="H1979" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट Chennai Petro खरीदें PRICE 1407.00 TARGET 1450/1480 STOP LOSS 1360</t>
@@ -83203,7 +83114,6 @@
       <c r="F1980" t="n">
         <v>555</v>
       </c>
-      <c r="G1980" t="inlineStr"/>
       <c r="H1980" t="inlineStr">
         <is>
           <t>SUPER SID Ather Energy खरीदें PRICE 1495.00 TARGET 1530/2200 STOP LOSS 555</t>
@@ -83245,7 +83155,6 @@
       <c r="F1981" t="n">
         <v>555</v>
       </c>
-      <c r="G1981" t="inlineStr"/>
       <c r="H1981" t="inlineStr">
         <is>
           <t>SUPER SID Ather Energy खरीदें PRICE 1495.00 TARGET 1530/2200 STOP LOSS 555</t>
@@ -83284,7 +83193,6 @@
       <c r="E1982" t="n">
         <v>1530</v>
       </c>
-      <c r="G1982" t="inlineStr"/>
       <c r="H1982" t="inlineStr">
         <is>
           <t>Ather Energy खरीदें PRICE 1493.30 TARGET 1530/2200 STOP LOSS --</t>
@@ -83323,7 +83231,6 @@
       <c r="E1983" t="n">
         <v>2200</v>
       </c>
-      <c r="G1983" t="inlineStr"/>
       <c r="H1983" t="inlineStr">
         <is>
           <t>Ather Energy खरीदें PRICE 1493.30 TARGET 1530/2200 STOP LOSS --</t>
@@ -83451,7 +83358,6 @@
       <c r="F1986" t="n">
         <v>1950</v>
       </c>
-      <c r="G1986" t="inlineStr"/>
       <c r="H1986" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह IPCA Labs (Cash) BUY PRICE 1997 TARGET 2020, 2035, 2050 STOP LOSS 1950</t>
@@ -83493,7 +83399,6 @@
       <c r="F1987" t="n">
         <v>1950</v>
       </c>
-      <c r="G1987" t="inlineStr"/>
       <c r="H1987" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह IPCA Labs (Cash) BUY PRICE 1997 TARGET 2020, 2035, 2050 STOP LOSS 1950</t>
@@ -83535,7 +83440,6 @@
       <c r="F1988" t="n">
         <v>1950</v>
       </c>
-      <c r="G1988" t="inlineStr"/>
       <c r="H1988" t="inlineStr">
         <is>
           <t>अनिल सिंघवी की सलाह IPCA Labs (Cash) BUY PRICE 1997 TARGET 2020, 2035, 2050 STOP LOSS 1950</t>
@@ -83577,7 +83481,6 @@
       <c r="F1989" t="n">
         <v>624</v>
       </c>
-      <c r="G1989" t="inlineStr"/>
       <c r="H1989" t="inlineStr">
         <is>
           <t>MY CHOICE SBI CARD FUT S 603 624</t>
@@ -83619,7 +83522,6 @@
       <c r="F1990" t="n">
         <v>1767</v>
       </c>
-      <c r="G1990" t="inlineStr"/>
       <c r="H1990" t="inlineStr">
         <is>
           <t>MY CHOICE ADANI PORTS B 1820 1767</t>
@@ -83658,7 +83560,6 @@
       <c r="E1991" t="n">
         <v>603</v>
       </c>
-      <c r="G1991" t="inlineStr"/>
       <c r="H1991" t="inlineStr">
         <is>
           <t>MY CHOICE SBI CARD FUT S 603</t>
@@ -83700,7 +83601,6 @@
       <c r="F1992" t="n">
         <v>176</v>
       </c>
-      <c r="G1992" t="inlineStr"/>
       <c r="H1992" t="inlineStr">
         <is>
           <t>MY CHOICE ADANI PORTS B 1820 176</t>
@@ -83742,7 +83642,6 @@
       <c r="F1993" t="n">
         <v>1941</v>
       </c>
-      <c r="G1993" t="inlineStr"/>
       <c r="H1993" t="inlineStr">
         <is>
           <t>CASH DR LAL PATHLABS B 2000 1941</t>
@@ -83784,7 +83683,6 @@
       <c r="F1994" t="n">
         <v>169</v>
       </c>
-      <c r="G1994" t="inlineStr"/>
       <c r="H1994" t="inlineStr">
         <is>
           <t>TECHNO WIPRO FUT S 157 169</t>
@@ -83826,7 +83724,6 @@
       <c r="F1995" t="n">
         <v>1818</v>
       </c>
-      <c r="G1995" t="inlineStr"/>
       <c r="H1995" t="inlineStr">
         <is>
           <t>FUTURE OBEROI REALTY FUT B 1895 1818</t>
@@ -83868,7 +83765,6 @@
       <c r="F1996" t="n">
         <v>1065</v>
       </c>
-      <c r="G1996" t="inlineStr"/>
       <c r="H1996" t="inlineStr">
         <is>
           <t>NEWS IMPACT 360 ONE WAM B 1110 1065</t>
@@ -83910,7 +83806,6 @@
       <c r="F1997" t="n">
         <v>330</v>
       </c>
-      <c r="G1997" t="inlineStr"/>
       <c r="H1997" t="inlineStr">
         <is>
           <t>MY CHOICE NYKAA B 343 330</t>
@@ -83952,7 +83847,6 @@
       <c r="F1998" t="n">
         <v>1675</v>
       </c>
-      <c r="G1998" t="inlineStr"/>
       <c r="H1998" t="inlineStr">
         <is>
           <t>MY CHOICE NUVAMA WEALTH B 1730 1675</t>
@@ -83991,7 +83885,6 @@
       <c r="E1999" t="n">
         <v>1110</v>
       </c>
-      <c r="G1999" t="inlineStr"/>
       <c r="H1999" t="inlineStr">
         <is>
           <t>NEWS IMPACT 360 ONE WAM B 1110 10</t>
@@ -84033,7 +83926,6 @@
       <c r="F2000" t="n">
         <v>490</v>
       </c>
-      <c r="G2000" t="inlineStr"/>
       <c r="H2000" t="inlineStr">
         <is>
           <t>FUNDA HIND COPPER B 505 490</t>
@@ -84115,7 +84007,6 @@
       <c r="E2002" t="n">
         <v>245</v>
       </c>
-      <c r="G2002" t="inlineStr"/>
       <c r="H2002" t="inlineStr">
         <is>
           <t>PICK OF THE DAY ONGC 239.00 2.10 BUY TGT 245</t>
@@ -84154,7 +84045,6 @@
       <c r="E2003" t="n">
         <v>1200</v>
       </c>
-      <c r="G2003" t="inlineStr"/>
       <c r="H2003" t="inlineStr">
         <is>
           <t>Shriram Finance 990.00 TARGET ₹1200</t>
@@ -84196,7 +84086,6 @@
       <c r="F2004" t="n">
         <v>2200</v>
       </c>
-      <c r="G2004" t="inlineStr"/>
       <c r="H2004" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -84243,7 +84132,6 @@
       <c r="F2005" t="n">
         <v>234</v>
       </c>
-      <c r="G2005" t="inlineStr"/>
       <c r="H2005" t="inlineStr">
         <is>
           <t>PICK OF THE DAY ONGC BUY PRICE 239.0 TARGET 245/2 STOP LOSS 234</t>
@@ -84285,7 +84173,6 @@
       <c r="F2006" t="n">
         <v>234</v>
       </c>
-      <c r="G2006" t="inlineStr"/>
       <c r="H2006" t="inlineStr">
         <is>
           <t>सुमित बगडिया की राय ONGC BUY PRICE 239.00 TARGET 245/250 STOP LOSS 234</t>
@@ -84327,7 +84214,6 @@
       <c r="F2007" t="n">
         <v>234</v>
       </c>
-      <c r="G2007" t="inlineStr"/>
       <c r="H2007" t="inlineStr">
         <is>
           <t>PICK OF THE DAY ONGC BU PRICE 239.00 TARGET 245/250 STOP LOSS 234</t>
@@ -84369,7 +84255,6 @@
       <c r="F2008" t="n">
         <v>3300</v>
       </c>
-      <c r="G2008" t="inlineStr"/>
       <c r="H2008" t="inlineStr">
         <is>
           <t>PICK OF THE DAY MCX 3427.70 53.70 BUY TGT 3570 SL 3300</t>
@@ -84408,7 +84293,6 @@
       <c r="E2009" t="n">
         <v>2590</v>
       </c>
-      <c r="G2009" t="inlineStr"/>
       <c r="H2009" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -84451,7 +84335,6 @@
       <c r="E2010" t="n">
         <v>8550</v>
       </c>
-      <c r="G2010" t="inlineStr"/>
       <c r="H2010" t="inlineStr">
         <is>
           <t>सिद्धार्थ सेहगल की राय
@@ -84495,7 +84378,6 @@
       <c r="E2011" t="n">
         <v>10600</v>
       </c>
-      <c r="G2011" t="inlineStr"/>
       <c r="H2011" t="inlineStr">
         <is>
           <t>सिद्धार्थ सेहगल की राय
@@ -84542,7 +84424,6 @@
       <c r="F2012" t="n">
         <v>3000</v>
       </c>
-      <c r="G2012" t="inlineStr"/>
       <c r="H2012" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Adani Ent Oct Fut SELL PRICE 2920.20 TARGET 2850/2800 STOP LOSS 3000</t>
@@ -84584,7 +84465,6 @@
       <c r="F2013" t="n">
         <v>3000</v>
       </c>
-      <c r="G2013" t="inlineStr"/>
       <c r="H2013" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Adani Ent Oct Fut SELL PRICE 2920.20 TARGET 2850/2800 STOP LOSS 3000</t>
@@ -84672,7 +84552,6 @@
       <c r="F2015" t="n">
         <v>1660</v>
       </c>
-      <c r="G2015" t="inlineStr"/>
       <c r="H2015" t="inlineStr">
         <is>
           <t>PICK OF THE DAY LG Electronics BUY PRICE 1697.70 TARGET 1740/1760 STOP LOSS 1660</t>
@@ -84714,7 +84593,6 @@
       <c r="F2016" t="n">
         <v>2200</v>
       </c>
-      <c r="G2016" t="inlineStr"/>
       <c r="H2016" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Galaxy Surfactants BUY PRICE 2246.60 TARGET 2320/2375 STOP LOSS 2200</t>
@@ -84756,7 +84634,6 @@
       <c r="F2017" t="n">
         <v>2200</v>
       </c>
-      <c r="G2017" t="inlineStr"/>
       <c r="H2017" t="inlineStr">
         <is>
           <t>PICK OF THE DAY Galaxy Surfactants BUY PRICE 2246.60 TARGET 2320/2375 STOP LOSS 2200</t>
@@ -84890,7 +84767,6 @@
       <c r="F2020" t="n">
         <v>2495</v>
       </c>
-      <c r="G2020" t="inlineStr"/>
       <c r="H2020" t="inlineStr">
         <is>
           <t>PICK OF THE DAY
@@ -84937,7 +84813,6 @@
       <c r="F2021" t="n">
         <v>2495</v>
       </c>
-      <c r="G2021" t="inlineStr"/>
       <c r="H2021" t="inlineStr">
         <is>
           <t>PICK OF THE DAY R R Kabel BUY PRICE 2529.80 TARGET 2590/2620 STOP LOSS 2495</t>
@@ -84976,7 +84851,6 @@
       <c r="E2022" t="n">
         <v>85</v>
       </c>
-      <c r="G2022" t="inlineStr"/>
       <c r="H2022" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -85022,7 +84896,6 @@
       <c r="F2023" t="n">
         <v>990</v>
       </c>
-      <c r="G2023" t="inlineStr"/>
       <c r="H2023" t="inlineStr">
         <is>
           <t>Godrej Ind खरीदें PRICE 1099.00 TARGET 1400 STOP LOSS 990</t>
@@ -85061,7 +84934,6 @@
       <c r="E2024" t="n">
         <v>1400</v>
       </c>
-      <c r="G2024" t="inlineStr"/>
       <c r="H2024" t="inlineStr">
         <is>
           <t>INVESTMENT GODREJ INDUSTRIES B 1400 12 MONTH</t>
@@ -85103,7 +84975,6 @@
       <c r="F2025" t="n">
         <v>2450</v>
       </c>
-      <c r="G2025" t="inlineStr"/>
       <c r="H2025" t="inlineStr">
         <is>
           <t>MY CHOICE WAAREE ENERGIES B 2530 2450</t>
@@ -85145,7 +85016,6 @@
       <c r="F2026" t="n">
         <v>7</v>
       </c>
-      <c r="G2026" t="inlineStr"/>
       <c r="H2026" t="inlineStr">
         <is>
           <t>OPTION BAJAJ FINANCE 980 CE@14 CALL B TGT 30 SL/DUR 7</t>
@@ -85187,7 +85057,6 @@
       <c r="F2027" t="n">
         <v>550</v>
       </c>
-      <c r="G2027" t="inlineStr"/>
       <c r="H2027" t="inlineStr">
         <is>
           <t>CASH NAVA CALL B TGT 575 SL/DUR 550</t>
@@ -85229,7 +85098,6 @@
       <c r="F2028" t="n">
         <v>624</v>
       </c>
-      <c r="G2028" t="inlineStr"/>
       <c r="H2028" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -85276,7 +85144,6 @@
       <c r="F2029" t="n">
         <v>1767</v>
       </c>
-      <c r="G2029" t="inlineStr"/>
       <c r="H2029" t="inlineStr">
         <is>
           <t>पूजा के शेयर Adani Ports खरीदें PRICE 1785.30 TARGET 1820 STOP LOSS 1767</t>
@@ -85318,7 +85185,6 @@
       <c r="F2030" t="n">
         <v>1356</v>
       </c>
-      <c r="G2030" t="inlineStr"/>
       <c r="H2030" t="inlineStr">
         <is>
           <t>MY CHOICE Cochin Shipyard खरीदें PRICE 1370.00 TARGET 1400 STOP LOSS 1356</t>
@@ -85357,7 +85223,6 @@
       <c r="E2031" t="n">
         <v>1400</v>
       </c>
-      <c r="G2031" t="inlineStr"/>
       <c r="H2031" t="inlineStr">
         <is>
           <t>MY CHOICE Cochin Shipyard PRICE 1370.00 TARGET 1400</t>
@@ -85399,7 +85264,6 @@
       <c r="F2032" t="n">
         <v>1675</v>
       </c>
-      <c r="G2032" t="inlineStr"/>
       <c r="H2032" t="inlineStr">
         <is>
           <t>MY CHOICE Nuvama Wealth खरीदें PRICE 1695.40 TARGET 1730 STOP LOSS 1675</t>
@@ -85438,7 +85302,6 @@
       <c r="E2033" t="n">
         <v>1730</v>
       </c>
-      <c r="G2033" t="inlineStr"/>
       <c r="H2033" t="inlineStr">
         <is>
           <t>MY CHOICE
@@ -85483,7 +85346,6 @@
       <c r="F2034" t="n">
         <v>330</v>
       </c>
-      <c r="G2034" t="inlineStr"/>
       <c r="H2034" t="inlineStr">
         <is>
           <t>MY CHOICE Nykaa खरीदें PRICE 335.30 TARGET 343 STOP LOSS 330</t>
@@ -85525,7 +85387,6 @@
       <c r="F2035" t="n">
         <v>2450</v>
       </c>
-      <c r="G2035" t="inlineStr"/>
       <c r="H2035" t="inlineStr">
         <is>
           <t>MY CHOICE Waaree Energies खरीदें PRICE 2482.00 TARGET 2530 STOP LOSS 2450</t>
@@ -85564,7 +85425,6 @@
       <c r="E2036" t="n">
         <v>2530</v>
       </c>
-      <c r="G2036" t="inlineStr"/>
       <c r="H2036" t="inlineStr">
         <is>
           <t>MY CHOICE Waaree Energies PRICE 2482.00 TARGET 2530</t>
@@ -85606,7 +85466,6 @@
       <c r="F2037" t="n">
         <v>814</v>
       </c>
-      <c r="G2037" t="inlineStr"/>
       <c r="H2037" t="inlineStr">
         <is>
           <t>पूजा के शेयर Sterlite Tech खरीदें PRICE 823.75 TARGET 870 STOP LOSS 814</t>
@@ -85645,7 +85504,6 @@
       <c r="E2038" t="n">
         <v>870</v>
       </c>
-      <c r="G2038" t="inlineStr"/>
       <c r="H2038" t="inlineStr">
         <is>
           <t>खबर के दम पर Sterlite Tech PRICE 823.75 TARGET 870</t>
@@ -85687,7 +85545,6 @@
       <c r="F2039" t="n">
         <v>1065</v>
       </c>
-      <c r="G2039" t="inlineStr"/>
       <c r="H2039" t="inlineStr">
         <is>
           <t>खबर के दम पर
@@ -85731,7 +85588,6 @@
       <c r="E2040" t="n">
         <v>1400</v>
       </c>
-      <c r="G2040" t="inlineStr"/>
       <c r="H2040" t="inlineStr">
         <is>
           <t>इन्वेस्टमेंट PICK Godrej Ind खरीदें PRICE 1099.00 TARGET 1400 DURATION 990</t>
@@ -85773,7 +85629,6 @@
       <c r="F2041" t="n">
         <v>490</v>
       </c>
-      <c r="G2041" t="inlineStr"/>
       <c r="H2041" t="inlineStr">
         <is>
           <t>Funda Pick Hind Copper खरीदें PRICE 495.70 TARGET 505 STOP LOSS 490</t>
@@ -85812,7 +85667,6 @@
       <c r="E2042" t="n">
         <v>85</v>
       </c>
-      <c r="G2042" t="inlineStr"/>
       <c r="H2042" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS SELL लक्ष्य ₹85</t>
@@ -85901,7 +85755,6 @@
       <c r="F2044" t="n">
         <v>3401</v>
       </c>
-      <c r="G2044" t="inlineStr"/>
       <c r="H2044" t="inlineStr">
         <is>
           <t>आज का FUTURE
@@ -85948,7 +85801,6 @@
       <c r="F2045" t="n">
         <v>1818</v>
       </c>
-      <c r="G2045" t="inlineStr"/>
       <c r="H2045" t="inlineStr">
         <is>
           <t>आज का FUTURE
@@ -85995,7 +85847,6 @@
       <c r="F2046" t="n">
         <v>1941</v>
       </c>
-      <c r="G2046" t="inlineStr"/>
       <c r="H2046" t="inlineStr">
         <is>
           <t>CASH का शेयर Dr Lal Path खरीदें PRICE 1961.30 TARGET 2000 STOP LOSS 1941</t>
@@ -86037,7 +85888,6 @@
       <c r="F2047" t="n">
         <v>550</v>
       </c>
-      <c r="G2047" t="inlineStr"/>
       <c r="H2047" t="inlineStr">
         <is>
           <t>नेहा के शेयर
@@ -86081,7 +85931,6 @@
       <c r="E2048" t="n">
         <v>1250</v>
       </c>
-      <c r="G2048" t="inlineStr"/>
       <c r="H2048" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -86127,7 +85976,6 @@
       <c r="F2049" t="n">
         <v>1035</v>
       </c>
-      <c r="G2049" t="inlineStr"/>
       <c r="H2049" t="inlineStr">
         <is>
           <t>श्रीकांत चौहान की राय AU Small Fin Fut बेचें PRICE 1002.60 TARGET 925 STOP LOSS 1035</t>
@@ -86169,7 +86017,6 @@
       <c r="F2050" t="n">
         <v>4700</v>
       </c>
-      <c r="G2050" t="inlineStr"/>
       <c r="H2050" t="inlineStr">
         <is>
           <t>TRADING CALL HAL खरीदें PRICE 4774.20 TARGET 4900 STOP LOSS 4700</t>
@@ -86208,7 +86055,6 @@
       <c r="E2051" t="n">
         <v>379</v>
       </c>
-      <c r="G2051" t="inlineStr"/>
       <c r="H2051" t="inlineStr">
         <is>
           <t>LONG-TERM CALL Karur V BUY TARGET 379 DURATION 6-12 महीने 325.00</t>
@@ -86250,7 +86096,6 @@
       <c r="F2052" t="n">
         <v>3900</v>
       </c>
-      <c r="G2052" t="inlineStr"/>
       <c r="H2052" t="inlineStr">
         <is>
           <t>सिद्धार्थ सेदानी की पसंद TVS Motor BUY TARGET 4500 STOP LOSS 3900 TVS Motor 4091.00 1.06%</t>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Latest by Stock" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$2052</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Website Signals'!$A$1:$J$2106</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest by Stock'!$A$1:$J$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2052"/>
+  <dimension ref="A1:J2106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -86112,8 +86112,2323 @@
         </is>
       </c>
     </row>
+    <row r="2053">
+      <c r="A2053" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:39:23</t>
+        </is>
+      </c>
+      <c r="B2053" t="inlineStr">
+        <is>
+          <t>MAHALXSE</t>
+        </is>
+      </c>
+      <c r="C2053" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2053" t="inlineStr"/>
+      <c r="E2053" t="n">
+        <v>800</v>
+      </c>
+      <c r="F2053" t="n">
+        <v>735</v>
+      </c>
+      <c r="G2053" t="inlineStr"/>
+      <c r="H2053" t="inlineStr">
+        <is>
+          <t>Maha Seamless खरीदें PRICE 749.30 TARGET 775/800 STOP LOSS 735</t>
+        </is>
+      </c>
+      <c r="I2053" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2053" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:39:23</t>
+        </is>
+      </c>
+      <c r="B2054" t="inlineStr">
+        <is>
+          <t>MAHALXSE</t>
+        </is>
+      </c>
+      <c r="C2054" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2054" t="inlineStr"/>
+      <c r="E2054" t="n">
+        <v>775</v>
+      </c>
+      <c r="F2054" t="n">
+        <v>735</v>
+      </c>
+      <c r="G2054" t="inlineStr"/>
+      <c r="H2054" t="inlineStr">
+        <is>
+          <t>Maha Seamless खरीदें PRICE 749.30 TARGET 775/800 STOP LOSS 735</t>
+        </is>
+      </c>
+      <c r="I2054" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2054" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:31:32</t>
+        </is>
+      </c>
+      <c r="B2055" t="inlineStr">
+        <is>
+          <t>STLTECH-BE</t>
+        </is>
+      </c>
+      <c r="C2055" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2055" t="inlineStr"/>
+      <c r="E2055" t="n">
+        <v>909.9</v>
+      </c>
+      <c r="G2055" t="inlineStr"/>
+      <c r="H2055" t="inlineStr">
+        <is>
+          <t>Sterlite Tech 909.90 INVESTMENT PICK 263.00 20/04/2026 RECO PRICE RETURN TILL NOW 646.90 245.97%</t>
+        </is>
+      </c>
+      <c r="I2055" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2055" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:30:00</t>
+        </is>
+      </c>
+      <c r="B2056" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C2056" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2056" t="n">
+        <v>277.25</v>
+      </c>
+      <c r="E2056" t="n">
+        <v>292</v>
+      </c>
+      <c r="F2056" t="n">
+        <v>267</v>
+      </c>
+      <c r="G2056" t="inlineStr"/>
+      <c r="H2056" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट
+BirlaSoft Tech
+खरीदें
+PRICE ▶ 277.80
+TARGET ▶ 286/292
+STOP LOSS ▶ 267</t>
+        </is>
+      </c>
+      <c r="I2056" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2056" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:30:00</t>
+        </is>
+      </c>
+      <c r="B2057" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C2057" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2057" t="n">
+        <v>277.25</v>
+      </c>
+      <c r="E2057" t="n">
+        <v>286</v>
+      </c>
+      <c r="F2057" t="n">
+        <v>267</v>
+      </c>
+      <c r="G2057" t="inlineStr"/>
+      <c r="H2057" t="inlineStr">
+        <is>
+          <t>सुमीत के सुपरहिट BirlaSoft Tech खरीदें PRICE 277.95 TARGET 286/292 STOP LOSS 267</t>
+        </is>
+      </c>
+      <c r="I2057" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2057" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:26:00</t>
+        </is>
+      </c>
+      <c r="B2058" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C2058" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2058" t="n">
+        <v>4972.5</v>
+      </c>
+      <c r="E2058" t="n">
+        <v>5050</v>
+      </c>
+      <c r="F2058" t="n">
+        <v>4850</v>
+      </c>
+      <c r="G2058" t="inlineStr"/>
+      <c r="H2058" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट Interglobe Aviation खरीदें PRICE 4959.00 TARGET 5050/5150 STOP LOSS 4850</t>
+        </is>
+      </c>
+      <c r="I2058" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2058" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:26:00</t>
+        </is>
+      </c>
+      <c r="B2059" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C2059" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2059" t="n">
+        <v>4972.5</v>
+      </c>
+      <c r="E2059" t="n">
+        <v>5150</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>4850</v>
+      </c>
+      <c r="G2059" t="inlineStr"/>
+      <c r="H2059" t="inlineStr">
+        <is>
+          <t>सुमित के सुपरहिट Interglobe Aviation खरीदें PRICE 4959.00 TARGET 5050/5150 STOP LOSS 4850</t>
+        </is>
+      </c>
+      <c r="I2059" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2059" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:25:00</t>
+        </is>
+      </c>
+      <c r="B2060" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C2060" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2060" t="n">
+        <v>4970</v>
+      </c>
+      <c r="E2060" t="n">
+        <v>5050</v>
+      </c>
+      <c r="F2060" t="n">
+        <v>4850</v>
+      </c>
+      <c r="G2060" t="inlineStr"/>
+      <c r="H2060" t="inlineStr">
+        <is>
+          <t>Interglobe Aviation खरीदें PRICE 4950.00 TARGET 5050/5150 STOP LOSS 4850</t>
+        </is>
+      </c>
+      <c r="I2060" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2060" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:25:00</t>
+        </is>
+      </c>
+      <c r="B2061" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C2061" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2061" t="n">
+        <v>4970</v>
+      </c>
+      <c r="E2061" t="n">
+        <v>5150</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>4850</v>
+      </c>
+      <c r="G2061" t="inlineStr"/>
+      <c r="H2061" t="inlineStr">
+        <is>
+          <t>Interglobe Aviation खरीदें PRICE 4950.00 TARGET 5050/5150 STOP LOSS 4850</t>
+        </is>
+      </c>
+      <c r="I2061" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2061" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:25:00</t>
+        </is>
+      </c>
+      <c r="B2062" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="C2062" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2062" t="n">
+        <v>4970</v>
+      </c>
+      <c r="F2062" t="n">
+        <v>375</v>
+      </c>
+      <c r="G2062" t="inlineStr"/>
+      <c r="H2062" t="inlineStr">
+        <is>
+          <t>InterGlobe Aviation 4948.00 76.00 1.56% Vol: 67.97 k लिस्टिंग पर सलाह कम रिस्क वाले इन्वेस्टर्स ₹375 के इश्यू प्राइस के नीचे SL लगाएं</t>
+        </is>
+      </c>
+      <c r="I2062" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2062" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2063" t="inlineStr">
+        <is>
+          <t>ICICIPRULI</t>
+        </is>
+      </c>
+      <c r="C2063" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2063" t="n">
+        <v>447.55</v>
+      </c>
+      <c r="E2063" t="n">
+        <v>540</v>
+      </c>
+      <c r="G2063" t="inlineStr">
+        <is>
+          <t>Sachin Gupta</t>
+        </is>
+      </c>
+      <c r="H2063" t="inlineStr">
+        <is>
+          <t>ICICI Pru 448.00 +3.45 OUTPERFORM लक्ष्य ₹700 से घटाकर ₹540</t>
+        </is>
+      </c>
+      <c r="I2063" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2063" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2064" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="C2064" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2064" t="n">
+        <v>232.33</v>
+      </c>
+      <c r="E2064" t="n">
+        <v>280</v>
+      </c>
+      <c r="G2064" t="inlineStr"/>
+      <c r="H2064" t="inlineStr">
+        <is>
+          <t>Bank of Baroda 230.40 OUTPERFORM लक्ष्य ₹270 से बढ़ाकर ₹280</t>
+        </is>
+      </c>
+      <c r="I2064" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2064" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2065" t="inlineStr">
+        <is>
+          <t>MOLBIO</t>
+        </is>
+      </c>
+      <c r="C2065" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2065" t="n">
+        <v>1345</v>
+      </c>
+      <c r="E2065" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G2065" t="inlineStr">
+        <is>
+          <t>Jefferies</t>
+        </is>
+      </c>
+      <c r="H2065" t="inlineStr">
+        <is>
+          <t>जेफरीज Molbio Diagnostics 1345.00 +89.40 BUY लक्ष्य ₹1600</t>
+        </is>
+      </c>
+      <c r="I2065" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2065" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2066" t="n">
+        <v>1515</v>
+      </c>
+      <c r="E2066" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G2066" t="inlineStr"/>
+      <c r="H2066" t="inlineStr">
+        <is>
+          <t>ICICI Lombard 1516.50 1.50 0.10% Vol: 127 PRE-OPEN BROKERAGE CALLS BUY लक्ष्य ₹1600</t>
+        </is>
+      </c>
+      <c r="I2066" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2066" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2067" t="n">
+        <v>1696.1</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G2067" t="inlineStr"/>
+      <c r="H2067" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Paytm
+1695.00 +12.00
+OUTPERFORM
+लक्ष्य ₹1235 से बढ़ाकर ₹2025</t>
+        </is>
+      </c>
+      <c r="I2067" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2067" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2068" t="n">
+        <v>1696.1</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G2068" t="inlineStr"/>
+      <c r="H2068" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Paytm 1695.00 +12.00 OUTPERFORM लक्ष्य ₹1235 से बढ़ाकर ₹2025</t>
+        </is>
+      </c>
+      <c r="I2068" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2068" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2069" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="C2069" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2069" t="n">
+        <v>680.2</v>
+      </c>
+      <c r="E2069" t="n">
+        <v>690</v>
+      </c>
+      <c r="F2069" t="n">
+        <v>667</v>
+      </c>
+      <c r="G2069" t="inlineStr"/>
+      <c r="H2069" t="inlineStr">
+        <is>
+          <t>MY CHOICE LENSKART B 690 667</t>
+        </is>
+      </c>
+      <c r="I2069" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2069" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2070" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C2070" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2070" t="n">
+        <v>325.85</v>
+      </c>
+      <c r="E2070" t="n">
+        <v>355</v>
+      </c>
+      <c r="G2070" t="inlineStr"/>
+      <c r="H2070" t="inlineStr">
+        <is>
+          <t>FUNDA ETERNAL B 355 6 MONTH</t>
+        </is>
+      </c>
+      <c r="I2070" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2070" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2071" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C2071" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2071" t="n">
+        <v>2540.5</v>
+      </c>
+      <c r="E2071" t="n">
+        <v>2648</v>
+      </c>
+      <c r="F2071" t="n">
+        <v>2470</v>
+      </c>
+      <c r="G2071" t="inlineStr"/>
+      <c r="H2071" t="inlineStr">
+        <is>
+          <t>PICK OF THE SERIES
+Mankind Pharma
+2545.00 109.40
+BUY
+TGT 2648
+SL 2470</t>
+        </is>
+      </c>
+      <c r="I2071" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2071" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2072" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C2072" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2072" t="n">
+        <v>557.3</v>
+      </c>
+      <c r="E2072" t="n">
+        <v>570</v>
+      </c>
+      <c r="F2072" t="n">
+        <v>518</v>
+      </c>
+      <c r="G2072" t="inlineStr">
+        <is>
+          <t>Aastha Jain</t>
+        </is>
+      </c>
+      <c r="H2072" t="inlineStr">
+        <is>
+          <t>आस्था जैन Sun TV 553.25 BUY TGT 570 SL 518</t>
+        </is>
+      </c>
+      <c r="I2072" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2072" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2073" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="C2073" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2073" t="n">
+        <v>1515</v>
+      </c>
+      <c r="E2073" t="n">
+        <v>1930</v>
+      </c>
+      <c r="G2073" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="H2073" t="inlineStr">
+        <is>
+          <t>FII INVESTMENT REPORT
+UBS
+NEUTRAL
+ICICI Lombard
+1515.00 ▼ 25.00
+TARGET ₹1930</t>
+        </is>
+      </c>
+      <c r="I2073" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2073" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2074" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C2074" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2074" t="n">
+        <v>2540.5</v>
+      </c>
+      <c r="E2074" t="n">
+        <v>2640</v>
+      </c>
+      <c r="F2074" t="n">
+        <v>2470</v>
+      </c>
+      <c r="G2074" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H2074" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय Mankind Pharma BUY PRICE 2545.00 TARGET 2640/2670 STOP LOSS 2470</t>
+        </is>
+      </c>
+      <c r="I2074" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2074" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2075" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C2075" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2075" t="n">
+        <v>2540.5</v>
+      </c>
+      <c r="E2075" t="n">
+        <v>2670</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>2470</v>
+      </c>
+      <c r="G2075" t="inlineStr">
+        <is>
+          <t>Sudeep Shah</t>
+        </is>
+      </c>
+      <c r="H2075" t="inlineStr">
+        <is>
+          <t>सुदीप शाह की राय Mankind Pharma BUY PRICE 2545.00 TARGET 2640/2670 STOP LOSS 2470</t>
+        </is>
+      </c>
+      <c r="I2075" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2075" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2076" t="inlineStr">
+        <is>
+          <t>AMBER27OCT26</t>
+        </is>
+      </c>
+      <c r="C2076" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2076" t="n">
+        <v>6680</v>
+      </c>
+      <c r="E2076" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F2076" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G2076" t="inlineStr"/>
+      <c r="H2076" t="inlineStr">
+        <is>
+          <t>PICK OF THE SERIES
+Amber Ent Fut
+SELL
+PRICE ▸ 6699.00
+TARGET ▸ 6000
+STOP LOSS ▸ 7000</t>
+        </is>
+      </c>
+      <c r="I2076" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2076" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2077" t="inlineStr">
+        <is>
+          <t>KFINTECH27OCT26</t>
+        </is>
+      </c>
+      <c r="C2077" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2077" t="n">
+        <v>835.8</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>780</v>
+      </c>
+      <c r="F2077" t="n">
+        <v>880</v>
+      </c>
+      <c r="G2077" t="inlineStr"/>
+      <c r="H2077" t="inlineStr">
+        <is>
+          <t>PICK OF THE SERIES Kfin Tech Fut SELL PRICE 832.35 TARGET 780 STOP LOSS 880</t>
+        </is>
+      </c>
+      <c r="I2077" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2077" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2078" t="inlineStr">
+        <is>
+          <t>KIRLOSBROS</t>
+        </is>
+      </c>
+      <c r="C2078" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2078" t="n">
+        <v>1847.5</v>
+      </c>
+      <c r="E2078" t="n">
+        <v>2425</v>
+      </c>
+      <c r="G2078" t="inlineStr"/>
+      <c r="H2078" t="inlineStr">
+        <is>
+          <t>PICK OF THE SERIES Kirloskar Brothers BUY PRICE 1848.30 TARGET 2425 STOP LOSS --</t>
+        </is>
+      </c>
+      <c r="I2078" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2078" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2079" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C2079" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2079" t="n">
+        <v>969.4</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>998</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>850</v>
+      </c>
+      <c r="G2079" t="inlineStr"/>
+      <c r="H2079" t="inlineStr">
+        <is>
+          <t>Bajaj Finance NEUTRAL लक्ष्य ₹850 से बढ़ाकर ₹998</t>
+        </is>
+      </c>
+      <c r="I2079" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2079" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2080" t="inlineStr">
+        <is>
+          <t>SBICARD</t>
+        </is>
+      </c>
+      <c r="C2080" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2080" t="n">
+        <v>586.2</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>600</v>
+      </c>
+      <c r="G2080" t="inlineStr"/>
+      <c r="H2080" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+SBI Card
+581.00 -10.00
+NEUTRAL
+लक्ष्य ₹725 से घटाकर ₹600</t>
+        </is>
+      </c>
+      <c r="I2080" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2080" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2081" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C2081" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2081" t="n">
+        <v>2943.1</v>
+      </c>
+      <c r="E2081" t="n">
+        <v>3155</v>
+      </c>
+      <c r="F2081" t="n">
+        <v>2875</v>
+      </c>
+      <c r="G2081" t="inlineStr"/>
+      <c r="H2081" t="inlineStr">
+        <is>
+          <t>FUNDA M&amp;M B 3155 2875</t>
+        </is>
+      </c>
+      <c r="I2081" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2081" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2082" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="C2082" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2082" t="n">
+        <v>3296</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>3507</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>3229</v>
+      </c>
+      <c r="G2082" t="inlineStr"/>
+      <c r="H2082" t="inlineStr">
+        <is>
+          <t>CASH ACUTAAS CHEMICALS B 3507 3229</t>
+        </is>
+      </c>
+      <c r="I2082" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2082" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2083" t="inlineStr">
+        <is>
+          <t>NATIONALUM27OCT26</t>
+        </is>
+      </c>
+      <c r="C2083" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2083" t="n">
+        <v>348.35</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>340</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>352</v>
+      </c>
+      <c r="G2083" t="inlineStr"/>
+      <c r="H2083" t="inlineStr">
+        <is>
+          <t>FUTURE NALCO FUT S 340 352</t>
+        </is>
+      </c>
+      <c r="I2083" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2083" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2084" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C2084" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2084" t="n">
+        <v>409.15</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>416</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>401</v>
+      </c>
+      <c r="G2084" t="inlineStr"/>
+      <c r="H2084" t="inlineStr">
+        <is>
+          <t>अंश के शेयर
+Kotak Bank
+खरीदें
+PRICE → 406.00
+TARGET → 416
+STOP LOSS → 401</t>
+        </is>
+      </c>
+      <c r="I2084" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2084" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2085" t="inlineStr">
+        <is>
+          <t>GODREJCP</t>
+        </is>
+      </c>
+      <c r="C2085" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2085" t="n">
+        <v>854.65</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>880</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>842</v>
+      </c>
+      <c r="G2085" t="inlineStr"/>
+      <c r="H2085" t="inlineStr">
+        <is>
+          <t>MY CHOICE Godrej Cons खरीदें PRICE 855.00 TARGET 880 STOP LOSS 842</t>
+        </is>
+      </c>
+      <c r="I2085" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2085" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2086" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="C2086" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2086" t="n">
+        <v>673.45</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>690</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>667</v>
+      </c>
+      <c r="G2086" t="inlineStr"/>
+      <c r="H2086" t="inlineStr">
+        <is>
+          <t>पूजा के शर र Lenskart खरीदें PRICE 674.60 TARGET 690 STOP LOSS 667</t>
+        </is>
+      </c>
+      <c r="I2086" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2086" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2087" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C2087" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2087" t="n">
+        <v>2943.1</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>4103</v>
+      </c>
+      <c r="G2087" t="inlineStr"/>
+      <c r="H2087" t="inlineStr">
+        <is>
+          <t>FUNDA PICK मैक्वारी की आउटपरफॉर्म की राय, लक्ष्य ₹4103 M&amp;M 2947.80 ▼ 1.58%</t>
+        </is>
+      </c>
+      <c r="I2087" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2087" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2088" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C2088" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2088" t="n">
+        <v>2943.1</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>3155</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>2875</v>
+      </c>
+      <c r="G2088" t="inlineStr"/>
+      <c r="H2088" t="inlineStr">
+        <is>
+          <t>FUNDA PICK
+M&amp;M
+खरीदें
+PRICE → 2947.80
+TARGET → 3155
+STOP LOSS → 2875</t>
+        </is>
+      </c>
+      <c r="I2088" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2088" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2089" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C2089" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2089" t="n">
+        <v>325.85</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>355</v>
+      </c>
+      <c r="G2089" t="inlineStr"/>
+      <c r="H2089" t="inlineStr">
+        <is>
+          <t>FUNDA PICK
+Eternal (Zomato)
+खरीदें
+PRICE → 327.85
+TARGET → 355
+DURATION → 3-6 महीने</t>
+        </is>
+      </c>
+      <c r="I2089" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2089" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2090" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="C2090" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2090" t="n">
+        <v>673.45</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>718</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>666</v>
+      </c>
+      <c r="G2090" t="inlineStr"/>
+      <c r="H2090" t="inlineStr">
+        <is>
+          <t>Lenskart 674.60 +2.96% OVERWEIGHT लक्ष्य ₹666 से बढ़ाकर ₹718</t>
+        </is>
+      </c>
+      <c r="I2090" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2090" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2091" t="inlineStr">
+        <is>
+          <t>ALKEM540027OCT26CE</t>
+        </is>
+      </c>
+      <c r="C2091" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2091" t="n">
+        <v>78</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>180</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>50</v>
+      </c>
+      <c r="G2091" t="inlineStr"/>
+      <c r="H2091" t="inlineStr">
+        <is>
+          <t>अंश के शेयर
+Alkem Lab 5400 की कॉल
+खरीदें
+STOP LOSS 50
+TARGET 180
+Alkem Lab 5250.00 ▲ 75.00</t>
+        </is>
+      </c>
+      <c r="I2091" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J2091" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2092" t="inlineStr">
+        <is>
+          <t>HINDALCO96027OCT26CE</t>
+        </is>
+      </c>
+      <c r="C2092" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2092" t="n">
+        <v>23</v>
+      </c>
+      <c r="E2092" t="n">
+        <v>50</v>
+      </c>
+      <c r="F2092" t="n">
+        <v>15</v>
+      </c>
+      <c r="G2092" t="inlineStr"/>
+      <c r="H2092" t="inlineStr">
+        <is>
+          <t>पूजा के शेयर Hindalco 960 की पुट @ 22.25 खरीदें STOP LOSS 15 TARGET 50</t>
+        </is>
+      </c>
+      <c r="I2092" t="inlineStr">
+        <is>
+          <t>660334625662a7f64ae8911d</t>
+        </is>
+      </c>
+      <c r="J2092" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2093" t="inlineStr">
+        <is>
+          <t>NATIONALUM27OCT26</t>
+        </is>
+      </c>
+      <c r="C2093" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D2093" t="n">
+        <v>348.35</v>
+      </c>
+      <c r="E2093" t="n">
+        <v>340</v>
+      </c>
+      <c r="F2093" t="n">
+        <v>352</v>
+      </c>
+      <c r="G2093" t="inlineStr"/>
+      <c r="H2093" t="inlineStr">
+        <is>
+          <t>आज का FUTURE NALCO Fut बेचें PRICE 349.25 TARGET 340 STOP LOSS 352</t>
+        </is>
+      </c>
+      <c r="I2093" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2093" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:16:00</t>
+        </is>
+      </c>
+      <c r="B2094" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C2094" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2094" t="n">
+        <v>1698.1</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G2094" t="inlineStr"/>
+      <c r="H2094" t="inlineStr">
+        <is>
+          <t>मैक्चायरी
+Paytm
+1683.00 +2.89%
+OUTPERFORM
+लक्ष्य ₹1235 से बढ़ाकर ₹2025</t>
+        </is>
+      </c>
+      <c r="I2094" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2094" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:16:00</t>
+        </is>
+      </c>
+      <c r="B2095" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="C2095" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2095" t="n">
+        <v>1698.1</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G2095" t="inlineStr"/>
+      <c r="H2095" t="inlineStr">
+        <is>
+          <t>मैक्वायरी
+Paytm
+1683.00 +47.20
+OUTPERFORM
+लक्ष्य ₹1235 से बढ़ाकर ₹2025</t>
+        </is>
+      </c>
+      <c r="I2095" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2095" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2096" t="inlineStr">
+        <is>
+          <t>PAYTM27OCT26</t>
+        </is>
+      </c>
+      <c r="C2096" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2096" t="n">
+        <v>1712</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>1785</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>1655</v>
+      </c>
+      <c r="G2096" t="inlineStr"/>
+      <c r="H2096" t="inlineStr">
+        <is>
+          <t>अंश के शेयर
+Paytm Fut
+खरीदें
+PRICE ▶ 1698.80
+TARGET ▶ 1785
+STOP LOSS ▶ 1655</t>
+        </is>
+      </c>
+      <c r="I2096" t="inlineStr">
+        <is>
+          <t>660334275662a7f64ae8911c</t>
+        </is>
+      </c>
+      <c r="J2096" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2097" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="C2097" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2097" t="n">
+        <v>3296</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>3507</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>3229</v>
+      </c>
+      <c r="G2097" t="inlineStr"/>
+      <c r="H2097" t="inlineStr">
+        <is>
+          <t>CASH का शेयर
+Acutaas Chemicals Ltd
+खरीदें
+PRICE → 3304.10
+TARGET → 3507
+STOP LOSS → 3229</t>
+        </is>
+      </c>
+      <c r="I2097" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2097" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2098" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C2098" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2098" t="n">
+        <v>969.4</v>
+      </c>
+      <c r="E2098" t="n">
+        <v>998</v>
+      </c>
+      <c r="F2098" t="n">
+        <v>850</v>
+      </c>
+      <c r="G2098" t="inlineStr"/>
+      <c r="H2098" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS Bajaj Finance 973.80 -11.20 NEUTRAL लक्ष्य ₹850 से बढ़ाकर ₹998 मनोज कुमार जैन पृथ्वी फिनमार्ट</t>
+        </is>
+      </c>
+      <c r="I2098" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2098" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2099" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C2099" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2099" t="n">
+        <v>2979.6</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>3070</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>2955</v>
+      </c>
+      <c r="G2099" t="inlineStr"/>
+      <c r="H2099" t="inlineStr">
+        <is>
+          <t>TRADING CALL Gland Pharma खरीदें PRICE 2989.70 TARGET 3070/3100 STOP LOSS 2955</t>
+        </is>
+      </c>
+      <c r="I2099" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2099" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2100" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C2100" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2100" t="n">
+        <v>2979.6</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>2955</v>
+      </c>
+      <c r="G2100" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H2100" t="inlineStr">
+        <is>
+          <t>सिद्धार्थ राय मंगला की राय Gland Pharma खरीदें PRICE 2989.70 TARGET 3070/3100 STOP LOSS 2955</t>
+        </is>
+      </c>
+      <c r="I2100" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2100" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2101" t="inlineStr">
+        <is>
+          <t>LENSKART</t>
+        </is>
+      </c>
+      <c r="C2101" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2101" t="n">
+        <v>673.45</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>718</v>
+      </c>
+      <c r="G2101" t="inlineStr">
+        <is>
+          <t>Siddharth Ray Mangla</t>
+        </is>
+      </c>
+      <c r="H2101" t="inlineStr">
+        <is>
+          <t>Lenskart 674.60 +19.40 OVERWEIGHT लक्ष्य ₹666 से बढ़ाकर ₹718</t>
+        </is>
+      </c>
+      <c r="I2101" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2101" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2102" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C2102" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2102" t="n">
+        <v>1084.3</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G2102" t="inlineStr"/>
+      <c r="H2102" t="inlineStr">
+        <is>
+          <t>CALLS
+PB Fintech
+1088.00
+NEUTRAL
+लक्ष्य ₹1950 से घटाकर ₹1150</t>
+        </is>
+      </c>
+      <c r="I2102" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2102" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2103" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C2103" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2103" t="n">
+        <v>969.4</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>980</v>
+      </c>
+      <c r="G2103" t="inlineStr"/>
+      <c r="H2103" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Bajaj Finance
+973.86
+NEUTRAL
+लक्ष्य ₹850 से बढ़ाकर ₹980</t>
+        </is>
+      </c>
+      <c r="I2103" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2103" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2104" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C2104" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2104" t="n">
+        <v>409.15</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>500</v>
+      </c>
+      <c r="G2104" t="inlineStr"/>
+      <c r="H2104" t="inlineStr">
+        <is>
+          <t>Kotak Bank 406.00 +4.45 OUTPERFORM लक्ष्य ₹455 से बढ़ाकर ₹500</t>
+        </is>
+      </c>
+      <c r="I2104" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2104" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2105" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C2105" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2105" t="n">
+        <v>969.4</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>990</v>
+      </c>
+      <c r="G2105" t="inlineStr"/>
+      <c r="H2105" t="inlineStr">
+        <is>
+          <t>BROKERAGE CALLS
+Bajaj Finance
+973.80 -11.20
+NEUTRAL
+लक्ष्य ₹850 से बढ़ाकर ₹990</t>
+        </is>
+      </c>
+      <c r="I2105" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2105" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" t="inlineStr">
+        <is>
+          <t>2026-09-30 09:15:00</t>
+        </is>
+      </c>
+      <c r="B2106" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="C2106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D2106" t="n">
+        <v>969.4</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>990</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>850</v>
+      </c>
+      <c r="G2106" t="inlineStr"/>
+      <c r="H2106" t="inlineStr">
+        <is>
+          <t>मैक्वायरी Bajaj Finance 973.80 NEUTRAL लक्ष्य ₹850 से बढ़ाकर ₹990</t>
+        </is>
+      </c>
+      <c r="I2106" t="inlineStr">
+        <is>
+          <t>660333e45662a7f64ae8911b</t>
+        </is>
+      </c>
+      <c r="J2106" t="inlineStr">
+        <is>
+          <t>https://www.zeebusinesslive.com/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J2052"/>
+  <autoFilter ref="A1:J2106"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/zeebiz_live_stocks.xlsx
+++ b/zeebiz_live_stocks.xlsx
@@ -86128,14 +86128,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D2053" t="inlineStr"/>
       <c r="E2053" t="n">
         <v>800</v>
       </c>
       <c r="F2053" t="n">
         <v>735</v>
       </c>
-      <c r="G2053" t="inlineStr"/>
       <c r="H2053" t="inlineStr">
         <is>
           <t>Maha Seamless खरीदें PRICE 749.30 TARGET 775/800 STOP LOSS 735</t>
@@ -86168,14 +86166,12 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D2054" t="inlineStr"/>
       <c r="E2054" t="n">
         <v>775</v>
       </c>
       <c r="F2054" t="n">
         <v>735</v>
       </c>
-      <c r="G2054" t="inlineStr"/>
       <c r="H2054" t="inlineStr">
         <is>
           <t>Maha Seamless खरीदें PRICE 749.30 TARGET 775/800 STOP LOSS 735</t>
@@ -86208,11 +86204,9 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="D2055" t="inlineStr"/>
       <c r="E2055" t="n">
         <v>909.9</v>
       </c>
-      <c r="G2055" t="inlineStr"/>
       <c r="H2055" t="inlineStr">
         <is>
           <t>Sterlite Tech 909.90 INVESTMENT PICK 263.00 20/04/2026 RECO PRICE RETURN TILL NOW 646.90 245.97%</t>
@@ -86254,7 +86248,6 @@
       <c r="F2056" t="n">
         <v>267</v>
       </c>
-      <c r="G2056" t="inlineStr"/>
       <c r="H2056" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट
@@ -86301,7 +86294,6 @@
       <c r="F2057" t="n">
         <v>267</v>
       </c>
-      <c r="G2057" t="inlineStr"/>
       <c r="H2057" t="inlineStr">
         <is>
           <t>सुमीत के सुपरहिट BirlaSoft Tech खरीदें PRICE 277.95 TARGET 286/292 STOP LOSS 267</t>
@@ -86343,7 +86335,6 @@
       <c r="F2058" t="n">
         <v>4850</v>
       </c>
-      <c r="G2058" t="inlineStr"/>
       <c r="H2058" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट Interglobe Aviation खरीदें PRICE 4959.00 TARGET 5050/5150 STOP LOSS 4850</t>
@@ -86385,7 +86376,6 @@
       <c r="F2059" t="n">
         <v>4850</v>
       </c>
-      <c r="G2059" t="inlineStr"/>
       <c r="H2059" t="inlineStr">
         <is>
           <t>सुमित के सुपरहिट Interglobe Aviation खरीदें PRICE 4959.00 TARGET 5050/5150 STOP LOSS 4850</t>
@@ -86427,7 +86417,6 @@
       <c r="F2060" t="n">
         <v>4850</v>
       </c>
-      <c r="G2060" t="inlineStr"/>
       <c r="H2060" t="inlineStr">
         <is>
           <t>Interglobe Aviation खरीदें PRICE 4950.00 TARGET 5050/5150 STOP LOSS 4850</t>
@@ -86469,7 +86458,6 @@
       <c r="F2061" t="n">
         <v>4850</v>
       </c>
-      <c r="G2061" t="inlineStr"/>
       <c r="H2061" t="inlineStr">
         <is>
           <t>Interglobe Aviation खरीदें PRICE 4950.00 TARGET 5050/5150 STOP LOSS 4850</t>
@@ -86508,7 +86496,6 @@
       <c r="F2062" t="n">
         <v>375</v>
       </c>
-      <c r="G2062" t="inlineStr"/>
       <c r="H2062" t="inlineStr">
         <is>
           <t>InterGlobe Aviation 4948.00 76.00 1.56% Vol: 67.97 k लिस्टिंग पर सलाह कम रिस्क वाले इन्वेस्टर्स ₹375 के इश्यू प्राइस के नीचे SL लगाएं</t>
@@ -86590,7 +86577,6 @@
       <c r="E2064" t="n">
         <v>280</v>
       </c>
-      <c r="G2064" t="inlineStr"/>
       <c r="H2064" t="inlineStr">
         <is>
           <t>Bank of Baroda 230.40 OUTPERFORM लक्ष्य ₹270 से बढ़ाकर ₹280</t>
@@ -86672,7 +86658,6 @@
       <c r="E2066" t="n">
         <v>1600</v>
       </c>
-      <c r="G2066" t="inlineStr"/>
       <c r="H2066" t="inlineStr">
         <is>
           <t>ICICI Lombard 1516.50 1.50 0.10% Vol: 127 PRE-OPEN BROKERAGE CALLS BUY लक्ष्य ₹1600</t>
@@ -86714,7 +86699,6 @@
       <c r="F2067" t="n">
         <v>1235</v>
       </c>
-      <c r="G2067" t="inlineStr"/>
       <c r="H2067" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -86757,7 +86741,6 @@
       <c r="E2068" t="n">
         <v>2025</v>
       </c>
-      <c r="G2068" t="inlineStr"/>
       <c r="H2068" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Paytm 1695.00 +12.00 OUTPERFORM लक्ष्य ₹1235 से बढ़ाकर ₹2025</t>
@@ -86799,7 +86782,6 @@
       <c r="F2069" t="n">
         <v>667</v>
       </c>
-      <c r="G2069" t="inlineStr"/>
       <c r="H2069" t="inlineStr">
         <is>
           <t>MY CHOICE LENSKART B 690 667</t>
@@ -86838,7 +86820,6 @@
       <c r="E2070" t="n">
         <v>355</v>
       </c>
-      <c r="G2070" t="inlineStr"/>
       <c r="H2070" t="inlineStr">
         <is>
           <t>FUNDA ETERNAL B 355 6 MONTH</t>
@@ -86880,7 +86861,6 @@
       <c r="F2071" t="n">
         <v>2470</v>
       </c>
-      <c r="G2071" t="inlineStr"/>
       <c r="H2071" t="inlineStr">
         <is>
           <t>PICK OF THE SERIES
@@ -87113,7 +87093,6 @@
       <c r="F2076" t="n">
         <v>7000</v>
       </c>
-      <c r="G2076" t="inlineStr"/>
       <c r="H2076" t="inlineStr">
         <is>
           <t>PICK OF THE SERIES
@@ -87160,7 +87139,6 @@
       <c r="F2077" t="n">
         <v>880</v>
       </c>
-      <c r="G2077" t="inlineStr"/>
       <c r="H2077" t="inlineStr">
         <is>
           <t>PICK OF THE SERIES Kfin Tech Fut SELL PRICE 832.35 TARGET 780 STOP LOSS 880</t>
@@ -87199,7 +87177,6 @@
       <c r="E2078" t="n">
         <v>2425</v>
       </c>
-      <c r="G2078" t="inlineStr"/>
       <c r="H2078" t="inlineStr">
         <is>
           <t>PICK OF THE SERIES Kirloskar Brothers BUY PRICE 1848.30 TARGET 2425 STOP LOSS --</t>
@@ -87241,7 +87218,6 @@
       <c r="F2079" t="n">
         <v>850</v>
       </c>
-      <c r="G2079" t="inlineStr"/>
       <c r="H2079" t="inlineStr">
         <is>
           <t>Bajaj Finance NEUTRAL लक्ष्य ₹850 से बढ़ाकर ₹998</t>
@@ -87280,7 +87256,6 @@
       <c r="E2080" t="n">
         <v>600</v>
       </c>
-      <c r="G2080" t="inlineStr"/>
       <c r="H2080" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -87326,7 +87301,6 @@
       <c r="F2081" t="n">
         <v>2875</v>
       </c>
-      <c r="G2081" t="inlineStr"/>
       <c r="H2081" t="inlineStr">
         <is>
           <t>FUNDA M&amp;M B 3155 2875</t>
@@ -87368,7 +87342,6 @@
       <c r="F2082" t="n">
         <v>3229</v>
       </c>
-      <c r="G2082" t="inlineStr"/>
       <c r="H2082" t="inlineStr">
         <is>
           <t>CASH ACUTAAS CHEMICALS B 3507 3229</t>
@@ -87410,7 +87383,6 @@
       <c r="F2083" t="n">
         <v>352</v>
       </c>
-      <c r="G2083" t="inlineStr"/>
       <c r="H2083" t="inlineStr">
         <is>
           <t>FUTURE NALCO FUT S 340 352</t>
@@ -87452,7 +87424,6 @@
       <c r="F2084" t="n">
         <v>401</v>
       </c>
-      <c r="G2084" t="inlineStr"/>
       <c r="H2084" t="inlineStr">
         <is>
           <t>अंश के शेयर
@@ -87499,7 +87470,6 @@
       <c r="F2085" t="n">
         <v>842</v>
       </c>
-      <c r="G2085" t="inlineStr"/>
       <c r="H2085" t="inlineStr">
         <is>
           <t>MY CHOICE Godrej Cons खरीदें PRICE 855.00 TARGET 880 STOP LOSS 842</t>
@@ -87541,7 +87511,6 @@
       <c r="F2086" t="n">
         <v>667</v>
       </c>
-      <c r="G2086" t="inlineStr"/>
       <c r="H2086" t="inlineStr">
         <is>
           <t>पूजा के शर र Lenskart खरीदें PRICE 674.60 TARGET 690 STOP LOSS 667</t>
@@ -87580,7 +87549,6 @@
       <c r="E2087" t="n">
         <v>4103</v>
       </c>
-      <c r="G2087" t="inlineStr"/>
       <c r="H2087" t="inlineStr">
         <is>
           <t>FUNDA PICK मैक्वारी की आउटपरफॉर्म की राय, लक्ष्य ₹4103 M&amp;M 2947.80 ▼ 1.58%</t>
@@ -87622,7 +87590,6 @@
       <c r="F2088" t="n">
         <v>2875</v>
       </c>
-      <c r="G2088" t="inlineStr"/>
       <c r="H2088" t="inlineStr">
         <is>
           <t>FUNDA PICK
@@ -87666,7 +87633,6 @@
       <c r="E2089" t="n">
         <v>355</v>
       </c>
-      <c r="G2089" t="inlineStr"/>
       <c r="H2089" t="inlineStr">
         <is>
           <t>FUNDA PICK
@@ -87713,7 +87679,6 @@
       <c r="F2090" t="n">
         <v>666</v>
       </c>
-      <c r="G2090" t="inlineStr"/>
       <c r="H2090" t="inlineStr">
         <is>
           <t>Lenskart 674.60 +2.96% OVERWEIGHT लक्ष्य ₹666 से बढ़ाकर ₹718</t>
@@ -87755,7 +87720,6 @@
       <c r="F2091" t="n">
         <v>50</v>
       </c>
-      <c r="G2091" t="inlineStr"/>
       <c r="H2091" t="inlineStr">
         <is>
           <t>अंश के शेयर
@@ -87802,7 +87766,6 @@
       <c r="F2092" t="n">
         <v>15</v>
       </c>
-      <c r="G2092" t="inlineStr"/>
       <c r="H2092" t="inlineStr">
         <is>
           <t>पूजा के शेयर Hindalco 960 की पुट @ 22.25 खरीदें STOP LOSS 15 TARGET 50</t>
@@ -87844,7 +87807,6 @@
       <c r="F2093" t="n">
         <v>352</v>
       </c>
-      <c r="G2093" t="inlineStr"/>
       <c r="H2093" t="inlineStr">
         <is>
           <t>आज का FUTURE NALCO Fut बेचें PRICE 349.25 TARGET 340 STOP LOSS 352</t>
@@ -87886,7 +87848,6 @@
       <c r="F2094" t="n">
         <v>1235</v>
       </c>
-      <c r="G2094" t="inlineStr"/>
       <c r="H2094" t="inlineStr">
         <is>
           <t>मैक्चायरी
@@ -87929,7 +87890,6 @@
       <c r="E2095" t="n">
         <v>2025</v>
       </c>
-      <c r="G2095" t="inlineStr"/>
       <c r="H2095" t="inlineStr">
         <is>
           <t>मैक्वायरी
@@ -87975,7 +87935,6 @@
       <c r="F2096" t="n">
         <v>1655</v>
       </c>
-      <c r="G2096" t="inlineStr"/>
       <c r="H2096" t="inlineStr">
         <is>
           <t>अंश के शेयर
@@ -88022,7 +87981,6 @@
       <c r="F2097" t="n">
         <v>3229</v>
       </c>
-      <c r="G2097" t="inlineStr"/>
       <c r="H2097" t="inlineStr">
         <is>
           <t>CASH का शेयर
@@ -88069,7 +88027,6 @@
       <c r="F2098" t="n">
         <v>850</v>
       </c>
-      <c r="G2098" t="inlineStr"/>
       <c r="H2098" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS Bajaj Finance 973.80 -11.20 NEUTRAL लक्ष्य ₹850 से बढ़ाकर ₹998 मनोज कुमार जैन पृथ्वी फिनमार्ट</t>
@@ -88111,7 +88068,6 @@
       <c r="F2099" t="n">
         <v>2955</v>
       </c>
-      <c r="G2099" t="inlineStr"/>
       <c r="H2099" t="inlineStr">
         <is>
           <t>TRADING CALL Gland Pharma खरीदें PRICE 2989.70 TARGET 3070/3100 STOP LOSS 2955</t>
@@ -88239,7 +88195,6 @@
       <c r="E2102" t="n">
         <v>1150</v>
       </c>
-      <c r="G2102" t="inlineStr"/>
       <c r="H2102" t="inlineStr">
         <is>
           <t>CALLS
@@ -88282,7 +88237,6 @@
       <c r="E2103" t="n">
         <v>980</v>
       </c>
-      <c r="G2103" t="inlineStr"/>
       <c r="H2103" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -88325,7 +88279,6 @@
       <c r="E2104" t="n">
         <v>500</v>
       </c>
-      <c r="G2104" t="inlineStr"/>
       <c r="H2104" t="inlineStr">
         <is>
           <t>Kotak Bank 406.00 +4.45 OUTPERFORM लक्ष्य ₹455 से बढ़ाकर ₹500</t>
@@ -88364,7 +88317,6 @@
       <c r="E2105" t="n">
         <v>990</v>
       </c>
-      <c r="G2105" t="inlineStr"/>
       <c r="H2105" t="inlineStr">
         <is>
           <t>BROKERAGE CALLS
@@ -88410,7 +88362,6 @@
       <c r="F2106" t="n">
         <v>850</v>
       </c>
-      <c r="G2106" t="inlineStr"/>
       <c r="H2106" t="inlineStr">
         <is>
           <t>मैक्वायरी Bajaj Finance 973.80 NEUTRAL लक्ष्य ₹850 से बढ़ाकर ₹990</t>
